--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G7">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G74">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G79">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G82">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G93">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G113">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G123">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G138">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G145">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G147">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G161">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G165">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G173">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G177">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G183">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G194">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G204">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G278">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G316">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G17">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G19">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G83">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G123">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G128">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G138">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G161">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G177">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G183">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G204">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G19">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G93">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G113">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G126">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G128">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G20">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G38">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G93">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G287">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G288">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G113">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G123">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G173">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G105">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G147">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G83">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G105">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G147">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G113">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G147">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G235">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G106">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G235">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU341"/>
+  <dimension ref="A1:AU342"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G68">
@@ -53889,27 +53889,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G329">
@@ -53932,7 +53932,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G333">
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-09-19 21:45:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00:00</t>
+          <t>2026-09-19 21:45:00</t>
         </is>
       </c>
     </row>
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G336">
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30:00</t>
+          <t>2026-09-19 22:00:00</t>
         </is>
       </c>
     </row>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G338">
@@ -55519,12 +55519,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G339">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00:00</t>
+          <t>2026-09-19 22:30:00</t>
         </is>
       </c>
     </row>
@@ -55682,7 +55682,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G340">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30:00</t>
+          <t>2026-09-19 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55850,151 +55850,314 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G341">
+        <v>0</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N341">
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <v>0</v>
+      </c>
+      <c r="R341">
+        <v>0</v>
+      </c>
+      <c r="S341">
+        <v>0</v>
+      </c>
+      <c r="T341">
+        <v>0</v>
+      </c>
+      <c r="U341">
+        <v>0</v>
+      </c>
+      <c r="V341">
+        <v>0</v>
+      </c>
+      <c r="W341">
+        <v>0</v>
+      </c>
+      <c r="X341">
+        <v>0</v>
+      </c>
+      <c r="Y341">
+        <v>0</v>
+      </c>
+      <c r="Z341">
+        <v>0</v>
+      </c>
+      <c r="AA341">
+        <v>0</v>
+      </c>
+      <c r="AB341">
+        <v>0</v>
+      </c>
+      <c r="AC341">
+        <v>0</v>
+      </c>
+      <c r="AD341">
+        <v>0</v>
+      </c>
+      <c r="AE341">
+        <v>0</v>
+      </c>
+      <c r="AF341">
+        <v>0</v>
+      </c>
+      <c r="AG341">
+        <v>0</v>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ341">
+        <v>0</v>
+      </c>
+      <c r="AK341">
+        <v>0</v>
+      </c>
+      <c r="AL341">
+        <v>0</v>
+      </c>
+      <c r="AM341">
+        <v>-1</v>
+      </c>
+      <c r="AN341">
+        <v>-1</v>
+      </c>
+      <c r="AO341">
+        <v>-1</v>
+      </c>
+      <c r="AP341">
+        <v>-1</v>
+      </c>
+      <c r="AQ341">
+        <v>0</v>
+      </c>
+      <c r="AR341">
+        <v>0</v>
+      </c>
+      <c r="AS341">
+        <v>0</v>
+      </c>
+      <c r="AT341">
+        <v>0</v>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D342" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
+      <c r="E342" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
+      <c r="F342" t="inlineStr">
         <is>
           <t>Atlanta United FC</t>
         </is>
       </c>
-      <c r="G341">
-        <v>0</v>
-      </c>
-      <c r="H341">
-        <v>0</v>
-      </c>
-      <c r="I341">
-        <v>0</v>
-      </c>
-      <c r="J341">
-        <v>0</v>
-      </c>
-      <c r="K341">
-        <v>0</v>
-      </c>
-      <c r="L341">
-        <v>0</v>
-      </c>
-      <c r="M341" t="inlineStr">
+      <c r="G342">
+        <v>0</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>0</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+      <c r="M342" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N341">
-        <v>0</v>
-      </c>
-      <c r="O341">
-        <v>0</v>
-      </c>
-      <c r="P341">
-        <v>0</v>
-      </c>
-      <c r="Q341">
-        <v>0</v>
-      </c>
-      <c r="R341">
-        <v>0</v>
-      </c>
-      <c r="S341">
-        <v>0</v>
-      </c>
-      <c r="T341">
-        <v>0</v>
-      </c>
-      <c r="U341">
-        <v>0</v>
-      </c>
-      <c r="V341">
-        <v>0</v>
-      </c>
-      <c r="W341">
-        <v>0</v>
-      </c>
-      <c r="X341">
-        <v>0</v>
-      </c>
-      <c r="Y341">
-        <v>0</v>
-      </c>
-      <c r="Z341">
-        <v>0</v>
-      </c>
-      <c r="AA341">
-        <v>0</v>
-      </c>
-      <c r="AB341">
-        <v>0</v>
-      </c>
-      <c r="AC341">
-        <v>0</v>
-      </c>
-      <c r="AD341">
-        <v>0</v>
-      </c>
-      <c r="AE341">
-        <v>0</v>
-      </c>
-      <c r="AF341">
-        <v>0</v>
-      </c>
-      <c r="AG341">
-        <v>0</v>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ341">
-        <v>0</v>
-      </c>
-      <c r="AK341">
-        <v>0</v>
-      </c>
-      <c r="AL341">
-        <v>0</v>
-      </c>
-      <c r="AM341">
-        <v>-1</v>
-      </c>
-      <c r="AN341">
-        <v>-1</v>
-      </c>
-      <c r="AO341">
-        <v>-1</v>
-      </c>
-      <c r="AP341">
-        <v>-1</v>
-      </c>
-      <c r="AQ341">
-        <v>0</v>
-      </c>
-      <c r="AR341">
-        <v>0</v>
-      </c>
-      <c r="AS341">
-        <v>0</v>
-      </c>
-      <c r="AT341">
-        <v>0</v>
-      </c>
-      <c r="AU341" t="inlineStr">
+      <c r="N342">
+        <v>0</v>
+      </c>
+      <c r="O342">
+        <v>0</v>
+      </c>
+      <c r="P342">
+        <v>0</v>
+      </c>
+      <c r="Q342">
+        <v>0</v>
+      </c>
+      <c r="R342">
+        <v>0</v>
+      </c>
+      <c r="S342">
+        <v>0</v>
+      </c>
+      <c r="T342">
+        <v>0</v>
+      </c>
+      <c r="U342">
+        <v>0</v>
+      </c>
+      <c r="V342">
+        <v>0</v>
+      </c>
+      <c r="W342">
+        <v>0</v>
+      </c>
+      <c r="X342">
+        <v>0</v>
+      </c>
+      <c r="Y342">
+        <v>0</v>
+      </c>
+      <c r="Z342">
+        <v>0</v>
+      </c>
+      <c r="AA342">
+        <v>0</v>
+      </c>
+      <c r="AB342">
+        <v>0</v>
+      </c>
+      <c r="AC342">
+        <v>0</v>
+      </c>
+      <c r="AD342">
+        <v>0</v>
+      </c>
+      <c r="AE342">
+        <v>0</v>
+      </c>
+      <c r="AF342">
+        <v>0</v>
+      </c>
+      <c r="AG342">
+        <v>0</v>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ342">
+        <v>0</v>
+      </c>
+      <c r="AK342">
+        <v>0</v>
+      </c>
+      <c r="AL342">
+        <v>0</v>
+      </c>
+      <c r="AM342">
+        <v>-1</v>
+      </c>
+      <c r="AN342">
+        <v>-1</v>
+      </c>
+      <c r="AO342">
+        <v>-1</v>
+      </c>
+      <c r="AP342">
+        <v>-1</v>
+      </c>
+      <c r="AQ342">
+        <v>0</v>
+      </c>
+      <c r="AR342">
+        <v>0</v>
+      </c>
+      <c r="AS342">
+        <v>0</v>
+      </c>
+      <c r="AT342">
+        <v>0</v>
+      </c>
+      <c r="AU342" t="inlineStr">
         <is>
           <t>2026-09-19 23:30:00</t>
         </is>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G68">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G106">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU342"/>
+  <dimension ref="A1:AU346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G194">
@@ -32047,12 +32047,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G195">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>2026-09-19 12:15:00</t>
+          <t>2026-09-19 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32210,27 +32210,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-09-19 12:15:00</t>
+          <t>2026-09-19 12:00:00</t>
         </is>
       </c>
     </row>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G197">
@@ -32536,27 +32536,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-09-19 12:30:00</t>
+          <t>2026-09-19 12:15:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-09-19 12:30:00</t>
+          <t>2026-09-19 12:15:00</t>
         </is>
       </c>
     </row>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,22 +33193,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G204">
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-09-19 12:45:00</t>
+          <t>2026-09-19 12:30:00</t>
         </is>
       </c>
     </row>
@@ -33840,27 +33840,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00:00</t>
+          <t>2026-09-19 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-09-19 13:00:00</t>
+          <t>2026-09-19 12:45:00</t>
         </is>
       </c>
     </row>
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,22 +34986,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,7 +35801,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G220">
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-09-19 13:15:00</t>
+          <t>2026-09-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30:00</t>
+          <t>2026-09-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36611,27 +36611,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-09-19 13:30:00</t>
+          <t>2026-09-19 13:15:00</t>
         </is>
       </c>
     </row>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,22 +36942,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G232">
@@ -38241,12 +38241,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G233">
@@ -38392,7 +38392,7 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>2026-09-19 13:45:00</t>
+          <t>2026-09-19 13:30:00</t>
         </is>
       </c>
     </row>
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G234">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-09-19 13:45:00</t>
+          <t>2026-09-19 13:30:00</t>
         </is>
       </c>
     </row>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G237">
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00:00</t>
+          <t>2026-09-19 13:45:00</t>
         </is>
       </c>
     </row>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-09-19 14:00:00</t>
+          <t>2026-09-19 13:45:00</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G252">
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-09-19 14:15:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
     </row>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-09-19 14:15:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
     </row>
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
     </row>
@@ -41990,12 +41990,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30:00</t>
+          <t>2026-09-19 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30:00</t>
+          <t>2026-09-19 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-19 14:30:00</t>
+          <t>2026-09-19 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O260">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P260">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42805,12 +42805,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00:00</t>
+          <t>2026-09-19 14:30:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00:00</t>
+          <t>2026-09-19 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00:00</t>
+          <t>2026-09-19 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-19 15:00:00</t>
+          <t>2026-09-19 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G266">
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G267">
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-19 15:15:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-19 15:15:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44598,27 +44598,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:15:00</t>
         </is>
       </c>
     </row>
@@ -44761,27 +44761,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:15:00</t>
         </is>
       </c>
     </row>
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-19 15:45:00</t>
+          <t>2026-09-19 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-19 15:45:00</t>
+          <t>2026-09-19 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G283">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-19 15:45:00</t>
+          <t>2026-09-19 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46554,12 +46554,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-09-19 15:45:00</t>
+          <t>2026-09-19 15:30:00</t>
         </is>
       </c>
     </row>
@@ -46722,22 +46722,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G288">
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00:00</t>
+          <t>2026-09-19 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47532,27 +47532,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00:00</t>
+          <t>2026-09-19 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00:00</t>
+          <t>2026-09-19 15:45:00</t>
         </is>
       </c>
     </row>
@@ -47858,12 +47858,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-09-19 16:00:00</t>
+          <t>2026-09-19 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G293">
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48510,27 +48510,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48673,27 +48673,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00:00</t>
+          <t>2026-09-19 16:30:00</t>
         </is>
       </c>
     </row>
@@ -48999,27 +48999,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00:00</t>
+          <t>2026-09-19 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-09-19 18:00:00</t>
+          <t>2026-09-19 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-19 18:00:00</t>
+          <t>2026-09-19 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-09-19 18:30:00</t>
+          <t>2026-09-19 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-19 18:30:00</t>
+          <t>2026-09-19 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G304">
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:00</t>
+          <t>2026-09-19 18:00:00</t>
         </is>
       </c>
     </row>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00:00</t>
+          <t>2026-09-19 18:00:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00:00</t>
+          <t>2026-09-19 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G307">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00:00</t>
+          <t>2026-09-19 18:30:00</t>
         </is>
       </c>
     </row>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G308">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-19 20:00:00</t>
+          <t>2026-09-19 19:30:00</t>
         </is>
       </c>
     </row>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G309">
@@ -50792,12 +50792,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-09-19 20:30:00</t>
+          <t>2026-09-19 20:00:00</t>
         </is>
       </c>
     </row>
@@ -50955,7 +50955,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-19 20:30:00</t>
+          <t>2026-09-19 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51118,7 +51118,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-09-19 20:30:00</t>
+          <t>2026-09-19 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G313">
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-19 20:30:00</t>
+          <t>2026-09-19 20:00:00</t>
         </is>
       </c>
     </row>
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,7 +51775,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G316">
@@ -51933,27 +51933,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G317">
@@ -52084,7 +52084,7 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>2026-09-19 21:00:00</t>
+          <t>2026-09-19 20:30:00</t>
         </is>
       </c>
     </row>
@@ -52096,27 +52096,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G318">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-19 21:00:00</t>
+          <t>2026-09-19 20:30:00</t>
         </is>
       </c>
     </row>
@@ -52259,12 +52259,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-09-19 21:00:00</t>
+          <t>2026-09-19 20:30:00</t>
         </is>
       </c>
     </row>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-09-19 21:00:00</t>
+          <t>2026-09-19 20:30:00</t>
         </is>
       </c>
     </row>
@@ -52590,7 +52590,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G321">
@@ -52753,7 +52753,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G322">
@@ -52916,22 +52916,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,22 +53079,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G326">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G329">
@@ -53932,7 +53932,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N329">
@@ -54052,27 +54052,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -54215,27 +54215,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -54378,27 +54378,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -54541,27 +54541,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G333">
@@ -54584,7 +54584,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-19 21:30:00</t>
+          <t>2026-09-19 21:00:00</t>
         </is>
       </c>
     </row>
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G334">
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-19 21:45:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G336">
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-09-19 22:00:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -55193,7 +55193,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G337">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -55356,7 +55356,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G338">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30:00</t>
+          <t>2026-09-19 21:30:00</t>
         </is>
       </c>
     </row>
@@ -55519,12 +55519,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G339">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>2026-09-19 22:30:00</t>
+          <t>2026-09-19 21:45:00</t>
         </is>
       </c>
     </row>
@@ -55682,7 +55682,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G340">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>2026-09-19 23:00:00</t>
+          <t>2026-09-19 22:00:00</t>
         </is>
       </c>
     </row>
@@ -55845,12 +55845,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G341">
@@ -55996,7 +55996,7 @@
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>2026-09-19 23:30:00</t>
+          <t>2026-09-19 22:30:00</t>
         </is>
       </c>
     </row>
@@ -56008,156 +56008,808 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="G342">
+        <v>0</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>0</v>
+      </c>
+      <c r="J342">
+        <v>0</v>
+      </c>
+      <c r="K342">
+        <v>0</v>
+      </c>
+      <c r="L342">
+        <v>0</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N342">
+        <v>0</v>
+      </c>
+      <c r="O342">
+        <v>0</v>
+      </c>
+      <c r="P342">
+        <v>0</v>
+      </c>
+      <c r="Q342">
+        <v>0</v>
+      </c>
+      <c r="R342">
+        <v>0</v>
+      </c>
+      <c r="S342">
+        <v>0</v>
+      </c>
+      <c r="T342">
+        <v>0</v>
+      </c>
+      <c r="U342">
+        <v>0</v>
+      </c>
+      <c r="V342">
+        <v>0</v>
+      </c>
+      <c r="W342">
+        <v>0</v>
+      </c>
+      <c r="X342">
+        <v>0</v>
+      </c>
+      <c r="Y342">
+        <v>0</v>
+      </c>
+      <c r="Z342">
+        <v>0</v>
+      </c>
+      <c r="AA342">
+        <v>0</v>
+      </c>
+      <c r="AB342">
+        <v>0</v>
+      </c>
+      <c r="AC342">
+        <v>0</v>
+      </c>
+      <c r="AD342">
+        <v>0</v>
+      </c>
+      <c r="AE342">
+        <v>0</v>
+      </c>
+      <c r="AF342">
+        <v>0</v>
+      </c>
+      <c r="AG342">
+        <v>0</v>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ342">
+        <v>0</v>
+      </c>
+      <c r="AK342">
+        <v>0</v>
+      </c>
+      <c r="AL342">
+        <v>0</v>
+      </c>
+      <c r="AM342">
+        <v>-1</v>
+      </c>
+      <c r="AN342">
+        <v>-1</v>
+      </c>
+      <c r="AO342">
+        <v>-1</v>
+      </c>
+      <c r="AP342">
+        <v>-1</v>
+      </c>
+      <c r="AQ342">
+        <v>0</v>
+      </c>
+      <c r="AR342">
+        <v>0</v>
+      </c>
+      <c r="AS342">
+        <v>0</v>
+      </c>
+      <c r="AT342">
+        <v>0</v>
+      </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="G343">
+        <v>0</v>
+      </c>
+      <c r="H343">
+        <v>0</v>
+      </c>
+      <c r="I343">
+        <v>0</v>
+      </c>
+      <c r="J343">
+        <v>0</v>
+      </c>
+      <c r="K343">
+        <v>0</v>
+      </c>
+      <c r="L343">
+        <v>0</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N343">
+        <v>0</v>
+      </c>
+      <c r="O343">
+        <v>0</v>
+      </c>
+      <c r="P343">
+        <v>0</v>
+      </c>
+      <c r="Q343">
+        <v>0</v>
+      </c>
+      <c r="R343">
+        <v>0</v>
+      </c>
+      <c r="S343">
+        <v>0</v>
+      </c>
+      <c r="T343">
+        <v>0</v>
+      </c>
+      <c r="U343">
+        <v>0</v>
+      </c>
+      <c r="V343">
+        <v>0</v>
+      </c>
+      <c r="W343">
+        <v>0</v>
+      </c>
+      <c r="X343">
+        <v>0</v>
+      </c>
+      <c r="Y343">
+        <v>0</v>
+      </c>
+      <c r="Z343">
+        <v>0</v>
+      </c>
+      <c r="AA343">
+        <v>0</v>
+      </c>
+      <c r="AB343">
+        <v>0</v>
+      </c>
+      <c r="AC343">
+        <v>0</v>
+      </c>
+      <c r="AD343">
+        <v>0</v>
+      </c>
+      <c r="AE343">
+        <v>0</v>
+      </c>
+      <c r="AF343">
+        <v>0</v>
+      </c>
+      <c r="AG343">
+        <v>0</v>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ343">
+        <v>0</v>
+      </c>
+      <c r="AK343">
+        <v>0</v>
+      </c>
+      <c r="AL343">
+        <v>0</v>
+      </c>
+      <c r="AM343">
+        <v>-1</v>
+      </c>
+      <c r="AN343">
+        <v>-1</v>
+      </c>
+      <c r="AO343">
+        <v>-1</v>
+      </c>
+      <c r="AP343">
+        <v>-1</v>
+      </c>
+      <c r="AQ343">
+        <v>0</v>
+      </c>
+      <c r="AR343">
+        <v>0</v>
+      </c>
+      <c r="AS343">
+        <v>0</v>
+      </c>
+      <c r="AT343">
+        <v>0</v>
+      </c>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="G344">
+        <v>0</v>
+      </c>
+      <c r="H344">
+        <v>0</v>
+      </c>
+      <c r="I344">
+        <v>0</v>
+      </c>
+      <c r="J344">
+        <v>0</v>
+      </c>
+      <c r="K344">
+        <v>0</v>
+      </c>
+      <c r="L344">
+        <v>0</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N344">
+        <v>0</v>
+      </c>
+      <c r="O344">
+        <v>0</v>
+      </c>
+      <c r="P344">
+        <v>0</v>
+      </c>
+      <c r="Q344">
+        <v>0</v>
+      </c>
+      <c r="R344">
+        <v>0</v>
+      </c>
+      <c r="S344">
+        <v>0</v>
+      </c>
+      <c r="T344">
+        <v>0</v>
+      </c>
+      <c r="U344">
+        <v>0</v>
+      </c>
+      <c r="V344">
+        <v>0</v>
+      </c>
+      <c r="W344">
+        <v>0</v>
+      </c>
+      <c r="X344">
+        <v>0</v>
+      </c>
+      <c r="Y344">
+        <v>0</v>
+      </c>
+      <c r="Z344">
+        <v>0</v>
+      </c>
+      <c r="AA344">
+        <v>0</v>
+      </c>
+      <c r="AB344">
+        <v>0</v>
+      </c>
+      <c r="AC344">
+        <v>0</v>
+      </c>
+      <c r="AD344">
+        <v>0</v>
+      </c>
+      <c r="AE344">
+        <v>0</v>
+      </c>
+      <c r="AF344">
+        <v>0</v>
+      </c>
+      <c r="AG344">
+        <v>0</v>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ344">
+        <v>0</v>
+      </c>
+      <c r="AK344">
+        <v>0</v>
+      </c>
+      <c r="AL344">
+        <v>0</v>
+      </c>
+      <c r="AM344">
+        <v>-1</v>
+      </c>
+      <c r="AN344">
+        <v>-1</v>
+      </c>
+      <c r="AO344">
+        <v>-1</v>
+      </c>
+      <c r="AP344">
+        <v>-1</v>
+      </c>
+      <c r="AQ344">
+        <v>0</v>
+      </c>
+      <c r="AR344">
+        <v>0</v>
+      </c>
+      <c r="AS344">
+        <v>0</v>
+      </c>
+      <c r="AT344">
+        <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="G345">
+        <v>0</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+      <c r="I345">
+        <v>0</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345">
+        <v>0</v>
+      </c>
+      <c r="L345">
+        <v>0</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N345">
+        <v>0</v>
+      </c>
+      <c r="O345">
+        <v>0</v>
+      </c>
+      <c r="P345">
+        <v>0</v>
+      </c>
+      <c r="Q345">
+        <v>0</v>
+      </c>
+      <c r="R345">
+        <v>0</v>
+      </c>
+      <c r="S345">
+        <v>0</v>
+      </c>
+      <c r="T345">
+        <v>0</v>
+      </c>
+      <c r="U345">
+        <v>0</v>
+      </c>
+      <c r="V345">
+        <v>0</v>
+      </c>
+      <c r="W345">
+        <v>0</v>
+      </c>
+      <c r="X345">
+        <v>0</v>
+      </c>
+      <c r="Y345">
+        <v>0</v>
+      </c>
+      <c r="Z345">
+        <v>0</v>
+      </c>
+      <c r="AA345">
+        <v>0</v>
+      </c>
+      <c r="AB345">
+        <v>0</v>
+      </c>
+      <c r="AC345">
+        <v>0</v>
+      </c>
+      <c r="AD345">
+        <v>0</v>
+      </c>
+      <c r="AE345">
+        <v>0</v>
+      </c>
+      <c r="AF345">
+        <v>0</v>
+      </c>
+      <c r="AG345">
+        <v>0</v>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ345">
+        <v>0</v>
+      </c>
+      <c r="AK345">
+        <v>0</v>
+      </c>
+      <c r="AL345">
+        <v>0</v>
+      </c>
+      <c r="AM345">
+        <v>-1</v>
+      </c>
+      <c r="AN345">
+        <v>-1</v>
+      </c>
+      <c r="AO345">
+        <v>-1</v>
+      </c>
+      <c r="AP345">
+        <v>-1</v>
+      </c>
+      <c r="AQ345">
+        <v>0</v>
+      </c>
+      <c r="AR345">
+        <v>0</v>
+      </c>
+      <c r="AS345">
+        <v>0</v>
+      </c>
+      <c r="AT345">
+        <v>0</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>2026-09-19 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D346" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
+      <c r="E346" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
+      <c r="F346" t="inlineStr">
         <is>
           <t>Atlanta United FC</t>
         </is>
       </c>
-      <c r="G342">
-        <v>0</v>
-      </c>
-      <c r="H342">
-        <v>0</v>
-      </c>
-      <c r="I342">
-        <v>0</v>
-      </c>
-      <c r="J342">
-        <v>0</v>
-      </c>
-      <c r="K342">
-        <v>0</v>
-      </c>
-      <c r="L342">
-        <v>0</v>
-      </c>
-      <c r="M342" t="inlineStr">
+      <c r="G346">
+        <v>0</v>
+      </c>
+      <c r="H346">
+        <v>0</v>
+      </c>
+      <c r="I346">
+        <v>0</v>
+      </c>
+      <c r="J346">
+        <v>0</v>
+      </c>
+      <c r="K346">
+        <v>0</v>
+      </c>
+      <c r="L346">
+        <v>0</v>
+      </c>
+      <c r="M346" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N342">
-        <v>0</v>
-      </c>
-      <c r="O342">
-        <v>0</v>
-      </c>
-      <c r="P342">
-        <v>0</v>
-      </c>
-      <c r="Q342">
-        <v>0</v>
-      </c>
-      <c r="R342">
-        <v>0</v>
-      </c>
-      <c r="S342">
-        <v>0</v>
-      </c>
-      <c r="T342">
-        <v>0</v>
-      </c>
-      <c r="U342">
-        <v>0</v>
-      </c>
-      <c r="V342">
-        <v>0</v>
-      </c>
-      <c r="W342">
-        <v>0</v>
-      </c>
-      <c r="X342">
-        <v>0</v>
-      </c>
-      <c r="Y342">
-        <v>0</v>
-      </c>
-      <c r="Z342">
-        <v>0</v>
-      </c>
-      <c r="AA342">
-        <v>0</v>
-      </c>
-      <c r="AB342">
-        <v>0</v>
-      </c>
-      <c r="AC342">
-        <v>0</v>
-      </c>
-      <c r="AD342">
-        <v>0</v>
-      </c>
-      <c r="AE342">
-        <v>0</v>
-      </c>
-      <c r="AF342">
-        <v>0</v>
-      </c>
-      <c r="AG342">
-        <v>0</v>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ342">
-        <v>0</v>
-      </c>
-      <c r="AK342">
-        <v>0</v>
-      </c>
-      <c r="AL342">
-        <v>0</v>
-      </c>
-      <c r="AM342">
-        <v>-1</v>
-      </c>
-      <c r="AN342">
-        <v>-1</v>
-      </c>
-      <c r="AO342">
-        <v>-1</v>
-      </c>
-      <c r="AP342">
-        <v>-1</v>
-      </c>
-      <c r="AQ342">
-        <v>0</v>
-      </c>
-      <c r="AR342">
-        <v>0</v>
-      </c>
-      <c r="AS342">
-        <v>0</v>
-      </c>
-      <c r="AT342">
-        <v>0</v>
-      </c>
-      <c r="AU342" t="inlineStr">
+      <c r="N346">
+        <v>0</v>
+      </c>
+      <c r="O346">
+        <v>0</v>
+      </c>
+      <c r="P346">
+        <v>0</v>
+      </c>
+      <c r="Q346">
+        <v>0</v>
+      </c>
+      <c r="R346">
+        <v>0</v>
+      </c>
+      <c r="S346">
+        <v>0</v>
+      </c>
+      <c r="T346">
+        <v>0</v>
+      </c>
+      <c r="U346">
+        <v>0</v>
+      </c>
+      <c r="V346">
+        <v>0</v>
+      </c>
+      <c r="W346">
+        <v>0</v>
+      </c>
+      <c r="X346">
+        <v>0</v>
+      </c>
+      <c r="Y346">
+        <v>0</v>
+      </c>
+      <c r="Z346">
+        <v>0</v>
+      </c>
+      <c r="AA346">
+        <v>0</v>
+      </c>
+      <c r="AB346">
+        <v>0</v>
+      </c>
+      <c r="AC346">
+        <v>0</v>
+      </c>
+      <c r="AD346">
+        <v>0</v>
+      </c>
+      <c r="AE346">
+        <v>0</v>
+      </c>
+      <c r="AF346">
+        <v>0</v>
+      </c>
+      <c r="AG346">
+        <v>0</v>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ346">
+        <v>0</v>
+      </c>
+      <c r="AK346">
+        <v>0</v>
+      </c>
+      <c r="AL346">
+        <v>0</v>
+      </c>
+      <c r="AM346">
+        <v>-1</v>
+      </c>
+      <c r="AN346">
+        <v>-1</v>
+      </c>
+      <c r="AO346">
+        <v>-1</v>
+      </c>
+      <c r="AP346">
+        <v>-1</v>
+      </c>
+      <c r="AQ346">
+        <v>0</v>
+      </c>
+      <c r="AR346">
+        <v>0</v>
+      </c>
+      <c r="AS346">
+        <v>0</v>
+      </c>
+      <c r="AT346">
+        <v>0</v>
+      </c>
+      <c r="AU346" t="inlineStr">
         <is>
           <t>2026-09-19 23:30:00</t>
         </is>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G138">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G237">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G116">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G161">
@@ -29658,55 +29658,55 @@
         <v>3.26</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S220">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T220">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U220">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V220">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X220">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z220">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC220">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD220">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG220">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK220">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37971,55 +37971,55 @@
         <v>0</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G237">
@@ -43350,55 +43350,55 @@
         <v>3.06</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL264">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="P8">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="Q8">
+        <v>4.4</v>
+      </c>
+      <c r="R8">
+        <v>2.18</v>
+      </c>
+      <c r="S8">
+        <v>1.34</v>
+      </c>
+      <c r="T8">
         <v>2.92</v>
       </c>
-      <c r="R8">
-        <v>2.22</v>
-      </c>
-      <c r="S8">
+      <c r="U8">
+        <v>2.6</v>
+      </c>
+      <c r="V8">
+        <v>1.42</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
         <v>1.26</v>
       </c>
-      <c r="T8">
-        <v>3.4</v>
-      </c>
-      <c r="U8">
-        <v>2.4</v>
-      </c>
-      <c r="V8">
-        <v>1.55</v>
-      </c>
-      <c r="W8">
-        <v>1.12</v>
-      </c>
-      <c r="X8">
-        <v>1.02</v>
-      </c>
-      <c r="Y8">
-        <v>1.19</v>
-      </c>
       <c r="Z8">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG8">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.93</v>
       </c>
       <c r="AK8">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>2.68</v>
+      </c>
+      <c r="O9">
+        <v>3.73</v>
+      </c>
+      <c r="P9">
+        <v>2.28</v>
+      </c>
+      <c r="Q9">
+        <v>2.92</v>
+      </c>
+      <c r="R9">
+        <v>2.22</v>
+      </c>
+      <c r="S9">
+        <v>1.26</v>
+      </c>
+      <c r="T9">
         <v>3.4</v>
       </c>
-      <c r="O9">
-        <v>3.45</v>
-      </c>
-      <c r="P9">
-        <v>1.88</v>
-      </c>
-      <c r="Q9">
-        <v>4.4</v>
-      </c>
-      <c r="R9">
-        <v>2.18</v>
-      </c>
-      <c r="S9">
-        <v>1.34</v>
-      </c>
-      <c r="T9">
-        <v>2.92</v>
-      </c>
       <c r="U9">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
+        <v>1.55</v>
+      </c>
+      <c r="W9">
+        <v>1.12</v>
+      </c>
+      <c r="X9">
+        <v>1.02</v>
+      </c>
+      <c r="Y9">
+        <v>1.19</v>
+      </c>
+      <c r="Z9">
+        <v>4.15</v>
+      </c>
+      <c r="AA9">
+        <v>1.65</v>
+      </c>
+      <c r="AB9">
+        <v>2.2</v>
+      </c>
+      <c r="AC9">
+        <v>2.47</v>
+      </c>
+      <c r="AD9">
         <v>1.42</v>
       </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1.26</v>
-      </c>
-      <c r="Z9">
-        <v>3.7</v>
-      </c>
-      <c r="AA9">
-        <v>1.8</v>
-      </c>
-      <c r="AB9">
-        <v>2</v>
-      </c>
-      <c r="AC9">
-        <v>2.83</v>
-      </c>
-      <c r="AD9">
-        <v>1.33</v>
-      </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.93</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.82</v>
+        <v>3.39</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="U15">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA15">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
-        <v>3.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD15">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q16">
-        <v>2.54</v>
+        <v>3.82</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="V16">
         <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="AD16">
+        <v>1.23</v>
+      </c>
+      <c r="AE16">
+        <v>1.05</v>
+      </c>
+      <c r="AF16">
+        <v>1.78</v>
+      </c>
+      <c r="AG16">
+        <v>1.91</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.5</v>
+      </c>
+      <c r="AK16">
         <v>1.3</v>
-      </c>
-      <c r="AE16">
-        <v>1.06</v>
-      </c>
-      <c r="AF16">
-        <v>1.74</v>
-      </c>
-      <c r="AG16">
-        <v>1.96</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.8</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
+        <v>1.37</v>
+      </c>
+      <c r="T17">
+        <v>2.98</v>
+      </c>
+      <c r="U17">
+        <v>2.72</v>
+      </c>
+      <c r="V17">
+        <v>1.36</v>
+      </c>
+      <c r="W17">
+        <v>1.04</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.25</v>
+      </c>
+      <c r="Z17">
+        <v>3.28</v>
+      </c>
+      <c r="AA17">
+        <v>1.87</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>3.32</v>
+      </c>
+      <c r="AD17">
         <v>1.3</v>
       </c>
-      <c r="T17">
-        <v>3.24</v>
-      </c>
-      <c r="U17">
-        <v>2.38</v>
-      </c>
-      <c r="V17">
-        <v>1.47</v>
-      </c>
-      <c r="W17">
-        <v>1.09</v>
-      </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
-      <c r="Y17">
-        <v>1.17</v>
-      </c>
-      <c r="Z17">
-        <v>3.99</v>
-      </c>
-      <c r="AA17">
-        <v>1.68</v>
-      </c>
-      <c r="AB17">
-        <v>2.07</v>
-      </c>
-      <c r="AC17">
-        <v>2.7</v>
-      </c>
-      <c r="AD17">
-        <v>1.36</v>
-      </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="O18">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>4.22</v>
+        <v>2.17</v>
       </c>
       <c r="R18">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>2.45</v>
+        <v>3.24</v>
       </c>
       <c r="U18">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>2.59</v>
+        <v>3.99</v>
       </c>
       <c r="AA18">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AC18">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD18">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>3.39</v>
+        <v>4.22</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="S19">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>3.12</v>
+        <v>2.45</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
+        <v>1.39</v>
+      </c>
+      <c r="Z19">
+        <v>2.59</v>
+      </c>
+      <c r="AA19">
+        <v>2.35</v>
+      </c>
+      <c r="AB19">
+        <v>1.57</v>
+      </c>
+      <c r="AC19">
+        <v>4.2</v>
+      </c>
+      <c r="AD19">
         <v>1.15</v>
       </c>
-      <c r="Z19">
-        <v>4.2</v>
-      </c>
-      <c r="AA19">
-        <v>1.66</v>
-      </c>
-      <c r="AB19">
-        <v>2.15</v>
-      </c>
-      <c r="AC19">
-        <v>2.52</v>
-      </c>
-      <c r="AD19">
-        <v>1.41</v>
-      </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AK19">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P36">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="U36">
         <v>2.25</v>
       </c>
       <c r="V36">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA36">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB36">
         <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF36">
         <v>1.51</v>
       </c>
       <c r="AG36">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q37">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U37">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="W37">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB37">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="AD37">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AG37">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>1.39</v>
+        <v>1.88</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>3.34</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
         <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z38">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="AA38">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AC38">
-        <v>2.39</v>
+        <v>2.09</v>
       </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AE38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF38">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK38">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="O107">
+        <v>3.85</v>
+      </c>
+      <c r="P107">
+        <v>2.05</v>
+      </c>
+      <c r="Q107">
+        <v>3.65</v>
+      </c>
+      <c r="R107">
+        <v>2.34</v>
+      </c>
+      <c r="S107">
+        <v>1.23</v>
+      </c>
+      <c r="T107">
         <v>3.5</v>
       </c>
-      <c r="P107">
-        <v>3.2</v>
-      </c>
-      <c r="Q107">
-        <v>0</v>
-      </c>
-      <c r="R107">
-        <v>0</v>
-      </c>
-      <c r="S107">
-        <v>0</v>
-      </c>
-      <c r="T107">
-        <v>0</v>
-      </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB107">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="O108">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q108">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S108">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T108">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V108">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W108">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z108">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB108">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC108">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG108">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK108">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
+        <v>2.3</v>
+      </c>
+      <c r="O125">
+        <v>3.1</v>
+      </c>
+      <c r="P125">
+        <v>2.75</v>
+      </c>
+      <c r="Q125">
+        <v>3.04</v>
+      </c>
+      <c r="R125">
         <v>2</v>
       </c>
-      <c r="O125">
-        <v>3.25</v>
-      </c>
-      <c r="P125">
-        <v>3.2</v>
-      </c>
-      <c r="Q125">
-        <v>2.62</v>
-      </c>
-      <c r="R125">
-        <v>2.06</v>
-      </c>
       <c r="S125">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T125">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="U125">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="V125">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W125">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y125">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z125">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AA125">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB125">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC125">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AD125">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE125">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG125">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK125">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P126">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q126">
+        <v>2.62</v>
+      </c>
+      <c r="R126">
+        <v>2.06</v>
+      </c>
+      <c r="S126">
+        <v>1.36</v>
+      </c>
+      <c r="T126">
+        <v>2.88</v>
+      </c>
+      <c r="U126">
+        <v>2.85</v>
+      </c>
+      <c r="V126">
+        <v>1.33</v>
+      </c>
+      <c r="W126">
+        <v>1.04</v>
+      </c>
+      <c r="X126">
+        <v>1.02</v>
+      </c>
+      <c r="Y126">
+        <v>1.29</v>
+      </c>
+      <c r="Z126">
         <v>3.04</v>
       </c>
-      <c r="R126">
-        <v>2</v>
-      </c>
-      <c r="S126">
-        <v>1.46</v>
-      </c>
-      <c r="T126">
-        <v>2.48</v>
-      </c>
-      <c r="U126">
-        <v>2.91</v>
-      </c>
-      <c r="V126">
-        <v>1.29</v>
-      </c>
-      <c r="W126">
-        <v>1.03</v>
-      </c>
-      <c r="X126">
-        <v>1.05</v>
-      </c>
-      <c r="Y126">
-        <v>1.35</v>
-      </c>
-      <c r="Z126">
-        <v>2.74</v>
-      </c>
       <c r="AA126">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB126">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AC126">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AD126">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG126">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,80 +21336,80 @@
         </is>
       </c>
       <c r="N129">
+        <v>2.37</v>
+      </c>
+      <c r="O129">
+        <v>3.4</v>
+      </c>
+      <c r="P129">
+        <v>3</v>
+      </c>
+      <c r="Q129">
+        <v>2.7</v>
+      </c>
+      <c r="R129">
+        <v>2.12</v>
+      </c>
+      <c r="S129">
+        <v>1.35</v>
+      </c>
+      <c r="T129">
+        <v>2.88</v>
+      </c>
+      <c r="U129">
+        <v>2.9</v>
+      </c>
+      <c r="V129">
+        <v>1.36</v>
+      </c>
+      <c r="W129">
+        <v>1.07</v>
+      </c>
+      <c r="X129">
+        <v>1.04</v>
+      </c>
+      <c r="Y129">
+        <v>1.3</v>
+      </c>
+      <c r="Z129">
+        <v>2.97</v>
+      </c>
+      <c r="AA129">
+        <v>2.02</v>
+      </c>
+      <c r="AB129">
+        <v>1.72</v>
+      </c>
+      <c r="AC129">
+        <v>3.42</v>
+      </c>
+      <c r="AD129">
+        <v>1.22</v>
+      </c>
+      <c r="AE129">
+        <v>1.05</v>
+      </c>
+      <c r="AF129">
+        <v>1.79</v>
+      </c>
+      <c r="AG129">
+        <v>1.92</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ129">
+        <v>1.26</v>
+      </c>
+      <c r="AK129">
         <v>1.48</v>
-      </c>
-      <c r="O129">
-        <v>4.55</v>
-      </c>
-      <c r="P129">
-        <v>5.75</v>
-      </c>
-      <c r="Q129">
-        <v>1.91</v>
-      </c>
-      <c r="R129">
-        <v>2.5</v>
-      </c>
-      <c r="S129">
-        <v>1.25</v>
-      </c>
-      <c r="T129">
-        <v>3.48</v>
-      </c>
-      <c r="U129">
-        <v>2.19</v>
-      </c>
-      <c r="V129">
-        <v>1.58</v>
-      </c>
-      <c r="W129">
-        <v>1.13</v>
-      </c>
-      <c r="X129">
-        <v>1.01</v>
-      </c>
-      <c r="Y129">
-        <v>1.13</v>
-      </c>
-      <c r="Z129">
-        <v>4.55</v>
-      </c>
-      <c r="AA129">
-        <v>1.57</v>
-      </c>
-      <c r="AB129">
-        <v>2.35</v>
-      </c>
-      <c r="AC129">
-        <v>2.38</v>
-      </c>
-      <c r="AD129">
-        <v>1.54</v>
-      </c>
-      <c r="AE129">
-        <v>1.2</v>
-      </c>
-      <c r="AF129">
-        <v>1.69</v>
-      </c>
-      <c r="AG129">
-        <v>2.2</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>1.16</v>
-      </c>
-      <c r="AK129">
-        <v>2.59</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="O131">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P131">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="Q131">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="R131">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S131">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T131">
-        <v>2.74</v>
+        <v>3.12</v>
       </c>
       <c r="U131">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V131">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z131">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA131">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AB131">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC131">
-        <v>3.36</v>
+        <v>2.59</v>
       </c>
       <c r="AD131">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE131">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF131">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AG131">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK131">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P132">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q132">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="R132">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S132">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T132">
-        <v>2.64</v>
+        <v>3.48</v>
       </c>
       <c r="U132">
-        <v>2.82</v>
+        <v>2.19</v>
       </c>
       <c r="V132">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W132">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z132">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA132">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB132">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC132">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD132">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AE132">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AF132">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG132">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK132">
-        <v>1.57</v>
+        <v>2.59</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="O133">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P133">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="Q133">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="R133">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S133">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T133">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="U133">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V133">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z133">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA133">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AB133">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC133">
-        <v>2.59</v>
+        <v>3.36</v>
       </c>
       <c r="AD133">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE133">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AG133">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK133">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O134">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="R134">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S134">
+        <v>1.37</v>
+      </c>
+      <c r="T134">
+        <v>2.64</v>
+      </c>
+      <c r="U134">
+        <v>2.82</v>
+      </c>
+      <c r="V134">
+        <v>1.36</v>
+      </c>
+      <c r="W134">
+        <v>1.03</v>
+      </c>
+      <c r="X134">
+        <v>1</v>
+      </c>
+      <c r="Y134">
         <v>1.3</v>
       </c>
-      <c r="T134">
-        <v>3.19</v>
-      </c>
-      <c r="U134">
-        <v>2.42</v>
-      </c>
-      <c r="V134">
-        <v>1.47</v>
-      </c>
-      <c r="W134">
-        <v>1.11</v>
-      </c>
-      <c r="X134">
-        <v>1.02</v>
-      </c>
-      <c r="Y134">
-        <v>1.24</v>
-      </c>
       <c r="Z134">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA134">
+        <v>1.98</v>
+      </c>
+      <c r="AB134">
+        <v>1.85</v>
+      </c>
+      <c r="AC134">
+        <v>3.28</v>
+      </c>
+      <c r="AD134">
+        <v>1.25</v>
+      </c>
+      <c r="AE134">
+        <v>1.05</v>
+      </c>
+      <c r="AF134">
         <v>1.73</v>
       </c>
-      <c r="AB134">
-        <v>2.01</v>
-      </c>
-      <c r="AC134">
-        <v>2.74</v>
-      </c>
-      <c r="AD134">
-        <v>1.35</v>
-      </c>
-      <c r="AE134">
-        <v>1.09</v>
-      </c>
-      <c r="AF134">
-        <v>1.65</v>
-      </c>
       <c r="AG134">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK134">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O135">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P135">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q135">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S135">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
+        <v>3.19</v>
+      </c>
+      <c r="U135">
+        <v>2.42</v>
+      </c>
+      <c r="V135">
+        <v>1.47</v>
+      </c>
+      <c r="W135">
+        <v>1.11</v>
+      </c>
+      <c r="X135">
+        <v>1.02</v>
+      </c>
+      <c r="Y135">
+        <v>1.24</v>
+      </c>
+      <c r="Z135">
+        <v>3.8</v>
+      </c>
+      <c r="AA135">
+        <v>1.73</v>
+      </c>
+      <c r="AB135">
+        <v>2.01</v>
+      </c>
+      <c r="AC135">
         <v>2.74</v>
       </c>
-      <c r="U135">
-        <v>2.54</v>
-      </c>
-      <c r="V135">
-        <v>1.44</v>
-      </c>
-      <c r="W135">
-        <v>1.07</v>
-      </c>
-      <c r="X135">
-        <v>1</v>
-      </c>
-      <c r="Y135">
-        <v>1.26</v>
-      </c>
-      <c r="Z135">
-        <v>3.71</v>
-      </c>
-      <c r="AA135">
-        <v>1.85</v>
-      </c>
-      <c r="AB135">
-        <v>1.95</v>
-      </c>
-      <c r="AC135">
-        <v>3.04</v>
-      </c>
       <c r="AD135">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE135">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF135">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG135">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.23</v>
       </c>
       <c r="AK135">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.48</v>
+        <v>2.08</v>
       </c>
       <c r="O136">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="P136">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q136">
-        <v>2.04</v>
+        <v>2.61</v>
       </c>
       <c r="R136">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S136">
+        <v>1.38</v>
+      </c>
+      <c r="T136">
+        <v>2.74</v>
+      </c>
+      <c r="U136">
+        <v>2.54</v>
+      </c>
+      <c r="V136">
+        <v>1.44</v>
+      </c>
+      <c r="W136">
+        <v>1.07</v>
+      </c>
+      <c r="X136">
+        <v>1</v>
+      </c>
+      <c r="Y136">
+        <v>1.26</v>
+      </c>
+      <c r="Z136">
+        <v>3.71</v>
+      </c>
+      <c r="AA136">
+        <v>1.85</v>
+      </c>
+      <c r="AB136">
+        <v>1.95</v>
+      </c>
+      <c r="AC136">
+        <v>3.04</v>
+      </c>
+      <c r="AD136">
         <v>1.29</v>
       </c>
-      <c r="T136">
-        <v>3.32</v>
-      </c>
-      <c r="U136">
-        <v>2.32</v>
-      </c>
-      <c r="V136">
-        <v>1.57</v>
-      </c>
-      <c r="W136">
-        <v>1.11</v>
-      </c>
-      <c r="X136">
-        <v>1.01</v>
-      </c>
-      <c r="Y136">
-        <v>1.14</v>
-      </c>
-      <c r="Z136">
-        <v>4.5</v>
-      </c>
-      <c r="AA136">
-        <v>1.66</v>
-      </c>
-      <c r="AB136">
-        <v>2.15</v>
-      </c>
-      <c r="AC136">
-        <v>2.33</v>
-      </c>
-      <c r="AD136">
-        <v>1.52</v>
-      </c>
       <c r="AE136">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF136">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG136">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P137">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q137">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="R137">
+        <v>2.38</v>
+      </c>
+      <c r="S137">
+        <v>1.29</v>
+      </c>
+      <c r="T137">
+        <v>3.32</v>
+      </c>
+      <c r="U137">
+        <v>2.32</v>
+      </c>
+      <c r="V137">
+        <v>1.57</v>
+      </c>
+      <c r="W137">
+        <v>1.11</v>
+      </c>
+      <c r="X137">
+        <v>1.01</v>
+      </c>
+      <c r="Y137">
+        <v>1.14</v>
+      </c>
+      <c r="Z137">
+        <v>4.5</v>
+      </c>
+      <c r="AA137">
+        <v>1.66</v>
+      </c>
+      <c r="AB137">
+        <v>2.15</v>
+      </c>
+      <c r="AC137">
+        <v>2.33</v>
+      </c>
+      <c r="AD137">
+        <v>1.52</v>
+      </c>
+      <c r="AE137">
+        <v>1.16</v>
+      </c>
+      <c r="AF137">
+        <v>1.64</v>
+      </c>
+      <c r="AG137">
         <v>2.1</v>
       </c>
-      <c r="S137">
-        <v>1.4</v>
-      </c>
-      <c r="T137">
-        <v>2.82</v>
-      </c>
-      <c r="U137">
-        <v>2.9</v>
-      </c>
-      <c r="V137">
-        <v>1.4</v>
-      </c>
-      <c r="W137">
-        <v>1.08</v>
-      </c>
-      <c r="X137">
-        <v>1.03</v>
-      </c>
-      <c r="Y137">
-        <v>1.28</v>
-      </c>
-      <c r="Z137">
-        <v>3.08</v>
-      </c>
-      <c r="AA137">
-        <v>2</v>
-      </c>
-      <c r="AB137">
-        <v>1.8</v>
-      </c>
-      <c r="AC137">
-        <v>3.48</v>
-      </c>
-      <c r="AD137">
-        <v>1.25</v>
-      </c>
-      <c r="AE137">
-        <v>1.06</v>
-      </c>
-      <c r="AF137">
-        <v>1.83</v>
-      </c>
-      <c r="AG137">
-        <v>1.91</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK137">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="O138">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P138">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q138">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="R138">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S138">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T138">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U138">
         <v>2.9</v>
       </c>
       <c r="V138">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W138">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z138">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA138">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB138">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC138">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD138">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE138">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF138">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG138">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK138">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="O153">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="P153">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q153">
-        <v>2.41</v>
+        <v>3.34</v>
       </c>
       <c r="R153">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S153">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U153">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V153">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W153">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z153">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AA153">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB153">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC153">
-        <v>2.92</v>
+        <v>2.46</v>
       </c>
       <c r="AD153">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE153">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF153">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG153">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="O154">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="P154">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q154">
-        <v>3.34</v>
+        <v>2.41</v>
       </c>
       <c r="R154">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S154">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T154">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U154">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V154">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W154">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y154">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z154">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA154">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB154">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC154">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="AD154">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE154">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF154">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG154">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK154">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="O226">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P226">
+        <v>5.8</v>
+      </c>
+      <c r="Q226">
+        <v>2</v>
+      </c>
+      <c r="R226">
+        <v>2.58</v>
+      </c>
+      <c r="S226">
+        <v>1.29</v>
+      </c>
+      <c r="T226">
+        <v>3.4</v>
+      </c>
+      <c r="U226">
+        <v>2.29</v>
+      </c>
+      <c r="V226">
+        <v>1.53</v>
+      </c>
+      <c r="W226">
+        <v>1.1</v>
+      </c>
+      <c r="X226">
+        <v>1.01</v>
+      </c>
+      <c r="Y226">
+        <v>1.14</v>
+      </c>
+      <c r="Z226">
+        <v>4.45</v>
+      </c>
+      <c r="AA226">
+        <v>1.57</v>
+      </c>
+      <c r="AB226">
         <v>2.35</v>
       </c>
-      <c r="Q226">
-        <v>3.7</v>
-      </c>
-      <c r="R226">
-        <v>2.04</v>
-      </c>
-      <c r="S226">
-        <v>1.4</v>
-      </c>
-      <c r="T226">
-        <v>2.62</v>
-      </c>
-      <c r="U226">
-        <v>2.96</v>
-      </c>
-      <c r="V226">
-        <v>1.33</v>
-      </c>
-      <c r="W226">
-        <v>1.04</v>
-      </c>
-      <c r="X226">
-        <v>1.05</v>
-      </c>
-      <c r="Y226">
-        <v>1.36</v>
-      </c>
-      <c r="Z226">
-        <v>2.9</v>
-      </c>
-      <c r="AA226">
-        <v>2.07</v>
-      </c>
-      <c r="AB226">
+      <c r="AC226">
+        <v>2.35</v>
+      </c>
+      <c r="AD226">
+        <v>1.47</v>
+      </c>
+      <c r="AE226">
+        <v>1.17</v>
+      </c>
+      <c r="AF226">
         <v>1.65</v>
       </c>
-      <c r="AC226">
-        <v>4</v>
-      </c>
-      <c r="AD226">
-        <v>1.22</v>
-      </c>
-      <c r="AE226">
-        <v>1.05</v>
-      </c>
-      <c r="AF226">
-        <v>1.83</v>
-      </c>
       <c r="AG226">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK226">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O227">
+        <v>3.2</v>
+      </c>
+      <c r="P227">
+        <v>2.35</v>
+      </c>
+      <c r="Q227">
+        <v>3.7</v>
+      </c>
+      <c r="R227">
+        <v>2.04</v>
+      </c>
+      <c r="S227">
+        <v>1.4</v>
+      </c>
+      <c r="T227">
+        <v>2.62</v>
+      </c>
+      <c r="U227">
+        <v>2.96</v>
+      </c>
+      <c r="V227">
+        <v>1.33</v>
+      </c>
+      <c r="W227">
+        <v>1.04</v>
+      </c>
+      <c r="X227">
+        <v>1.05</v>
+      </c>
+      <c r="Y227">
+        <v>1.36</v>
+      </c>
+      <c r="Z227">
+        <v>2.9</v>
+      </c>
+      <c r="AA227">
+        <v>2.07</v>
+      </c>
+      <c r="AB227">
+        <v>1.65</v>
+      </c>
+      <c r="AC227">
         <v>4</v>
       </c>
-      <c r="P227">
-        <v>5.8</v>
-      </c>
-      <c r="Q227">
-        <v>2</v>
-      </c>
-      <c r="R227">
-        <v>2.58</v>
-      </c>
-      <c r="S227">
-        <v>1.29</v>
-      </c>
-      <c r="T227">
-        <v>3.4</v>
-      </c>
-      <c r="U227">
-        <v>2.29</v>
-      </c>
-      <c r="V227">
-        <v>1.53</v>
-      </c>
-      <c r="W227">
-        <v>1.1</v>
-      </c>
-      <c r="X227">
-        <v>1.01</v>
-      </c>
-      <c r="Y227">
-        <v>1.14</v>
-      </c>
-      <c r="Z227">
-        <v>4.45</v>
-      </c>
-      <c r="AA227">
-        <v>1.57</v>
-      </c>
-      <c r="AB227">
-        <v>2.35</v>
-      </c>
-      <c r="AC227">
-        <v>2.35</v>
-      </c>
       <c r="AD227">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AE227">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG227">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK227">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G275">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G278">
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48107,10 +48107,10 @@
         <v>0</v>
       </c>
       <c r="AA293">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB293">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC293">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL301">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.69</v>
+        <v>1.98</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>3.18</v>
       </c>
       <c r="Q15">
-        <v>3.39</v>
+        <v>2.68</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA15">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>2.32</v>
+        <v>1.79</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>3.82</v>
+        <v>3.39</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>3.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.18</v>
+        <v>2.41</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>3.82</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
         <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,31 +3113,31 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB17">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="O36">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q36">
+        <v>2.25</v>
+      </c>
+      <c r="R36">
         <v>2.3</v>
       </c>
-      <c r="R36">
-        <v>2.28</v>
-      </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="U36">
         <v>2.25</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB36">
         <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="AD36">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
         <v>1.51</v>
       </c>
       <c r="AG36">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK36">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P37">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="U37">
         <v>2.25</v>
       </c>
       <c r="V37">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB37">
         <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="AD37">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF37">
         <v>1.51</v>
       </c>
       <c r="AG37">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="O104">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q104">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="S104">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T104">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="U104">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W104">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z104">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA104">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AB104">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AC104">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE104">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG104">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="O105">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="Q105">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="R105">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T105">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U105">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V105">
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z105">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AA105">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB105">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC105">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AD105">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG105">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,31 +17587,31 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>3.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q106">
-        <v>2.34</v>
+        <v>3.7</v>
       </c>
       <c r="R106">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="S106">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U106">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="V106">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W106">
         <v>1.11</v>
@@ -17620,31 +17620,31 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z106">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA106">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB106">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AC106">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD106">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE106">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG106">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O130">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P130">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q130">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="R130">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S130">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T130">
-        <v>2.64</v>
+        <v>3.48</v>
       </c>
       <c r="U130">
-        <v>2.82</v>
+        <v>2.19</v>
       </c>
       <c r="V130">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W130">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA130">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB130">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC130">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD130">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AE130">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AF130">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG130">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK130">
-        <v>1.57</v>
+        <v>2.59</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="O131">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P131">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q131">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="R131">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S131">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T131">
-        <v>3.48</v>
+        <v>3.19</v>
       </c>
       <c r="U131">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="V131">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z131">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA131">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB131">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AC131">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="AD131">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AE131">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF131">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG131">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK131">
-        <v>2.59</v>
+        <v>1.81</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
+        <v>2.08</v>
+      </c>
+      <c r="O132">
+        <v>3.55</v>
+      </c>
+      <c r="P132">
+        <v>3.4</v>
+      </c>
+      <c r="Q132">
+        <v>2.61</v>
+      </c>
+      <c r="R132">
+        <v>2.08</v>
+      </c>
+      <c r="S132">
+        <v>1.38</v>
+      </c>
+      <c r="T132">
+        <v>2.74</v>
+      </c>
+      <c r="U132">
+        <v>2.54</v>
+      </c>
+      <c r="V132">
+        <v>1.44</v>
+      </c>
+      <c r="W132">
+        <v>1.07</v>
+      </c>
+      <c r="X132">
+        <v>1</v>
+      </c>
+      <c r="Y132">
+        <v>1.26</v>
+      </c>
+      <c r="Z132">
+        <v>3.71</v>
+      </c>
+      <c r="AA132">
+        <v>1.85</v>
+      </c>
+      <c r="AB132">
         <v>1.95</v>
       </c>
-      <c r="O132">
-        <v>3.6</v>
-      </c>
-      <c r="P132">
-        <v>3.7</v>
-      </c>
-      <c r="Q132">
-        <v>2.5</v>
-      </c>
-      <c r="R132">
-        <v>2.15</v>
-      </c>
-      <c r="S132">
-        <v>1.3</v>
-      </c>
-      <c r="T132">
-        <v>3.19</v>
-      </c>
-      <c r="U132">
-        <v>2.42</v>
-      </c>
-      <c r="V132">
-        <v>1.47</v>
-      </c>
-      <c r="W132">
-        <v>1.11</v>
-      </c>
-      <c r="X132">
-        <v>1.02</v>
-      </c>
-      <c r="Y132">
-        <v>1.24</v>
-      </c>
-      <c r="Z132">
-        <v>3.8</v>
-      </c>
-      <c r="AA132">
-        <v>1.73</v>
-      </c>
-      <c r="AB132">
-        <v>2.01</v>
-      </c>
       <c r="AC132">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD132">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG132">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.23</v>
       </c>
       <c r="AK132">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O133">
         <v>3.4</v>
       </c>
       <c r="P133">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q133">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="R133">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U133">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V133">
         <v>1.36</v>
       </c>
       <c r="W133">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y133">
         <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB133">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC133">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE133">
         <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG133">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK133">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="O134">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q134">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R134">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S134">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W134">
         <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y134">
+        <v>1.3</v>
+      </c>
+      <c r="Z134">
+        <v>2.97</v>
+      </c>
+      <c r="AA134">
+        <v>2.02</v>
+      </c>
+      <c r="AB134">
+        <v>1.72</v>
+      </c>
+      <c r="AC134">
+        <v>3.42</v>
+      </c>
+      <c r="AD134">
+        <v>1.22</v>
+      </c>
+      <c r="AE134">
+        <v>1.05</v>
+      </c>
+      <c r="AF134">
+        <v>1.79</v>
+      </c>
+      <c r="AG134">
+        <v>1.92</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.26</v>
       </c>
-      <c r="Z134">
-        <v>3.71</v>
-      </c>
-      <c r="AA134">
-        <v>1.85</v>
-      </c>
-      <c r="AB134">
-        <v>1.95</v>
-      </c>
-      <c r="AC134">
-        <v>3.04</v>
-      </c>
-      <c r="AD134">
-        <v>1.29</v>
-      </c>
-      <c r="AE134">
-        <v>1.12</v>
-      </c>
-      <c r="AF134">
-        <v>1.68</v>
-      </c>
-      <c r="AG134">
-        <v>2.03</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.23</v>
-      </c>
       <c r="AK134">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.95</v>
+        <v>1.68</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P143">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="Q143">
-        <v>3.32</v>
+        <v>2.25</v>
       </c>
       <c r="R143">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
         <v>1.33</v>
       </c>
       <c r="T143">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U143">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V143">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X143">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z143">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="AA143">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB143">
         <v>2</v>
       </c>
       <c r="AC143">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="AD143">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE143">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF143">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG143">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AK143">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="O144">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>4.8</v>
+        <v>2.24</v>
       </c>
       <c r="Q144">
-        <v>2.25</v>
+        <v>3.32</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S144">
         <v>1.33</v>
       </c>
       <c r="T144">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="U144">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W144">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X144">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y144">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z144">
-        <v>3.93</v>
+        <v>4.01</v>
       </c>
       <c r="AA144">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB144">
         <v>2</v>
       </c>
       <c r="AC144">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="AD144">
+        <v>1.36</v>
+      </c>
+      <c r="AE144">
+        <v>1.11</v>
+      </c>
+      <c r="AF144">
+        <v>1.6</v>
+      </c>
+      <c r="AG144">
+        <v>2.16</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>1.57</v>
+      </c>
+      <c r="AK144">
         <v>1.33</v>
-      </c>
-      <c r="AE144">
-        <v>1.09</v>
-      </c>
-      <c r="AF144">
-        <v>1.7</v>
-      </c>
-      <c r="AG144">
-        <v>2</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.14</v>
-      </c>
-      <c r="AK144">
-        <v>2.05</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
+        <v>2.75</v>
+      </c>
+      <c r="O154">
+        <v>3.68</v>
+      </c>
+      <c r="P154">
         <v>2.37</v>
       </c>
-      <c r="O154">
-        <v>3.3</v>
-      </c>
-      <c r="P154">
-        <v>2.91</v>
-      </c>
       <c r="Q154">
-        <v>2.86</v>
+        <v>3.34</v>
       </c>
       <c r="R154">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S154">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T154">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U154">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="V154">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="W154">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X154">
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z154">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="AA154">
-        <v>2.11</v>
+        <v>1.61</v>
       </c>
       <c r="AB154">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC154">
-        <v>3.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD154">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AE154">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF154">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AG154">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK154">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O155">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P155">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q155">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="R155">
+        <v>2.16</v>
+      </c>
+      <c r="S155">
+        <v>1.32</v>
+      </c>
+      <c r="T155">
+        <v>3.24</v>
+      </c>
+      <c r="U155">
         <v>2.45</v>
       </c>
-      <c r="S155">
-        <v>1.26</v>
-      </c>
-      <c r="T155">
-        <v>3.4</v>
-      </c>
-      <c r="U155">
-        <v>2.24</v>
-      </c>
       <c r="V155">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W155">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y155">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z155">
-        <v>4.84</v>
+        <v>4.15</v>
       </c>
       <c r="AA155">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB155">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AC155">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="AD155">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AG155">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK155">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O156">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>2.37</v>
+        <v>2.91</v>
       </c>
       <c r="Q156">
-        <v>3.34</v>
+        <v>2.86</v>
       </c>
       <c r="R156">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S156">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T156">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="U156">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V156">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W156">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
         <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z156">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="AA156">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AB156">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC156">
-        <v>2.46</v>
+        <v>3.58</v>
       </c>
       <c r="AD156">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK156">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,65 +25900,65 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="O157">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q157">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="R157">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="S157">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T157">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
+        <v>2.24</v>
+      </c>
+      <c r="V157">
+        <v>1.57</v>
+      </c>
+      <c r="W157">
+        <v>1.11</v>
+      </c>
+      <c r="X157">
+        <v>1.03</v>
+      </c>
+      <c r="Y157">
+        <v>1.17</v>
+      </c>
+      <c r="Z157">
+        <v>4.84</v>
+      </c>
+      <c r="AA157">
+        <v>1.59</v>
+      </c>
+      <c r="AB157">
+        <v>2.35</v>
+      </c>
+      <c r="AC157">
+        <v>2.48</v>
+      </c>
+      <c r="AD157">
+        <v>1.46</v>
+      </c>
+      <c r="AE157">
+        <v>1.21</v>
+      </c>
+      <c r="AF157">
+        <v>1.47</v>
+      </c>
+      <c r="AG157">
         <v>2.45</v>
       </c>
-      <c r="V157">
-        <v>1.44</v>
-      </c>
-      <c r="W157">
-        <v>1.08</v>
-      </c>
-      <c r="X157">
-        <v>1</v>
-      </c>
-      <c r="Y157">
-        <v>1.22</v>
-      </c>
-      <c r="Z157">
-        <v>4.15</v>
-      </c>
-      <c r="AA157">
-        <v>1.75</v>
-      </c>
-      <c r="AB157">
-        <v>2.05</v>
-      </c>
-      <c r="AC157">
-        <v>2.92</v>
-      </c>
-      <c r="AD157">
-        <v>1.35</v>
-      </c>
-      <c r="AE157">
-        <v>1.1</v>
-      </c>
-      <c r="AF157">
-        <v>1.65</v>
-      </c>
-      <c r="AG157">
-        <v>2.1</v>
-      </c>
       <c r="AH157" t="inlineStr">
         <is>
           <t>[]</t>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK157">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G177">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="O15">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
-        <v>3.39</v>
+        <v>4.22</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="S15">
+        <v>1.44</v>
+      </c>
+      <c r="T15">
+        <v>2.45</v>
+      </c>
+      <c r="U15">
+        <v>3.06</v>
+      </c>
+      <c r="V15">
         <v>1.29</v>
       </c>
-      <c r="T15">
-        <v>3.25</v>
-      </c>
-      <c r="U15">
-        <v>2.38</v>
-      </c>
-      <c r="V15">
-        <v>1.47</v>
-      </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
+        <v>1.39</v>
+      </c>
+      <c r="Z15">
+        <v>2.59</v>
+      </c>
+      <c r="AA15">
+        <v>2.35</v>
+      </c>
+      <c r="AB15">
+        <v>1.57</v>
+      </c>
+      <c r="AC15">
+        <v>4.2</v>
+      </c>
+      <c r="AD15">
         <v>1.15</v>
       </c>
-      <c r="Z15">
-        <v>4.25</v>
-      </c>
-      <c r="AA15">
-        <v>1.66</v>
-      </c>
-      <c r="AB15">
-        <v>2.15</v>
-      </c>
-      <c r="AC15">
-        <v>2.52</v>
-      </c>
-      <c r="AD15">
-        <v>1.41</v>
-      </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>4.22</v>
+        <v>3.82</v>
       </c>
       <c r="R16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>3.06</v>
+        <v>2.77</v>
       </c>
       <c r="V16">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AA16">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AB16">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD16">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="Q17">
-        <v>3.82</v>
+        <v>2.68</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="U17">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB17">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC17">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.98</v>
+        <v>2.51</v>
       </c>
       <c r="O18">
+        <v>3.65</v>
+      </c>
+      <c r="P18">
+        <v>2.2</v>
+      </c>
+      <c r="Q18">
+        <v>3.39</v>
+      </c>
+      <c r="R18">
+        <v>2.15</v>
+      </c>
+      <c r="S18">
+        <v>1.29</v>
+      </c>
+      <c r="T18">
         <v>3.25</v>
       </c>
-      <c r="P18">
-        <v>3.22</v>
-      </c>
-      <c r="Q18">
-        <v>2.68</v>
-      </c>
-      <c r="R18">
-        <v>1.98</v>
-      </c>
-      <c r="S18">
-        <v>1.42</v>
-      </c>
-      <c r="T18">
-        <v>2.51</v>
-      </c>
       <c r="U18">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>2.83</v>
+        <v>4.25</v>
       </c>
       <c r="AA18">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AB18">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AC18">
-        <v>3.76</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AG18">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="O36">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="R36">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="U36">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
         <v>1.11</v>
@@ -6210,31 +6210,31 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="AA36">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB36">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC36">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="Q37">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="U37">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
         <v>1.11</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA37">
+        <v>1.48</v>
+      </c>
+      <c r="AB37">
+        <v>2.33</v>
+      </c>
+      <c r="AC37">
+        <v>2.31</v>
+      </c>
+      <c r="AD37">
         <v>1.57</v>
       </c>
-      <c r="AB37">
-        <v>2.31</v>
-      </c>
-      <c r="AC37">
-        <v>2.35</v>
-      </c>
-      <c r="AD37">
-        <v>1.47</v>
-      </c>
       <c r="AE37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG37">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,28 +8332,28 @@
         <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="AA49">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AB49">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC49">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK49">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q50">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
+        <v>2.38</v>
+      </c>
+      <c r="S50">
+        <v>1.25</v>
+      </c>
+      <c r="T50">
+        <v>3.3</v>
+      </c>
+      <c r="U50">
         <v>2.34</v>
       </c>
-      <c r="S50">
-        <v>1.29</v>
-      </c>
-      <c r="T50">
-        <v>3.4</v>
-      </c>
-      <c r="U50">
-        <v>2.21</v>
-      </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8495,28 +8495,28 @@
         <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="AA50">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AD50">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG50">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="O76">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q76">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="R76">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
+        <v>1.33</v>
+      </c>
+      <c r="T76">
+        <v>2.83</v>
+      </c>
+      <c r="U76">
+        <v>2.51</v>
+      </c>
+      <c r="V76">
+        <v>1.42</v>
+      </c>
+      <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>1.21</v>
+      </c>
+      <c r="Z76">
+        <v>3.58</v>
+      </c>
+      <c r="AA76">
+        <v>1.73</v>
+      </c>
+      <c r="AB76">
+        <v>2.03</v>
+      </c>
+      <c r="AC76">
+        <v>2.7</v>
+      </c>
+      <c r="AD76">
         <v>1.36</v>
       </c>
-      <c r="T76">
-        <v>2.64</v>
-      </c>
-      <c r="U76">
-        <v>2.8</v>
-      </c>
-      <c r="V76">
-        <v>1.34</v>
-      </c>
-      <c r="W76">
-        <v>1.04</v>
-      </c>
-      <c r="X76">
-        <v>1.01</v>
-      </c>
-      <c r="Y76">
-        <v>1.27</v>
-      </c>
-      <c r="Z76">
-        <v>3.14</v>
-      </c>
-      <c r="AA76">
-        <v>2</v>
-      </c>
-      <c r="AB76">
-        <v>1.79</v>
-      </c>
-      <c r="AC76">
-        <v>3.45</v>
-      </c>
-      <c r="AD76">
-        <v>1.28</v>
-      </c>
       <c r="AE76">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG76">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P77">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q77">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.83</v>
+        <v>2.64</v>
       </c>
       <c r="U77">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="V77">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z77">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA77">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AC77">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AD77">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK77">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="O111">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P111">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="Q111">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="R111">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="S111">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T111">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="U111">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="V111">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W111">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z111">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA111">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB111">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AC111">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="AD111">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE111">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AF111">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AG111">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="O112">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="Q112">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="R112">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="S112">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T112">
-        <v>3.56</v>
+        <v>3.84</v>
       </c>
       <c r="U112">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="V112">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W112">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z112">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA112">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB112">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="AC112">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AD112">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE112">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF112">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG112">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.48</v>
+        <v>2.37</v>
       </c>
       <c r="O133">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="P133">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q133">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="R133">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="S133">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="U133">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="V133">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>4.8</v>
+        <v>2.97</v>
       </c>
       <c r="AA133">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="AB133">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="AC133">
-        <v>2.29</v>
+        <v>3.48</v>
       </c>
       <c r="AD133">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AE133">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AG133">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK133">
-        <v>2.62</v>
+        <v>1.52</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="O134">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="P134">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q134">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="R134">
+        <v>2.46</v>
+      </c>
+      <c r="S134">
+        <v>1.21</v>
+      </c>
+      <c r="T134">
+        <v>3.65</v>
+      </c>
+      <c r="U134">
         <v>2.12</v>
       </c>
-      <c r="S134">
-        <v>1.35</v>
-      </c>
-      <c r="T134">
-        <v>2.88</v>
-      </c>
-      <c r="U134">
-        <v>2.75</v>
-      </c>
       <c r="V134">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="W134">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X134">
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="Z134">
-        <v>2.97</v>
+        <v>4.8</v>
       </c>
       <c r="AA134">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AB134">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="AC134">
-        <v>3.48</v>
+        <v>2.29</v>
       </c>
       <c r="AD134">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF134">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AG134">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK134">
-        <v>1.52</v>
+        <v>2.62</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O144">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P144">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q144">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R144">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S144">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U144">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V144">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z144">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AA144">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB144">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC144">
         <v>2.96</v>
       </c>
       <c r="AD144">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE144">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF144">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG144">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK144">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O145">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P145">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q145">
-        <v>2.23</v>
+        <v>3.64</v>
       </c>
       <c r="R145">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S145">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T145">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U145">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="V145">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z145">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA145">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB145">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC145">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="AD145">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE145">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF145">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK145">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="O146">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="P146">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q146">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="R146">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
+        <v>3.08</v>
+      </c>
+      <c r="U146">
+        <v>2.66</v>
+      </c>
+      <c r="V146">
+        <v>1.45</v>
+      </c>
+      <c r="W146">
+        <v>1.07</v>
+      </c>
+      <c r="X146">
+        <v>1.03</v>
+      </c>
+      <c r="Y146">
+        <v>1.19</v>
+      </c>
+      <c r="Z146">
+        <v>3.4</v>
+      </c>
+      <c r="AA146">
+        <v>1.8</v>
+      </c>
+      <c r="AB146">
+        <v>1.99</v>
+      </c>
+      <c r="AC146">
+        <v>2.83</v>
+      </c>
+      <c r="AD146">
         <v>1.33</v>
       </c>
-      <c r="T146">
-        <v>2.96</v>
-      </c>
-      <c r="U146">
-        <v>2.6</v>
-      </c>
-      <c r="V146">
-        <v>1.42</v>
-      </c>
-      <c r="W146">
-        <v>1.08</v>
-      </c>
-      <c r="X146">
-        <v>1.01</v>
-      </c>
-      <c r="Y146">
-        <v>1.29</v>
-      </c>
-      <c r="Z146">
-        <v>3.2</v>
-      </c>
-      <c r="AA146">
-        <v>1.84</v>
-      </c>
-      <c r="AB146">
-        <v>1.9</v>
-      </c>
-      <c r="AC146">
-        <v>2.96</v>
-      </c>
-      <c r="AD146">
-        <v>1.29</v>
-      </c>
       <c r="AE146">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG146">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK146">
-        <v>1.43</v>
+        <v>2.09</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="O156">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q156">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="R156">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S156">
         <v>1.26</v>
       </c>
       <c r="T156">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U156">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="V156">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X156">
         <v>1.03</v>
       </c>
       <c r="Y156">
+        <v>1.13</v>
+      </c>
+      <c r="Z156">
+        <v>4.55</v>
+      </c>
+      <c r="AA156">
+        <v>1.57</v>
+      </c>
+      <c r="AB156">
+        <v>2.27</v>
+      </c>
+      <c r="AC156">
+        <v>2.38</v>
+      </c>
+      <c r="AD156">
+        <v>1.46</v>
+      </c>
+      <c r="AE156">
         <v>1.15</v>
       </c>
-      <c r="Z156">
-        <v>4.3</v>
-      </c>
-      <c r="AA156">
-        <v>1.61</v>
-      </c>
-      <c r="AB156">
-        <v>2.23</v>
-      </c>
-      <c r="AC156">
-        <v>2.63</v>
-      </c>
-      <c r="AD156">
-        <v>1.43</v>
-      </c>
-      <c r="AE156">
-        <v>1.14</v>
-      </c>
       <c r="AF156">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG156">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK156">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O157">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P157">
-        <v>2.5</v>
+        <v>3.31</v>
       </c>
       <c r="Q157">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="R157">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S157">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T157">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="U157">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="V157">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="W157">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z157">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA157">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB157">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="AC157">
-        <v>2.38</v>
+        <v>3.17</v>
       </c>
       <c r="AD157">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE157">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF157">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AG157">
-        <v>2.47</v>
+        <v>2.02</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="O158">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="P158">
-        <v>3.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q158">
-        <v>2.44</v>
+        <v>3.32</v>
       </c>
       <c r="R158">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S158">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T158">
-        <v>2.82</v>
+        <v>3.38</v>
       </c>
       <c r="U158">
+        <v>2.34</v>
+      </c>
+      <c r="V158">
+        <v>1.51</v>
+      </c>
+      <c r="W158">
+        <v>1.09</v>
+      </c>
+      <c r="X158">
+        <v>1.03</v>
+      </c>
+      <c r="Y158">
+        <v>1.15</v>
+      </c>
+      <c r="Z158">
+        <v>4.3</v>
+      </c>
+      <c r="AA158">
+        <v>1.61</v>
+      </c>
+      <c r="AB158">
+        <v>2.23</v>
+      </c>
+      <c r="AC158">
         <v>2.63</v>
       </c>
-      <c r="V158">
+      <c r="AD158">
+        <v>1.43</v>
+      </c>
+      <c r="AE158">
+        <v>1.14</v>
+      </c>
+      <c r="AF158">
+        <v>1.51</v>
+      </c>
+      <c r="AG158">
+        <v>2.39</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
+        <v>1.24</v>
+      </c>
+      <c r="AK158">
         <v>1.41</v>
-      </c>
-      <c r="W158">
-        <v>1.05</v>
-      </c>
-      <c r="X158">
-        <v>1.01</v>
-      </c>
-      <c r="Y158">
-        <v>1.22</v>
-      </c>
-      <c r="Z158">
-        <v>3.5</v>
-      </c>
-      <c r="AA158">
-        <v>1.82</v>
-      </c>
-      <c r="AB158">
-        <v>1.92</v>
-      </c>
-      <c r="AC158">
-        <v>3.17</v>
-      </c>
-      <c r="AD158">
-        <v>1.31</v>
-      </c>
-      <c r="AE158">
-        <v>1.08</v>
-      </c>
-      <c r="AF158">
-        <v>1.71</v>
-      </c>
-      <c r="AG158">
-        <v>2.02</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>1.22</v>
-      </c>
-      <c r="AK158">
-        <v>1.88</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>3.2</v>
+        <v>1.61</v>
       </c>
       <c r="O278">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P278">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q278">
-        <v>4.38</v>
+        <v>2.3</v>
       </c>
       <c r="R278">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="S278">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T278">
         <v>2.2</v>
       </c>
       <c r="U278">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X278">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y278">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Z278">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AA278">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="AB278">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AC278">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="AD278">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE278">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF278">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AG278">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
+        <v>3.2</v>
+      </c>
+      <c r="O279">
+        <v>2.7</v>
+      </c>
+      <c r="P279">
+        <v>2.4</v>
+      </c>
+      <c r="Q279">
+        <v>4.38</v>
+      </c>
+      <c r="R279">
+        <v>1.74</v>
+      </c>
+      <c r="S279">
         <v>1.61</v>
-      </c>
-      <c r="O279">
-        <v>3.1</v>
-      </c>
-      <c r="P279">
-        <v>5.75</v>
-      </c>
-      <c r="Q279">
-        <v>2.3</v>
-      </c>
-      <c r="R279">
-        <v>2</v>
-      </c>
-      <c r="S279">
-        <v>1.57</v>
       </c>
       <c r="T279">
         <v>2.2</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y279">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Z279">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AA279">
-        <v>2.49</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC279">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="AD279">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE279">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF279">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AG279">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK279">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,80 +46601,80 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.86</v>
+        <v>3.05</v>
       </c>
       <c r="O284">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P284">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="Q284">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="R284">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="S284">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="T284">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="U284">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V284">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W284">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X284">
+        <v>1.03</v>
+      </c>
+      <c r="Y284">
+        <v>1.38</v>
+      </c>
+      <c r="Z284">
+        <v>2.62</v>
+      </c>
+      <c r="AA284">
+        <v>2.35</v>
+      </c>
+      <c r="AB284">
+        <v>1.57</v>
+      </c>
+      <c r="AC284">
+        <v>4.25</v>
+      </c>
+      <c r="AD284">
+        <v>1.15</v>
+      </c>
+      <c r="AE284">
         <v>1.01</v>
       </c>
-      <c r="Y284">
-        <v>1.26</v>
-      </c>
-      <c r="Z284">
-        <v>3.2</v>
-      </c>
-      <c r="AA284">
-        <v>1.89</v>
-      </c>
-      <c r="AB284">
-        <v>1.78</v>
-      </c>
-      <c r="AC284">
-        <v>3.14</v>
-      </c>
-      <c r="AD284">
+      <c r="AF284">
+        <v>1.92</v>
+      </c>
+      <c r="AG284">
+        <v>1.75</v>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ284">
         <v>1.27</v>
       </c>
-      <c r="AE284">
-        <v>1.06</v>
-      </c>
-      <c r="AF284">
-        <v>1.75</v>
-      </c>
-      <c r="AG284">
-        <v>1.93</v>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ284">
-        <v>1.24</v>
-      </c>
       <c r="AK284">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="O285">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P285">
-        <v>2.31</v>
+        <v>3.6</v>
       </c>
       <c r="Q285">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="R285">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="S285">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T285">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="U285">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="V285">
+        <v>1.36</v>
+      </c>
+      <c r="W285">
+        <v>1.06</v>
+      </c>
+      <c r="X285">
+        <v>1.01</v>
+      </c>
+      <c r="Y285">
         <v>1.26</v>
       </c>
-      <c r="W285">
-        <v>1.01</v>
-      </c>
-      <c r="X285">
-        <v>1.03</v>
-      </c>
-      <c r="Y285">
-        <v>1.38</v>
-      </c>
       <c r="Z285">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA285">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AB285">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC285">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD285">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AE285">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF285">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG285">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK285">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -50676,22 +50676,22 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="O309">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P309">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q309">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R309">
         <v>1.83</v>
       </c>
       <c r="S309">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T309">
         <v>2.34</v>
@@ -50712,7 +50712,7 @@
         <v>1.49</v>
       </c>
       <c r="Z309">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AA309">
         <v>2.41</v>
@@ -50721,19 +50721,19 @@
         <v>1.45</v>
       </c>
       <c r="AC309">
-        <v>5.14</v>
+        <v>4.5</v>
       </c>
       <c r="AD309">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE309">
         <v>1.01</v>
       </c>
       <c r="AF309">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG309">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>1.36</v>
       </c>
       <c r="AK309">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51002,46 +51002,46 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="O311">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P311">
-        <v>5.4</v>
+        <v>5.65</v>
       </c>
       <c r="Q311">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R311">
         <v>2.63</v>
       </c>
       <c r="S311">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T311">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="U311">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V311">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W311">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X311">
         <v>1.02</v>
       </c>
       <c r="Y311">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z311">
         <v>5.5</v>
       </c>
       <c r="AA311">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB311">
         <v>2.56</v>
@@ -51050,16 +51050,16 @@
         <v>2.1</v>
       </c>
       <c r="AD311">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE311">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF311">
         <v>1.57</v>
       </c>
       <c r="AG311">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51165,19 +51165,19 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O312">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P312">
         <v>5.6</v>
       </c>
       <c r="Q312">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R312">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="S312">
         <v>1.2</v>
@@ -51189,10 +51189,10 @@
         <v>2.13</v>
       </c>
       <c r="V312">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W312">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X312">
         <v>1.02</v>
@@ -51207,19 +51207,19 @@
         <v>1.5</v>
       </c>
       <c r="AB312">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC312">
         <v>2.17</v>
       </c>
       <c r="AD312">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE312">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF312">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG312">
         <v>2.16</v>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK312">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51328,16 +51328,16 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="O313">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P313">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="Q313">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="R313">
         <v>2.09</v>
@@ -51349,7 +51349,7 @@
         <v>2.95</v>
       </c>
       <c r="U313">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V313">
         <v>1.4</v>
@@ -51370,7 +51370,7 @@
         <v>1.86</v>
       </c>
       <c r="AB313">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC313">
         <v>3.2</v>
@@ -51385,7 +51385,7 @@
         <v>1.68</v>
       </c>
       <c r="AG313">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51497,13 +51497,13 @@
         <v>2.95</v>
       </c>
       <c r="P314">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q314">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="R314">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S314">
         <v>1.49</v>
@@ -51515,10 +51515,10 @@
         <v>3.4</v>
       </c>
       <c r="V314">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W314">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X314">
         <v>1.05</v>
@@ -51530,10 +51530,10 @@
         <v>2.44</v>
       </c>
       <c r="AA314">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB314">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC314">
         <v>4.8</v>
@@ -51545,10 +51545,10 @@
         <v>1.01</v>
       </c>
       <c r="AF314">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG314">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK314">
         <v>1.5</v>
@@ -51654,28 +51654,28 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O315">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P315">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q315">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R315">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="S315">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T315">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U315">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V315">
         <v>1.5</v>
@@ -51696,7 +51696,7 @@
         <v>1.7</v>
       </c>
       <c r="AB315">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AC315">
         <v>2.59</v>
@@ -51727,7 +51727,7 @@
         <v>1.16</v>
       </c>
       <c r="AK315">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -53280,7 +53280,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N325">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q6">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
         <v>2.54</v>
@@ -1311,16 +1311,16 @@
         <v>2.85</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
         <v>2.97</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="O16">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="Q16">
-        <v>3.82</v>
+        <v>2.68</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="U16">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA16">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC16">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="Q17">
-        <v>2.68</v>
+        <v>3.82</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
+        <v>1.31</v>
+      </c>
+      <c r="Z17">
+        <v>2.92</v>
+      </c>
+      <c r="AA17">
+        <v>2.07</v>
+      </c>
+      <c r="AB17">
+        <v>1.72</v>
+      </c>
+      <c r="AC17">
+        <v>3.42</v>
+      </c>
+      <c r="AD17">
+        <v>1.23</v>
+      </c>
+      <c r="AE17">
+        <v>1.05</v>
+      </c>
+      <c r="AF17">
+        <v>1.78</v>
+      </c>
+      <c r="AG17">
+        <v>1.91</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.27</v>
+      </c>
+      <c r="AK17">
         <v>1.33</v>
-      </c>
-      <c r="Z17">
-        <v>2.83</v>
-      </c>
-      <c r="AA17">
-        <v>2.2</v>
-      </c>
-      <c r="AB17">
-        <v>1.63</v>
-      </c>
-      <c r="AC17">
-        <v>3.76</v>
-      </c>
-      <c r="AD17">
-        <v>1.19</v>
-      </c>
-      <c r="AE17">
-        <v>1.03</v>
-      </c>
-      <c r="AF17">
-        <v>1.87</v>
-      </c>
-      <c r="AG17">
-        <v>1.79</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.25</v>
-      </c>
-      <c r="AK17">
-        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P48">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="R48">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>3.34</v>
+        <v>4.39</v>
       </c>
       <c r="AA48">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="AD48">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>4.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="U50">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>4.39</v>
+        <v>3.34</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AB50">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC50">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="AD50">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>1.48</v>
       </c>
       <c r="O71">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="P71">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>2.88</v>
       </c>
       <c r="AA73">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB73">
         <v>1.65</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O74">
         <v>2.95</v>
       </c>
       <c r="P74">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="Q74">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R74">
         <v>1.94</v>
@@ -12410,10 +12410,10 @@
         <v>2.7</v>
       </c>
       <c r="AA74">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB74">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC74">
         <v>3.9</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK74">
         <v>1.32</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="O111">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P111">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="Q111">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="R111">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="S111">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T111">
-        <v>3.56</v>
+        <v>3.84</v>
       </c>
       <c r="U111">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="V111">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W111">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z111">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA111">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB111">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="AC111">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AD111">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE111">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF111">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AG111">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK111">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P112">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="Q112">
-        <v>2.77</v>
+        <v>3.42</v>
       </c>
       <c r="R112">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="S112">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T112">
-        <v>3.84</v>
+        <v>3.56</v>
       </c>
       <c r="U112">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="V112">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W112">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z112">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA112">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB112">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AC112">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="AD112">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE112">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AF112">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AG112">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O114">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P114">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q114">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="R114">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S114">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U114">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V114">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA114">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AB114">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC114">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="AD114">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P115">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q115">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="R115">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T115">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U115">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V115">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA115">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB115">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC115">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE115">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK115">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="O134">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="Q134">
-        <v>1.9</v>
+        <v>2.61</v>
       </c>
       <c r="R134">
-        <v>2.46</v>
+        <v>2.09</v>
       </c>
       <c r="S134">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="U134">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="V134">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W134">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
         <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Z134">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA134">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB134">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AC134">
-        <v>2.29</v>
+        <v>3.04</v>
       </c>
       <c r="AD134">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG134">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>2.62</v>
+        <v>1.71</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P135">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q135">
-        <v>2.83</v>
+        <v>1.9</v>
       </c>
       <c r="R135">
-        <v>2.07</v>
+        <v>2.46</v>
       </c>
       <c r="S135">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="T135">
-        <v>2.78</v>
+        <v>3.65</v>
       </c>
       <c r="U135">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="V135">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="Z135">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA135">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="AB135">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AC135">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD135">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AE135">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG135">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>2.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,80 +22477,80 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O136">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="Q136">
-        <v>2.61</v>
+        <v>2.83</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S136">
+        <v>1.37</v>
+      </c>
+      <c r="T136">
+        <v>2.78</v>
+      </c>
+      <c r="U136">
+        <v>2.82</v>
+      </c>
+      <c r="V136">
+        <v>1.36</v>
+      </c>
+      <c r="W136">
+        <v>1.06</v>
+      </c>
+      <c r="X136">
+        <v>1.02</v>
+      </c>
+      <c r="Y136">
+        <v>1.26</v>
+      </c>
+      <c r="Z136">
+        <v>3.2</v>
+      </c>
+      <c r="AA136">
+        <v>1.94</v>
+      </c>
+      <c r="AB136">
+        <v>1.79</v>
+      </c>
+      <c r="AC136">
+        <v>3.28</v>
+      </c>
+      <c r="AD136">
+        <v>1.25</v>
+      </c>
+      <c r="AE136">
+        <v>1.05</v>
+      </c>
+      <c r="AF136">
+        <v>1.73</v>
+      </c>
+      <c r="AG136">
+        <v>2</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
         <v>1.33</v>
       </c>
-      <c r="T136">
-        <v>2.97</v>
-      </c>
-      <c r="U136">
-        <v>2.54</v>
-      </c>
-      <c r="V136">
-        <v>1.44</v>
-      </c>
-      <c r="W136">
-        <v>1.07</v>
-      </c>
-      <c r="X136">
-        <v>1.01</v>
-      </c>
-      <c r="Y136">
-        <v>1.22</v>
-      </c>
-      <c r="Z136">
-        <v>3.5</v>
-      </c>
-      <c r="AA136">
-        <v>1.84</v>
-      </c>
-      <c r="AB136">
-        <v>1.89</v>
-      </c>
-      <c r="AC136">
-        <v>3.04</v>
-      </c>
-      <c r="AD136">
-        <v>1.29</v>
-      </c>
-      <c r="AE136">
-        <v>1.07</v>
-      </c>
-      <c r="AF136">
-        <v>1.68</v>
-      </c>
-      <c r="AG136">
-        <v>2.06</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>1.27</v>
-      </c>
       <c r="AK136">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="O137">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="Q137">
-        <v>4.23</v>
+        <v>2.54</v>
       </c>
       <c r="R137">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U137">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="V137">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W137">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA137">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB137">
+        <v>1.77</v>
+      </c>
+      <c r="AC137">
+        <v>3.28</v>
+      </c>
+      <c r="AD137">
+        <v>1.25</v>
+      </c>
+      <c r="AE137">
+        <v>1.06</v>
+      </c>
+      <c r="AF137">
+        <v>1.8</v>
+      </c>
+      <c r="AG137">
         <v>1.9</v>
       </c>
-      <c r="AC137">
-        <v>2.97</v>
-      </c>
-      <c r="AD137">
-        <v>1.3</v>
-      </c>
-      <c r="AE137">
-        <v>1.07</v>
-      </c>
-      <c r="AF137">
-        <v>1.67</v>
-      </c>
-      <c r="AG137">
-        <v>2.05</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK137">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="O138">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
-        <v>5.25</v>
+        <v>2</v>
       </c>
       <c r="Q138">
-        <v>2.01</v>
+        <v>4.23</v>
       </c>
       <c r="R138">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="S138">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T138">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U138">
-        <v>2.27</v>
+        <v>2.63</v>
       </c>
       <c r="V138">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="W138">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X138">
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z138">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA138">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AB138">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="AC138">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AD138">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AE138">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF138">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG138">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="O139">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P139">
-        <v>3.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q139">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="R139">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T139">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U139">
-        <v>2.67</v>
+        <v>2.27</v>
       </c>
       <c r="V139">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W139">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X139">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z139">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="AA139">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="AB139">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="AC139">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD139">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE139">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AF139">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG139">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK139">
-        <v>1.62</v>
+        <v>2.39</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
+        <v>2.51</v>
+      </c>
+      <c r="O156">
+        <v>3.68</v>
+      </c>
+      <c r="P156">
         <v>2.2</v>
       </c>
-      <c r="O156">
-        <v>3.7</v>
-      </c>
-      <c r="P156">
-        <v>2.5</v>
-      </c>
       <c r="Q156">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="R156">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S156">
         <v>1.26</v>
       </c>
       <c r="T156">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U156">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="V156">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W156">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X156">
         <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z156">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="AA156">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB156">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AC156">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AD156">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AE156">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF156">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AG156">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK156">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O157">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="Q157">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="R157">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S157">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="T157">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="V157">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z157">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA157">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AB157">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="AC157">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="AD157">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AE157">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF157">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AG157">
-        <v>2.02</v>
+        <v>2.47</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK157">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.51</v>
+        <v>1.85</v>
       </c>
       <c r="O158">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="P158">
-        <v>2.2</v>
+        <v>3.31</v>
       </c>
       <c r="Q158">
-        <v>3.32</v>
+        <v>2.44</v>
       </c>
       <c r="R158">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S158">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T158">
-        <v>3.38</v>
+        <v>2.82</v>
       </c>
       <c r="U158">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="V158">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W158">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z158">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA158">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB158">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AC158">
-        <v>2.63</v>
+        <v>3.17</v>
       </c>
       <c r="AD158">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE158">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF158">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AG158">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -33896,7 +33896,7 @@
         <v>3</v>
       </c>
       <c r="Q206">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R206">
         <v>2.02</v>
@@ -34092,7 +34092,7 @@
         <v>1.93</v>
       </c>
       <c r="AB207">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC207">
         <v>3.28</v>
@@ -36332,25 +36332,25 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="O221">
+        <v>3.3</v>
+      </c>
+      <c r="P221">
         <v>3.35</v>
       </c>
-      <c r="P221">
-        <v>3.25</v>
-      </c>
       <c r="Q221">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R221">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S221">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T221">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="U221">
         <v>2.74</v>
@@ -36362,7 +36362,7 @@
         <v>1.08</v>
       </c>
       <c r="X221">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y221">
         <v>1.25</v>
@@ -36371,7 +36371,7 @@
         <v>3.28</v>
       </c>
       <c r="AA221">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB221">
         <v>1.85</v>
@@ -36383,7 +36383,7 @@
         <v>1.26</v>
       </c>
       <c r="AE221">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF221">
         <v>1.73</v>
@@ -36405,7 +36405,7 @@
         <v>1.28</v>
       </c>
       <c r="AK221">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36504,10 +36504,10 @@
         <v>3</v>
       </c>
       <c r="Q222">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R222">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S222">
         <v>1.4</v>
@@ -36552,7 +36552,7 @@
         <v>1.79</v>
       </c>
       <c r="AG222">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -46438,16 +46438,16 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O283">
         <v>3.75</v>
       </c>
       <c r="P283">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q283">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R283">
         <v>2.09</v>
@@ -46477,7 +46477,7 @@
         <v>3.34</v>
       </c>
       <c r="AA283">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB283">
         <v>1.83</v>
@@ -46610,7 +46610,7 @@
         <v>2.31</v>
       </c>
       <c r="Q284">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="R284">
         <v>1.92</v>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46779,19 +46779,19 @@
         <v>2.02</v>
       </c>
       <c r="S285">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T285">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U285">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V285">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W285">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X285">
         <v>1.01</v>
@@ -46803,10 +46803,10 @@
         <v>3.2</v>
       </c>
       <c r="AA285">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB285">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC285">
         <v>3.14</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G321">

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="Q46">
-        <v>3.47</v>
+        <v>3.04</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S46">
+        <v>1.4</v>
+      </c>
+      <c r="T46">
+        <v>2.66</v>
+      </c>
+      <c r="U46">
+        <v>2.66</v>
+      </c>
+      <c r="V46">
+        <v>1.4</v>
+      </c>
+      <c r="W46">
+        <v>1.06</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.26</v>
+      </c>
+      <c r="Z46">
+        <v>3.2</v>
+      </c>
+      <c r="AA46">
+        <v>1.9</v>
+      </c>
+      <c r="AB46">
+        <v>1.9</v>
+      </c>
+      <c r="AC46">
+        <v>3.28</v>
+      </c>
+      <c r="AD46">
+        <v>1.25</v>
+      </c>
+      <c r="AE46">
+        <v>1.06</v>
+      </c>
+      <c r="AF46">
+        <v>1.72</v>
+      </c>
+      <c r="AG46">
+        <v>2.01</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.31</v>
       </c>
-      <c r="T46">
-        <v>3.08</v>
-      </c>
-      <c r="U46">
-        <v>2.61</v>
-      </c>
-      <c r="V46">
-        <v>1.46</v>
-      </c>
-      <c r="W46">
-        <v>1.09</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.2</v>
-      </c>
-      <c r="Z46">
-        <v>3.7</v>
-      </c>
-      <c r="AA46">
-        <v>1.75</v>
-      </c>
-      <c r="AB46">
-        <v>1.99</v>
-      </c>
-      <c r="AC46">
-        <v>2.74</v>
-      </c>
-      <c r="AD46">
-        <v>1.35</v>
-      </c>
-      <c r="AE46">
-        <v>1.1</v>
-      </c>
-      <c r="AF46">
-        <v>1.64</v>
-      </c>
-      <c r="AG46">
-        <v>2.05</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.26</v>
-      </c>
       <c r="AK46">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="O47">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="Q47">
-        <v>3.04</v>
+        <v>3.47</v>
       </c>
       <c r="R47">
+        <v>2.15</v>
+      </c>
+      <c r="S47">
+        <v>1.31</v>
+      </c>
+      <c r="T47">
+        <v>3.08</v>
+      </c>
+      <c r="U47">
+        <v>2.61</v>
+      </c>
+      <c r="V47">
+        <v>1.46</v>
+      </c>
+      <c r="W47">
+        <v>1.09</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.2</v>
+      </c>
+      <c r="Z47">
+        <v>3.7</v>
+      </c>
+      <c r="AA47">
+        <v>1.75</v>
+      </c>
+      <c r="AB47">
+        <v>1.99</v>
+      </c>
+      <c r="AC47">
+        <v>2.74</v>
+      </c>
+      <c r="AD47">
+        <v>1.35</v>
+      </c>
+      <c r="AE47">
+        <v>1.1</v>
+      </c>
+      <c r="AF47">
+        <v>1.64</v>
+      </c>
+      <c r="AG47">
         <v>2.05</v>
       </c>
-      <c r="S47">
-        <v>1.4</v>
-      </c>
-      <c r="T47">
-        <v>2.66</v>
-      </c>
-      <c r="U47">
-        <v>2.66</v>
-      </c>
-      <c r="V47">
-        <v>1.4</v>
-      </c>
-      <c r="W47">
-        <v>1.06</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
         <v>1.26</v>
       </c>
-      <c r="Z47">
-        <v>3.2</v>
-      </c>
-      <c r="AA47">
-        <v>1.9</v>
-      </c>
-      <c r="AB47">
-        <v>1.9</v>
-      </c>
-      <c r="AC47">
-        <v>3.28</v>
-      </c>
-      <c r="AD47">
-        <v>1.25</v>
-      </c>
-      <c r="AE47">
-        <v>1.06</v>
-      </c>
-      <c r="AF47">
-        <v>1.72</v>
-      </c>
-      <c r="AG47">
-        <v>2.01</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.31</v>
-      </c>
       <c r="AK47">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="O48">
         <v>4</v>
       </c>
       <c r="P48">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W48">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="AA48">
         <v>1.58</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AC48">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
         <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>2.14</v>
+        <v>1.21</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="O49">
         <v>4</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>4.35</v>
+        <v>4.54</v>
       </c>
       <c r="AA49">
         <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AD49">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.21</v>
+        <v>2.14</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O114">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P114">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q114">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="R114">
+        <v>2.25</v>
+      </c>
+      <c r="S114">
+        <v>1.33</v>
+      </c>
+      <c r="T114">
+        <v>3.35</v>
+      </c>
+      <c r="U114">
         <v>2.4</v>
       </c>
-      <c r="S114">
-        <v>1.28</v>
-      </c>
-      <c r="T114">
-        <v>3.5</v>
-      </c>
-      <c r="U114">
-        <v>2.3</v>
-      </c>
       <c r="V114">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA114">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB114">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC114">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="AD114">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P115">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q115">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="R115">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T115">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U115">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V115">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA115">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AB115">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC115">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE115">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="O121">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="P121">
-        <v>1.98</v>
+        <v>7.5</v>
       </c>
       <c r="Q121">
-        <v>3.83</v>
+        <v>1.62</v>
       </c>
       <c r="R121">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="S121">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="T121">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="U121">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="V121">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z121">
-        <v>3.72</v>
+        <v>4.75</v>
       </c>
       <c r="AA121">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AB121">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="AC121">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AD121">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE121">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AF121">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AG121">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK121">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,80 +20195,80 @@
         </is>
       </c>
       <c r="N122">
+        <v>3.35</v>
+      </c>
+      <c r="O122">
+        <v>3.65</v>
+      </c>
+      <c r="P122">
+        <v>1.98</v>
+      </c>
+      <c r="Q122">
+        <v>3.83</v>
+      </c>
+      <c r="R122">
+        <v>2.17</v>
+      </c>
+      <c r="S122">
+        <v>1.28</v>
+      </c>
+      <c r="T122">
+        <v>3.12</v>
+      </c>
+      <c r="U122">
+        <v>2.63</v>
+      </c>
+      <c r="V122">
+        <v>1.44</v>
+      </c>
+      <c r="W122">
+        <v>1.08</v>
+      </c>
+      <c r="X122">
+        <v>1.04</v>
+      </c>
+      <c r="Y122">
+        <v>1.2</v>
+      </c>
+      <c r="Z122">
+        <v>3.72</v>
+      </c>
+      <c r="AA122">
+        <v>1.75</v>
+      </c>
+      <c r="AB122">
+        <v>1.93</v>
+      </c>
+      <c r="AC122">
+        <v>2.88</v>
+      </c>
+      <c r="AD122">
+        <v>1.32</v>
+      </c>
+      <c r="AE122">
+        <v>1.08</v>
+      </c>
+      <c r="AF122">
+        <v>1.63</v>
+      </c>
+      <c r="AG122">
+        <v>2.12</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
         <v>1.25</v>
       </c>
-      <c r="O122">
-        <v>5.2</v>
-      </c>
-      <c r="P122">
-        <v>7.5</v>
-      </c>
-      <c r="Q122">
-        <v>1.62</v>
-      </c>
-      <c r="R122">
-        <v>2.7</v>
-      </c>
-      <c r="S122">
-        <v>1.23</v>
-      </c>
-      <c r="T122">
-        <v>3.7</v>
-      </c>
-      <c r="U122">
-        <v>2.2</v>
-      </c>
-      <c r="V122">
-        <v>1.6</v>
-      </c>
-      <c r="W122">
-        <v>1.14</v>
-      </c>
-      <c r="X122">
-        <v>1.02</v>
-      </c>
-      <c r="Y122">
-        <v>1.12</v>
-      </c>
-      <c r="Z122">
-        <v>4.75</v>
-      </c>
-      <c r="AA122">
-        <v>1.48</v>
-      </c>
-      <c r="AB122">
-        <v>2.42</v>
-      </c>
-      <c r="AC122">
-        <v>2.35</v>
-      </c>
-      <c r="AD122">
-        <v>1.56</v>
-      </c>
-      <c r="AE122">
-        <v>1.21</v>
-      </c>
-      <c r="AF122">
-        <v>1.92</v>
-      </c>
-      <c r="AG122">
-        <v>1.77</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.1</v>
-      </c>
       <c r="AK122">
-        <v>3.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P134">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q134">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R134">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T134">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U134">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="V134">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W134">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X134">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
         <v>1.3</v>
       </c>
       <c r="Z134">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="AA134">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB134">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AC134">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="AD134">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE134">
         <v>1.05</v>
       </c>
       <c r="AF134">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG134">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK134">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O135">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q135">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R135">
         <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T135">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U135">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V135">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z135">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="AA135">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB135">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC135">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD135">
         <v>1.25</v>
       </c>
       <c r="AE135">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG135">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O136">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T136">
+        <v>2.88</v>
+      </c>
+      <c r="U136">
+        <v>2.77</v>
+      </c>
+      <c r="V136">
+        <v>1.38</v>
+      </c>
+      <c r="W136">
+        <v>1.06</v>
+      </c>
+      <c r="X136">
+        <v>1.04</v>
+      </c>
+      <c r="Y136">
+        <v>1.3</v>
+      </c>
+      <c r="Z136">
         <v>2.97</v>
       </c>
-      <c r="U136">
-        <v>2.75</v>
-      </c>
-      <c r="V136">
-        <v>1.41</v>
-      </c>
-      <c r="W136">
-        <v>1.07</v>
-      </c>
-      <c r="X136">
-        <v>1.01</v>
-      </c>
-      <c r="Y136">
-        <v>1.26</v>
-      </c>
-      <c r="Z136">
-        <v>3.71</v>
-      </c>
       <c r="AA136">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB136">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AC136">
-        <v>2.97</v>
+        <v>3.69</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK136">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P137">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q137">
         <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S137">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U137">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V137">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>3.05</v>
+        <v>3.71</v>
       </c>
       <c r="AA137">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB137">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC137">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AG137">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK137">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="O143">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P143">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q143">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="R143">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S143">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T143">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U143">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V143">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W143">
+        <v>1.08</v>
+      </c>
+      <c r="X143">
+        <v>1.01</v>
+      </c>
+      <c r="Y143">
+        <v>1.29</v>
+      </c>
+      <c r="Z143">
+        <v>3.67</v>
+      </c>
+      <c r="AA143">
+        <v>1.83</v>
+      </c>
+      <c r="AB143">
+        <v>1.87</v>
+      </c>
+      <c r="AC143">
+        <v>2.95</v>
+      </c>
+      <c r="AD143">
+        <v>1.29</v>
+      </c>
+      <c r="AE143">
         <v>1.07</v>
       </c>
-      <c r="X143">
-        <v>1.02</v>
-      </c>
-      <c r="Y143">
-        <v>1.19</v>
-      </c>
-      <c r="Z143">
-        <v>3.93</v>
-      </c>
-      <c r="AA143">
-        <v>1.8</v>
-      </c>
-      <c r="AB143">
-        <v>1.99</v>
-      </c>
-      <c r="AC143">
-        <v>2.83</v>
-      </c>
-      <c r="AD143">
-        <v>1.33</v>
-      </c>
-      <c r="AE143">
-        <v>1.09</v>
-      </c>
       <c r="AF143">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG143">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK143">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.7</v>
+        <v>1.68</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P144">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="R144">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T144">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U144">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W144">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z144">
-        <v>3.67</v>
+        <v>3.93</v>
       </c>
       <c r="AA144">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB144">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AC144">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AD144">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF144">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG144">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK144">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O145">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P145">
-        <v>2.2</v>
+        <v>3.46</v>
       </c>
       <c r="Q145">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="R145">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S145">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T145">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U145">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="V145">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W145">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z145">
-        <v>4</v>
+        <v>2.94</v>
       </c>
       <c r="AA145">
+        <v>2.05</v>
+      </c>
+      <c r="AB145">
+        <v>1.76</v>
+      </c>
+      <c r="AC145">
+        <v>3.42</v>
+      </c>
+      <c r="AD145">
+        <v>1.23</v>
+      </c>
+      <c r="AE145">
+        <v>1.04</v>
+      </c>
+      <c r="AF145">
         <v>1.79</v>
       </c>
-      <c r="AB145">
-        <v>1.97</v>
-      </c>
-      <c r="AC145">
-        <v>2.7</v>
-      </c>
-      <c r="AD145">
-        <v>1.4</v>
-      </c>
-      <c r="AE145">
-        <v>1.15</v>
-      </c>
-      <c r="AF145">
-        <v>1.6</v>
-      </c>
       <c r="AG145">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O146">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P146">
-        <v>3.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q146">
-        <v>2.68</v>
+        <v>3.64</v>
       </c>
       <c r="R146">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S146">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T146">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U146">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="V146">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W146">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z146">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="AA146">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB146">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC146">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD146">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AE146">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF146">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="O156">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P156">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="Q156">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="R156">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T156">
         <v>3.32</v>
       </c>
       <c r="U156">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V156">
+        <v>1.53</v>
+      </c>
+      <c r="W156">
+        <v>1.12</v>
+      </c>
+      <c r="X156">
+        <v>1.01</v>
+      </c>
+      <c r="Y156">
+        <v>1.15</v>
+      </c>
+      <c r="Z156">
+        <v>3.8</v>
+      </c>
+      <c r="AA156">
+        <v>1.62</v>
+      </c>
+      <c r="AB156">
+        <v>2.26</v>
+      </c>
+      <c r="AC156">
+        <v>2.49</v>
+      </c>
+      <c r="AD156">
+        <v>1.47</v>
+      </c>
+      <c r="AE156">
+        <v>1.13</v>
+      </c>
+      <c r="AF156">
         <v>1.52</v>
       </c>
-      <c r="W156">
-        <v>1.1</v>
-      </c>
-      <c r="X156">
-        <v>1.03</v>
-      </c>
-      <c r="Y156">
-        <v>1.17</v>
-      </c>
-      <c r="Z156">
-        <v>4.2</v>
-      </c>
-      <c r="AA156">
-        <v>1.61</v>
-      </c>
-      <c r="AB156">
-        <v>2.23</v>
-      </c>
-      <c r="AC156">
-        <v>2.42</v>
-      </c>
-      <c r="AD156">
-        <v>1.44</v>
-      </c>
-      <c r="AE156">
-        <v>1.19</v>
-      </c>
-      <c r="AF156">
-        <v>1.47</v>
-      </c>
       <c r="AG156">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="O157">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P157">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="Q157">
-        <v>4.46</v>
+        <v>2.84</v>
       </c>
       <c r="R157">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S157">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T157">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="V157">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z157">
-        <v>3.92</v>
+        <v>4.84</v>
       </c>
       <c r="AA157">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB157">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AC157">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AD157">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE157">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF157">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AG157">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK157">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="O158">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q158">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="R158">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="S158">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="U158">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V158">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W158">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X158">
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z158">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA158">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB158">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AC158">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="AD158">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF158">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG158">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK158">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O159">
-        <v>3.43</v>
+        <v>4.2</v>
       </c>
       <c r="P159">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q159">
-        <v>2.82</v>
+        <v>4.46</v>
       </c>
       <c r="R159">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S159">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U159">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="V159">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W159">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z159">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="AA159">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AB159">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC159">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AD159">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE159">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF159">
         <v>1.73</v>
       </c>
       <c r="AG159">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK159">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="O160">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P160">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="Q160">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R160">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S160">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T160">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U160">
+        <v>2.3</v>
+      </c>
+      <c r="V160">
+        <v>1.52</v>
+      </c>
+      <c r="W160">
+        <v>1.1</v>
+      </c>
+      <c r="X160">
+        <v>1.03</v>
+      </c>
+      <c r="Y160">
+        <v>1.17</v>
+      </c>
+      <c r="Z160">
+        <v>4.2</v>
+      </c>
+      <c r="AA160">
+        <v>1.61</v>
+      </c>
+      <c r="AB160">
+        <v>2.23</v>
+      </c>
+      <c r="AC160">
         <v>2.42</v>
       </c>
-      <c r="V160">
-        <v>1.48</v>
-      </c>
-      <c r="W160">
-        <v>1.09</v>
-      </c>
-      <c r="X160">
-        <v>1.01</v>
-      </c>
-      <c r="Y160">
-        <v>1.18</v>
-      </c>
-      <c r="Z160">
-        <v>3.9</v>
-      </c>
-      <c r="AA160">
-        <v>1.75</v>
-      </c>
-      <c r="AB160">
-        <v>1.99</v>
-      </c>
-      <c r="AC160">
-        <v>3.07</v>
-      </c>
       <c r="AD160">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE160">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF160">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG160">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK160">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="O161">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P161">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q161">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R161">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="S161">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U161">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W161">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X161">
         <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z161">
-        <v>4.84</v>
+        <v>3.28</v>
       </c>
       <c r="AA161">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB161">
-        <v>2.27</v>
+        <v>1.88</v>
       </c>
       <c r="AC161">
-        <v>2.47</v>
+        <v>3.14</v>
       </c>
       <c r="AD161">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE161">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AF161">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK161">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
+        <v>3.2</v>
+      </c>
+      <c r="O278">
+        <v>2.7</v>
+      </c>
+      <c r="P278">
+        <v>2.4</v>
+      </c>
+      <c r="Q278">
+        <v>4.38</v>
+      </c>
+      <c r="R278">
+        <v>1.74</v>
+      </c>
+      <c r="S278">
         <v>1.61</v>
-      </c>
-      <c r="O278">
-        <v>3.1</v>
-      </c>
-      <c r="P278">
-        <v>5.75</v>
-      </c>
-      <c r="Q278">
-        <v>2.3</v>
-      </c>
-      <c r="R278">
-        <v>2</v>
-      </c>
-      <c r="S278">
-        <v>1.57</v>
       </c>
       <c r="T278">
         <v>2.2</v>
       </c>
       <c r="U278">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y278">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Z278">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AA278">
-        <v>2.49</v>
+        <v>2.87</v>
       </c>
       <c r="AB278">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC278">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="AD278">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE278">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF278">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AG278">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK278">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.2</v>
+        <v>1.61</v>
       </c>
       <c r="O279">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P279">
-        <v>2.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q279">
-        <v>4.38</v>
+        <v>2.3</v>
       </c>
       <c r="R279">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="S279">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T279">
         <v>2.2</v>
       </c>
       <c r="U279">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X279">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Z279">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AA279">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="AB279">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AC279">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="AD279">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE279">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AG279">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="AL279">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1308,7 +1308,7 @@
         <v>2.54</v>
       </c>
       <c r="U6">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1326,10 +1326,10 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB6">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC6">
         <v>3.42</v>
@@ -1341,10 +1341,10 @@
         <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P48">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>3.13</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="U48">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="V48">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>4.35</v>
+        <v>3.34</v>
       </c>
       <c r="AA48">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AB48">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AC48">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="AD48">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="O49">
         <v>4</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="AA49">
         <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>2.14</v>
+        <v>1.21</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q50">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.83</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>3.34</v>
+        <v>4.54</v>
       </c>
       <c r="AA50">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AB50">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="O55">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P55">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q55">
-        <v>3.12</v>
+        <v>3.61</v>
       </c>
       <c r="R55">
+        <v>2.3</v>
+      </c>
+      <c r="S55">
+        <v>1.22</v>
+      </c>
+      <c r="T55">
+        <v>3.48</v>
+      </c>
+      <c r="U55">
         <v>2.2</v>
       </c>
-      <c r="S55">
-        <v>1.35</v>
-      </c>
-      <c r="T55">
-        <v>3</v>
-      </c>
-      <c r="U55">
-        <v>2.7</v>
-      </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AB55">
-        <v>1.87</v>
+        <v>2.44</v>
       </c>
       <c r="AC55">
-        <v>3.04</v>
+        <v>2.19</v>
       </c>
       <c r="AD55">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="AE55">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AF55">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AG55">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AK55">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q56">
-        <v>3.61</v>
+        <v>3.12</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="U56">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA56">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AB56">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="AC56">
-        <v>2.19</v>
+        <v>3.04</v>
       </c>
       <c r="AD56">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="AE56">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
+        <v>1.68</v>
+      </c>
+      <c r="AG56">
+        <v>2.06</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.44</v>
       </c>
-      <c r="AG56">
-        <v>2.5</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.73</v>
-      </c>
       <c r="AK56">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9938,22 +9938,22 @@
         <v>1.25</v>
       </c>
       <c r="R59">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="S59">
         <v>1.11</v>
       </c>
       <c r="T59">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="U59">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V59">
         <v>1.94</v>
       </c>
       <c r="W59">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9968,7 +9968,7 @@
         <v>1.22</v>
       </c>
       <c r="AB59">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC59">
         <v>1.63</v>
@@ -9980,7 +9980,7 @@
         <v>1.47</v>
       </c>
       <c r="AF59">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AG59">
         <v>1.5</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q73">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R73">
         <v>1.96</v>
@@ -12235,7 +12235,7 @@
         <v>1.33</v>
       </c>
       <c r="W73">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12247,10 +12247,10 @@
         <v>2.88</v>
       </c>
       <c r="AA73">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB73">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC73">
         <v>3.84</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O74">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P74">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q74">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="R74">
         <v>1.94</v>
@@ -12389,16 +12389,16 @@
         <v>1.44</v>
       </c>
       <c r="T74">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U74">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V74">
         <v>1.3</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X74">
         <v>1.04</v>
@@ -12413,7 +12413,7 @@
         <v>2.17</v>
       </c>
       <c r="AB74">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC74">
         <v>3.9</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,34 +18565,34 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="O112">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P112">
+        <v>2.23</v>
+      </c>
+      <c r="Q112">
+        <v>3</v>
+      </c>
+      <c r="R112">
         <v>2.3</v>
-      </c>
-      <c r="Q112">
-        <v>3.48</v>
-      </c>
-      <c r="R112">
-        <v>2.38</v>
       </c>
       <c r="S112">
         <v>1.26</v>
       </c>
       <c r="T112">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U112">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V112">
         <v>1.64</v>
       </c>
       <c r="W112">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X112">
         <v>1.03</v>
@@ -18601,28 +18601,28 @@
         <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA112">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AB112">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AC112">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AD112">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE112">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF112">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG112">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK112">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,34 +18728,34 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="O113">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P113">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="R113">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S113">
         <v>1.26</v>
       </c>
       <c r="T113">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U113">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V113">
         <v>1.64</v>
       </c>
       <c r="W113">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X113">
         <v>1.03</v>
@@ -18764,28 +18764,28 @@
         <v>1.14</v>
       </c>
       <c r="Z113">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA113">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AB113">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AC113">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AD113">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE113">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF113">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG113">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
+        <v>1.25</v>
+      </c>
+      <c r="O120">
+        <v>5.2</v>
+      </c>
+      <c r="P120">
+        <v>7.5</v>
+      </c>
+      <c r="Q120">
+        <v>1.62</v>
+      </c>
+      <c r="R120">
+        <v>2.7</v>
+      </c>
+      <c r="S120">
+        <v>1.23</v>
+      </c>
+      <c r="T120">
         <v>3.7</v>
       </c>
-      <c r="O120">
-        <v>3.55</v>
-      </c>
-      <c r="P120">
-        <v>1.89</v>
-      </c>
-      <c r="Q120">
-        <v>3.96</v>
-      </c>
-      <c r="R120">
+      <c r="U120">
         <v>2.2</v>
       </c>
-      <c r="S120">
-        <v>1.33</v>
-      </c>
-      <c r="T120">
-        <v>3.12</v>
-      </c>
-      <c r="U120">
-        <v>2.63</v>
-      </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X120">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="Z120">
-        <v>3.49</v>
+        <v>4.75</v>
       </c>
       <c r="AA120">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AB120">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="AC120">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="AD120">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE120">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF120">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AG120">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK120">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
+        <v>3.7</v>
+      </c>
+      <c r="O121">
+        <v>3.55</v>
+      </c>
+      <c r="P121">
+        <v>1.89</v>
+      </c>
+      <c r="Q121">
+        <v>3.96</v>
+      </c>
+      <c r="R121">
+        <v>2.2</v>
+      </c>
+      <c r="S121">
+        <v>1.33</v>
+      </c>
+      <c r="T121">
+        <v>3.12</v>
+      </c>
+      <c r="U121">
+        <v>2.63</v>
+      </c>
+      <c r="V121">
+        <v>1.44</v>
+      </c>
+      <c r="W121">
+        <v>1.07</v>
+      </c>
+      <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="Y121">
+        <v>1.28</v>
+      </c>
+      <c r="Z121">
+        <v>3.49</v>
+      </c>
+      <c r="AA121">
+        <v>1.81</v>
+      </c>
+      <c r="AB121">
+        <v>1.86</v>
+      </c>
+      <c r="AC121">
+        <v>3.04</v>
+      </c>
+      <c r="AD121">
+        <v>1.33</v>
+      </c>
+      <c r="AE121">
+        <v>1.07</v>
+      </c>
+      <c r="AF121">
+        <v>1.7</v>
+      </c>
+      <c r="AG121">
+        <v>2.05</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.25</v>
       </c>
-      <c r="O121">
-        <v>5.2</v>
-      </c>
-      <c r="P121">
-        <v>7.5</v>
-      </c>
-      <c r="Q121">
-        <v>1.62</v>
-      </c>
-      <c r="R121">
-        <v>2.7</v>
-      </c>
-      <c r="S121">
-        <v>1.23</v>
-      </c>
-      <c r="T121">
-        <v>3.7</v>
-      </c>
-      <c r="U121">
-        <v>2.2</v>
-      </c>
-      <c r="V121">
-        <v>1.6</v>
-      </c>
-      <c r="W121">
-        <v>1.14</v>
-      </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.12</v>
-      </c>
-      <c r="Z121">
-        <v>4.75</v>
-      </c>
-      <c r="AA121">
-        <v>1.48</v>
-      </c>
-      <c r="AB121">
-        <v>2.42</v>
-      </c>
-      <c r="AC121">
-        <v>2.35</v>
-      </c>
-      <c r="AD121">
-        <v>1.56</v>
-      </c>
-      <c r="AE121">
-        <v>1.21</v>
-      </c>
-      <c r="AF121">
-        <v>1.92</v>
-      </c>
-      <c r="AG121">
-        <v>1.77</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.1</v>
-      </c>
       <c r="AK121">
-        <v>3.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="O133">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="Q133">
-        <v>1.88</v>
+        <v>3</v>
       </c>
       <c r="R133">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S133">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="U133">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="V133">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>4.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA133">
-        <v>1.45</v>
+        <v>2.02</v>
       </c>
       <c r="AB133">
-        <v>2.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC133">
-        <v>2.18</v>
+        <v>3.69</v>
       </c>
       <c r="AD133">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AE133">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG133">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK133">
-        <v>2.66</v>
+        <v>1.5</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="O134">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P134">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q134">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S134">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="U134">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="V134">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="W134">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X134">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
-        <v>3.41</v>
+        <v>4.95</v>
       </c>
       <c r="AA134">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AB134">
-        <v>1.77</v>
+        <v>2.67</v>
       </c>
       <c r="AC134">
-        <v>3.5</v>
+        <v>2.18</v>
       </c>
       <c r="AD134">
+        <v>1.61</v>
+      </c>
+      <c r="AE134">
         <v>1.25</v>
       </c>
-      <c r="AE134">
-        <v>1.05</v>
-      </c>
       <c r="AF134">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG134">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK134">
-        <v>1.58</v>
+        <v>2.66</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P135">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q135">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R135">
         <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U135">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V135">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z135">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="AA135">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB135">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC135">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD135">
         <v>1.25</v>
       </c>
       <c r="AE135">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AG135">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P136">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="Q136">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U136">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V136">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
+        <v>1.26</v>
+      </c>
+      <c r="Z136">
+        <v>3.71</v>
+      </c>
+      <c r="AA136">
+        <v>1.8</v>
+      </c>
+      <c r="AB136">
+        <v>1.89</v>
+      </c>
+      <c r="AC136">
+        <v>2.97</v>
+      </c>
+      <c r="AD136">
         <v>1.3</v>
       </c>
-      <c r="Z136">
-        <v>2.97</v>
-      </c>
-      <c r="AA136">
-        <v>2.02</v>
-      </c>
-      <c r="AB136">
-        <v>1.69</v>
-      </c>
-      <c r="AC136">
-        <v>3.69</v>
-      </c>
-      <c r="AD136">
-        <v>1.22</v>
-      </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG136">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O137">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q137">
         <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T137">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U137">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="V137">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W137">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>3.71</v>
+        <v>3.05</v>
       </c>
       <c r="AA137">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB137">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AD137">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF137">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AG137">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK137">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P143">
-        <v>2.45</v>
+        <v>3.46</v>
       </c>
       <c r="Q143">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="R143">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S143">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T143">
         <v>2.88</v>
       </c>
       <c r="U143">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="V143">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W143">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z143">
-        <v>3.67</v>
+        <v>2.94</v>
       </c>
       <c r="AA143">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB143">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC143">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AD143">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE143">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF143">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG143">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="O144">
+        <v>3.6</v>
+      </c>
+      <c r="P144">
+        <v>2.2</v>
+      </c>
+      <c r="Q144">
+        <v>3.64</v>
+      </c>
+      <c r="R144">
+        <v>2.2</v>
+      </c>
+      <c r="S144">
+        <v>1.32</v>
+      </c>
+      <c r="T144">
+        <v>3.02</v>
+      </c>
+      <c r="U144">
+        <v>2.42</v>
+      </c>
+      <c r="V144">
+        <v>1.48</v>
+      </c>
+      <c r="W144">
+        <v>1.1</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+      <c r="Y144">
+        <v>1.24</v>
+      </c>
+      <c r="Z144">
         <v>4</v>
       </c>
-      <c r="P144">
-        <v>4.8</v>
-      </c>
-      <c r="Q144">
-        <v>2.23</v>
-      </c>
-      <c r="R144">
-        <v>2.25</v>
-      </c>
-      <c r="S144">
-        <v>1.31</v>
-      </c>
-      <c r="T144">
-        <v>3.08</v>
-      </c>
-      <c r="U144">
-        <v>2.66</v>
-      </c>
-      <c r="V144">
-        <v>1.45</v>
-      </c>
-      <c r="W144">
-        <v>1.07</v>
-      </c>
-      <c r="X144">
-        <v>1.02</v>
-      </c>
-      <c r="Y144">
-        <v>1.19</v>
-      </c>
-      <c r="Z144">
-        <v>3.93</v>
-      </c>
       <c r="AA144">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB144">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC144">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD144">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE144">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF144">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG144">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK144">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.1</v>
+        <v>2.89</v>
       </c>
       <c r="O145">
+        <v>3.45</v>
+      </c>
+      <c r="P145">
+        <v>2.3</v>
+      </c>
+      <c r="Q145">
+        <v>3.53</v>
+      </c>
+      <c r="R145">
+        <v>2.18</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
         <v>3.4</v>
       </c>
-      <c r="P145">
-        <v>3.46</v>
-      </c>
-      <c r="Q145">
-        <v>2.68</v>
-      </c>
-      <c r="R145">
-        <v>2.05</v>
-      </c>
-      <c r="S145">
-        <v>1.39</v>
-      </c>
-      <c r="T145">
-        <v>2.88</v>
-      </c>
       <c r="U145">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="V145">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W145">
+        <v>1.08</v>
+      </c>
+      <c r="X145">
         <v>1.02</v>
       </c>
-      <c r="X145">
-        <v>1.03</v>
-      </c>
       <c r="Y145">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z145">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="AA145">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB145">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AC145">
-        <v>3.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD145">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK145">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q146">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S146">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T146">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U146">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="V146">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W146">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z146">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AA146">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB146">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AC146">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD146">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE146">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG146">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.89</v>
+        <v>1.68</v>
       </c>
       <c r="O147">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P147">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
-        <v>3.53</v>
+        <v>2.23</v>
       </c>
       <c r="R147">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T147">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U147">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="V147">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W147">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X147">
         <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z147">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="AA147">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB147">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC147">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AD147">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE147">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF147">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG147">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="Q156">
-        <v>3.36</v>
+        <v>2.84</v>
       </c>
       <c r="R156">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="S156">
+        <v>1.26</v>
+      </c>
+      <c r="T156">
+        <v>3.4</v>
+      </c>
+      <c r="U156">
+        <v>2.25</v>
+      </c>
+      <c r="V156">
+        <v>1.57</v>
+      </c>
+      <c r="W156">
+        <v>1.11</v>
+      </c>
+      <c r="X156">
+        <v>1.03</v>
+      </c>
+      <c r="Y156">
+        <v>1.17</v>
+      </c>
+      <c r="Z156">
+        <v>4.84</v>
+      </c>
+      <c r="AA156">
+        <v>1.6</v>
+      </c>
+      <c r="AB156">
+        <v>2.27</v>
+      </c>
+      <c r="AC156">
+        <v>2.47</v>
+      </c>
+      <c r="AD156">
+        <v>1.46</v>
+      </c>
+      <c r="AE156">
+        <v>1.21</v>
+      </c>
+      <c r="AF156">
+        <v>1.48</v>
+      </c>
+      <c r="AG156">
+        <v>2.45</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>1.27</v>
       </c>
-      <c r="T156">
-        <v>3.32</v>
-      </c>
-      <c r="U156">
-        <v>2.44</v>
-      </c>
-      <c r="V156">
-        <v>1.53</v>
-      </c>
-      <c r="W156">
-        <v>1.12</v>
-      </c>
-      <c r="X156">
-        <v>1.01</v>
-      </c>
-      <c r="Y156">
-        <v>1.15</v>
-      </c>
-      <c r="Z156">
-        <v>3.8</v>
-      </c>
-      <c r="AA156">
-        <v>1.62</v>
-      </c>
-      <c r="AB156">
-        <v>2.26</v>
-      </c>
-      <c r="AC156">
-        <v>2.49</v>
-      </c>
-      <c r="AD156">
-        <v>1.47</v>
-      </c>
-      <c r="AE156">
-        <v>1.13</v>
-      </c>
-      <c r="AF156">
-        <v>1.52</v>
-      </c>
-      <c r="AG156">
-        <v>2.37</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.25</v>
-      </c>
       <c r="AK156">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="O157">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P157">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q157">
-        <v>2.84</v>
+        <v>3.36</v>
       </c>
       <c r="R157">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="S157">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U157">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V157">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W157">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z157">
-        <v>4.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA157">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB157">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AC157">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AD157">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE157">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF157">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AG157">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK157">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="O158">
+        <v>3.7</v>
+      </c>
+      <c r="P158">
+        <v>4</v>
+      </c>
+      <c r="Q158">
+        <v>2.38</v>
+      </c>
+      <c r="R158">
+        <v>2.11</v>
+      </c>
+      <c r="S158">
+        <v>1.35</v>
+      </c>
+      <c r="T158">
+        <v>2.88</v>
+      </c>
+      <c r="U158">
+        <v>2.73</v>
+      </c>
+      <c r="V158">
+        <v>1.41</v>
+      </c>
+      <c r="W158">
+        <v>1.06</v>
+      </c>
+      <c r="X158">
+        <v>1.02</v>
+      </c>
+      <c r="Y158">
+        <v>1.22</v>
+      </c>
+      <c r="Z158">
         <v>3.5</v>
       </c>
-      <c r="P158">
-        <v>2.45</v>
-      </c>
-      <c r="Q158">
-        <v>3</v>
-      </c>
-      <c r="R158">
-        <v>2.16</v>
-      </c>
-      <c r="S158">
-        <v>1.3</v>
-      </c>
-      <c r="T158">
-        <v>3.14</v>
-      </c>
-      <c r="U158">
-        <v>2.42</v>
-      </c>
-      <c r="V158">
-        <v>1.48</v>
-      </c>
-      <c r="W158">
-        <v>1.09</v>
-      </c>
-      <c r="X158">
-        <v>1.01</v>
-      </c>
-      <c r="Y158">
-        <v>1.18</v>
-      </c>
-      <c r="Z158">
-        <v>3.9</v>
-      </c>
       <c r="AA158">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB158">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC158">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AD158">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE158">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG158">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="O159">
+        <v>3.35</v>
+      </c>
+      <c r="P159">
+        <v>2.33</v>
+      </c>
+      <c r="Q159">
+        <v>3.14</v>
+      </c>
+      <c r="R159">
+        <v>2.26</v>
+      </c>
+      <c r="S159">
+        <v>1.25</v>
+      </c>
+      <c r="T159">
+        <v>3.32</v>
+      </c>
+      <c r="U159">
+        <v>2.3</v>
+      </c>
+      <c r="V159">
+        <v>1.52</v>
+      </c>
+      <c r="W159">
+        <v>1.1</v>
+      </c>
+      <c r="X159">
+        <v>1.03</v>
+      </c>
+      <c r="Y159">
+        <v>1.17</v>
+      </c>
+      <c r="Z159">
         <v>4.2</v>
       </c>
-      <c r="P159">
+      <c r="AA159">
         <v>1.61</v>
       </c>
-      <c r="Q159">
-        <v>4.46</v>
-      </c>
-      <c r="R159">
-        <v>2.24</v>
-      </c>
-      <c r="S159">
-        <v>1.3</v>
-      </c>
-      <c r="T159">
-        <v>3.3</v>
-      </c>
-      <c r="U159">
-        <v>2.54</v>
-      </c>
-      <c r="V159">
+      <c r="AB159">
+        <v>2.23</v>
+      </c>
+      <c r="AC159">
+        <v>2.42</v>
+      </c>
+      <c r="AD159">
+        <v>1.44</v>
+      </c>
+      <c r="AE159">
+        <v>1.19</v>
+      </c>
+      <c r="AF159">
+        <v>1.47</v>
+      </c>
+      <c r="AG159">
+        <v>2.39</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
+        <v>1.25</v>
+      </c>
+      <c r="AK159">
         <v>1.45</v>
-      </c>
-      <c r="W159">
-        <v>1.07</v>
-      </c>
-      <c r="X159">
-        <v>1.01</v>
-      </c>
-      <c r="Y159">
-        <v>1.23</v>
-      </c>
-      <c r="Z159">
-        <v>3.92</v>
-      </c>
-      <c r="AA159">
-        <v>1.65</v>
-      </c>
-      <c r="AB159">
-        <v>2.1</v>
-      </c>
-      <c r="AC159">
-        <v>2.62</v>
-      </c>
-      <c r="AD159">
-        <v>1.38</v>
-      </c>
-      <c r="AE159">
-        <v>1.13</v>
-      </c>
-      <c r="AF159">
-        <v>1.73</v>
-      </c>
-      <c r="AG159">
-        <v>2.1</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>2.25</v>
-      </c>
-      <c r="AK159">
-        <v>1.15</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="O160">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P160">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q160">
+        <v>3</v>
+      </c>
+      <c r="R160">
+        <v>2.16</v>
+      </c>
+      <c r="S160">
+        <v>1.3</v>
+      </c>
+      <c r="T160">
         <v>3.14</v>
       </c>
-      <c r="R160">
-        <v>2.26</v>
-      </c>
-      <c r="S160">
-        <v>1.25</v>
-      </c>
-      <c r="T160">
-        <v>3.32</v>
-      </c>
       <c r="U160">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="V160">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W160">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X160">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z160">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA160">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB160">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AC160">
-        <v>2.42</v>
+        <v>3.07</v>
       </c>
       <c r="AD160">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE160">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF160">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG160">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O161">
-        <v>3.43</v>
+        <v>4.2</v>
       </c>
       <c r="P161">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q161">
-        <v>2.82</v>
+        <v>4.46</v>
       </c>
       <c r="R161">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S161">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T161">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U161">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="V161">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W161">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X161">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z161">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="AA161">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AB161">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC161">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AD161">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE161">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF161">
         <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK161">
-        <v>1.64</v>
+        <v>1.15</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,58 +26715,58 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="O162">
-        <v>3.7</v>
+        <v>3.43</v>
       </c>
       <c r="P162">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q162">
-        <v>2.38</v>
+        <v>2.82</v>
       </c>
       <c r="R162">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S162">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T162">
+        <v>3</v>
+      </c>
+      <c r="U162">
         <v>2.88</v>
       </c>
-      <c r="U162">
-        <v>2.73</v>
-      </c>
       <c r="V162">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W162">
         <v>1.06</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y162">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z162">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA162">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AB162">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC162">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD162">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE162">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF162">
         <v>1.73</v>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK162">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -34059,10 +34059,10 @@
         <v>3</v>
       </c>
       <c r="Q207">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R207">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S207">
         <v>1.38</v>
@@ -34071,7 +34071,7 @@
         <v>2.64</v>
       </c>
       <c r="U207">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="V207">
         <v>1.36</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK207">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,19 +34213,19 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O208">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P208">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q208">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R208">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S208">
         <v>1.36</v>
@@ -34234,10 +34234,10 @@
         <v>2.73</v>
       </c>
       <c r="U208">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V208">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W208">
         <v>1.07</v>
@@ -34255,7 +34255,7 @@
         <v>2</v>
       </c>
       <c r="AB208">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC208">
         <v>3.28</v>
@@ -34267,10 +34267,10 @@
         <v>1.06</v>
       </c>
       <c r="AF208">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG208">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK208">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35230,10 +35230,10 @@
         <v>0</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC214">
         <v>0</v>
@@ -35523,7 +35523,7 @@
         <v>3.2</v>
       </c>
       <c r="P216">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q216">
         <v>2.5</v>
@@ -35559,7 +35559,7 @@
         <v>2.09</v>
       </c>
       <c r="AB216">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC216">
         <v>3.58</v>
@@ -35568,13 +35568,13 @@
         <v>1.21</v>
       </c>
       <c r="AE216">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF216">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG216">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35689,55 +35689,55 @@
         <v>0</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>2.1</v>
       </c>
       <c r="S222">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T222">
         <v>2.78</v>
@@ -36519,10 +36519,10 @@
         <v>2.74</v>
       </c>
       <c r="V222">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W222">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X222">
         <v>1.02</v>
@@ -36549,26 +36549,26 @@
         <v>1.06</v>
       </c>
       <c r="AF222">
+        <v>1.72</v>
+      </c>
+      <c r="AG222">
+        <v>2.01</v>
+      </c>
+      <c r="AH222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ222">
+        <v>1.25</v>
+      </c>
+      <c r="AK222">
         <v>1.73</v>
-      </c>
-      <c r="AG222">
-        <v>1.97</v>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ222">
-        <v>1.28</v>
-      </c>
-      <c r="AK222">
-        <v>1.67</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36667,10 +36667,10 @@
         <v>3</v>
       </c>
       <c r="Q223">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R223">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S223">
         <v>1.4</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>0</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC231">
         <v>0</v>
@@ -38469,13 +38469,13 @@
         <v>1.25</v>
       </c>
       <c r="T234">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U234">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V234">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W234">
         <v>1.12</v>
@@ -38487,7 +38487,7 @@
         <v>1.15</v>
       </c>
       <c r="Z234">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA234">
         <v>1.59</v>
@@ -38505,10 +38505,10 @@
         <v>1.15</v>
       </c>
       <c r="AF234">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG234">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK234">
         <v>2.88</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q235">
         <v>3</v>
       </c>
       <c r="R235">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S235">
         <v>1.4</v>
       </c>
       <c r="T235">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="U235">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="V235">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W235">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X235">
         <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z235">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA235">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB235">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC235">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD235">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE235">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF235">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG235">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK235">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,80 +38777,80 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O236">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P236">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q236">
         <v>3</v>
       </c>
       <c r="R236">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S236">
         <v>1.4</v>
       </c>
       <c r="T236">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U236">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="V236">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W236">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X236">
         <v>1.01</v>
       </c>
       <c r="Y236">
+        <v>1.33</v>
+      </c>
+      <c r="Z236">
+        <v>3</v>
+      </c>
+      <c r="AA236">
+        <v>2.15</v>
+      </c>
+      <c r="AB236">
+        <v>1.66</v>
+      </c>
+      <c r="AC236">
+        <v>3.74</v>
+      </c>
+      <c r="AD236">
+        <v>1.22</v>
+      </c>
+      <c r="AE236">
+        <v>1.02</v>
+      </c>
+      <c r="AF236">
+        <v>1.91</v>
+      </c>
+      <c r="AG236">
+        <v>1.91</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
         <v>1.3</v>
       </c>
-      <c r="Z236">
-        <v>3.25</v>
-      </c>
-      <c r="AA236">
-        <v>2</v>
-      </c>
-      <c r="AB236">
-        <v>1.76</v>
-      </c>
-      <c r="AC236">
-        <v>3.34</v>
-      </c>
-      <c r="AD236">
-        <v>1.24</v>
-      </c>
-      <c r="AE236">
-        <v>1.05</v>
-      </c>
-      <c r="AF236">
-        <v>1.75</v>
-      </c>
-      <c r="AG236">
-        <v>1.97</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>1.28</v>
-      </c>
       <c r="AK236">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41913,10 +41913,10 @@
         <v>0</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC255">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43543,10 +43543,10 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC265">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,10 +46314,10 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC282">
         <v>0</v>
@@ -46438,28 +46438,28 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O283">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P283">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q283">
         <v>2</v>
       </c>
       <c r="R283">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S283">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T283">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="U283">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="V283">
         <v>1.37</v>
@@ -46480,7 +46480,7 @@
         <v>1.9</v>
       </c>
       <c r="AB283">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC283">
         <v>2.97</v>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK283">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46610,7 +46610,7 @@
         <v>2.31</v>
       </c>
       <c r="Q284">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="R284">
         <v>1.92</v>
@@ -46622,10 +46622,10 @@
         <v>2.39</v>
       </c>
       <c r="U284">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="V284">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W284">
         <v>1.01</v>
@@ -46634,10 +46634,10 @@
         <v>1.03</v>
       </c>
       <c r="Y284">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z284">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA284">
         <v>2.35</v>
@@ -46655,7 +46655,7 @@
         <v>1.01</v>
       </c>
       <c r="AF284">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG284">
         <v>1.75</v>
@@ -46764,19 +46764,19 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="O285">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P285">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q285">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R285">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S285">
         <v>1.36</v>
@@ -46818,10 +46818,10 @@
         <v>1.06</v>
       </c>
       <c r="AF285">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG285">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK285">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL285">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q55">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="R55">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="U55">
+        <v>2.7</v>
+      </c>
+      <c r="V55">
+        <v>1.4</v>
+      </c>
+      <c r="W55">
+        <v>1.08</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
+        <v>3.65</v>
+      </c>
+      <c r="AA55">
+        <v>1.93</v>
+      </c>
+      <c r="AB55">
+        <v>1.87</v>
+      </c>
+      <c r="AC55">
+        <v>3.04</v>
+      </c>
+      <c r="AD55">
+        <v>1.29</v>
+      </c>
+      <c r="AE55">
+        <v>1.07</v>
+      </c>
+      <c r="AF55">
+        <v>1.65</v>
+      </c>
+      <c r="AG55">
         <v>2.1</v>
-      </c>
-      <c r="V55">
-        <v>1.65</v>
-      </c>
-      <c r="W55">
-        <v>1.14</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.13</v>
-      </c>
-      <c r="Z55">
-        <v>5.5</v>
-      </c>
-      <c r="AA55">
-        <v>1.47</v>
-      </c>
-      <c r="AB55">
-        <v>2.45</v>
-      </c>
-      <c r="AC55">
-        <v>2.17</v>
-      </c>
-      <c r="AD55">
-        <v>1.63</v>
-      </c>
-      <c r="AE55">
-        <v>1.23</v>
-      </c>
-      <c r="AF55">
-        <v>1.44</v>
-      </c>
-      <c r="AG55">
-        <v>2.5</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>3.25</v>
+      </c>
+      <c r="O56">
+        <v>3.8</v>
+      </c>
+      <c r="P56">
+        <v>2.05</v>
+      </c>
+      <c r="Q56">
+        <v>3.8</v>
+      </c>
+      <c r="R56">
+        <v>2.32</v>
+      </c>
+      <c r="S56">
+        <v>1.22</v>
+      </c>
+      <c r="T56">
+        <v>3.48</v>
+      </c>
+      <c r="U56">
+        <v>2.1</v>
+      </c>
+      <c r="V56">
+        <v>1.65</v>
+      </c>
+      <c r="W56">
+        <v>1.14</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.13</v>
+      </c>
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.47</v>
+      </c>
+      <c r="AB56">
+        <v>2.45</v>
+      </c>
+      <c r="AC56">
+        <v>2.17</v>
+      </c>
+      <c r="AD56">
+        <v>1.63</v>
+      </c>
+      <c r="AE56">
+        <v>1.23</v>
+      </c>
+      <c r="AF56">
+        <v>1.44</v>
+      </c>
+      <c r="AG56">
         <v>2.5</v>
-      </c>
-      <c r="O56">
-        <v>3.45</v>
-      </c>
-      <c r="P56">
-        <v>2.48</v>
-      </c>
-      <c r="Q56">
-        <v>3.12</v>
-      </c>
-      <c r="R56">
-        <v>2.2</v>
-      </c>
-      <c r="S56">
-        <v>1.35</v>
-      </c>
-      <c r="T56">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>2.7</v>
-      </c>
-      <c r="V56">
-        <v>1.4</v>
-      </c>
-      <c r="W56">
-        <v>1.08</v>
-      </c>
-      <c r="X56">
-        <v>1.04</v>
-      </c>
-      <c r="Y56">
-        <v>1.29</v>
-      </c>
-      <c r="Z56">
-        <v>3.65</v>
-      </c>
-      <c r="AA56">
-        <v>1.93</v>
-      </c>
-      <c r="AB56">
-        <v>1.87</v>
-      </c>
-      <c r="AC56">
-        <v>3.04</v>
-      </c>
-      <c r="AD56">
-        <v>1.29</v>
-      </c>
-      <c r="AE56">
-        <v>1.07</v>
-      </c>
-      <c r="AF56">
-        <v>1.65</v>
-      </c>
-      <c r="AG56">
-        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O76">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="P76">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q76">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="R76">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V76">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W76">
         <v>1.07</v>
@@ -12730,31 +12730,31 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z76">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB76">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC76">
         <v>3.45</v>
       </c>
       <c r="AD76">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="O77">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="P77">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="U77">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12893,47 +12893,47 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z77">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA77">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC77">
         <v>3.45</v>
       </c>
       <c r="AD77">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG77">
+        <v>1.85</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.29</v>
+      </c>
+      <c r="AK77">
         <v>2</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.3</v>
-      </c>
-      <c r="AK77">
-        <v>1.55</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O114">
+        <v>3.7</v>
+      </c>
+      <c r="P114">
         <v>4.2</v>
       </c>
-      <c r="P114">
-        <v>5</v>
-      </c>
       <c r="Q114">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="R114">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U114">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V114">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z114">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA114">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AB114">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AC114">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="AD114">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
+        <v>2.08</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
+        <v>1.2</v>
+      </c>
+      <c r="AK114">
         <v>2.1</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.18</v>
-      </c>
-      <c r="AK114">
-        <v>2.27</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P115">
+        <v>5</v>
+      </c>
+      <c r="Q115">
+        <v>2</v>
+      </c>
+      <c r="R115">
+        <v>2.4</v>
+      </c>
+      <c r="S115">
+        <v>1.28</v>
+      </c>
+      <c r="T115">
+        <v>3.5</v>
+      </c>
+      <c r="U115">
+        <v>2.47</v>
+      </c>
+      <c r="V115">
+        <v>1.57</v>
+      </c>
+      <c r="W115">
+        <v>1.14</v>
+      </c>
+      <c r="X115">
+        <v>1.03</v>
+      </c>
+      <c r="Y115">
+        <v>1.15</v>
+      </c>
+      <c r="Z115">
         <v>4.2</v>
       </c>
-      <c r="Q115">
-        <v>2.26</v>
-      </c>
-      <c r="R115">
-        <v>2.3</v>
-      </c>
-      <c r="S115">
-        <v>1.33</v>
-      </c>
-      <c r="T115">
-        <v>3.3</v>
-      </c>
-      <c r="U115">
-        <v>2.39</v>
-      </c>
-      <c r="V115">
-        <v>1.53</v>
-      </c>
-      <c r="W115">
-        <v>1.12</v>
-      </c>
-      <c r="X115">
-        <v>1.01</v>
-      </c>
-      <c r="Y115">
-        <v>1.23</v>
-      </c>
-      <c r="Z115">
-        <v>3.74</v>
-      </c>
       <c r="AA115">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AB115">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AC115">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE115">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="O121">
         <v>3.55</v>
       </c>
       <c r="P121">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R121">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T121">
         <v>3.12</v>
       </c>
       <c r="U121">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V121">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W121">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z121">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="AA121">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC121">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE121">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK121">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O122">
         <v>3.55</v>
       </c>
       <c r="P122">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q122">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
         <v>3.12</v>
       </c>
       <c r="U122">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="AA122">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD122">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG122">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P133">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="Q133">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="S133">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="T133">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="U133">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="V133">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X133">
         <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z133">
-        <v>3.2</v>
+        <v>5.62</v>
       </c>
       <c r="AA133">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AB133">
-        <v>1.81</v>
+        <v>2.43</v>
       </c>
       <c r="AC133">
-        <v>3.28</v>
+        <v>2.2</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AF133">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG133">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AK133">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q134">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R134">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T134">
         <v>2.88</v>
       </c>
       <c r="U134">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="V134">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
+        <v>1.08</v>
+      </c>
+      <c r="X134">
         <v>1.05</v>
       </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
       <c r="Y134">
+        <v>1.28</v>
+      </c>
+      <c r="Z134">
+        <v>3.08</v>
+      </c>
+      <c r="AA134">
+        <v>1.97</v>
+      </c>
+      <c r="AB134">
+        <v>1.75</v>
+      </c>
+      <c r="AC134">
+        <v>3.42</v>
+      </c>
+      <c r="AD134">
         <v>1.3</v>
       </c>
-      <c r="Z134">
-        <v>2.97</v>
-      </c>
-      <c r="AA134">
-        <v>2.02</v>
-      </c>
-      <c r="AB134">
-        <v>1.73</v>
-      </c>
-      <c r="AC134">
-        <v>3.48</v>
-      </c>
-      <c r="AD134">
-        <v>1.22</v>
-      </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG134">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O135">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="Q135">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R135">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="S135">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T135">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="U135">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="V135">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z135">
-        <v>5.62</v>
+        <v>3.71</v>
       </c>
       <c r="AA135">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB135">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="AC135">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD135">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE135">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG135">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK135">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T136">
+        <v>2.88</v>
+      </c>
+      <c r="U136">
+        <v>3.07</v>
+      </c>
+      <c r="V136">
+        <v>1.37</v>
+      </c>
+      <c r="W136">
+        <v>1.05</v>
+      </c>
+      <c r="X136">
+        <v>1.01</v>
+      </c>
+      <c r="Y136">
+        <v>1.3</v>
+      </c>
+      <c r="Z136">
         <v>2.97</v>
       </c>
-      <c r="U136">
-        <v>2.56</v>
-      </c>
-      <c r="V136">
-        <v>1.43</v>
-      </c>
-      <c r="W136">
-        <v>1.07</v>
-      </c>
-      <c r="X136">
-        <v>1.03</v>
-      </c>
-      <c r="Y136">
-        <v>1.26</v>
-      </c>
-      <c r="Z136">
-        <v>3.71</v>
-      </c>
       <c r="AA136">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AB136">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK136">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R137">
         <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="V137">
         <v>1.4</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X137">
+        <v>1.02</v>
+      </c>
+      <c r="Y137">
+        <v>1.26</v>
+      </c>
+      <c r="Z137">
+        <v>3.2</v>
+      </c>
+      <c r="AA137">
+        <v>1.98</v>
+      </c>
+      <c r="AB137">
+        <v>1.81</v>
+      </c>
+      <c r="AC137">
+        <v>3.28</v>
+      </c>
+      <c r="AD137">
+        <v>1.25</v>
+      </c>
+      <c r="AE137">
         <v>1.05</v>
       </c>
-      <c r="Y137">
+      <c r="AF137">
+        <v>1.73</v>
+      </c>
+      <c r="AG137">
+        <v>1.97</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>1.28</v>
       </c>
-      <c r="Z137">
-        <v>3.08</v>
-      </c>
-      <c r="AA137">
-        <v>1.97</v>
-      </c>
-      <c r="AB137">
-        <v>1.75</v>
-      </c>
-      <c r="AC137">
-        <v>3.42</v>
-      </c>
-      <c r="AD137">
-        <v>1.3</v>
-      </c>
-      <c r="AE137">
-        <v>1.1</v>
-      </c>
-      <c r="AF137">
-        <v>1.83</v>
-      </c>
-      <c r="AG137">
-        <v>1.9</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.27</v>
-      </c>
       <c r="AK137">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
+        <v>2.1</v>
+      </c>
+      <c r="O143">
+        <v>3.4</v>
+      </c>
+      <c r="P143">
+        <v>3.3</v>
+      </c>
+      <c r="Q143">
+        <v>2.68</v>
+      </c>
+      <c r="R143">
+        <v>2.05</v>
+      </c>
+      <c r="S143">
+        <v>1.4</v>
+      </c>
+      <c r="T143">
         <v>2.88</v>
       </c>
-      <c r="O143">
-        <v>3.46</v>
-      </c>
-      <c r="P143">
-        <v>2.3</v>
-      </c>
-      <c r="Q143">
-        <v>3.5</v>
-      </c>
-      <c r="R143">
-        <v>2.4</v>
-      </c>
-      <c r="S143">
-        <v>1.29</v>
-      </c>
-      <c r="T143">
-        <v>3.4</v>
-      </c>
       <c r="U143">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="V143">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X143">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y143">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z143">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA143">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB143">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC143">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD143">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE143">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF143">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG143">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P144">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R144">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S144">
+        <v>1.29</v>
+      </c>
+      <c r="T144">
+        <v>2.87</v>
+      </c>
+      <c r="U144">
+        <v>2.5</v>
+      </c>
+      <c r="V144">
+        <v>1.44</v>
+      </c>
+      <c r="W144">
+        <v>1.1</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+      <c r="Y144">
+        <v>1.24</v>
+      </c>
+      <c r="Z144">
+        <v>4.02</v>
+      </c>
+      <c r="AA144">
+        <v>1.74</v>
+      </c>
+      <c r="AB144">
+        <v>1.97</v>
+      </c>
+      <c r="AC144">
+        <v>2.95</v>
+      </c>
+      <c r="AD144">
         <v>1.36</v>
       </c>
-      <c r="T144">
-        <v>3.06</v>
-      </c>
-      <c r="U144">
-        <v>2.75</v>
-      </c>
-      <c r="V144">
-        <v>1.4</v>
-      </c>
-      <c r="W144">
-        <v>1.08</v>
-      </c>
-      <c r="X144">
-        <v>1.04</v>
-      </c>
-      <c r="Y144">
-        <v>1.29</v>
-      </c>
-      <c r="Z144">
-        <v>3.15</v>
-      </c>
-      <c r="AA144">
-        <v>1.84</v>
-      </c>
-      <c r="AB144">
-        <v>1.83</v>
-      </c>
-      <c r="AC144">
-        <v>2.99</v>
-      </c>
-      <c r="AD144">
-        <v>1.29</v>
-      </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG144">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK144">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O145">
+        <v>3.46</v>
+      </c>
+      <c r="P145">
+        <v>2.3</v>
+      </c>
+      <c r="Q145">
+        <v>3.5</v>
+      </c>
+      <c r="R145">
+        <v>2.4</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
         <v>3.4</v>
       </c>
-      <c r="P145">
-        <v>3.3</v>
-      </c>
-      <c r="Q145">
-        <v>2.68</v>
-      </c>
-      <c r="R145">
-        <v>2.05</v>
-      </c>
-      <c r="S145">
-        <v>1.4</v>
-      </c>
-      <c r="T145">
-        <v>2.88</v>
-      </c>
       <c r="U145">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="V145">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W145">
+        <v>1.1</v>
+      </c>
+      <c r="X145">
         <v>1.02</v>
       </c>
-      <c r="X145">
-        <v>1.05</v>
-      </c>
       <c r="Y145">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z145">
-        <v>2.94</v>
+        <v>4.15</v>
       </c>
       <c r="AA145">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB145">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC145">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD145">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK145">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q146">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S146">
+        <v>1.36</v>
+      </c>
+      <c r="T146">
+        <v>3.06</v>
+      </c>
+      <c r="U146">
+        <v>2.75</v>
+      </c>
+      <c r="V146">
+        <v>1.4</v>
+      </c>
+      <c r="W146">
+        <v>1.08</v>
+      </c>
+      <c r="X146">
+        <v>1.04</v>
+      </c>
+      <c r="Y146">
         <v>1.29</v>
       </c>
-      <c r="T146">
-        <v>2.87</v>
-      </c>
-      <c r="U146">
-        <v>2.5</v>
-      </c>
-      <c r="V146">
-        <v>1.44</v>
-      </c>
-      <c r="W146">
-        <v>1.1</v>
-      </c>
-      <c r="X146">
-        <v>1</v>
-      </c>
-      <c r="Y146">
-        <v>1.24</v>
-      </c>
       <c r="Z146">
-        <v>4.02</v>
+        <v>3.15</v>
       </c>
       <c r="AA146">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AB146">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AC146">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AD146">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE146">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF146">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG146">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="O157">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P157">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="Q157">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R157">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S157">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U157">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="V157">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W157">
         <v>1.11</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
+        <v>1.21</v>
+      </c>
+      <c r="Z157">
+        <v>3.8</v>
+      </c>
+      <c r="AA157">
+        <v>1.62</v>
+      </c>
+      <c r="AB157">
+        <v>2.19</v>
+      </c>
+      <c r="AC157">
+        <v>2.49</v>
+      </c>
+      <c r="AD157">
+        <v>1.47</v>
+      </c>
+      <c r="AE157">
         <v>1.18</v>
       </c>
-      <c r="Z157">
-        <v>3.82</v>
-      </c>
-      <c r="AA157">
-        <v>1.75</v>
-      </c>
-      <c r="AB157">
-        <v>2.08</v>
-      </c>
-      <c r="AC157">
-        <v>3.07</v>
-      </c>
-      <c r="AD157">
-        <v>1.36</v>
-      </c>
-      <c r="AE157">
-        <v>1.11</v>
-      </c>
       <c r="AF157">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG157">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK157">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O158">
-        <v>3.43</v>
+        <v>4.2</v>
       </c>
       <c r="P158">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q158">
-        <v>2.81</v>
+        <v>4.46</v>
       </c>
       <c r="R158">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="U158">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="V158">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W158">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z158">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AA158">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AB158">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC158">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AD158">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE158">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF158">
         <v>1.73</v>
       </c>
       <c r="AG158">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK158">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="O160">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P160">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q160">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R160">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S160">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T160">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="U160">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="V160">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W160">
         <v>1.11</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z160">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA160">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB160">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC160">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="AD160">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE160">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF160">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG160">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O161">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="P161">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="Q161">
-        <v>4.46</v>
+        <v>2.81</v>
       </c>
       <c r="R161">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S161">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="U161">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W161">
+        <v>1.08</v>
+      </c>
+      <c r="X161">
+        <v>1.03</v>
+      </c>
+      <c r="Y161">
+        <v>1.25</v>
+      </c>
+      <c r="Z161">
+        <v>3.54</v>
+      </c>
+      <c r="AA161">
+        <v>1.93</v>
+      </c>
+      <c r="AB161">
+        <v>1.88</v>
+      </c>
+      <c r="AC161">
+        <v>3.14</v>
+      </c>
+      <c r="AD161">
+        <v>1.32</v>
+      </c>
+      <c r="AE161">
         <v>1.07</v>
-      </c>
-      <c r="X161">
-        <v>1.02</v>
-      </c>
-      <c r="Y161">
-        <v>1.23</v>
-      </c>
-      <c r="Z161">
-        <v>3.6</v>
-      </c>
-      <c r="AA161">
-        <v>1.67</v>
-      </c>
-      <c r="AB161">
-        <v>2.15</v>
-      </c>
-      <c r="AC161">
-        <v>2.62</v>
-      </c>
-      <c r="AD161">
-        <v>1.38</v>
-      </c>
-      <c r="AE161">
-        <v>1.13</v>
       </c>
       <c r="AF161">
         <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -28360,10 +28360,10 @@
         <v>2.09</v>
       </c>
       <c r="S172">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T172">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U172">
         <v>2.7</v>
@@ -28372,7 +28372,7 @@
         <v>1.39</v>
       </c>
       <c r="W172">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X172">
         <v>1.03</v>
@@ -28381,7 +28381,7 @@
         <v>1.32</v>
       </c>
       <c r="Z172">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="AA172">
         <v>2</v>
@@ -28402,7 +28402,7 @@
         <v>1.91</v>
       </c>
       <c r="AG172">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK172">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -38288,16 +38288,16 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O233">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P233">
         <v>4.1</v>
       </c>
       <c r="Q233">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R233">
         <v>2.28</v>
@@ -38361,7 +38361,7 @@
         <v>1.29</v>
       </c>
       <c r="AK233">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G247">
@@ -40579,55 +40579,55 @@
         <v>0</v>
       </c>
       <c r="Q247">
-        <v>3.08</v>
+        <v>4.25</v>
       </c>
       <c r="R247">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T247">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U247">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="V247">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W247">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z247">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="AA247">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB247">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC247">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AD247">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE247">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG247">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK247">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G248">
@@ -40742,71 +40742,71 @@
         <v>0</v>
       </c>
       <c r="Q248">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S248">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T248">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U248">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V248">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W248">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X248">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z248">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="AA248">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB248">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC248">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AD248">
+        <v>1.31</v>
+      </c>
+      <c r="AE248">
+        <v>1.06</v>
+      </c>
+      <c r="AF248">
+        <v>1.66</v>
+      </c>
+      <c r="AG248">
+        <v>2.07</v>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ248">
         <v>1.38</v>
       </c>
-      <c r="AE248">
-        <v>1.12</v>
-      </c>
-      <c r="AF248">
-        <v>1.6</v>
-      </c>
-      <c r="AG248">
-        <v>2.18</v>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ248">
-        <v>1.26</v>
-      </c>
       <c r="AK248">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -45460,7 +45460,7 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O277">
         <v>2.62</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.61</v>
+        <v>3.2</v>
       </c>
       <c r="O278">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P278">
-        <v>5.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q278">
-        <v>2.3</v>
+        <v>4.11</v>
       </c>
       <c r="R278">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S278">
         <v>1.57</v>
       </c>
       <c r="T278">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U278">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y278">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Z278">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AA278">
-        <v>2.49</v>
+        <v>2.87</v>
       </c>
       <c r="AB278">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC278">
-        <v>4.85</v>
+        <v>5.55</v>
       </c>
       <c r="AD278">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE278">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF278">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="AG278">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK278">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O279">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P279">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q279">
-        <v>4.38</v>
+        <v>2.36</v>
       </c>
       <c r="R279">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="S279">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="T279">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U279">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X279">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="Z279">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AA279">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB279">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC279">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="AD279">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE279">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AG279">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="O280">
+        <v>2.7</v>
+      </c>
+      <c r="P280">
         <v>2.75</v>
-      </c>
-      <c r="P280">
-        <v>2.62</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O296">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P296">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="Q296">
         <v>2.5</v>
@@ -48578,16 +48578,16 @@
         <v>2.2</v>
       </c>
       <c r="U296">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="V296">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W296">
         <v>1.01</v>
       </c>
       <c r="X296">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y296">
         <v>1.53</v>
@@ -48605,16 +48605,16 @@
         <v>5.25</v>
       </c>
       <c r="AD296">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE296">
         <v>1.04</v>
       </c>
       <c r="AF296">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG296">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -49055,10 +49055,10 @@
         <v>1.22</v>
       </c>
       <c r="Q299">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="R299">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="S299">
         <v>1.18</v>
@@ -49094,16 +49094,16 @@
         <v>1.81</v>
       </c>
       <c r="AD299">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE299">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AF299">
         <v>1.73</v>
       </c>
       <c r="AG299">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK299">
         <v>1.02</v>
@@ -49737,7 +49737,7 @@
         <v>2.56</v>
       </c>
       <c r="AA303">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AB303">
         <v>1.55</v>
@@ -49746,7 +49746,7 @@
         <v>4.2</v>
       </c>
       <c r="AD303">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE303">
         <v>1.02</v>
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -51059,7 +51059,7 @@
         <v>2.06</v>
       </c>
       <c r="AG311">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>3.11</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>4.54</v>
+        <v>3.34</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AC49">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD49">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q50">
-        <v>3.11</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="V50">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>3.34</v>
+        <v>4.54</v>
       </c>
       <c r="AA50">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AC50">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.68</v>
+        <v>2.31</v>
       </c>
       <c r="R53">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V53">
+        <v>1.49</v>
+      </c>
+      <c r="W53">
+        <v>1.09</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.16</v>
+      </c>
+      <c r="Z53">
+        <v>4.1</v>
+      </c>
+      <c r="AA53">
+        <v>1.64</v>
+      </c>
+      <c r="AB53">
+        <v>2.08</v>
+      </c>
+      <c r="AC53">
+        <v>2.56</v>
+      </c>
+      <c r="AD53">
         <v>1.4</v>
       </c>
-      <c r="W53">
-        <v>1.06</v>
-      </c>
-      <c r="X53">
-        <v>1</v>
-      </c>
-      <c r="Y53">
-        <v>1.24</v>
-      </c>
-      <c r="Z53">
-        <v>3.34</v>
-      </c>
-      <c r="AA53">
-        <v>1.81</v>
-      </c>
-      <c r="AB53">
-        <v>1.86</v>
-      </c>
-      <c r="AC53">
-        <v>2.97</v>
-      </c>
-      <c r="AD53">
-        <v>1.3</v>
-      </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q54">
-        <v>2.31</v>
+        <v>2.68</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S54">
+        <v>1.33</v>
+      </c>
+      <c r="T54">
+        <v>2.83</v>
+      </c>
+      <c r="U54">
+        <v>2.75</v>
+      </c>
+      <c r="V54">
+        <v>1.4</v>
+      </c>
+      <c r="W54">
+        <v>1.06</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.24</v>
+      </c>
+      <c r="Z54">
+        <v>3.34</v>
+      </c>
+      <c r="AA54">
+        <v>1.81</v>
+      </c>
+      <c r="AB54">
+        <v>1.86</v>
+      </c>
+      <c r="AC54">
+        <v>2.97</v>
+      </c>
+      <c r="AD54">
+        <v>1.3</v>
+      </c>
+      <c r="AE54">
+        <v>1.08</v>
+      </c>
+      <c r="AF54">
+        <v>1.66</v>
+      </c>
+      <c r="AG54">
+        <v>2.05</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
         <v>1.28</v>
       </c>
-      <c r="T54">
-        <v>3.12</v>
-      </c>
-      <c r="U54">
-        <v>2.32</v>
-      </c>
-      <c r="V54">
-        <v>1.49</v>
-      </c>
-      <c r="W54">
-        <v>1.09</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.16</v>
-      </c>
-      <c r="Z54">
-        <v>4.1</v>
-      </c>
-      <c r="AA54">
-        <v>1.64</v>
-      </c>
-      <c r="AB54">
-        <v>2.08</v>
-      </c>
-      <c r="AC54">
-        <v>2.56</v>
-      </c>
-      <c r="AD54">
-        <v>1.4</v>
-      </c>
-      <c r="AE54">
-        <v>1.12</v>
-      </c>
-      <c r="AF54">
-        <v>1.59</v>
-      </c>
-      <c r="AG54">
-        <v>2.17</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.15</v>
-      </c>
       <c r="AK54">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>3.25</v>
+      </c>
+      <c r="O55">
+        <v>3.8</v>
+      </c>
+      <c r="P55">
+        <v>2.05</v>
+      </c>
+      <c r="Q55">
+        <v>3.8</v>
+      </c>
+      <c r="R55">
+        <v>2.32</v>
+      </c>
+      <c r="S55">
+        <v>1.22</v>
+      </c>
+      <c r="T55">
+        <v>3.48</v>
+      </c>
+      <c r="U55">
+        <v>2.1</v>
+      </c>
+      <c r="V55">
+        <v>1.65</v>
+      </c>
+      <c r="W55">
+        <v>1.14</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.13</v>
+      </c>
+      <c r="Z55">
+        <v>5.5</v>
+      </c>
+      <c r="AA55">
+        <v>1.47</v>
+      </c>
+      <c r="AB55">
+        <v>2.45</v>
+      </c>
+      <c r="AC55">
+        <v>2.17</v>
+      </c>
+      <c r="AD55">
+        <v>1.63</v>
+      </c>
+      <c r="AE55">
+        <v>1.23</v>
+      </c>
+      <c r="AF55">
+        <v>1.44</v>
+      </c>
+      <c r="AG55">
         <v>2.5</v>
-      </c>
-      <c r="O55">
-        <v>3.45</v>
-      </c>
-      <c r="P55">
-        <v>2.48</v>
-      </c>
-      <c r="Q55">
-        <v>3.12</v>
-      </c>
-      <c r="R55">
-        <v>2.2</v>
-      </c>
-      <c r="S55">
-        <v>1.35</v>
-      </c>
-      <c r="T55">
-        <v>3</v>
-      </c>
-      <c r="U55">
-        <v>2.7</v>
-      </c>
-      <c r="V55">
-        <v>1.4</v>
-      </c>
-      <c r="W55">
-        <v>1.08</v>
-      </c>
-      <c r="X55">
-        <v>1.04</v>
-      </c>
-      <c r="Y55">
-        <v>1.29</v>
-      </c>
-      <c r="Z55">
-        <v>3.65</v>
-      </c>
-      <c r="AA55">
-        <v>1.93</v>
-      </c>
-      <c r="AB55">
-        <v>1.87</v>
-      </c>
-      <c r="AC55">
-        <v>3.04</v>
-      </c>
-      <c r="AD55">
-        <v>1.29</v>
-      </c>
-      <c r="AE55">
-        <v>1.07</v>
-      </c>
-      <c r="AF55">
-        <v>1.65</v>
-      </c>
-      <c r="AG55">
-        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q56">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="R56">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="U56">
+        <v>2.7</v>
+      </c>
+      <c r="V56">
+        <v>1.4</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.04</v>
+      </c>
+      <c r="Y56">
+        <v>1.29</v>
+      </c>
+      <c r="Z56">
+        <v>3.65</v>
+      </c>
+      <c r="AA56">
+        <v>1.93</v>
+      </c>
+      <c r="AB56">
+        <v>1.87</v>
+      </c>
+      <c r="AC56">
+        <v>3.04</v>
+      </c>
+      <c r="AD56">
+        <v>1.29</v>
+      </c>
+      <c r="AE56">
+        <v>1.07</v>
+      </c>
+      <c r="AF56">
+        <v>1.65</v>
+      </c>
+      <c r="AG56">
         <v>2.1</v>
-      </c>
-      <c r="V56">
-        <v>1.65</v>
-      </c>
-      <c r="W56">
-        <v>1.14</v>
-      </c>
-      <c r="X56">
-        <v>1.02</v>
-      </c>
-      <c r="Y56">
-        <v>1.13</v>
-      </c>
-      <c r="Z56">
-        <v>5.5</v>
-      </c>
-      <c r="AA56">
-        <v>1.47</v>
-      </c>
-      <c r="AB56">
-        <v>2.45</v>
-      </c>
-      <c r="AC56">
-        <v>2.17</v>
-      </c>
-      <c r="AD56">
-        <v>1.63</v>
-      </c>
-      <c r="AE56">
-        <v>1.23</v>
-      </c>
-      <c r="AF56">
-        <v>1.44</v>
-      </c>
-      <c r="AG56">
-        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
+        <v>2.06</v>
+      </c>
+      <c r="O122">
+        <v>3.4</v>
+      </c>
+      <c r="P122">
+        <v>3.15</v>
+      </c>
+      <c r="Q122">
+        <v>2.6</v>
+      </c>
+      <c r="R122">
+        <v>2.15</v>
+      </c>
+      <c r="S122">
+        <v>1.31</v>
+      </c>
+      <c r="T122">
+        <v>2.94</v>
+      </c>
+      <c r="U122">
+        <v>2.51</v>
+      </c>
+      <c r="V122">
+        <v>1.42</v>
+      </c>
+      <c r="W122">
+        <v>1.11</v>
+      </c>
+      <c r="X122">
+        <v>1</v>
+      </c>
+      <c r="Y122">
+        <v>1.2</v>
+      </c>
+      <c r="Z122">
         <v>3.7</v>
       </c>
-      <c r="O122">
-        <v>3.55</v>
-      </c>
-      <c r="P122">
-        <v>1.89</v>
-      </c>
-      <c r="Q122">
-        <v>4.2</v>
-      </c>
-      <c r="R122">
-        <v>2.2</v>
-      </c>
-      <c r="S122">
-        <v>1.33</v>
-      </c>
-      <c r="T122">
-        <v>3.12</v>
-      </c>
-      <c r="U122">
-        <v>2.75</v>
-      </c>
-      <c r="V122">
-        <v>1.4</v>
-      </c>
-      <c r="W122">
-        <v>1.07</v>
-      </c>
-      <c r="X122">
-        <v>1.01</v>
-      </c>
-      <c r="Y122">
-        <v>1.27</v>
-      </c>
-      <c r="Z122">
-        <v>3.52</v>
-      </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF122">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG122">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK122">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P123">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q123">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S123">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U123">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W123">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA123">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC123">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AD123">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE123">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF123">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG123">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK123">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="O133">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="Q133">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R133">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="U133">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="V133">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
         <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>5.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA133">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AB133">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="AC133">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD133">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE133">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG133">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S134">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T134">
         <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="V134">
+        <v>1.37</v>
+      </c>
+      <c r="W134">
+        <v>1.05</v>
+      </c>
+      <c r="X134">
+        <v>1.01</v>
+      </c>
+      <c r="Y134">
+        <v>1.3</v>
+      </c>
+      <c r="Z134">
+        <v>2.97</v>
+      </c>
+      <c r="AA134">
+        <v>2.02</v>
+      </c>
+      <c r="AB134">
+        <v>1.73</v>
+      </c>
+      <c r="AC134">
+        <v>3.48</v>
+      </c>
+      <c r="AD134">
+        <v>1.22</v>
+      </c>
+      <c r="AE134">
+        <v>1.05</v>
+      </c>
+      <c r="AF134">
+        <v>1.79</v>
+      </c>
+      <c r="AG134">
+        <v>1.91</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.4</v>
       </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
-        <v>3.08</v>
-      </c>
-      <c r="AA134">
-        <v>1.97</v>
-      </c>
-      <c r="AB134">
-        <v>1.75</v>
-      </c>
-      <c r="AC134">
-        <v>3.42</v>
-      </c>
-      <c r="AD134">
-        <v>1.3</v>
-      </c>
-      <c r="AE134">
-        <v>1.1</v>
-      </c>
-      <c r="AF134">
-        <v>1.83</v>
-      </c>
-      <c r="AG134">
-        <v>1.9</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.27</v>
-      </c>
       <c r="AK134">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.07</v>
+        <v>1.48</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P135">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="Q135">
+        <v>1.87</v>
+      </c>
+      <c r="R135">
+        <v>2.6</v>
+      </c>
+      <c r="S135">
+        <v>1.19</v>
+      </c>
+      <c r="T135">
+        <v>3.8</v>
+      </c>
+      <c r="U135">
+        <v>2.15</v>
+      </c>
+      <c r="V135">
+        <v>1.67</v>
+      </c>
+      <c r="W135">
+        <v>1.16</v>
+      </c>
+      <c r="X135">
+        <v>1.02</v>
+      </c>
+      <c r="Y135">
+        <v>1.13</v>
+      </c>
+      <c r="Z135">
+        <v>5.62</v>
+      </c>
+      <c r="AA135">
+        <v>1.47</v>
+      </c>
+      <c r="AB135">
+        <v>2.43</v>
+      </c>
+      <c r="AC135">
+        <v>2.2</v>
+      </c>
+      <c r="AD135">
+        <v>1.62</v>
+      </c>
+      <c r="AE135">
+        <v>1.21</v>
+      </c>
+      <c r="AF135">
+        <v>1.62</v>
+      </c>
+      <c r="AG135">
+        <v>2.16</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>1.08</v>
+      </c>
+      <c r="AK135">
         <v>2.5</v>
-      </c>
-      <c r="R135">
-        <v>2.09</v>
-      </c>
-      <c r="S135">
-        <v>1.33</v>
-      </c>
-      <c r="T135">
-        <v>2.97</v>
-      </c>
-      <c r="U135">
-        <v>2.56</v>
-      </c>
-      <c r="V135">
-        <v>1.43</v>
-      </c>
-      <c r="W135">
-        <v>1.07</v>
-      </c>
-      <c r="X135">
-        <v>1.03</v>
-      </c>
-      <c r="Y135">
-        <v>1.26</v>
-      </c>
-      <c r="Z135">
-        <v>3.71</v>
-      </c>
-      <c r="AA135">
-        <v>1.84</v>
-      </c>
-      <c r="AB135">
-        <v>1.86</v>
-      </c>
-      <c r="AC135">
-        <v>3.2</v>
-      </c>
-      <c r="AD135">
-        <v>1.3</v>
-      </c>
-      <c r="AE135">
-        <v>1.07</v>
-      </c>
-      <c r="AF135">
-        <v>1.65</v>
-      </c>
-      <c r="AG135">
-        <v>2.06</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.23</v>
-      </c>
-      <c r="AK135">
-        <v>1.7</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.97</v>
+      </c>
+      <c r="U136">
+        <v>2.56</v>
+      </c>
+      <c r="V136">
         <v>1.43</v>
       </c>
-      <c r="T136">
-        <v>2.88</v>
-      </c>
-      <c r="U136">
-        <v>3.07</v>
-      </c>
-      <c r="V136">
-        <v>1.37</v>
-      </c>
       <c r="W136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
+        <v>1.26</v>
+      </c>
+      <c r="Z136">
+        <v>3.71</v>
+      </c>
+      <c r="AA136">
+        <v>1.84</v>
+      </c>
+      <c r="AB136">
+        <v>1.86</v>
+      </c>
+      <c r="AC136">
+        <v>3.2</v>
+      </c>
+      <c r="AD136">
         <v>1.3</v>
       </c>
-      <c r="Z136">
-        <v>2.97</v>
-      </c>
-      <c r="AA136">
-        <v>2.02</v>
-      </c>
-      <c r="AB136">
-        <v>1.73</v>
-      </c>
-      <c r="AC136">
-        <v>3.48</v>
-      </c>
-      <c r="AD136">
-        <v>1.22</v>
-      </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O137">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q137">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R137">
         <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T137">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U137">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
         <v>1.4</v>
       </c>
       <c r="W137">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA137">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB137">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG137">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK137">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O143">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P143">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q143">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="R143">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S143">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T143">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U143">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="V143">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W143">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X143">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y143">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z143">
-        <v>2.94</v>
+        <v>4.02</v>
       </c>
       <c r="AA143">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AB143">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC143">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="AD143">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE143">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF143">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG143">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK143">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="O144">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P144">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q144">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="R144">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S144">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T144">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U144">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V144">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X144">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z144">
-        <v>4.02</v>
+        <v>3.78</v>
       </c>
       <c r="AA144">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB144">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AC144">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AD144">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE144">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF144">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG144">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="AK144">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="O145">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q145">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R145">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="S145">
+        <v>1.36</v>
+      </c>
+      <c r="T145">
+        <v>3.06</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>1.4</v>
+      </c>
+      <c r="W145">
+        <v>1.08</v>
+      </c>
+      <c r="X145">
+        <v>1.04</v>
+      </c>
+      <c r="Y145">
         <v>1.29</v>
       </c>
-      <c r="T145">
-        <v>3.4</v>
-      </c>
-      <c r="U145">
-        <v>2.47</v>
-      </c>
-      <c r="V145">
-        <v>1.52</v>
-      </c>
-      <c r="W145">
-        <v>1.1</v>
-      </c>
-      <c r="X145">
-        <v>1.02</v>
-      </c>
-      <c r="Y145">
-        <v>1.16</v>
-      </c>
       <c r="Z145">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="AA145">
+        <v>1.84</v>
+      </c>
+      <c r="AB145">
+        <v>1.83</v>
+      </c>
+      <c r="AC145">
+        <v>2.99</v>
+      </c>
+      <c r="AD145">
+        <v>1.29</v>
+      </c>
+      <c r="AE145">
+        <v>1.07</v>
+      </c>
+      <c r="AF145">
         <v>1.65</v>
       </c>
-      <c r="AB145">
-        <v>2.15</v>
-      </c>
-      <c r="AC145">
-        <v>2.49</v>
-      </c>
-      <c r="AD145">
-        <v>1.42</v>
-      </c>
-      <c r="AE145">
-        <v>1.13</v>
-      </c>
-      <c r="AF145">
-        <v>1.57</v>
-      </c>
       <c r="AG145">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="O146">
+        <v>3.46</v>
+      </c>
+      <c r="P146">
+        <v>2.3</v>
+      </c>
+      <c r="Q146">
         <v>3.5</v>
       </c>
-      <c r="P146">
-        <v>2.45</v>
-      </c>
-      <c r="Q146">
+      <c r="R146">
+        <v>2.4</v>
+      </c>
+      <c r="S146">
+        <v>1.29</v>
+      </c>
+      <c r="T146">
         <v>3.4</v>
       </c>
-      <c r="R146">
-        <v>2.09</v>
-      </c>
-      <c r="S146">
+      <c r="U146">
+        <v>2.47</v>
+      </c>
+      <c r="V146">
+        <v>1.52</v>
+      </c>
+      <c r="W146">
+        <v>1.1</v>
+      </c>
+      <c r="X146">
+        <v>1.02</v>
+      </c>
+      <c r="Y146">
+        <v>1.16</v>
+      </c>
+      <c r="Z146">
+        <v>4.15</v>
+      </c>
+      <c r="AA146">
+        <v>1.65</v>
+      </c>
+      <c r="AB146">
+        <v>2.15</v>
+      </c>
+      <c r="AC146">
+        <v>2.49</v>
+      </c>
+      <c r="AD146">
+        <v>1.42</v>
+      </c>
+      <c r="AE146">
+        <v>1.13</v>
+      </c>
+      <c r="AF146">
+        <v>1.57</v>
+      </c>
+      <c r="AG146">
+        <v>2.31</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
+        <v>1.58</v>
+      </c>
+      <c r="AK146">
         <v>1.36</v>
-      </c>
-      <c r="T146">
-        <v>3.06</v>
-      </c>
-      <c r="U146">
-        <v>2.75</v>
-      </c>
-      <c r="V146">
-        <v>1.4</v>
-      </c>
-      <c r="W146">
-        <v>1.08</v>
-      </c>
-      <c r="X146">
-        <v>1.04</v>
-      </c>
-      <c r="Y146">
-        <v>1.29</v>
-      </c>
-      <c r="Z146">
-        <v>3.15</v>
-      </c>
-      <c r="AA146">
-        <v>1.84</v>
-      </c>
-      <c r="AB146">
-        <v>1.83</v>
-      </c>
-      <c r="AC146">
-        <v>2.99</v>
-      </c>
-      <c r="AD146">
-        <v>1.29</v>
-      </c>
-      <c r="AE146">
-        <v>1.07</v>
-      </c>
-      <c r="AF146">
-        <v>1.65</v>
-      </c>
-      <c r="AG146">
-        <v>2.05</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.25</v>
-      </c>
-      <c r="AK146">
-        <v>1.37</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="O147">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q147">
-        <v>2.23</v>
+        <v>2.68</v>
       </c>
       <c r="R147">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S147">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T147">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U147">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="V147">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W147">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X147">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y147">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z147">
-        <v>3.78</v>
+        <v>2.94</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB147">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AC147">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AD147">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE147">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF147">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG147">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O158">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="P158">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="Q158">
-        <v>4.46</v>
+        <v>2.81</v>
       </c>
       <c r="R158">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S158">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="U158">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V158">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W158">
+        <v>1.08</v>
+      </c>
+      <c r="X158">
+        <v>1.03</v>
+      </c>
+      <c r="Y158">
+        <v>1.25</v>
+      </c>
+      <c r="Z158">
+        <v>3.54</v>
+      </c>
+      <c r="AA158">
+        <v>1.93</v>
+      </c>
+      <c r="AB158">
+        <v>1.88</v>
+      </c>
+      <c r="AC158">
+        <v>3.14</v>
+      </c>
+      <c r="AD158">
+        <v>1.32</v>
+      </c>
+      <c r="AE158">
         <v>1.07</v>
-      </c>
-      <c r="X158">
-        <v>1.02</v>
-      </c>
-      <c r="Y158">
-        <v>1.23</v>
-      </c>
-      <c r="Z158">
-        <v>3.6</v>
-      </c>
-      <c r="AA158">
-        <v>1.67</v>
-      </c>
-      <c r="AB158">
-        <v>2.15</v>
-      </c>
-      <c r="AC158">
-        <v>2.62</v>
-      </c>
-      <c r="AD158">
-        <v>1.38</v>
-      </c>
-      <c r="AE158">
-        <v>1.13</v>
       </c>
       <c r="AF158">
         <v>1.73</v>
       </c>
       <c r="AG158">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK158">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="O159">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="P159">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="Q159">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R159">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S159">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U159">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
+        <v>1.23</v>
+      </c>
+      <c r="Z159">
+        <v>3.6</v>
+      </c>
+      <c r="AA159">
+        <v>1.67</v>
+      </c>
+      <c r="AB159">
+        <v>2.15</v>
+      </c>
+      <c r="AC159">
+        <v>2.62</v>
+      </c>
+      <c r="AD159">
+        <v>1.38</v>
+      </c>
+      <c r="AE159">
+        <v>1.13</v>
+      </c>
+      <c r="AF159">
+        <v>1.73</v>
+      </c>
+      <c r="AG159">
+        <v>2.1</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.15</v>
       </c>
-      <c r="Z159">
-        <v>4.2</v>
-      </c>
-      <c r="AA159">
-        <v>1.61</v>
-      </c>
-      <c r="AB159">
-        <v>2.23</v>
-      </c>
-      <c r="AC159">
-        <v>2.42</v>
-      </c>
-      <c r="AD159">
-        <v>1.44</v>
-      </c>
-      <c r="AE159">
-        <v>1.17</v>
-      </c>
-      <c r="AF159">
-        <v>1.51</v>
-      </c>
-      <c r="AG159">
-        <v>2.4</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.22</v>
-      </c>
       <c r="AK159">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="O160">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P160">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Q160">
         <v>3</v>
       </c>
       <c r="R160">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S160">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T160">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U160">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V160">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z160">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA160">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB160">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AC160">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="AD160">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE160">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF160">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG160">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="O161">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P161">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q161">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="R161">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S161">
+        <v>1.33</v>
+      </c>
+      <c r="T161">
+        <v>3.14</v>
+      </c>
+      <c r="U161">
+        <v>2.7</v>
+      </c>
+      <c r="V161">
+        <v>1.43</v>
+      </c>
+      <c r="W161">
+        <v>1.11</v>
+      </c>
+      <c r="X161">
+        <v>1.02</v>
+      </c>
+      <c r="Y161">
+        <v>1.18</v>
+      </c>
+      <c r="Z161">
+        <v>3.82</v>
+      </c>
+      <c r="AA161">
+        <v>1.75</v>
+      </c>
+      <c r="AB161">
+        <v>2.08</v>
+      </c>
+      <c r="AC161">
+        <v>3.07</v>
+      </c>
+      <c r="AD161">
         <v>1.36</v>
       </c>
-      <c r="T161">
-        <v>2.83</v>
-      </c>
-      <c r="U161">
-        <v>2.88</v>
-      </c>
-      <c r="V161">
-        <v>1.4</v>
-      </c>
-      <c r="W161">
-        <v>1.08</v>
-      </c>
-      <c r="X161">
-        <v>1.03</v>
-      </c>
-      <c r="Y161">
-        <v>1.25</v>
-      </c>
-      <c r="Z161">
-        <v>3.54</v>
-      </c>
-      <c r="AA161">
-        <v>1.93</v>
-      </c>
-      <c r="AB161">
-        <v>1.88</v>
-      </c>
-      <c r="AC161">
-        <v>3.14</v>
-      </c>
-      <c r="AD161">
-        <v>1.32</v>
-      </c>
       <c r="AE161">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK161">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -30962,7 +30962,7 @@
         <v>4.8</v>
       </c>
       <c r="Q188">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R188">
         <v>2.4</v>
@@ -31010,7 +31010,7 @@
         <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK188">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31125,7 +31125,7 @@
         <v>6.2</v>
       </c>
       <c r="Q189">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R189">
         <v>2.27</v>
@@ -31149,7 +31149,7 @@
         <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z189">
         <v>4.05</v>
@@ -31167,13 +31167,13 @@
         <v>1.39</v>
       </c>
       <c r="AE189">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF189">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG189">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G247">
@@ -40579,71 +40579,71 @@
         <v>0</v>
       </c>
       <c r="Q247">
-        <v>4.25</v>
+        <v>3.08</v>
       </c>
       <c r="R247">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S247">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T247">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="U247">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="V247">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W247">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X247">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z247">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="AA247">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB247">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC247">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AD247">
+        <v>1.31</v>
+      </c>
+      <c r="AE247">
+        <v>1.06</v>
+      </c>
+      <c r="AF247">
+        <v>1.66</v>
+      </c>
+      <c r="AG247">
+        <v>2.07</v>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ247">
         <v>1.38</v>
       </c>
-      <c r="AE247">
-        <v>1.12</v>
-      </c>
-      <c r="AF247">
-        <v>1.6</v>
-      </c>
-      <c r="AG247">
-        <v>2.18</v>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ247">
-        <v>1.26</v>
-      </c>
       <c r="AK247">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q248">
-        <v>3.08</v>
+        <v>4.25</v>
       </c>
       <c r="R248">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T248">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U248">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="V248">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W248">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X248">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z248">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="AA248">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB248">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC248">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AD248">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE248">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF248">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG248">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK248">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O278">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P278">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q278">
-        <v>4.11</v>
+        <v>2.36</v>
       </c>
       <c r="R278">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S278">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T278">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="U278">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X278">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y278">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Z278">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA278">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB278">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC278">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AD278">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE278">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF278">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AG278">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O279">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P279">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q279">
-        <v>2.36</v>
+        <v>4.11</v>
       </c>
       <c r="R279">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S279">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T279">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y279">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Z279">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AA279">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
+        <v>1.35</v>
+      </c>
+      <c r="AC279">
+        <v>5.55</v>
+      </c>
+      <c r="AD279">
+        <v>1.08</v>
+      </c>
+      <c r="AE279">
+        <v>1.03</v>
+      </c>
+      <c r="AF279">
+        <v>2.23</v>
+      </c>
+      <c r="AG279">
+        <v>1.57</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.44</v>
       </c>
-      <c r="AC279">
-        <v>4.85</v>
-      </c>
-      <c r="AD279">
-        <v>1.11</v>
-      </c>
-      <c r="AE279">
-        <v>1.01</v>
-      </c>
-      <c r="AF279">
-        <v>2.4</v>
-      </c>
-      <c r="AG279">
-        <v>1.48</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.25</v>
-      </c>
       <c r="AK279">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -48433,10 +48433,10 @@
         <v>0</v>
       </c>
       <c r="AA295">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB295">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC295">
         <v>0</v>
@@ -49707,40 +49707,40 @@
         <v>3</v>
       </c>
       <c r="Q303">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="R303">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="S303">
         <v>1.49</v>
       </c>
       <c r="T303">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="U303">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V303">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W303">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X303">
         <v>1.05</v>
       </c>
       <c r="Y303">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z303">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA303">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB303">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC303">
         <v>4.2</v>
@@ -49755,7 +49755,7 @@
         <v>1.95</v>
       </c>
       <c r="AG303">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49771,7 +49771,7 @@
         <v>1.33</v>
       </c>
       <c r="AK303">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49870,19 +49870,19 @@
         <v>3.1</v>
       </c>
       <c r="Q304">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="R304">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="S304">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T304">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="U304">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V304">
         <v>1.36</v>
@@ -49891,31 +49891,31 @@
         <v>1.06</v>
       </c>
       <c r="X304">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z304">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA304">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB304">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC304">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AD304">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE304">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF304">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG304">
         <v>2</v>
@@ -50685,7 +50685,7 @@
         <v>2.5</v>
       </c>
       <c r="Q309">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="R309">
         <v>2.2</v>
@@ -50715,13 +50715,13 @@
         <v>3.34</v>
       </c>
       <c r="AA309">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB309">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC309">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD309">
         <v>1.3</v>
@@ -51047,7 +51047,7 @@
         <v>1.45</v>
       </c>
       <c r="AC311">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD311">
         <v>1.13</v>
@@ -51385,7 +51385,7 @@
         <v>1.57</v>
       </c>
       <c r="AG313">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51663,19 +51663,19 @@
         <v>2.8</v>
       </c>
       <c r="Q315">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R315">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S315">
         <v>1.33</v>
       </c>
       <c r="T315">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U315">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="V315">
         <v>1.44</v>
@@ -51684,7 +51684,7 @@
         <v>1.08</v>
       </c>
       <c r="X315">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y315">
         <v>1.21</v>
@@ -51693,25 +51693,25 @@
         <v>3.58</v>
       </c>
       <c r="AA315">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB315">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC315">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD315">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE315">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF315">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG315">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="O316">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="P316">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q316">
         <v>3.02</v>
@@ -51844,7 +51844,7 @@
         <v>1.25</v>
       </c>
       <c r="W316">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X316">
         <v>1.05</v>
@@ -51853,7 +51853,7 @@
         <v>1.51</v>
       </c>
       <c r="Z316">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AA316">
         <v>2.6</v>
@@ -51871,7 +51871,7 @@
         <v>1</v>
       </c>
       <c r="AF316">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG316">
         <v>1.66</v>
@@ -52010,7 +52010,7 @@
         <v>1.09</v>
       </c>
       <c r="X317">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y317">
         <v>1.18</v>
@@ -52034,10 +52034,10 @@
         <v>1.13</v>
       </c>
       <c r="AF317">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG317">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>1</v>
       </c>
       <c r="Y318">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z318">
         <v>3.5</v>
@@ -52197,7 +52197,7 @@
         <v>1.13</v>
       </c>
       <c r="AF318">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG318">
         <v>1.79</v>
@@ -52315,16 +52315,16 @@
         <v>6.65</v>
       </c>
       <c r="Q319">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R319">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S319">
         <v>1.25</v>
       </c>
       <c r="T319">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U319">
         <v>2.3</v>
@@ -52336,7 +52336,7 @@
         <v>1.09</v>
       </c>
       <c r="X319">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y319">
         <v>1.14</v>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK319">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52484,7 +52484,7 @@
         <v>2.63</v>
       </c>
       <c r="S320">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T320">
         <v>3.85</v>
@@ -52493,7 +52493,7 @@
         <v>2.2</v>
       </c>
       <c r="V320">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="W320">
         <v>1.17</v>
@@ -53296,7 +53296,7 @@
         <v>2.5</v>
       </c>
       <c r="R325">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S325">
         <v>1.43</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK325">
         <v>1.78</v>
@@ -54968,10 +54968,10 @@
         <v>1.16</v>
       </c>
       <c r="AF335">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG335">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -55575,10 +55575,10 @@
         <v>2.87</v>
       </c>
       <c r="Q339">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R339">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S339">
         <v>1.33</v>
@@ -55605,7 +55605,7 @@
         <v>3.92</v>
       </c>
       <c r="AA339">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB339">
         <v>2.09</v>
@@ -55620,7 +55620,7 @@
         <v>1.16</v>
       </c>
       <c r="AF339">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG339">
         <v>2.25</v>
@@ -55729,19 +55729,19 @@
         </is>
       </c>
       <c r="N340">
+        <v>2.14</v>
+      </c>
+      <c r="O340">
+        <v>3.45</v>
+      </c>
+      <c r="P340">
+        <v>3.1</v>
+      </c>
+      <c r="Q340">
+        <v>2.58</v>
+      </c>
+      <c r="R340">
         <v>2.21</v>
-      </c>
-      <c r="O340">
-        <v>3.5</v>
-      </c>
-      <c r="P340">
-        <v>2.9</v>
-      </c>
-      <c r="Q340">
-        <v>2.7</v>
-      </c>
-      <c r="R340">
-        <v>2.23</v>
       </c>
       <c r="S340">
         <v>1.3</v>
@@ -55783,10 +55783,10 @@
         <v>1.1</v>
       </c>
       <c r="AF340">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG340">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK340">
         <v>1.62</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1308,7 +1308,7 @@
         <v>2.54</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1341,10 +1341,10 @@
         <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z15">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA15">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="AB15">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC15">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="O16">
-        <v>3.27</v>
+        <v>3.65</v>
       </c>
       <c r="P16">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
         <v>1.07</v>
@@ -2950,31 +2950,31 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>2.97</v>
+        <v>4.25</v>
       </c>
       <c r="AA16">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>3.42</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>3.1</v>
+      </c>
+      <c r="P17">
+        <v>3.3</v>
+      </c>
+      <c r="Q17">
+        <v>2.7</v>
+      </c>
+      <c r="R17">
+        <v>1.98</v>
+      </c>
+      <c r="S17">
+        <v>1.42</v>
+      </c>
+      <c r="T17">
         <v>2.51</v>
       </c>
-      <c r="O17">
-        <v>3.65</v>
-      </c>
-      <c r="P17">
-        <v>2.2</v>
-      </c>
-      <c r="Q17">
-        <v>3.28</v>
-      </c>
-      <c r="R17">
-        <v>2.19</v>
-      </c>
-      <c r="S17">
-        <v>1.28</v>
-      </c>
-      <c r="T17">
-        <v>3.12</v>
-      </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>3.78</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="AG17">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="R18">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="U18">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z18">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AA18">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AB18">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AD18">
         <v>1.19</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK18">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P26">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>1.99</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="P27">
         <v>3.15</v>
@@ -4725,10 +4725,10 @@
         <v>2.29</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U27">
         <v>2.2</v>
@@ -4740,7 +4740,7 @@
         <v>1.14</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.13</v>
@@ -5045,16 +5045,16 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
         <v>3.12</v>
@@ -5063,7 +5063,7 @@
         <v>1.28</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
         <v>1.03</v>
@@ -5078,10 +5078,10 @@
         <v>2.17</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC29">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AD29">
         <v>1.17</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7173,7 +7173,7 @@
         <v>1.45</v>
       </c>
       <c r="T42">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U42">
         <v>3.2</v>
@@ -7209,7 +7209,7 @@
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG42">
         <v>1.79</v>
@@ -7659,7 +7659,7 @@
         <v>1.95</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
         <v>3</v>
@@ -7680,28 +7680,28 @@
         <v>1.26</v>
       </c>
       <c r="Z45">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB45">
         <v>1.79</v>
       </c>
       <c r="AC45">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE45">
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AK45">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
-        <v>3.11</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>3.34</v>
+        <v>4.54</v>
       </c>
       <c r="AA49">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AC49">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AD49">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>3.11</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S50">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="U50">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="V50">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z50">
-        <v>4.54</v>
+        <v>3.34</v>
       </c>
       <c r="AA50">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD50">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q55">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="R55">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="U55">
+        <v>2.7</v>
+      </c>
+      <c r="V55">
+        <v>1.4</v>
+      </c>
+      <c r="W55">
+        <v>1.08</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
+        <v>3.65</v>
+      </c>
+      <c r="AA55">
+        <v>1.93</v>
+      </c>
+      <c r="AB55">
+        <v>1.87</v>
+      </c>
+      <c r="AC55">
+        <v>3.04</v>
+      </c>
+      <c r="AD55">
+        <v>1.29</v>
+      </c>
+      <c r="AE55">
+        <v>1.07</v>
+      </c>
+      <c r="AF55">
+        <v>1.65</v>
+      </c>
+      <c r="AG55">
         <v>2.1</v>
-      </c>
-      <c r="V55">
-        <v>1.65</v>
-      </c>
-      <c r="W55">
-        <v>1.14</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.13</v>
-      </c>
-      <c r="Z55">
-        <v>5.5</v>
-      </c>
-      <c r="AA55">
-        <v>1.47</v>
-      </c>
-      <c r="AB55">
-        <v>2.45</v>
-      </c>
-      <c r="AC55">
-        <v>2.17</v>
-      </c>
-      <c r="AD55">
-        <v>1.63</v>
-      </c>
-      <c r="AE55">
-        <v>1.23</v>
-      </c>
-      <c r="AF55">
-        <v>1.44</v>
-      </c>
-      <c r="AG55">
-        <v>2.5</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
+        <v>3.25</v>
+      </c>
+      <c r="O56">
+        <v>3.8</v>
+      </c>
+      <c r="P56">
+        <v>2.05</v>
+      </c>
+      <c r="Q56">
+        <v>3.8</v>
+      </c>
+      <c r="R56">
+        <v>2.32</v>
+      </c>
+      <c r="S56">
+        <v>1.22</v>
+      </c>
+      <c r="T56">
+        <v>3.48</v>
+      </c>
+      <c r="U56">
+        <v>2.1</v>
+      </c>
+      <c r="V56">
+        <v>1.65</v>
+      </c>
+      <c r="W56">
+        <v>1.14</v>
+      </c>
+      <c r="X56">
+        <v>1.02</v>
+      </c>
+      <c r="Y56">
+        <v>1.13</v>
+      </c>
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.47</v>
+      </c>
+      <c r="AB56">
+        <v>2.45</v>
+      </c>
+      <c r="AC56">
+        <v>2.17</v>
+      </c>
+      <c r="AD56">
+        <v>1.63</v>
+      </c>
+      <c r="AE56">
+        <v>1.23</v>
+      </c>
+      <c r="AF56">
+        <v>1.44</v>
+      </c>
+      <c r="AG56">
         <v>2.5</v>
-      </c>
-      <c r="O56">
-        <v>3.45</v>
-      </c>
-      <c r="P56">
-        <v>2.48</v>
-      </c>
-      <c r="Q56">
-        <v>3.12</v>
-      </c>
-      <c r="R56">
-        <v>2.2</v>
-      </c>
-      <c r="S56">
-        <v>1.35</v>
-      </c>
-      <c r="T56">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>2.7</v>
-      </c>
-      <c r="V56">
-        <v>1.4</v>
-      </c>
-      <c r="W56">
-        <v>1.08</v>
-      </c>
-      <c r="X56">
-        <v>1.04</v>
-      </c>
-      <c r="Y56">
-        <v>1.29</v>
-      </c>
-      <c r="Z56">
-        <v>3.65</v>
-      </c>
-      <c r="AA56">
-        <v>1.93</v>
-      </c>
-      <c r="AB56">
-        <v>1.87</v>
-      </c>
-      <c r="AC56">
-        <v>3.04</v>
-      </c>
-      <c r="AD56">
-        <v>1.29</v>
-      </c>
-      <c r="AE56">
-        <v>1.07</v>
-      </c>
-      <c r="AF56">
-        <v>1.65</v>
-      </c>
-      <c r="AG56">
-        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9944,25 +9944,25 @@
         <v>1.11</v>
       </c>
       <c r="T59">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="U59">
         <v>1.73</v>
       </c>
       <c r="V59">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W59">
         <v>1.29</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA59">
         <v>1.22</v>
@@ -9971,16 +9971,16 @@
         <v>3.5</v>
       </c>
       <c r="AC59">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AD59">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE59">
         <v>1.47</v>
       </c>
       <c r="AF59">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG59">
         <v>1.5</v>
@@ -10101,7 +10101,7 @@
         <v>2.4</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S60">
         <v>1.39</v>
@@ -10128,7 +10128,7 @@
         <v>2.88</v>
       </c>
       <c r="AA60">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB60">
         <v>1.67</v>
@@ -10143,10 +10143,10 @@
         <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG60">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -12208,25 +12208,25 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="O73">
         <v>3.1</v>
       </c>
       <c r="P73">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q73">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R73">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S73">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T73">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="U73">
         <v>3</v>
@@ -12253,19 +12253,19 @@
         <v>1.67</v>
       </c>
       <c r="AC73">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AD73">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE73">
         <v>1.02</v>
       </c>
       <c r="AF73">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG73">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O74">
         <v>3</v>
       </c>
       <c r="P74">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q74">
         <v>3.7</v>
@@ -12428,7 +12428,7 @@
         <v>1.86</v>
       </c>
       <c r="AG74">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="O77">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q77">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="R77">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W77">
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z77">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB77">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AC77">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="AD77">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE77">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P78">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
       <c r="R78">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="U78">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V78">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W78">
         <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AA78">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AB78">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AC78">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AD78">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG78">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK78">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14185,10 +14185,10 @@
         <v>3.25</v>
       </c>
       <c r="U85">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V85">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W85">
         <v>1.11</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O86">
         <v>3.2</v>
       </c>
       <c r="P86">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q86">
         <v>2.45</v>
@@ -14342,16 +14342,16 @@
         <v>2.15</v>
       </c>
       <c r="S86">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T86">
         <v>2.8</v>
       </c>
       <c r="U86">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="V86">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
         <v>1.06</v>
@@ -14363,7 +14363,7 @@
         <v>1.3</v>
       </c>
       <c r="Z86">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA86">
         <v>2.09</v>
@@ -14372,35 +14372,35 @@
         <v>1.73</v>
       </c>
       <c r="AC86">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD86">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE86">
         <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG86">
+        <v>1.89</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.28</v>
+      </c>
+      <c r="AK86">
         <v>1.9</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.29</v>
-      </c>
-      <c r="AK86">
-        <v>1.79</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14517,10 +14517,10 @@
         <v>1.47</v>
       </c>
       <c r="W87">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.22</v>
@@ -14840,7 +14840,7 @@
         <v>3.5</v>
       </c>
       <c r="V89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W89">
         <v>1.04</v>
@@ -14858,7 +14858,7 @@
         <v>2.46</v>
       </c>
       <c r="AB89">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC89">
         <v>4.85</v>
@@ -16845,7 +16845,7 @@
         <v>1.37</v>
       </c>
       <c r="AK101">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16983,7 +16983,7 @@
         <v>3.2</v>
       </c>
       <c r="AD102">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE102">
         <v>1.06</v>
@@ -16992,7 +16992,7 @@
         <v>1.83</v>
       </c>
       <c r="AG102">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17303,7 +17303,7 @@
         <v>1.78</v>
       </c>
       <c r="AB104">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC104">
         <v>2.7</v>
@@ -17334,7 +17334,7 @@
         <v>1.24</v>
       </c>
       <c r="AK104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>3.86</v>
       </c>
       <c r="AA105">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB105">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC105">
         <v>2.74</v>
@@ -17478,10 +17478,10 @@
         <v>1.14</v>
       </c>
       <c r="AF105">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG105">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -18085,10 +18085,10 @@
         <v>1.64</v>
       </c>
       <c r="Q109">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="R109">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S109">
         <v>1.33</v>
@@ -18097,7 +18097,7 @@
         <v>2.97</v>
       </c>
       <c r="U109">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="V109">
         <v>1.4</v>
@@ -18115,10 +18115,10 @@
         <v>3.34</v>
       </c>
       <c r="AA109">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB109">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC109">
         <v>3.14</v>
@@ -18260,7 +18260,7 @@
         <v>4.1</v>
       </c>
       <c r="U110">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="V110">
         <v>1.77</v>
@@ -18272,10 +18272,10 @@
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z110">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA110">
         <v>1.39</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O111">
         <v>3.8</v>
@@ -18414,7 +18414,7 @@
         <v>2.78</v>
       </c>
       <c r="R111">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S111">
         <v>1.22</v>
@@ -18447,7 +18447,7 @@
         <v>2.78</v>
       </c>
       <c r="AC111">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD111">
         <v>1.74</v>
@@ -18752,7 +18752,7 @@
         <v>2.29</v>
       </c>
       <c r="V113">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W113">
         <v>1.14</v>
@@ -18764,7 +18764,7 @@
         <v>1.12</v>
       </c>
       <c r="Z113">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA113">
         <v>1.56</v>
@@ -18782,7 +18782,7 @@
         <v>1.2</v>
       </c>
       <c r="AF113">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG113">
         <v>2.5</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P122">
-        <v>3.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q122">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S122">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U122">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA122">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.78</v>
+        <v>3.04</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG122">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
+        <v>2.06</v>
+      </c>
+      <c r="O123">
+        <v>3.4</v>
+      </c>
+      <c r="P123">
+        <v>3.15</v>
+      </c>
+      <c r="Q123">
+        <v>2.6</v>
+      </c>
+      <c r="R123">
+        <v>2.15</v>
+      </c>
+      <c r="S123">
+        <v>1.31</v>
+      </c>
+      <c r="T123">
+        <v>2.94</v>
+      </c>
+      <c r="U123">
+        <v>2.51</v>
+      </c>
+      <c r="V123">
+        <v>1.42</v>
+      </c>
+      <c r="W123">
+        <v>1.11</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>1.2</v>
+      </c>
+      <c r="Z123">
         <v>3.7</v>
       </c>
-      <c r="O123">
-        <v>3.55</v>
-      </c>
-      <c r="P123">
-        <v>1.89</v>
-      </c>
-      <c r="Q123">
-        <v>4.2</v>
-      </c>
-      <c r="R123">
-        <v>2.2</v>
-      </c>
-      <c r="S123">
-        <v>1.33</v>
-      </c>
-      <c r="T123">
-        <v>3.12</v>
-      </c>
-      <c r="U123">
-        <v>2.75</v>
-      </c>
-      <c r="V123">
-        <v>1.4</v>
-      </c>
-      <c r="W123">
-        <v>1.07</v>
-      </c>
-      <c r="X123">
-        <v>1.01</v>
-      </c>
-      <c r="Y123">
-        <v>1.27</v>
-      </c>
-      <c r="Z123">
-        <v>3.52</v>
-      </c>
       <c r="AA123">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB123">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC123">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AD123">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE123">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG123">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK123">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q133">
+        <v>3</v>
+      </c>
+      <c r="R133">
+        <v>2</v>
+      </c>
+      <c r="S133">
+        <v>1.43</v>
+      </c>
+      <c r="T133">
         <v>2.88</v>
       </c>
-      <c r="R133">
-        <v>2.1</v>
-      </c>
-      <c r="S133">
+      <c r="U133">
+        <v>3.07</v>
+      </c>
+      <c r="V133">
         <v>1.37</v>
       </c>
-      <c r="T133">
-        <v>2.78</v>
-      </c>
-      <c r="U133">
-        <v>2.67</v>
-      </c>
-      <c r="V133">
-        <v>1.4</v>
-      </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA133">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB133">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC133">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE133">
         <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG133">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK133">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P134">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="Q134">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="R134">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="S134">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="T134">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U134">
-        <v>3.07</v>
+        <v>2.15</v>
       </c>
       <c r="V134">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="W134">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X134">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
-        <v>2.97</v>
+        <v>5.62</v>
       </c>
       <c r="AA134">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AB134">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="AC134">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="AD134">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AF134">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG134">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK134">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="O135">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="Q135">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R135">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="T135">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="U135">
-        <v>2.15</v>
+        <v>2.67</v>
       </c>
       <c r="V135">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
         <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z135">
-        <v>5.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA135">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AB135">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="AC135">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD135">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE135">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG135">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="O144">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q144">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S144">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="U144">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V144">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W144">
+        <v>1.08</v>
+      </c>
+      <c r="X144">
+        <v>1.04</v>
+      </c>
+      <c r="Y144">
+        <v>1.29</v>
+      </c>
+      <c r="Z144">
+        <v>3.15</v>
+      </c>
+      <c r="AA144">
+        <v>1.84</v>
+      </c>
+      <c r="AB144">
+        <v>1.83</v>
+      </c>
+      <c r="AC144">
+        <v>2.99</v>
+      </c>
+      <c r="AD144">
+        <v>1.29</v>
+      </c>
+      <c r="AE144">
         <v>1.07</v>
       </c>
-      <c r="X144">
-        <v>1.02</v>
-      </c>
-      <c r="Y144">
-        <v>1.19</v>
-      </c>
-      <c r="Z144">
-        <v>3.78</v>
-      </c>
-      <c r="AA144">
-        <v>1.8</v>
-      </c>
-      <c r="AB144">
-        <v>1.99</v>
-      </c>
-      <c r="AC144">
-        <v>2.83</v>
-      </c>
-      <c r="AD144">
+      <c r="AF144">
+        <v>1.65</v>
+      </c>
+      <c r="AG144">
+        <v>2.05</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>1.25</v>
+      </c>
+      <c r="AK144">
         <v>1.37</v>
-      </c>
-      <c r="AE144">
-        <v>1.15</v>
-      </c>
-      <c r="AF144">
-        <v>1.7</v>
-      </c>
-      <c r="AG144">
-        <v>2</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.14</v>
-      </c>
-      <c r="AK144">
-        <v>2.11</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P145">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q145">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="R145">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S145">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T145">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="U145">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="V145">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
+        <v>1.05</v>
+      </c>
+      <c r="Y145">
+        <v>1.33</v>
+      </c>
+      <c r="Z145">
+        <v>2.94</v>
+      </c>
+      <c r="AA145">
+        <v>2.05</v>
+      </c>
+      <c r="AB145">
+        <v>1.76</v>
+      </c>
+      <c r="AC145">
+        <v>3.42</v>
+      </c>
+      <c r="AD145">
+        <v>1.23</v>
+      </c>
+      <c r="AE145">
         <v>1.04</v>
       </c>
-      <c r="Y145">
-        <v>1.29</v>
-      </c>
-      <c r="Z145">
-        <v>3.15</v>
-      </c>
-      <c r="AA145">
-        <v>1.84</v>
-      </c>
-      <c r="AB145">
-        <v>1.83</v>
-      </c>
-      <c r="AC145">
-        <v>2.99</v>
-      </c>
-      <c r="AD145">
-        <v>1.29</v>
-      </c>
-      <c r="AE145">
-        <v>1.07</v>
-      </c>
       <c r="AF145">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG145">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P147">
+        <v>4.5</v>
+      </c>
+      <c r="Q147">
+        <v>2.23</v>
+      </c>
+      <c r="R147">
+        <v>2.25</v>
+      </c>
+      <c r="S147">
+        <v>1.31</v>
+      </c>
+      <c r="T147">
         <v>3.3</v>
       </c>
-      <c r="Q147">
-        <v>2.68</v>
-      </c>
-      <c r="R147">
-        <v>2.05</v>
-      </c>
-      <c r="S147">
-        <v>1.4</v>
-      </c>
-      <c r="T147">
-        <v>2.88</v>
-      </c>
       <c r="U147">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="V147">
+        <v>1.45</v>
+      </c>
+      <c r="W147">
+        <v>1.07</v>
+      </c>
+      <c r="X147">
+        <v>1.02</v>
+      </c>
+      <c r="Y147">
+        <v>1.19</v>
+      </c>
+      <c r="Z147">
+        <v>3.78</v>
+      </c>
+      <c r="AA147">
+        <v>1.8</v>
+      </c>
+      <c r="AB147">
+        <v>1.99</v>
+      </c>
+      <c r="AC147">
+        <v>2.83</v>
+      </c>
+      <c r="AD147">
         <v>1.37</v>
       </c>
-      <c r="W147">
-        <v>1.02</v>
-      </c>
-      <c r="X147">
-        <v>1.05</v>
-      </c>
-      <c r="Y147">
-        <v>1.33</v>
-      </c>
-      <c r="Z147">
-        <v>2.94</v>
-      </c>
-      <c r="AA147">
-        <v>2.05</v>
-      </c>
-      <c r="AB147">
-        <v>1.76</v>
-      </c>
-      <c r="AC147">
-        <v>3.42</v>
-      </c>
-      <c r="AD147">
-        <v>1.23</v>
-      </c>
       <c r="AE147">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF147">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG147">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="O157">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P157">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q157">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R157">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S157">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T157">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="U157">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="V157">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W157">
         <v>1.11</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z157">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA157">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB157">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AC157">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="AD157">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE157">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF157">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG157">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="O159">
+        <v>3.35</v>
+      </c>
+      <c r="P159">
+        <v>2.33</v>
+      </c>
+      <c r="Q159">
+        <v>3</v>
+      </c>
+      <c r="R159">
+        <v>2.3</v>
+      </c>
+      <c r="S159">
+        <v>1.25</v>
+      </c>
+      <c r="T159">
+        <v>3.32</v>
+      </c>
+      <c r="U159">
+        <v>2.3</v>
+      </c>
+      <c r="V159">
+        <v>1.52</v>
+      </c>
+      <c r="W159">
+        <v>1.1</v>
+      </c>
+      <c r="X159">
+        <v>1.01</v>
+      </c>
+      <c r="Y159">
+        <v>1.15</v>
+      </c>
+      <c r="Z159">
         <v>4.2</v>
       </c>
-      <c r="P159">
+      <c r="AA159">
         <v>1.61</v>
       </c>
-      <c r="Q159">
-        <v>4.46</v>
-      </c>
-      <c r="R159">
-        <v>2.24</v>
-      </c>
-      <c r="S159">
-        <v>1.3</v>
-      </c>
-      <c r="T159">
-        <v>3.3</v>
-      </c>
-      <c r="U159">
-        <v>2.54</v>
-      </c>
-      <c r="V159">
-        <v>1.45</v>
-      </c>
-      <c r="W159">
-        <v>1.07</v>
-      </c>
-      <c r="X159">
-        <v>1.02</v>
-      </c>
-      <c r="Y159">
-        <v>1.23</v>
-      </c>
-      <c r="Z159">
-        <v>3.6</v>
-      </c>
-      <c r="AA159">
-        <v>1.67</v>
-      </c>
       <c r="AB159">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC159">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD159">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF159">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG159">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK159">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="O160">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P160">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="Q160">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R160">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S160">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T160">
         <v>3.32</v>
       </c>
       <c r="U160">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V160">
         <v>1.52</v>
       </c>
       <c r="W160">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X160">
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z160">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA160">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB160">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC160">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD160">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE160">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF160">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG160">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK160">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O161">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P161">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="Q161">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R161">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S161">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T161">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U161">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="V161">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W161">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X161">
         <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z161">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA161">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB161">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC161">
-        <v>3.07</v>
+        <v>2.62</v>
       </c>
       <c r="AD161">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE161">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF161">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK161">
-        <v>1.49</v>
+        <v>1.13</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27095,10 +27095,10 @@
         <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG164">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>2.45</v>
       </c>
       <c r="R165">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S165">
         <v>1.28</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB170">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O173">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P173">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q173">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="R173">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S173">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T173">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="U173">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="V173">
         <v>1.29</v>
       </c>
       <c r="W173">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X173">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z173">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AA173">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB173">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC173">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AD173">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE173">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF173">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG173">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK173">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         <v>1.82</v>
       </c>
       <c r="AB181">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC181">
         <v>3</v>
@@ -29866,10 +29866,10 @@
         <v>1.08</v>
       </c>
       <c r="AF181">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -30476,49 +30476,49 @@
         <v>2.25</v>
       </c>
       <c r="R185">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="S185">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T185">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="U185">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V185">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W185">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X185">
         <v>1.02</v>
       </c>
       <c r="Y185">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z185">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA185">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB185">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC185">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD185">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE185">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF185">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG185">
         <v>2.5</v>
@@ -30651,7 +30651,7 @@
         <v>1.91</v>
       </c>
       <c r="V186">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W186">
         <v>1.22</v>
@@ -30669,7 +30669,7 @@
         <v>1.32</v>
       </c>
       <c r="AB186">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AC186">
         <v>1.82</v>
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="O195">
         <v>3</v>
       </c>
       <c r="P195">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32330,7 +32330,7 @@
         <v>1.24</v>
       </c>
       <c r="AK196">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O197">
         <v>3.4</v>
       </c>
       <c r="P197">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q197">
         <v>2.38</v>
@@ -32444,7 +32444,7 @@
         <v>2.61</v>
       </c>
       <c r="V197">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W197">
         <v>1.06</v>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK197">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32592,10 +32592,10 @@
         <v>3</v>
       </c>
       <c r="Q198">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="R198">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S198">
         <v>1.29</v>
@@ -32625,7 +32625,7 @@
         <v>1.7</v>
       </c>
       <c r="AB198">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC198">
         <v>2.74</v>
@@ -32767,7 +32767,7 @@
         <v>2.62</v>
       </c>
       <c r="U199">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="V199">
         <v>1.37</v>
@@ -32816,7 +32816,7 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK199">
         <v>1.73</v>
@@ -33244,7 +33244,7 @@
         <v>2.5</v>
       </c>
       <c r="Q202">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="R202">
         <v>1.84</v>
@@ -33280,7 +33280,7 @@
         <v>1.41</v>
       </c>
       <c r="AC202">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AD202">
         <v>1.1</v>
@@ -33308,7 +33308,7 @@
         <v>1.33</v>
       </c>
       <c r="AK202">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -34059,16 +34059,16 @@
         <v>3</v>
       </c>
       <c r="Q207">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R207">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S207">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T207">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="U207">
         <v>2.88</v>
@@ -34083,31 +34083,31 @@
         <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z207">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA207">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB207">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AC207">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD207">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE207">
         <v>1.07</v>
       </c>
       <c r="AF207">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG207">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>1.25</v>
       </c>
       <c r="AK207">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,16 +34213,16 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O208">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P208">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q208">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="R208">
         <v>2.1</v>
@@ -34234,7 +34234,7 @@
         <v>2.73</v>
       </c>
       <c r="U208">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V208">
         <v>1.36</v>
@@ -34246,10 +34246,10 @@
         <v>1.02</v>
       </c>
       <c r="Y208">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z208">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA208">
         <v>2</v>
@@ -34258,19 +34258,19 @@
         <v>1.8</v>
       </c>
       <c r="AC208">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD208">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE208">
         <v>1.06</v>
       </c>
       <c r="AF208">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG208">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>1.29</v>
       </c>
       <c r="AK208">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34385,55 +34385,55 @@
         <v>0</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>4.75</v>
+        <v>5.17</v>
       </c>
       <c r="O214">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="P214">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35574,7 +35574,7 @@
         <v>1.86</v>
       </c>
       <c r="AG216">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q217">
         <v>2.99</v>
@@ -36181,7 +36181,7 @@
         <v>4.3</v>
       </c>
       <c r="R220">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S220">
         <v>1.2</v>
@@ -36193,7 +36193,7 @@
         <v>2.25</v>
       </c>
       <c r="V220">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W220">
         <v>1.13</v>
@@ -36208,13 +36208,13 @@
         <v>4.7</v>
       </c>
       <c r="AA220">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB220">
         <v>2.31</v>
       </c>
       <c r="AC220">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD220">
         <v>1.61</v>
@@ -36371,10 +36371,10 @@
         <v>2.84</v>
       </c>
       <c r="AA221">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB221">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC221">
         <v>3.9</v>
@@ -36495,16 +36495,16 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="O222">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P222">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="Q222">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R222">
         <v>2.1</v>
@@ -36513,7 +36513,7 @@
         <v>1.36</v>
       </c>
       <c r="T222">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U222">
         <v>2.74</v>
@@ -36537,22 +36537,22 @@
         <v>1.91</v>
       </c>
       <c r="AB222">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC222">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD222">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE222">
         <v>1.06</v>
       </c>
       <c r="AF222">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG222">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>1.25</v>
       </c>
       <c r="AK222">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36667,7 +36667,7 @@
         <v>3</v>
       </c>
       <c r="Q223">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R223">
         <v>2</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="O224">
         <v>3.3</v>
@@ -36848,10 +36848,10 @@
         <v>1.54</v>
       </c>
       <c r="W224">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X224">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y224">
         <v>1.16</v>
@@ -36863,7 +36863,7 @@
         <v>1.61</v>
       </c>
       <c r="AB224">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC224">
         <v>2.39</v>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AK224">
         <v>1.45</v>
@@ -36984,7 +36984,7 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O225">
         <v>4.12</v>
@@ -38128,10 +38128,10 @@
         <v>1.62</v>
       </c>
       <c r="O232">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P232">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38460,19 +38460,19 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R234">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S234">
         <v>1.25</v>
       </c>
       <c r="T234">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U234">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="V234">
         <v>1.55</v>
@@ -38481,25 +38481,25 @@
         <v>1.12</v>
       </c>
       <c r="X234">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y234">
         <v>1.15</v>
       </c>
       <c r="Z234">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA234">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB234">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC234">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AD234">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE234">
         <v>1.15</v>
@@ -38508,7 +38508,7 @@
         <v>1.85</v>
       </c>
       <c r="AG234">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38964,10 +38964,10 @@
         <v>2.04</v>
       </c>
       <c r="V237">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W237">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X237">
         <v>1.02</v>
@@ -38982,7 +38982,7 @@
         <v>1.36</v>
       </c>
       <c r="AB237">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="AC237">
         <v>1.9</v>
@@ -38991,7 +38991,7 @@
         <v>1.91</v>
       </c>
       <c r="AE237">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF237">
         <v>1.36</v>
@@ -39013,7 +39013,7 @@
         <v>1.44</v>
       </c>
       <c r="AK237">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39124,7 +39124,7 @@
         <v>2.57</v>
       </c>
       <c r="U238">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39272,7 +39272,7 @@
         <v>3.4</v>
       </c>
       <c r="P239">
-        <v>4.51</v>
+        <v>4.35</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39764,7 +39764,7 @@
         <v>2.6</v>
       </c>
       <c r="Q242">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="R242">
         <v>2.29</v>
@@ -39782,7 +39782,7 @@
         <v>1.64</v>
       </c>
       <c r="W242">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X242">
         <v>1.02</v>
@@ -39797,7 +39797,7 @@
         <v>1.44</v>
       </c>
       <c r="AB242">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC242">
         <v>2.14</v>
@@ -39924,7 +39924,7 @@
         <v>4.1</v>
       </c>
       <c r="P243">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="Q243">
         <v>2.09</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="O249">
         <v>3</v>
       </c>
       <c r="P249">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41065,7 +41065,7 @@
         <v>3.1</v>
       </c>
       <c r="P250">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q250">
         <v>3.25</v>
@@ -41095,7 +41095,7 @@
         <v>1.23</v>
       </c>
       <c r="Z250">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="AA250">
         <v>1.81</v>
@@ -41132,7 +41132,7 @@
         <v>1.44</v>
       </c>
       <c r="AK250">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41228,7 +41228,7 @@
         <v>3.45</v>
       </c>
       <c r="P251">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q251">
         <v>2.46</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O256">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P256">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q257">
         <v>2.4</v>
@@ -42224,7 +42224,7 @@
         <v>2.75</v>
       </c>
       <c r="V257">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W257">
         <v>1.07</v>
@@ -42239,10 +42239,10 @@
         <v>3.28</v>
       </c>
       <c r="AA257">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB257">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC257">
         <v>3.2</v>
@@ -42873,7 +42873,7 @@
         <v>2.99</v>
       </c>
       <c r="U261">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V261">
         <v>1.4</v>
@@ -42906,10 +42906,10 @@
         <v>1.09</v>
       </c>
       <c r="AF261">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG261">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O265">
         <v>3</v>
       </c>
       <c r="P265">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43685,10 +43685,10 @@
         <v>1.25</v>
       </c>
       <c r="T266">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="U266">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V266">
         <v>1.57</v>
@@ -43700,22 +43700,22 @@
         <v>1</v>
       </c>
       <c r="Y266">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z266">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA266">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB266">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC266">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD266">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE266">
         <v>1.19</v>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK266">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43869,10 +43869,10 @@
         <v>2.49</v>
       </c>
       <c r="AA267">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AB267">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC267">
         <v>4.7</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44820,52 +44820,52 @@
         <v>1.62</v>
       </c>
       <c r="R273">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="S273">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T273">
         <v>4.8</v>
       </c>
       <c r="U273">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V273">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="W273">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="X273">
         <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z273">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA273">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB273">
-        <v>3.57</v>
+        <v>3.68</v>
       </c>
       <c r="AC273">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD273">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AE273">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF273">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG273">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>1.12</v>
       </c>
       <c r="AK273">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,80 +45623,80 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O278">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P278">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q278">
-        <v>2.36</v>
+        <v>4.11</v>
       </c>
       <c r="R278">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S278">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T278">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="U278">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y278">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Z278">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AA278">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB278">
+        <v>1.35</v>
+      </c>
+      <c r="AC278">
+        <v>5.55</v>
+      </c>
+      <c r="AD278">
+        <v>1.08</v>
+      </c>
+      <c r="AE278">
+        <v>1.03</v>
+      </c>
+      <c r="AF278">
+        <v>2.23</v>
+      </c>
+      <c r="AG278">
+        <v>1.57</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
         <v>1.44</v>
       </c>
-      <c r="AC278">
-        <v>4.85</v>
-      </c>
-      <c r="AD278">
-        <v>1.11</v>
-      </c>
-      <c r="AE278">
-        <v>1.01</v>
-      </c>
-      <c r="AF278">
-        <v>2.4</v>
-      </c>
-      <c r="AG278">
-        <v>1.48</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.25</v>
-      </c>
       <c r="AK278">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O279">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P279">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q279">
-        <v>4.11</v>
+        <v>2.36</v>
       </c>
       <c r="R279">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S279">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T279">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="U279">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X279">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Z279">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA279">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB279">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC279">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AD279">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE279">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AG279">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46450,16 +46450,16 @@
         <v>2</v>
       </c>
       <c r="R283">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S283">
         <v>1.33</v>
       </c>
       <c r="T283">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="U283">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V283">
         <v>1.37</v>
@@ -46480,22 +46480,22 @@
         <v>1.9</v>
       </c>
       <c r="AB283">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC283">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD283">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE283">
         <v>1.08</v>
       </c>
       <c r="AF283">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG283">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46601,16 +46601,16 @@
         </is>
       </c>
       <c r="N284">
+        <v>2.9</v>
+      </c>
+      <c r="O284">
         <v>3.05</v>
       </c>
-      <c r="O284">
-        <v>3.15</v>
-      </c>
       <c r="P284">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="Q284">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="R284">
         <v>1.92</v>
@@ -46628,16 +46628,16 @@
         <v>1.26</v>
       </c>
       <c r="W284">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X284">
         <v>1.03</v>
       </c>
       <c r="Y284">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z284">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA284">
         <v>2.35</v>
@@ -46776,7 +46776,7 @@
         <v>2.2</v>
       </c>
       <c r="R285">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S285">
         <v>1.36</v>
@@ -46818,10 +46818,10 @@
         <v>1.06</v>
       </c>
       <c r="AF285">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG285">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK285">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47905,31 +47905,31 @@
         </is>
       </c>
       <c r="N292">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O292">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P292">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q292">
         <v>3.9</v>
       </c>
       <c r="R292">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S292">
         <v>1.37</v>
       </c>
       <c r="T292">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U292">
         <v>2.55</v>
       </c>
       <c r="V292">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W292">
         <v>1.07</v>
@@ -48231,7 +48231,7 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O294">
         <v>3.64</v>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AK300">
         <v>1.5</v>
@@ -50220,10 +50220,10 @@
         <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z306">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA306">
         <v>1.5</v>
@@ -51174,7 +51174,7 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R312">
         <v>2.27</v>
@@ -51207,7 +51207,7 @@
         <v>1.57</v>
       </c>
       <c r="AB312">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC312">
         <v>2.46</v>
@@ -51235,7 +51235,7 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK312">
         <v>1.4</v>
@@ -54781,7 +54781,7 @@
         <v>0</v>
       </c>
       <c r="X334">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y334">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -668,7 +668,7 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z2">
         <v>2.9</v>
@@ -686,7 +686,7 @@
         <v>1.23</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
         <v>1.85</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="R4">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>4.33</v>
+      </c>
+      <c r="AA4">
+        <v>1.57</v>
+      </c>
+      <c r="AB4">
+        <v>2.3</v>
+      </c>
+      <c r="AC4">
+        <v>2.5</v>
+      </c>
+      <c r="AD4">
+        <v>1.52</v>
+      </c>
+      <c r="AE4">
+        <v>1.15</v>
+      </c>
+      <c r="AF4">
+        <v>1.53</v>
+      </c>
+      <c r="AG4">
+        <v>2.25</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.22</v>
       </c>
-      <c r="Z4">
-        <v>3.74</v>
-      </c>
-      <c r="AA4">
-        <v>1.8</v>
-      </c>
-      <c r="AB4">
-        <v>1.93</v>
-      </c>
-      <c r="AC4">
-        <v>3.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.37</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.65</v>
-      </c>
-      <c r="AG4">
-        <v>2.1</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.23</v>
-      </c>
       <c r="AK4">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD5">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
         <v>2.6</v>
@@ -1652,10 +1652,10 @@
         <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
         <v>3.12</v>
@@ -1667,7 +1667,7 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
         <v>2.05</v>
@@ -1830,23 +1830,23 @@
         <v>1.14</v>
       </c>
       <c r="AF9">
+        <v>1.51</v>
+      </c>
+      <c r="AG9">
+        <v>2.39</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.53</v>
-      </c>
-      <c r="AG9">
-        <v>2.35</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.28</v>
       </c>
       <c r="AK9">
         <v>1.41</v>
@@ -1972,7 +1972,7 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
         <v>3.58</v>
@@ -1993,7 +1993,7 @@
         <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
         <v>2.1</v>
@@ -2111,10 +2111,10 @@
         <v>3.8</v>
       </c>
       <c r="Q11">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2138,10 +2138,10 @@
         <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB11">
         <v>1.87</v>
@@ -2274,7 +2274,7 @@
         <v>4.5</v>
       </c>
       <c r="Q12">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
         <v>2.04</v>
@@ -2298,10 +2298,10 @@
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA12">
         <v>2.09</v>
@@ -2338,7 +2338,7 @@
         <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>3.5</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.23</v>
       </c>
       <c r="P13">
         <v>1.95</v>
@@ -2787,10 +2787,10 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z15">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="AA15">
         <v>1.99</v>
@@ -2929,7 +2929,7 @@
         <v>3.28</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S16">
         <v>1.28</v>
@@ -2947,13 +2947,13 @@
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA16">
         <v>1.66</v>
@@ -2962,19 +2962,19 @@
         <v>2.15</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD16">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
         <v>1.51</v>
       </c>
       <c r="AG16">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>1.65</v>
       </c>
       <c r="AC17">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AD17">
         <v>1.19</v>
@@ -3261,7 +3261,7 @@
         <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U18">
         <v>3.06</v>
@@ -3279,7 +3279,7 @@
         <v>1.39</v>
       </c>
       <c r="Z18">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="AA18">
         <v>2.27</v>
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="R19">
         <v>2.05</v>
@@ -3424,7 +3424,7 @@
         <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U19">
         <v>2.72</v>
@@ -3439,7 +3439,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
         <v>3.4</v>
@@ -3587,7 +3587,7 @@
         <v>1.26</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U20">
         <v>2.38</v>
@@ -3626,7 +3626,7 @@
         <v>1.69</v>
       </c>
       <c r="AG20">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="O23">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="Q23">
         <v>2.25</v>
@@ -4088,7 +4088,7 @@
         <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.18</v>
@@ -4239,7 +4239,7 @@
         <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="U24">
         <v>2.81</v>
@@ -4263,7 +4263,7 @@
         <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
         <v>3.27</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
         <v>1.85</v>
@@ -4903,7 +4903,7 @@
         <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y28">
         <v>1.2</v>
@@ -4927,7 +4927,7 @@
         <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
         <v>2.14</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.8</v>
@@ -6346,25 +6346,25 @@
         <v>4.05</v>
       </c>
       <c r="P37">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R37">
         <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W37">
         <v>1.17</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC37">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AD37">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF37">
         <v>1.44</v>
       </c>
       <c r="AG37">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>1.3</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AK38">
         <v>1.37</v>
@@ -6669,61 +6669,61 @@
         <v>1.88</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6841,7 +6841,7 @@
         <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S40">
         <v>1.3</v>
@@ -6856,7 +6856,7 @@
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK40">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,25 +6992,25 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O41">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="P41">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q41">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R41">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U41">
         <v>2.32</v>
@@ -7019,7 +7019,7 @@
         <v>1.49</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,25 +7031,25 @@
         <v>4.3</v>
       </c>
       <c r="AA41">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC41">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD41">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK41">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7517,16 +7517,16 @@
         <v>1.26</v>
       </c>
       <c r="Z44">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA44">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB44">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC44">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD44">
         <v>1.4</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
         <v>1.86</v>
@@ -7982,13 +7982,13 @@
         <v>3.47</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S47">
         <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
         <v>2.61</v>
@@ -8006,7 +8006,7 @@
         <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA47">
         <v>1.8</v>
@@ -8015,16 +8015,16 @@
         <v>2.03</v>
       </c>
       <c r="AC47">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD47">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
         <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
         <v>2.05</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
         <v>1.29</v>
@@ -8145,7 +8145,7 @@
         <v>4.2</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
         <v>1.29</v>
@@ -8154,13 +8154,13 @@
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8190,7 +8190,7 @@
         <v>1.54</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8299,13 +8299,13 @@
         <v>1.73</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R49">
         <v>2.38</v>
@@ -8314,13 +8314,13 @@
         <v>1.23</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
         <v>2.34</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
         <v>1.11</v>
@@ -8332,22 +8332,22 @@
         <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="AA49">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD49">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK49">
         <v>2.14</v>
@@ -8462,7 +8462,7 @@
         <v>2.6</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
         <v>2.7</v>
@@ -8794,16 +8794,16 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S52">
         <v>1.33</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U52">
         <v>2.75</v>
@@ -8818,31 +8818,31 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB52">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC52">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD52">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="R53">
         <v>2.15</v>
@@ -8966,7 +8966,7 @@
         <v>1.28</v>
       </c>
       <c r="T53">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
         <v>2.32</v>
@@ -8984,7 +8984,7 @@
         <v>1.16</v>
       </c>
       <c r="Z53">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA53">
         <v>1.64</v>
@@ -9132,43 +9132,43 @@
         <v>2.83</v>
       </c>
       <c r="U54">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z54">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA54">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB54">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC54">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD54">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>2.48</v>
       </c>
       <c r="Q55">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="R55">
         <v>2.2</v>
@@ -9446,7 +9446,7 @@
         <v>2.05</v>
       </c>
       <c r="Q56">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="R56">
         <v>2.32</v>
@@ -9461,10 +9461,10 @@
         <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X56">
         <v>1.02</v>
@@ -10424,10 +10424,10 @@
         <v>1.85</v>
       </c>
       <c r="Q62">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R62">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S62">
         <v>1.37</v>
@@ -10445,7 +10445,7 @@
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
         <v>1.22</v>
@@ -10488,7 +10488,7 @@
         <v>1.78</v>
       </c>
       <c r="AK62">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10617,7 +10617,7 @@
         <v>3.05</v>
       </c>
       <c r="AA63">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB63">
         <v>1.69</v>
@@ -10651,7 +10651,7 @@
         <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10771,7 +10771,7 @@
         <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
         <v>1.17</v>
@@ -10786,7 +10786,7 @@
         <v>2.11</v>
       </c>
       <c r="AC64">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AD64">
         <v>1.4</v>
@@ -10798,7 +10798,7 @@
         <v>1.54</v>
       </c>
       <c r="AG64">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="R65">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="S65">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T65">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="U65">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V65">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA65">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AB65">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AC65">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AD65">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AE65">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF65">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AG65">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,28 +11067,28 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O66">
         <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="Q66">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="R66">
         <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="U66">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V66">
         <v>1.62</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z66">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AC66">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AD66">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AG66">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G67">
@@ -11233,62 +11233,62 @@
         <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R67">
+        <v>2.24</v>
+      </c>
+      <c r="S67">
+        <v>1.25</v>
+      </c>
+      <c r="T67">
+        <v>3.46</v>
+      </c>
+      <c r="U67">
+        <v>2.22</v>
+      </c>
+      <c r="V67">
+        <v>1.53</v>
+      </c>
+      <c r="W67">
+        <v>1.14</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.13</v>
+      </c>
+      <c r="Z67">
+        <v>4.6</v>
+      </c>
+      <c r="AA67">
+        <v>1.56</v>
+      </c>
+      <c r="AB67">
+        <v>2.22</v>
+      </c>
+      <c r="AC67">
+        <v>2.46</v>
+      </c>
+      <c r="AD67">
+        <v>1.46</v>
+      </c>
+      <c r="AE67">
+        <v>1.2</v>
+      </c>
+      <c r="AF67">
+        <v>1.48</v>
+      </c>
+      <c r="AG67">
         <v>2.4</v>
       </c>
-      <c r="S67">
-        <v>1.22</v>
-      </c>
-      <c r="T67">
-        <v>3.75</v>
-      </c>
-      <c r="U67">
-        <v>2.2</v>
-      </c>
-      <c r="V67">
-        <v>1.57</v>
-      </c>
-      <c r="W67">
-        <v>1.11</v>
-      </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.1</v>
-      </c>
-      <c r="Z67">
-        <v>5</v>
-      </c>
-      <c r="AA67">
-        <v>1.46</v>
-      </c>
-      <c r="AB67">
-        <v>2.38</v>
-      </c>
-      <c r="AC67">
-        <v>2.22</v>
-      </c>
-      <c r="AD67">
-        <v>1.56</v>
-      </c>
-      <c r="AE67">
-        <v>1.19</v>
-      </c>
-      <c r="AF67">
-        <v>1.4</v>
-      </c>
-      <c r="AG67">
-        <v>2.75</v>
-      </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R68">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T68">
-        <v>3.46</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="W68">
         <v>1.14</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z68">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AB68">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>2.46</v>
+        <v>2.01</v>
       </c>
       <c r="AD68">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF68">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q69">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
         <v>1.4</v>
       </c>
       <c r="T69">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="U69">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V69">
         <v>1.37</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z69">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AA69">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB69">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC69">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="AD69">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG69">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK69">
         <v>1.6</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O75">
         <v>3.55</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q75">
         <v>2.61</v>
       </c>
       <c r="R75">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
         <v>1.32</v>
@@ -12573,13 +12573,13 @@
         <v>3.58</v>
       </c>
       <c r="AA75">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB75">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC75">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD75">
         <v>1.36</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
         <v>1.68</v>
@@ -12736,16 +12736,16 @@
         <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB76">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC76">
         <v>3.45</v>
       </c>
       <c r="AD76">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
         <v>1.04</v>
@@ -12754,7 +12754,7 @@
         <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12884,7 +12884,7 @@
         <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12908,16 +12908,16 @@
         <v>2.7</v>
       </c>
       <c r="AD77">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
         <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O78">
         <v>3.55</v>
@@ -13032,7 +13032,7 @@
         <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
         <v>2.07</v>
@@ -13041,13 +13041,13 @@
         <v>1.39</v>
       </c>
       <c r="T78">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U78">
         <v>2.75</v>
       </c>
       <c r="V78">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W78">
         <v>1.07</v>
@@ -13059,19 +13059,19 @@
         <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA78">
         <v>2</v>
       </c>
       <c r="AB78">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC78">
         <v>3.45</v>
       </c>
       <c r="AD78">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
         <v>1.06</v>
@@ -13080,7 +13080,7 @@
         <v>1.83</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
         <v>2</v>
@@ -13189,10 +13189,10 @@
         <v>1.55</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P79">
-        <v>4.7</v>
+        <v>4.86</v>
       </c>
       <c r="Q79">
         <v>2.05</v>
@@ -13219,16 +13219,16 @@
         <v>1</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="AA79">
         <v>1.87</v>
       </c>
       <c r="AB79">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC79">
         <v>3.14</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O80">
         <v>3.2</v>
@@ -13358,13 +13358,13 @@
         <v>2.9</v>
       </c>
       <c r="Q80">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="R80">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S80">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
         <v>2.88</v>
@@ -13382,28 +13382,28 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA80">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB80">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC80">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="AD80">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG80">
         <v>1.91</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,16 +13521,16 @@
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R81">
         <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U81">
         <v>2.75</v>
@@ -13539,7 +13539,7 @@
         <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -13585,7 +13585,7 @@
         <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13714,13 +13714,13 @@
         <v>2.74</v>
       </c>
       <c r="AA82">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB82">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC82">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AD82">
         <v>1.17</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O83">
         <v>3.25</v>
@@ -13868,7 +13868,7 @@
         <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
         <v>1.35</v>
@@ -13911,7 +13911,7 @@
         <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15142,55 +15142,55 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="R91">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S91">
         <v>1.28</v>
       </c>
       <c r="T91">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="U91">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="V91">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W91">
         <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
         <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="AA91">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB91">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE91">
         <v>1.13</v>
@@ -15199,7 +15199,7 @@
         <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15335,7 +15335,7 @@
         <v>1.07</v>
       </c>
       <c r="X92">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
         <v>1.25</v>
@@ -15471,40 +15471,40 @@
         <v>1.83</v>
       </c>
       <c r="O93">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q93">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="R93">
         <v>2.29</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="U93">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V93">
         <v>1.46</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
         <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AA93">
         <v>1.69</v>
@@ -15513,19 +15513,19 @@
         <v>2.08</v>
       </c>
       <c r="AC93">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD93">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE93">
         <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16307,7 +16307,7 @@
         <v>2.35</v>
       </c>
       <c r="V98">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W98">
         <v>1.08</v>
@@ -16325,7 +16325,7 @@
         <v>1.68</v>
       </c>
       <c r="AB98">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC98">
         <v>2.59</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AK98">
         <v>1.33</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O99">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="P99">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q99">
         <v>3.67</v>
@@ -16464,19 +16464,19 @@
         <v>1.3</v>
       </c>
       <c r="T99">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U99">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V99">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W99">
         <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.21</v>
@@ -16500,10 +16500,10 @@
         <v>1.11</v>
       </c>
       <c r="AF99">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG99">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O100">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P100">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17756,7 +17756,7 @@
         <v>3.48</v>
       </c>
       <c r="P107">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17928,13 +17928,13 @@
         <v>2.38</v>
       </c>
       <c r="S108">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T108">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="U108">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V108">
         <v>1.55</v>
@@ -17943,7 +17943,7 @@
         <v>1.12</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
         <v>1.18</v>
@@ -17952,7 +17952,7 @@
         <v>4.54</v>
       </c>
       <c r="AA108">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB108">
         <v>2.27</v>
@@ -17970,7 +17970,7 @@
         <v>1.5</v>
       </c>
       <c r="AG108">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18894,13 +18894,13 @@
         <v>1.8</v>
       </c>
       <c r="O114">
-        <v>3.7</v>
+        <v>3.47</v>
       </c>
       <c r="P114">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q114">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R114">
         <v>2.3</v>
@@ -18921,28 +18921,28 @@
         <v>1.12</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z114">
         <v>3.74</v>
       </c>
       <c r="AA114">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB114">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC114">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD114">
         <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
@@ -19075,7 +19075,7 @@
         <v>3.5</v>
       </c>
       <c r="U115">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V115">
         <v>1.57</v>
@@ -19090,13 +19090,13 @@
         <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA115">
         <v>1.57</v>
       </c>
       <c r="AB115">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC115">
         <v>2.57</v>
@@ -19108,7 +19108,7 @@
         <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG115">
         <v>2.1</v>
@@ -19127,7 +19127,7 @@
         <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,7 +19217,7 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O116">
         <v>3.9</v>
@@ -19229,13 +19229,13 @@
         <v>4.82</v>
       </c>
       <c r="R116">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S116">
         <v>1.34</v>
       </c>
       <c r="T116">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="U116">
         <v>2.55</v>
@@ -19247,13 +19247,13 @@
         <v>1.09</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
         <v>1.22</v>
       </c>
       <c r="Z116">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA116">
         <v>1.84</v>
@@ -19262,10 +19262,10 @@
         <v>2.12</v>
       </c>
       <c r="AC116">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="AD116">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE116">
         <v>1.11</v>
@@ -19431,7 +19431,7 @@
         <v>1.18</v>
       </c>
       <c r="AE117">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
         <v>1.93</v>
@@ -19549,10 +19549,10 @@
         <v>3.4</v>
       </c>
       <c r="P118">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="R118">
         <v>2.02</v>
@@ -19561,10 +19561,10 @@
         <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U118">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="V118">
         <v>1.36</v>
@@ -19715,10 +19715,10 @@
         <v>3</v>
       </c>
       <c r="Q119">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="R119">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S119">
         <v>1.42</v>
@@ -19739,31 +19739,31 @@
         <v>1.03</v>
       </c>
       <c r="Y119">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z119">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA119">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB119">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC119">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD119">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE119">
         <v>1.05</v>
       </c>
       <c r="AF119">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG119">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.27</v>
       </c>
       <c r="AK119">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19875,13 +19875,13 @@
         <v>5.2</v>
       </c>
       <c r="P120">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Q120">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R120">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="S120">
         <v>1.23</v>
@@ -19890,7 +19890,7 @@
         <v>3.7</v>
       </c>
       <c r="U120">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="V120">
         <v>1.62</v>
@@ -19905,19 +19905,19 @@
         <v>1.11</v>
       </c>
       <c r="Z120">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="AA120">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB120">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC120">
         <v>2.24</v>
       </c>
       <c r="AD120">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE120">
         <v>1.22</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O121">
         <v>3.55</v>
       </c>
       <c r="P121">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="Q121">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R121">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S121">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T121">
         <v>3.12</v>
       </c>
       <c r="U121">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V121">
         <v>1.44</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z121">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="AA121">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB121">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD121">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE121">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF121">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG121">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AK121">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O122">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R122">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T122">
         <v>3.12</v>
       </c>
       <c r="U122">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.52</v>
+        <v>3.76</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC122">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG122">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="O123">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P123">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -20379,10 +20379,10 @@
         <v>2.94</v>
       </c>
       <c r="U123">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
         <v>1.11</v>
@@ -20400,10 +20400,10 @@
         <v>1.78</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC123">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD123">
         <v>1.34</v>
@@ -20415,7 +20415,7 @@
         <v>1.61</v>
       </c>
       <c r="AG123">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
         <v>1.67</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="O124">
         <v>3.25</v>
       </c>
       <c r="P124">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Q124">
         <v>3.3</v>
@@ -20557,7 +20557,7 @@
         <v>1.23</v>
       </c>
       <c r="Z124">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA124">
         <v>1.82</v>
@@ -20847,28 +20847,28 @@
         </is>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P126">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q126">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R126">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S126">
         <v>1.49</v>
       </c>
       <c r="T126">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U126">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="V126">
         <v>1.33</v>
@@ -20880,28 +20880,28 @@
         <v>1.07</v>
       </c>
       <c r="Y126">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z126">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA126">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB126">
         <v>1.6</v>
       </c>
       <c r="AC126">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="AD126">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE126">
         <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG126">
         <v>1.87</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK126">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21064,7 +21064,7 @@
         <v>1.06</v>
       </c>
       <c r="AF127">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG127">
         <v>2</v>
@@ -21176,7 +21176,7 @@
         <v>4</v>
       </c>
       <c r="O128">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P128">
         <v>1.73</v>
@@ -21188,7 +21188,7 @@
         <v>2.2</v>
       </c>
       <c r="S128">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T128">
         <v>3.1</v>
@@ -21212,16 +21212,16 @@
         <v>4.1</v>
       </c>
       <c r="AA128">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB128">
         <v>1.96</v>
       </c>
       <c r="AC128">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD128">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE128">
         <v>1.11</v>
@@ -21246,7 +21246,7 @@
         <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21351,13 +21351,13 @@
         <v>2.1</v>
       </c>
       <c r="S129">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T129">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="U129">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V129">
         <v>1.38</v>
@@ -21387,13 +21387,13 @@
         <v>1.25</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF129">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG129">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,7 +21508,7 @@
         <v>4.4</v>
       </c>
       <c r="Q130">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R130">
         <v>2.47</v>
@@ -21529,13 +21529,13 @@
         <v>1.08</v>
       </c>
       <c r="X130">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z130">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA130">
         <v>1.65</v>
@@ -21553,10 +21553,10 @@
         <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG130">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK130">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,31 +21825,31 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="P132">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="Q132">
         <v>2.68</v>
       </c>
       <c r="R132">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T132">
         <v>3.12</v>
       </c>
       <c r="U132">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V132">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W132">
         <v>1.08</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
         <v>1.55</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P133">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="R133">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="S133">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="T133">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U133">
-        <v>3.07</v>
+        <v>2.15</v>
       </c>
       <c r="V133">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>5.62</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AB133">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="AC133">
-        <v>3.48</v>
+        <v>2.2</v>
       </c>
       <c r="AD133">
+        <v>1.62</v>
+      </c>
+      <c r="AE133">
         <v>1.22</v>
       </c>
-      <c r="AE133">
-        <v>1.05</v>
-      </c>
       <c r="AF133">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG133">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK133">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O134">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P134">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="Q134">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R134">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="S134">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="U134">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="V134">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="W134">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>5.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA134">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB134">
-        <v>2.43</v>
+        <v>1.85</v>
       </c>
       <c r="AC134">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD134">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG134">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK134">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
+        <v>2.8</v>
+      </c>
+      <c r="Q135">
         <v>3.1</v>
       </c>
-      <c r="Q135">
+      <c r="R135">
+        <v>2</v>
+      </c>
+      <c r="S135">
+        <v>1.43</v>
+      </c>
+      <c r="T135">
         <v>2.88</v>
       </c>
-      <c r="R135">
-        <v>2.1</v>
-      </c>
-      <c r="S135">
+      <c r="U135">
+        <v>3.07</v>
+      </c>
+      <c r="V135">
         <v>1.37</v>
       </c>
-      <c r="T135">
-        <v>2.78</v>
-      </c>
-      <c r="U135">
-        <v>2.67</v>
-      </c>
-      <c r="V135">
-        <v>1.4</v>
-      </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z135">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA135">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB135">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC135">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE135">
         <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG135">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T136">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="U136">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V136">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
         <v>1.26</v>
       </c>
       <c r="Z136">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="AA136">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AB136">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22821,7 +22821,7 @@
         <v>1.3</v>
       </c>
       <c r="T138">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U138">
         <v>2.75</v>
@@ -22969,16 +22969,16 @@
         <v>1.55</v>
       </c>
       <c r="O139">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P139">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q139">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R139">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S139">
         <v>1.25</v>
@@ -22987,10 +22987,10 @@
         <v>3.6</v>
       </c>
       <c r="U139">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V139">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W139">
         <v>1.11</v>
@@ -22999,22 +22999,22 @@
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z139">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA139">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB139">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AC139">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AD139">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AE139">
         <v>1.18</v>
@@ -23138,7 +23138,7 @@
         <v>1.54</v>
       </c>
       <c r="Q140">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="R140">
         <v>2.52</v>
@@ -23156,7 +23156,7 @@
         <v>1.68</v>
       </c>
       <c r="W140">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X140">
         <v>1.02</v>
@@ -23186,7 +23186,7 @@
         <v>1.55</v>
       </c>
       <c r="AG140">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK140">
         <v>1.15</v>
@@ -23301,7 +23301,7 @@
         <v>1.61</v>
       </c>
       <c r="Q141">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R141">
         <v>2.49</v>
@@ -23310,13 +23310,13 @@
         <v>1.16</v>
       </c>
       <c r="T141">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U141">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V141">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W141">
         <v>1.21</v>
@@ -23365,7 +23365,7 @@
         <v>1.14</v>
       </c>
       <c r="AK141">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23464,7 +23464,7 @@
         <v>2.15</v>
       </c>
       <c r="Q142">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="R142">
         <v>2.98</v>
@@ -23473,7 +23473,7 @@
         <v>1.11</v>
       </c>
       <c r="T142">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="U142">
         <v>1.62</v>
@@ -23482,7 +23482,7 @@
         <v>2.15</v>
       </c>
       <c r="W142">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X142">
         <v>0</v>
@@ -23494,19 +23494,19 @@
         <v>11</v>
       </c>
       <c r="AA142">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AB142">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AC142">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD142">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AE142">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF142">
         <v>1.2</v>
@@ -23528,7 +23528,7 @@
         <v>1.22</v>
       </c>
       <c r="AK142">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23657,7 +23657,7 @@
         <v>4.02</v>
       </c>
       <c r="AA143">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB143">
         <v>1.97</v>
@@ -23669,13 +23669,13 @@
         <v>1.36</v>
       </c>
       <c r="AE143">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF143">
         <v>1.57</v>
       </c>
       <c r="AG143">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23781,10 +23781,10 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
         <v>2.45</v>
@@ -23796,10 +23796,10 @@
         <v>2.09</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T144">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="U144">
         <v>2.75</v>
@@ -23817,7 +23817,7 @@
         <v>1.29</v>
       </c>
       <c r="Z144">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA144">
         <v>1.84</v>
@@ -23826,7 +23826,7 @@
         <v>1.83</v>
       </c>
       <c r="AC144">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AD144">
         <v>1.29</v>
@@ -23838,7 +23838,7 @@
         <v>1.65</v>
       </c>
       <c r="AG144">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23950,7 +23950,7 @@
         <v>3.4</v>
       </c>
       <c r="P145">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="Q145">
         <v>2.68</v>
@@ -24318,10 +24318,10 @@
         <v>2.83</v>
       </c>
       <c r="AD147">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE147">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF147">
         <v>1.7</v>
@@ -24472,13 +24472,13 @@
         <v>3.5</v>
       </c>
       <c r="AA148">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB148">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC148">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AD148">
         <v>1.31</v>
@@ -24813,7 +24813,7 @@
         <v>1.18</v>
       </c>
       <c r="AF150">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG150">
         <v>2.15</v>
@@ -24943,13 +24943,13 @@
         <v>3.24</v>
       </c>
       <c r="U151">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V151">
         <v>1.53</v>
       </c>
       <c r="W151">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X151">
         <v>1.01</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O152">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q152">
         <v>3.64</v>
@@ -25595,7 +25595,7 @@
         <v>2.75</v>
       </c>
       <c r="U155">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="V155">
         <v>1.36</v>
@@ -25610,7 +25610,7 @@
         <v>1.33</v>
       </c>
       <c r="Z155">
-        <v>2.76</v>
+        <v>3.07</v>
       </c>
       <c r="AA155">
         <v>2.15</v>
@@ -25625,10 +25625,10 @@
         <v>1.21</v>
       </c>
       <c r="AE155">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF155">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG155">
         <v>1.86</v>
@@ -25779,7 +25779,7 @@
         <v>1.6</v>
       </c>
       <c r="AB156">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AC156">
         <v>2.47</v>
@@ -25791,7 +25791,7 @@
         <v>1.15</v>
       </c>
       <c r="AF156">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG156">
         <v>2.45</v>
@@ -25906,7 +25906,7 @@
         <v>3.5</v>
       </c>
       <c r="P157">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q157">
         <v>3</v>
@@ -25933,7 +25933,7 @@
         <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z157">
         <v>3.82</v>
@@ -26072,7 +26072,7 @@
         <v>3.4</v>
       </c>
       <c r="Q158">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="R158">
         <v>2.07</v>
@@ -26099,13 +26099,13 @@
         <v>1.25</v>
       </c>
       <c r="Z158">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="AA158">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB158">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC158">
         <v>3.14</v>
@@ -26136,7 +26136,7 @@
         <v>1.23</v>
       </c>
       <c r="AK158">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,19 +26226,19 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="O159">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P159">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q159">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R159">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S159">
         <v>1.25</v>
@@ -26247,43 +26247,43 @@
         <v>3.32</v>
       </c>
       <c r="U159">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V159">
         <v>1.52</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z159">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA159">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB159">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC159">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD159">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE159">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF159">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG159">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK159">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,19 +26389,19 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="O160">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P160">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="Q160">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R160">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S160">
         <v>1.27</v>
@@ -26410,43 +26410,43 @@
         <v>3.32</v>
       </c>
       <c r="U160">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V160">
         <v>1.52</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X160">
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z160">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA160">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB160">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AC160">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AD160">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE160">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF160">
         <v>1.53</v>
       </c>
       <c r="AG160">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26606,7 +26606,7 @@
         <v>1.13</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG161">
         <v>2.1</v>
@@ -26625,7 +26625,7 @@
         <v>1.15</v>
       </c>
       <c r="AK161">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,10 +26715,10 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O162">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P162">
         <v>4</v>
@@ -26745,13 +26745,13 @@
         <v>1.06</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
         <v>1.22</v>
       </c>
       <c r="Z162">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA162">
         <v>1.78</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O163">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="P163">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q163">
         <v>2.66</v>
@@ -26911,10 +26911,10 @@
         <v>1.04</v>
       </c>
       <c r="Y163">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z163">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA163">
         <v>1.88</v>
@@ -26929,7 +26929,7 @@
         <v>1.28</v>
       </c>
       <c r="AE163">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF163">
         <v>1.68</v>
@@ -27554,7 +27554,7 @@
         <v>2.35</v>
       </c>
       <c r="V167">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W167">
         <v>1.12</v>
@@ -27563,10 +27563,10 @@
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z167">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA167">
         <v>1.52</v>
@@ -27575,19 +27575,19 @@
         <v>2.24</v>
       </c>
       <c r="AC167">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AD167">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE167">
         <v>1.19</v>
       </c>
       <c r="AF167">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG167">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27859,10 +27859,10 @@
         <v>3.35</v>
       </c>
       <c r="O169">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="P169">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q169">
         <v>3.98</v>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AK169">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>5</v>
       </c>
       <c r="Q172">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R172">
         <v>2.09</v>
@@ -28381,7 +28381,7 @@
         <v>1.32</v>
       </c>
       <c r="Z172">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AA172">
         <v>2</v>
@@ -28402,7 +28402,7 @@
         <v>1.91</v>
       </c>
       <c r="AG172">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK172">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O176">
+        <v>3.8</v>
+      </c>
+      <c r="P176">
         <v>3.85</v>
       </c>
-      <c r="P176">
-        <v>3.95</v>
-      </c>
       <c r="Q176">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R176">
         <v>2.4</v>
       </c>
       <c r="S176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U176">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="V176">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W176">
         <v>1.14</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z176">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="AA176">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB176">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="AC176">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AD176">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AE176">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AF176">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AG176">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>1.18</v>
       </c>
       <c r="AK176">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29486,22 +29486,22 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O179">
         <v>3.35</v>
       </c>
       <c r="P179">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q179">
         <v>2.62</v>
       </c>
       <c r="R179">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S179">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T179">
         <v>2.6</v>
@@ -29519,22 +29519,22 @@
         <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z179">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA179">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB179">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC179">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD179">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE179">
         <v>1.02</v>
@@ -29543,7 +29543,7 @@
         <v>2</v>
       </c>
       <c r="AG179">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK179">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29667,7 +29667,7 @@
         <v>1.44</v>
       </c>
       <c r="T180">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="U180">
         <v>2.9</v>
@@ -29694,7 +29694,7 @@
         <v>1.72</v>
       </c>
       <c r="AC180">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD180">
         <v>1.22</v>
@@ -29703,7 +29703,7 @@
         <v>1.04</v>
       </c>
       <c r="AF180">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG180">
         <v>1.85</v>
@@ -30974,10 +30974,10 @@
         <v>3.24</v>
       </c>
       <c r="U188">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="V188">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W188">
         <v>1.1</v>
@@ -31007,10 +31007,10 @@
         <v>1.16</v>
       </c>
       <c r="AF188">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG188">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>6.2</v>
       </c>
       <c r="Q189">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R189">
         <v>2.27</v>
@@ -31158,7 +31158,7 @@
         <v>1.75</v>
       </c>
       <c r="AB189">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AC189">
         <v>2.59</v>
@@ -31170,10 +31170,10 @@
         <v>1.13</v>
       </c>
       <c r="AF189">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG189">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>1.14</v>
       </c>
       <c r="AK189">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31460,7 +31460,7 @@
         <v>1.16</v>
       </c>
       <c r="T191">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="U191">
         <v>1.98</v>
@@ -31487,10 +31487,10 @@
         <v>2.7</v>
       </c>
       <c r="AC191">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AD191">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE191">
         <v>1.3</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="AK191">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31786,7 +31786,7 @@
         <v>1.33</v>
       </c>
       <c r="T193">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U193">
         <v>2.53</v>
@@ -31955,7 +31955,7 @@
         <v>2.55</v>
       </c>
       <c r="V194">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W194">
         <v>1.08</v>
@@ -31967,7 +31967,7 @@
         <v>1.17</v>
       </c>
       <c r="Z194">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA194">
         <v>1.71</v>
@@ -31985,10 +31985,10 @@
         <v>1.11</v>
       </c>
       <c r="AF194">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG194">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AK194">
         <v>1.36</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O201">
         <v>3.7</v>
@@ -33126,7 +33126,7 @@
         <v>1.15</v>
       </c>
       <c r="AF201">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG201">
         <v>2.3</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK201">
         <v>1.73</v>
@@ -33404,13 +33404,13 @@
         <v>3.45</v>
       </c>
       <c r="P203">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="Q203">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R203">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S203">
         <v>1.31</v>
@@ -33419,7 +33419,7 @@
         <v>3.08</v>
       </c>
       <c r="U203">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V203">
         <v>1.53</v>
@@ -33428,7 +33428,7 @@
         <v>1.08</v>
       </c>
       <c r="X203">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
         <v>1.19</v>
@@ -33437,7 +33437,7 @@
         <v>4.43</v>
       </c>
       <c r="AA203">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB203">
         <v>2.2</v>
@@ -33446,7 +33446,7 @@
         <v>2.5</v>
       </c>
       <c r="AD203">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE203">
         <v>1.14</v>
@@ -33471,7 +33471,7 @@
         <v>1.2</v>
       </c>
       <c r="AK203">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33561,7 +33561,7 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O204">
         <v>3.9</v>
@@ -33606,7 +33606,7 @@
         <v>2.07</v>
       </c>
       <c r="AC204">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD204">
         <v>1.35</v>
@@ -33730,7 +33730,7 @@
         <v>3.4</v>
       </c>
       <c r="P205">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="Q205">
         <v>2.8</v>
@@ -33763,7 +33763,7 @@
         <v>4</v>
       </c>
       <c r="AA205">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB205">
         <v>2.11</v>
@@ -33778,10 +33778,10 @@
         <v>1.12</v>
       </c>
       <c r="AF205">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG205">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>1.36</v>
       </c>
       <c r="AK205">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33899,7 +33899,7 @@
         <v>5</v>
       </c>
       <c r="R206">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S206">
         <v>1.2</v>
@@ -33941,7 +33941,7 @@
         <v>1.29</v>
       </c>
       <c r="AF206">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG206">
         <v>2.3</v>
@@ -34702,31 +34702,31 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O211">
         <v>3.9</v>
       </c>
       <c r="P211">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q211">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="R211">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S211">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T211">
         <v>4.4</v>
       </c>
       <c r="U211">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V211">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W211">
         <v>1.2</v>
@@ -34738,28 +34738,28 @@
         <v>1.07</v>
       </c>
       <c r="Z211">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="AA211">
         <v>1.33</v>
       </c>
       <c r="AB211">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC211">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD211">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE211">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF211">
         <v>1.4</v>
       </c>
       <c r="AG211">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK211">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34922,7 +34922,7 @@
         <v>1.44</v>
       </c>
       <c r="AG212">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK212">
         <v>2.05</v>
@@ -35037,7 +35037,7 @@
         <v>2.7</v>
       </c>
       <c r="Q213">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R213">
         <v>2.03</v>
@@ -35082,7 +35082,7 @@
         <v>1.08</v>
       </c>
       <c r="AF213">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG213">
         <v>2.05</v>
@@ -35101,7 +35101,7 @@
         <v>1.25</v>
       </c>
       <c r="AK213">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35366,7 +35366,7 @@
         <v>1.62</v>
       </c>
       <c r="R215">
-        <v>2.72</v>
+        <v>2.91</v>
       </c>
       <c r="S215">
         <v>1.12</v>
@@ -35381,7 +35381,7 @@
         <v>2.06</v>
       </c>
       <c r="W215">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X215">
         <v>1</v>
@@ -35390,13 +35390,13 @@
         <v>1.01</v>
       </c>
       <c r="Z215">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA215">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB215">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC215">
         <v>1.53</v>
@@ -35405,13 +35405,13 @@
         <v>2.3</v>
       </c>
       <c r="AE215">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF215">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG215">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK215">
         <v>3</v>
@@ -37147,25 +37147,25 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O226">
         <v>3.9</v>
       </c>
       <c r="P226">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q226">
         <v>2.21</v>
       </c>
       <c r="R226">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S226">
         <v>1.35</v>
       </c>
       <c r="T226">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U226">
         <v>2.74</v>
@@ -37177,7 +37177,7 @@
         <v>1.08</v>
       </c>
       <c r="X226">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y226">
         <v>1.21</v>
@@ -37186,7 +37186,7 @@
         <v>3.84</v>
       </c>
       <c r="AA226">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB226">
         <v>2</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q227">
         <v>1.83</v>
@@ -37349,10 +37349,10 @@
         <v>3.28</v>
       </c>
       <c r="AA227">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB227">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC227">
         <v>3.08</v>
@@ -37364,10 +37364,10 @@
         <v>1.07</v>
       </c>
       <c r="AF227">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG227">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>1.14</v>
       </c>
       <c r="AK227">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37639,10 +37639,10 @@
         <v>1.53</v>
       </c>
       <c r="O229">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P229">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q229">
         <v>2.02</v>
@@ -37660,7 +37660,7 @@
         <v>2.5</v>
       </c>
       <c r="V229">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W229">
         <v>1.08</v>
@@ -37811,7 +37811,7 @@
         <v>3.56</v>
       </c>
       <c r="R230">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S230">
         <v>1.4</v>
@@ -38291,13 +38291,13 @@
         <v>1.85</v>
       </c>
       <c r="O233">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P233">
         <v>4.1</v>
       </c>
       <c r="Q233">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="R233">
         <v>2.28</v>
@@ -38312,19 +38312,19 @@
         <v>2.4</v>
       </c>
       <c r="V233">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W233">
         <v>1.1</v>
       </c>
       <c r="X233">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
         <v>1.18</v>
       </c>
       <c r="Z233">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA233">
         <v>1.66</v>
@@ -38333,19 +38333,19 @@
         <v>2.2</v>
       </c>
       <c r="AC233">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AD233">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE233">
         <v>1.13</v>
       </c>
       <c r="AF233">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG233">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.29</v>
       </c>
       <c r="AK233">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38641,7 +38641,7 @@
         <v>1.39</v>
       </c>
       <c r="W235">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X235">
         <v>1.01</v>
@@ -38662,7 +38662,7 @@
         <v>3.34</v>
       </c>
       <c r="AD235">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE235">
         <v>1.05</v>
@@ -38816,7 +38816,7 @@
         <v>3</v>
       </c>
       <c r="AA236">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB236">
         <v>1.68</v>
@@ -38825,13 +38825,13 @@
         <v>3.74</v>
       </c>
       <c r="AD236">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE236">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF236">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG236">
         <v>1.87</v>
@@ -39604,7 +39604,7 @@
         <v>4.75</v>
       </c>
       <c r="R241">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S241">
         <v>1.25</v>
@@ -40090,7 +40090,7 @@
         <v>5.5</v>
       </c>
       <c r="Q244">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R244">
         <v>2.38</v>
@@ -40099,7 +40099,7 @@
         <v>1.29</v>
       </c>
       <c r="T244">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U244">
         <v>2.38</v>
@@ -40126,7 +40126,7 @@
         <v>2.25</v>
       </c>
       <c r="AC244">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD244">
         <v>1.51</v>
@@ -40265,7 +40265,7 @@
         <v>3.78</v>
       </c>
       <c r="U245">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V245">
         <v>1.7</v>
@@ -40289,7 +40289,7 @@
         <v>2.88</v>
       </c>
       <c r="AC245">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AD245">
         <v>1.78</v>
@@ -40317,7 +40317,7 @@
         <v>1.25</v>
       </c>
       <c r="AK245">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>5.2</v>
       </c>
       <c r="AA246">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB246">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC246">
         <v>2.08</v>
@@ -40464,7 +40464,7 @@
         <v>2.14</v>
       </c>
       <c r="AG246">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,7 +40477,7 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK246">
         <v>4.7</v>
@@ -40579,10 +40579,10 @@
         <v>0</v>
       </c>
       <c r="Q247">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R247">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S247">
         <v>1.34</v>
@@ -41421,7 +41421,7 @@
         <v>1.13</v>
       </c>
       <c r="Z252">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="AA252">
         <v>1.49</v>
@@ -41569,7 +41569,7 @@
         <v>4</v>
       </c>
       <c r="U253">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V253">
         <v>1.69</v>
@@ -41578,28 +41578,28 @@
         <v>1.17</v>
       </c>
       <c r="X253">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y253">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z253">
-        <v>5.69</v>
+        <v>5.77</v>
       </c>
       <c r="AA253">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB253">
         <v>2.75</v>
       </c>
       <c r="AC253">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD253">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE253">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF253">
         <v>1.5</v>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AK253">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41720,7 +41720,7 @@
         <v>4</v>
       </c>
       <c r="Q254">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R254">
         <v>2.2</v>
@@ -41732,7 +41732,7 @@
         <v>2.62</v>
       </c>
       <c r="U254">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V254">
         <v>1.39</v>
@@ -42526,13 +42526,13 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O259">
         <v>4.33</v>
       </c>
       <c r="P259">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q259">
         <v>1.92</v>
@@ -43036,7 +43036,7 @@
         <v>3.75</v>
       </c>
       <c r="U262">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V262">
         <v>1.58</v>
@@ -43051,13 +43051,13 @@
         <v>1.13</v>
       </c>
       <c r="Z262">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA262">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB262">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="AC262">
         <v>2.4</v>
@@ -43069,10 +43069,10 @@
         <v>1.21</v>
       </c>
       <c r="AF262">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG262">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>1.36</v>
       </c>
       <c r="T263">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U263">
         <v>2.69</v>
@@ -43208,7 +43208,7 @@
         <v>1.05</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
         <v>1.31</v>
@@ -43229,10 +43229,10 @@
         <v>1.25</v>
       </c>
       <c r="AE263">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF263">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG263">
         <v>2</v>
@@ -43341,16 +43341,16 @@
         </is>
       </c>
       <c r="N264">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O264">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P264">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q264">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R264">
         <v>2.4</v>
@@ -43377,7 +43377,7 @@
         <v>1.1</v>
       </c>
       <c r="Z264">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA264">
         <v>1.5</v>
@@ -43386,19 +43386,19 @@
         <v>2.53</v>
       </c>
       <c r="AC264">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD264">
         <v>1.61</v>
       </c>
       <c r="AE264">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF264">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG264">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>1.14</v>
       </c>
       <c r="AK264">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -44334,7 +44334,7 @@
         <v>2.2</v>
       </c>
       <c r="S270">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T270">
         <v>2.88</v>
@@ -44355,7 +44355,7 @@
         <v>1.16</v>
       </c>
       <c r="Z270">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AA270">
         <v>1.7</v>
@@ -44364,7 +44364,7 @@
         <v>2.11</v>
       </c>
       <c r="AC270">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD270">
         <v>1.4</v>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK270">
         <v>1.24</v>
@@ -44491,7 +44491,7 @@
         <v>3.5</v>
       </c>
       <c r="Q271">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R271">
         <v>2.18</v>
@@ -44512,7 +44512,7 @@
         <v>1.11</v>
       </c>
       <c r="X271">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y271">
         <v>1.18</v>
@@ -44555,7 +44555,7 @@
         <v>1.22</v>
       </c>
       <c r="AK271">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,7 +44645,7 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="O272">
         <v>3.7</v>
@@ -44669,7 +44669,7 @@
         <v>2.25</v>
       </c>
       <c r="V272">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W272">
         <v>1.11</v>
@@ -44980,71 +44980,71 @@
         <v>0</v>
       </c>
       <c r="Q274">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="R274">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="S274">
         <v>1.32</v>
       </c>
       <c r="T274">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U274">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="V274">
         <v>1.5</v>
       </c>
       <c r="W274">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X274">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z274">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="AA274">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB274">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC274">
+        <v>2.75</v>
+      </c>
+      <c r="AD274">
+        <v>1.45</v>
+      </c>
+      <c r="AE274">
+        <v>1.13</v>
+      </c>
+      <c r="AF274">
+        <v>1.91</v>
+      </c>
+      <c r="AG274">
+        <v>1.78</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ274">
+        <v>1.14</v>
+      </c>
+      <c r="AK274">
         <v>2.8</v>
-      </c>
-      <c r="AD274">
-        <v>1.42</v>
-      </c>
-      <c r="AE274">
-        <v>1.11</v>
-      </c>
-      <c r="AF274">
-        <v>1.83</v>
-      </c>
-      <c r="AG274">
-        <v>1.83</v>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ274">
-        <v>1.17</v>
-      </c>
-      <c r="AK274">
-        <v>2.4</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45137,7 +45137,7 @@
         <v>3.1</v>
       </c>
       <c r="O275">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P275">
         <v>2.05</v>
@@ -45158,7 +45158,7 @@
         <v>2.3</v>
       </c>
       <c r="V275">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W275">
         <v>1.11</v>
@@ -45312,16 +45312,16 @@
         <v>2.75</v>
       </c>
       <c r="S276">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T276">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U276">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V276">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W276">
         <v>1.18</v>
@@ -45330,10 +45330,10 @@
         <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z276">
-        <v>6.28</v>
+        <v>6.66</v>
       </c>
       <c r="AA276">
         <v>1.4</v>
@@ -45342,13 +45342,13 @@
         <v>2.87</v>
       </c>
       <c r="AC276">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AD276">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE276">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF276">
         <v>1.5</v>
@@ -45367,7 +45367,7 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK276">
         <v>2.5</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O278">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="P278">
-        <v>2.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q278">
-        <v>4.11</v>
+        <v>2.36</v>
       </c>
       <c r="R278">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S278">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T278">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="U278">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V278">
         <v>1.22</v>
       </c>
       <c r="W278">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X278">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y278">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Z278">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AA278">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB278">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AC278">
-        <v>5.55</v>
+        <v>4.85</v>
       </c>
       <c r="AD278">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE278">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF278">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AG278">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O279">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P279">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q279">
-        <v>2.36</v>
+        <v>4.11</v>
       </c>
       <c r="R279">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S279">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T279">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V279">
         <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y279">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Z279">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AA279">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
+        <v>1.35</v>
+      </c>
+      <c r="AC279">
+        <v>5.55</v>
+      </c>
+      <c r="AD279">
+        <v>1.08</v>
+      </c>
+      <c r="AE279">
+        <v>1.03</v>
+      </c>
+      <c r="AF279">
+        <v>2.23</v>
+      </c>
+      <c r="AG279">
+        <v>1.57</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.44</v>
       </c>
-      <c r="AC279">
-        <v>4.85</v>
-      </c>
-      <c r="AD279">
-        <v>1.11</v>
-      </c>
-      <c r="AE279">
-        <v>1.01</v>
-      </c>
-      <c r="AF279">
-        <v>2.4</v>
-      </c>
-      <c r="AG279">
-        <v>1.48</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.25</v>
-      </c>
       <c r="AK279">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46145,16 +46145,16 @@
         <v>1.02</v>
       </c>
       <c r="Y281">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z281">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA281">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AB281">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="AC281">
         <v>2.14</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AK281">
         <v>1.53</v>
@@ -47108,7 +47108,7 @@
         <v>1.43</v>
       </c>
       <c r="T287">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U287">
         <v>2.96</v>
@@ -47129,7 +47129,7 @@
         <v>3.14</v>
       </c>
       <c r="AA287">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB287">
         <v>1.87</v>
@@ -47144,10 +47144,10 @@
         <v>1.06</v>
       </c>
       <c r="AF287">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG287">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47265,7 +47265,7 @@
         <v>3.3</v>
       </c>
       <c r="R288">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S288">
         <v>1.36</v>
@@ -47277,10 +47277,10 @@
         <v>2.75</v>
       </c>
       <c r="V288">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W288">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X288">
         <v>1</v>
@@ -47289,16 +47289,16 @@
         <v>1.26</v>
       </c>
       <c r="Z288">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="AA288">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB288">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC288">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AD288">
         <v>1.37</v>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AK288">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,19 +47416,19 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="O289">
         <v>3.6</v>
       </c>
       <c r="P289">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="Q289">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R289">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S289">
         <v>1.38</v>
@@ -47437,7 +47437,7 @@
         <v>2.88</v>
       </c>
       <c r="U289">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V289">
         <v>1.4</v>
@@ -47449,22 +47449,22 @@
         <v>1.01</v>
       </c>
       <c r="Y289">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z289">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA289">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB289">
         <v>1.88</v>
       </c>
       <c r="AC289">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD289">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE289">
         <v>1.07</v>
@@ -47473,7 +47473,7 @@
         <v>1.83</v>
       </c>
       <c r="AG289">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK289">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47621,7 +47621,7 @@
         <v>1.5</v>
       </c>
       <c r="AB290">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC290">
         <v>2.35</v>
@@ -47633,7 +47633,7 @@
         <v>1.21</v>
       </c>
       <c r="AF290">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG290">
         <v>2.56</v>
@@ -48738,7 +48738,7 @@
         <v>1.39</v>
       </c>
       <c r="T297">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U297">
         <v>2.63</v>
@@ -48750,7 +48750,7 @@
         <v>1.06</v>
       </c>
       <c r="X297">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y297">
         <v>1.25</v>
@@ -48759,10 +48759,10 @@
         <v>3.5</v>
       </c>
       <c r="AA297">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB297">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC297">
         <v>2.92</v>
@@ -48793,7 +48793,7 @@
         <v>1.3</v>
       </c>
       <c r="AK297">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49046,80 +49046,80 @@
         </is>
       </c>
       <c r="N299">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O299">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P299">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Q299">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R299">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="S299">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T299">
-        <v>4.35</v>
+        <v>4.85</v>
       </c>
       <c r="U299">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V299">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="W299">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X299">
         <v>1.01</v>
       </c>
       <c r="Y299">
+        <v>1.05</v>
+      </c>
+      <c r="Z299">
+        <v>7.1</v>
+      </c>
+      <c r="AA299">
+        <v>1.27</v>
+      </c>
+      <c r="AB299">
+        <v>3.3</v>
+      </c>
+      <c r="AC299">
+        <v>1.66</v>
+      </c>
+      <c r="AD299">
+        <v>2.06</v>
+      </c>
+      <c r="AE299">
+        <v>1.49</v>
+      </c>
+      <c r="AF299">
+        <v>1.67</v>
+      </c>
+      <c r="AG299">
+        <v>2.04</v>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ299">
         <v>1.06</v>
       </c>
-      <c r="Z299">
-        <v>6.05</v>
-      </c>
-      <c r="AA299">
-        <v>1.33</v>
-      </c>
-      <c r="AB299">
-        <v>2.95</v>
-      </c>
-      <c r="AC299">
-        <v>1.81</v>
-      </c>
-      <c r="AD299">
-        <v>1.86</v>
-      </c>
-      <c r="AE299">
-        <v>1.38</v>
-      </c>
-      <c r="AF299">
-        <v>1.73</v>
-      </c>
-      <c r="AG299">
-        <v>1.95</v>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ299">
-        <v>1.07</v>
-      </c>
       <c r="AK299">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49547,22 +49547,22 @@
         <v>1.53</v>
       </c>
       <c r="R302">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S302">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T302">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U302">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="V302">
         <v>1.68</v>
       </c>
       <c r="W302">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X302">
         <v>1.01</v>
@@ -49586,7 +49586,7 @@
         <v>1.79</v>
       </c>
       <c r="AE302">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AF302">
         <v>1.91</v>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK302">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49707,25 +49707,25 @@
         <v>3</v>
       </c>
       <c r="Q303">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="R303">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="S303">
         <v>1.49</v>
       </c>
       <c r="T303">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="U303">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V303">
         <v>1.29</v>
       </c>
       <c r="W303">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X303">
         <v>1.05</v>
@@ -49734,19 +49734,19 @@
         <v>1.4</v>
       </c>
       <c r="Z303">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AA303">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB303">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC303">
-        <v>4.2</v>
+        <v>4.53</v>
       </c>
       <c r="AD303">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE303">
         <v>1.02</v>
@@ -49771,7 +49771,7 @@
         <v>1.33</v>
       </c>
       <c r="AK303">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O308">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P308">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O310">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P310">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -50878,10 +50878,10 @@
         <v>0</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC310">
         <v>0</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O326">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="P326">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53486,10 +53486,10 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB326">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AC326">
         <v>0</v>
@@ -53613,61 +53613,61 @@
         <v>1.75</v>
       </c>
       <c r="O327">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P327">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S327">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T327">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U327">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V327">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W327">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y327">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z327">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE327">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF327">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG327">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK327">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -54760,55 +54760,55 @@
         <v>0</v>
       </c>
       <c r="Q334">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R334">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S334">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T334">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U334">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V334">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W334">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X334">
         <v>1.03</v>
       </c>
       <c r="Y334">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z334">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA334">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB334">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC334">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD334">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE334">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF334">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG334">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
@@ -54821,10 +54821,10 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK334">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL334">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -804,7 +804,7 @@
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
         <v>3.28</v>
@@ -840,13 +840,13 @@
         <v>1.99</v>
       </c>
       <c r="AB3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
@@ -997,7 +997,7 @@
         <v>1.14</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA4">
         <v>1.57</v>
@@ -1009,13 +1009,13 @@
         <v>2.5</v>
       </c>
       <c r="AD4">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
         <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
         <v>2.25</v>
@@ -1142,16 +1142,16 @@
         <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="U5">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="V5">
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1160,13 +1160,13 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="AA5">
         <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <v>3.1</v>
@@ -1181,7 +1181,7 @@
         <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1326,16 +1326,16 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
         <v>1.05</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
         <v>1.17</v>
@@ -2636,10 +2636,10 @@
         <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
         <v>1.12</v>
@@ -3753,7 +3753,7 @@
         <v>2.97</v>
       </c>
       <c r="U21">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
         <v>1.39</v>
@@ -3777,7 +3777,7 @@
         <v>1.8</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="AD21">
         <v>1.27</v>
@@ -3925,7 +3925,7 @@
         <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.11</v>
@@ -3934,7 +3934,7 @@
         <v>4.85</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
         <v>2.4</v>
@@ -5579,10 +5579,10 @@
         <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.99</v>
       </c>
       <c r="AK32">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>3.41</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Q33">
         <v>2.5</v>
@@ -5703,7 +5703,7 @@
         <v>2.39</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
         <v>3.4</v>
@@ -5718,13 +5718,13 @@
         <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
@@ -5742,10 +5742,10 @@
         <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -7372,10 +7372,10 @@
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
+        <v>3.25</v>
+      </c>
+      <c r="O55">
+        <v>3.8</v>
+      </c>
+      <c r="P55">
+        <v>2.05</v>
+      </c>
+      <c r="Q55">
+        <v>3.13</v>
+      </c>
+      <c r="R55">
+        <v>2.32</v>
+      </c>
+      <c r="S55">
+        <v>1.22</v>
+      </c>
+      <c r="T55">
+        <v>3.48</v>
+      </c>
+      <c r="U55">
+        <v>2.1</v>
+      </c>
+      <c r="V55">
+        <v>1.67</v>
+      </c>
+      <c r="W55">
+        <v>1.17</v>
+      </c>
+      <c r="X55">
+        <v>1.02</v>
+      </c>
+      <c r="Y55">
+        <v>1.13</v>
+      </c>
+      <c r="Z55">
+        <v>5.5</v>
+      </c>
+      <c r="AA55">
+        <v>1.47</v>
+      </c>
+      <c r="AB55">
+        <v>2.45</v>
+      </c>
+      <c r="AC55">
+        <v>2.17</v>
+      </c>
+      <c r="AD55">
+        <v>1.63</v>
+      </c>
+      <c r="AE55">
+        <v>1.23</v>
+      </c>
+      <c r="AF55">
+        <v>1.44</v>
+      </c>
+      <c r="AG55">
         <v>2.5</v>
-      </c>
-      <c r="O55">
-        <v>3.45</v>
-      </c>
-      <c r="P55">
-        <v>2.48</v>
-      </c>
-      <c r="Q55">
-        <v>3.17</v>
-      </c>
-      <c r="R55">
-        <v>2.2</v>
-      </c>
-      <c r="S55">
-        <v>1.35</v>
-      </c>
-      <c r="T55">
-        <v>3</v>
-      </c>
-      <c r="U55">
-        <v>2.7</v>
-      </c>
-      <c r="V55">
-        <v>1.4</v>
-      </c>
-      <c r="W55">
-        <v>1.08</v>
-      </c>
-      <c r="X55">
-        <v>1.04</v>
-      </c>
-      <c r="Y55">
-        <v>1.29</v>
-      </c>
-      <c r="Z55">
-        <v>3.65</v>
-      </c>
-      <c r="AA55">
-        <v>1.93</v>
-      </c>
-      <c r="AB55">
-        <v>1.87</v>
-      </c>
-      <c r="AC55">
-        <v>3.04</v>
-      </c>
-      <c r="AD55">
-        <v>1.29</v>
-      </c>
-      <c r="AE55">
-        <v>1.07</v>
-      </c>
-      <c r="AF55">
-        <v>1.65</v>
-      </c>
-      <c r="AG55">
-        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P56">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q56">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R56">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T56">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="U56">
+        <v>2.7</v>
+      </c>
+      <c r="V56">
+        <v>1.4</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.04</v>
+      </c>
+      <c r="Y56">
+        <v>1.29</v>
+      </c>
+      <c r="Z56">
+        <v>3.65</v>
+      </c>
+      <c r="AA56">
+        <v>1.93</v>
+      </c>
+      <c r="AB56">
+        <v>1.87</v>
+      </c>
+      <c r="AC56">
+        <v>3.04</v>
+      </c>
+      <c r="AD56">
+        <v>1.29</v>
+      </c>
+      <c r="AE56">
+        <v>1.07</v>
+      </c>
+      <c r="AF56">
+        <v>1.65</v>
+      </c>
+      <c r="AG56">
         <v>2.1</v>
-      </c>
-      <c r="V56">
-        <v>1.66</v>
-      </c>
-      <c r="W56">
-        <v>1.16</v>
-      </c>
-      <c r="X56">
-        <v>1.02</v>
-      </c>
-      <c r="Y56">
-        <v>1.13</v>
-      </c>
-      <c r="Z56">
-        <v>5.5</v>
-      </c>
-      <c r="AA56">
-        <v>1.47</v>
-      </c>
-      <c r="AB56">
-        <v>2.45</v>
-      </c>
-      <c r="AC56">
-        <v>2.17</v>
-      </c>
-      <c r="AD56">
-        <v>1.63</v>
-      </c>
-      <c r="AE56">
-        <v>1.23</v>
-      </c>
-      <c r="AF56">
-        <v>1.44</v>
-      </c>
-      <c r="AG56">
-        <v>2.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
         <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="R65">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V65">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
         <v>1.14</v>
@@ -10937,31 +10937,31 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA65">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AD65">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
         <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T66">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="U66">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W66">
         <v>1.14</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB66">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AC66">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AD66">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF66">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK69">
         <v>1.6</v>
@@ -12703,7 +12703,7 @@
         <v>3.15</v>
       </c>
       <c r="P76">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q76">
         <v>2.87</v>
@@ -12712,7 +12712,7 @@
         <v>2.15</v>
       </c>
       <c r="S76">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T76">
         <v>2.88</v>
@@ -12730,10 +12730,10 @@
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z76">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA76">
         <v>1.95</v>
@@ -12751,10 +12751,10 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG76">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12884,16 +12884,16 @@
         <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
         <v>3.58</v>
@@ -12917,7 +12917,7 @@
         <v>1.62</v>
       </c>
       <c r="AG77">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>1.76</v>
       </c>
       <c r="AC78">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AD78">
         <v>1.25</v>
@@ -13189,10 +13189,10 @@
         <v>1.55</v>
       </c>
       <c r="O79">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="Q79">
         <v>2.05</v>
@@ -13231,10 +13231,10 @@
         <v>1.83</v>
       </c>
       <c r="AC79">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="AD79">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE79">
         <v>1.11</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="O80">
         <v>3.2</v>
@@ -13358,10 +13358,10 @@
         <v>2.9</v>
       </c>
       <c r="Q80">
-        <v>2.77</v>
+        <v>3.06</v>
       </c>
       <c r="R80">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S80">
         <v>1.36</v>
@@ -13382,22 +13382,22 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AA80">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB80">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC80">
         <v>3.53</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE80">
         <v>1.06</v>
@@ -13527,7 +13527,7 @@
         <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
         <v>2.9</v>
@@ -13539,7 +13539,7 @@
         <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -13566,11 +13566,11 @@
         <v>1.07</v>
       </c>
       <c r="AF81">
+        <v>1.78</v>
+      </c>
+      <c r="AG81">
         <v>1.91</v>
       </c>
-      <c r="AG81">
-        <v>1.8</v>
-      </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK81">
         <v>1.99</v>
@@ -13684,7 +13684,7 @@
         <v>3.5</v>
       </c>
       <c r="Q82">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R82">
         <v>2</v>
@@ -13714,13 +13714,13 @@
         <v>2.74</v>
       </c>
       <c r="AA82">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB82">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC82">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD82">
         <v>1.17</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK82">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13865,7 +13865,7 @@
         <v>1.31</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.03</v>
@@ -13880,7 +13880,7 @@
         <v>2.06</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC83">
         <v>3.81</v>
@@ -15685,10 +15685,10 @@
         <v>1.17</v>
       </c>
       <c r="AF94">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG94">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U95">
         <v>2.5</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O121">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P121">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R121">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T121">
         <v>3.12</v>
       </c>
       <c r="U121">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V121">
         <v>1.44</v>
       </c>
       <c r="W121">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z121">
-        <v>3.52</v>
+        <v>3.76</v>
       </c>
       <c r="AA121">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC121">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD121">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE121">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AG121">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="AK121">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P122">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="Q122">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S122">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
         <v>3.12</v>
       </c>
       <c r="U122">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V122">
         <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="AA122">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD122">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG122">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AK122">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,80 +21988,80 @@
         </is>
       </c>
       <c r="N133">
+        <v>2.3</v>
+      </c>
+      <c r="O133">
+        <v>3.5</v>
+      </c>
+      <c r="P133">
+        <v>2.8</v>
+      </c>
+      <c r="Q133">
+        <v>3.1</v>
+      </c>
+      <c r="R133">
+        <v>2</v>
+      </c>
+      <c r="S133">
+        <v>1.43</v>
+      </c>
+      <c r="T133">
+        <v>2.88</v>
+      </c>
+      <c r="U133">
+        <v>3.07</v>
+      </c>
+      <c r="V133">
+        <v>1.37</v>
+      </c>
+      <c r="W133">
+        <v>1.05</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
+        <v>1.3</v>
+      </c>
+      <c r="Z133">
+        <v>2.97</v>
+      </c>
+      <c r="AA133">
+        <v>2</v>
+      </c>
+      <c r="AB133">
+        <v>1.73</v>
+      </c>
+      <c r="AC133">
+        <v>3.5</v>
+      </c>
+      <c r="AD133">
+        <v>1.22</v>
+      </c>
+      <c r="AE133">
+        <v>1.05</v>
+      </c>
+      <c r="AF133">
+        <v>1.79</v>
+      </c>
+      <c r="AG133">
+        <v>1.93</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
+        <v>1.4</v>
+      </c>
+      <c r="AK133">
         <v>1.48</v>
-      </c>
-      <c r="O133">
-        <v>4.6</v>
-      </c>
-      <c r="P133">
-        <v>6</v>
-      </c>
-      <c r="Q133">
-        <v>1.87</v>
-      </c>
-      <c r="R133">
-        <v>2.6</v>
-      </c>
-      <c r="S133">
-        <v>1.19</v>
-      </c>
-      <c r="T133">
-        <v>3.8</v>
-      </c>
-      <c r="U133">
-        <v>2.15</v>
-      </c>
-      <c r="V133">
-        <v>1.67</v>
-      </c>
-      <c r="W133">
-        <v>1.15</v>
-      </c>
-      <c r="X133">
-        <v>1.02</v>
-      </c>
-      <c r="Y133">
-        <v>1.13</v>
-      </c>
-      <c r="Z133">
-        <v>5.62</v>
-      </c>
-      <c r="AA133">
-        <v>1.47</v>
-      </c>
-      <c r="AB133">
-        <v>2.43</v>
-      </c>
-      <c r="AC133">
-        <v>2.2</v>
-      </c>
-      <c r="AD133">
-        <v>1.62</v>
-      </c>
-      <c r="AE133">
-        <v>1.22</v>
-      </c>
-      <c r="AF133">
-        <v>1.62</v>
-      </c>
-      <c r="AG133">
-        <v>2.16</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>1.08</v>
-      </c>
-      <c r="AK133">
-        <v>2.5</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R134">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T134">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="U134">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V134">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X134">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
         <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA134">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AB134">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC134">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD134">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF134">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG134">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK134">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P135">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="Q135">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="R135">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="S135">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U135">
-        <v>3.07</v>
+        <v>2.15</v>
       </c>
       <c r="V135">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z135">
-        <v>2.97</v>
+        <v>5.62</v>
       </c>
       <c r="AA135">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AB135">
-        <v>1.73</v>
+        <v>2.43</v>
       </c>
       <c r="AC135">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD135">
+        <v>1.62</v>
+      </c>
+      <c r="AE135">
         <v>1.22</v>
       </c>
-      <c r="AE135">
-        <v>1.05</v>
-      </c>
       <c r="AF135">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG135">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK135">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O136">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="U136">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="V136">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W136">
+        <v>1.07</v>
+      </c>
+      <c r="X136">
         <v>1.03</v>
-      </c>
-      <c r="X136">
-        <v>1.02</v>
       </c>
       <c r="Y136">
         <v>1.26</v>
       </c>
       <c r="Z136">
+        <v>3.6</v>
+      </c>
+      <c r="AA136">
+        <v>1.84</v>
+      </c>
+      <c r="AB136">
+        <v>1.85</v>
+      </c>
+      <c r="AC136">
         <v>3.2</v>
       </c>
-      <c r="AA136">
-        <v>1.98</v>
-      </c>
-      <c r="AB136">
-        <v>1.81</v>
-      </c>
-      <c r="AC136">
-        <v>3.28</v>
-      </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG136">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O144">
         <v>3.4</v>
       </c>
       <c r="P144">
-        <v>2.45</v>
+        <v>3.11</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="R144">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T144">
         <v>2.88</v>
       </c>
       <c r="U144">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W144">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X144">
+        <v>1.05</v>
+      </c>
+      <c r="Y144">
+        <v>1.33</v>
+      </c>
+      <c r="Z144">
+        <v>2.94</v>
+      </c>
+      <c r="AA144">
+        <v>2.05</v>
+      </c>
+      <c r="AB144">
+        <v>1.76</v>
+      </c>
+      <c r="AC144">
+        <v>3.42</v>
+      </c>
+      <c r="AD144">
+        <v>1.23</v>
+      </c>
+      <c r="AE144">
         <v>1.04</v>
       </c>
-      <c r="Y144">
-        <v>1.29</v>
-      </c>
-      <c r="Z144">
-        <v>3.2</v>
-      </c>
-      <c r="AA144">
-        <v>1.84</v>
-      </c>
-      <c r="AB144">
-        <v>1.83</v>
-      </c>
-      <c r="AC144">
-        <v>2.97</v>
-      </c>
-      <c r="AD144">
-        <v>1.29</v>
-      </c>
-      <c r="AE144">
-        <v>1.07</v>
-      </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG144">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O145">
+        <v>3.46</v>
+      </c>
+      <c r="P145">
+        <v>2.3</v>
+      </c>
+      <c r="Q145">
+        <v>3.5</v>
+      </c>
+      <c r="R145">
+        <v>2.4</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
         <v>3.4</v>
       </c>
-      <c r="P145">
-        <v>3.11</v>
-      </c>
-      <c r="Q145">
-        <v>2.68</v>
-      </c>
-      <c r="R145">
-        <v>2.05</v>
-      </c>
-      <c r="S145">
-        <v>1.4</v>
-      </c>
-      <c r="T145">
-        <v>2.88</v>
-      </c>
       <c r="U145">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="V145">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W145">
+        <v>1.1</v>
+      </c>
+      <c r="X145">
         <v>1.02</v>
       </c>
-      <c r="X145">
-        <v>1.05</v>
-      </c>
       <c r="Y145">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z145">
-        <v>2.94</v>
+        <v>4.15</v>
       </c>
       <c r="AA145">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB145">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC145">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD145">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK145">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
+        <v>2.8</v>
+      </c>
+      <c r="O146">
+        <v>3.4</v>
+      </c>
+      <c r="P146">
+        <v>2.45</v>
+      </c>
+      <c r="Q146">
+        <v>3.4</v>
+      </c>
+      <c r="R146">
+        <v>2.09</v>
+      </c>
+      <c r="S146">
+        <v>1.35</v>
+      </c>
+      <c r="T146">
         <v>2.88</v>
       </c>
-      <c r="O146">
-        <v>3.46</v>
-      </c>
-      <c r="P146">
-        <v>2.3</v>
-      </c>
-      <c r="Q146">
-        <v>3.5</v>
-      </c>
-      <c r="R146">
-        <v>2.4</v>
-      </c>
-      <c r="S146">
+      <c r="U146">
+        <v>2.75</v>
+      </c>
+      <c r="V146">
+        <v>1.4</v>
+      </c>
+      <c r="W146">
+        <v>1.08</v>
+      </c>
+      <c r="X146">
+        <v>1.04</v>
+      </c>
+      <c r="Y146">
         <v>1.29</v>
       </c>
-      <c r="T146">
-        <v>3.4</v>
-      </c>
-      <c r="U146">
-        <v>2.47</v>
-      </c>
-      <c r="V146">
-        <v>1.52</v>
-      </c>
-      <c r="W146">
-        <v>1.1</v>
-      </c>
-      <c r="X146">
-        <v>1.02</v>
-      </c>
-      <c r="Y146">
-        <v>1.16</v>
-      </c>
       <c r="Z146">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA146">
+        <v>1.84</v>
+      </c>
+      <c r="AB146">
+        <v>1.83</v>
+      </c>
+      <c r="AC146">
+        <v>2.97</v>
+      </c>
+      <c r="AD146">
+        <v>1.29</v>
+      </c>
+      <c r="AE146">
+        <v>1.07</v>
+      </c>
+      <c r="AF146">
         <v>1.65</v>
       </c>
-      <c r="AB146">
-        <v>2.15</v>
-      </c>
-      <c r="AC146">
-        <v>2.49</v>
-      </c>
-      <c r="AD146">
-        <v>1.42</v>
-      </c>
-      <c r="AE146">
-        <v>1.13</v>
-      </c>
-      <c r="AF146">
-        <v>1.57</v>
-      </c>
       <c r="AG146">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25592,7 +25592,7 @@
         <v>1.4</v>
       </c>
       <c r="T155">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U155">
         <v>3.2</v>
@@ -25610,7 +25610,7 @@
         <v>1.33</v>
       </c>
       <c r="Z155">
-        <v>3.07</v>
+        <v>2.76</v>
       </c>
       <c r="AA155">
         <v>2.15</v>
@@ -25628,7 +25628,7 @@
         <v>1.04</v>
       </c>
       <c r="AF155">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG155">
         <v>1.86</v>
@@ -25767,7 +25767,7 @@
         <v>1.11</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
         <v>1.17</v>
@@ -25779,7 +25779,7 @@
         <v>1.6</v>
       </c>
       <c r="AB156">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC156">
         <v>2.47</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="O157">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="Q157">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R157">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S157">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T157">
-        <v>3.14</v>
+        <v>2.82</v>
       </c>
       <c r="U157">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V157">
         <v>1.43</v>
       </c>
       <c r="W157">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X157">
         <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z157">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA157">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB157">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC157">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AD157">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE157">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF157">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG157">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="O158">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="P158">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q158">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R158">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T158">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="U158">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="V158">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W158">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA158">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AB158">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AC158">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="AD158">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE158">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF158">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AG158">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AK158">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,25 +26226,25 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="O159">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P159">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q159">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R159">
         <v>2.31</v>
       </c>
       <c r="S159">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T159">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U159">
         <v>2.44</v>
@@ -26259,7 +26259,7 @@
         <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z159">
         <v>3.8</v>
@@ -26268,7 +26268,7 @@
         <v>1.62</v>
       </c>
       <c r="AB159">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC159">
         <v>2.49</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,65 +26389,65 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="O160">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P160">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="Q160">
         <v>3</v>
       </c>
       <c r="R160">
+        <v>2.15</v>
+      </c>
+      <c r="S160">
+        <v>1.33</v>
+      </c>
+      <c r="T160">
+        <v>3.14</v>
+      </c>
+      <c r="U160">
+        <v>2.7</v>
+      </c>
+      <c r="V160">
+        <v>1.43</v>
+      </c>
+      <c r="W160">
+        <v>1.11</v>
+      </c>
+      <c r="X160">
+        <v>1.02</v>
+      </c>
+      <c r="Y160">
+        <v>1.19</v>
+      </c>
+      <c r="Z160">
+        <v>3.82</v>
+      </c>
+      <c r="AA160">
+        <v>1.75</v>
+      </c>
+      <c r="AB160">
+        <v>2.08</v>
+      </c>
+      <c r="AC160">
+        <v>3.07</v>
+      </c>
+      <c r="AD160">
+        <v>1.36</v>
+      </c>
+      <c r="AE160">
+        <v>1.11</v>
+      </c>
+      <c r="AF160">
+        <v>1.57</v>
+      </c>
+      <c r="AG160">
         <v>2.3</v>
       </c>
-      <c r="S160">
-        <v>1.27</v>
-      </c>
-      <c r="T160">
-        <v>3.32</v>
-      </c>
-      <c r="U160">
-        <v>2.3</v>
-      </c>
-      <c r="V160">
-        <v>1.52</v>
-      </c>
-      <c r="W160">
-        <v>1.1</v>
-      </c>
-      <c r="X160">
-        <v>1.01</v>
-      </c>
-      <c r="Y160">
-        <v>1.15</v>
-      </c>
-      <c r="Z160">
-        <v>4.2</v>
-      </c>
-      <c r="AA160">
-        <v>1.61</v>
-      </c>
-      <c r="AB160">
-        <v>2.23</v>
-      </c>
-      <c r="AC160">
-        <v>2.42</v>
-      </c>
-      <c r="AD160">
-        <v>1.44</v>
-      </c>
-      <c r="AE160">
-        <v>1.17</v>
-      </c>
-      <c r="AF160">
-        <v>1.53</v>
-      </c>
-      <c r="AG160">
-        <v>2.4</v>
-      </c>
       <c r="AH160" t="inlineStr">
         <is>
           <t>[]</t>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="O161">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="P161">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="Q161">
-        <v>4.46</v>
+        <v>2.67</v>
       </c>
       <c r="R161">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="S161">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T161">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U161">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W161">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X161">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z161">
         <v>3.6</v>
       </c>
       <c r="AA161">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AB161">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC161">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AD161">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE161">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF161">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O162">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P162">
-        <v>4</v>
+        <v>1.61</v>
       </c>
       <c r="Q162">
-        <v>2.4</v>
+        <v>4.46</v>
       </c>
       <c r="R162">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S162">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U162">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="V162">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W162">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X162">
         <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z162">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA162">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB162">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC162">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD162">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE162">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF162">
         <v>1.72</v>
       </c>
       <c r="AG162">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK162">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26878,16 +26878,16 @@
         </is>
       </c>
       <c r="N163">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O163">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="P163">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q163">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R163">
         <v>2.06</v>
@@ -26908,7 +26908,7 @@
         <v>1.07</v>
       </c>
       <c r="X163">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y163">
         <v>1.22</v>
@@ -26929,7 +26929,7 @@
         <v>1.28</v>
       </c>
       <c r="AE163">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF163">
         <v>1.68</v>
@@ -27095,7 +27095,7 @@
         <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG164">
         <v>1.65</v>
@@ -27216,7 +27216,7 @@
         <v>2.45</v>
       </c>
       <c r="R165">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S165">
         <v>1.28</v>
@@ -27240,7 +27240,7 @@
         <v>1.23</v>
       </c>
       <c r="Z165">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AA165">
         <v>1.72</v>
@@ -27258,7 +27258,7 @@
         <v>1.14</v>
       </c>
       <c r="AF165">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG165">
         <v>2.1</v>
@@ -27277,7 +27277,7 @@
         <v>1.25</v>
       </c>
       <c r="AK165">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O192">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P192">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q192">
         <v>2.5</v>
@@ -31629,7 +31629,7 @@
         <v>2.4</v>
       </c>
       <c r="V192">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W192">
         <v>1.1</v>
@@ -31638,13 +31638,13 @@
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z192">
         <v>4.21</v>
       </c>
       <c r="AA192">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB192">
         <v>2.13</v>
@@ -31662,7 +31662,7 @@
         <v>1.57</v>
       </c>
       <c r="AG192">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>3.68</v>
       </c>
       <c r="R228">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S228">
         <v>1.26</v>
@@ -37494,7 +37494,7 @@
         <v>3.24</v>
       </c>
       <c r="U228">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V228">
         <v>1.51</v>
@@ -44114,22 +44114,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44195,10 +44195,10 @@
         <v>0</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC269">
         <v>0</v>
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O270">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P270">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q270">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R270">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S270">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T270">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U270">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V270">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W270">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X270">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y270">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z270">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA270">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB270">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC270">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD270">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE270">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF270">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG270">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK270">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="O271">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P271">
-        <v>3.5</v>
+        <v>1.99</v>
       </c>
       <c r="Q271">
-        <v>2.4</v>
+        <v>4.07</v>
       </c>
       <c r="R271">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S271">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T271">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U271">
         <v>2.45</v>
       </c>
       <c r="V271">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W271">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X271">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y271">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z271">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA271">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB271">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AC271">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="AD271">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE271">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF271">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG271">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK271">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O272">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P272">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q272">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R272">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S272">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T272">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U272">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V272">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W272">
         <v>1.11</v>
       </c>
       <c r="X272">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y272">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z272">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="AA272">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB272">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AC272">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="AD272">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE272">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF272">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AG272">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>1.22</v>
       </c>
       <c r="AK272">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="O273">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="P273">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="Q273">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="R273">
-        <v>3.13</v>
+        <v>2.21</v>
       </c>
       <c r="S273">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="T273">
-        <v>4.8</v>
+        <v>3.24</v>
       </c>
       <c r="U273">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="V273">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="W273">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="X273">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="Z273">
-        <v>7.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA273">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="AB273">
-        <v>3.68</v>
+        <v>2.08</v>
       </c>
       <c r="AC273">
-        <v>1.67</v>
+        <v>2.52</v>
       </c>
       <c r="AD273">
-        <v>2.12</v>
+        <v>1.41</v>
       </c>
       <c r="AE273">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AF273">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG273">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
-        <v>3.58</v>
+        <v>1.86</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q274">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="R274">
-        <v>2.57</v>
+        <v>3.13</v>
       </c>
       <c r="S274">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="T274">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="U274">
-        <v>2.49</v>
+        <v>1.79</v>
       </c>
       <c r="V274">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="W274">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="X274">
         <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="Z274">
-        <v>3.78</v>
+        <v>7.2</v>
       </c>
       <c r="AA274">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="AB274">
-        <v>2.02</v>
+        <v>3.68</v>
       </c>
       <c r="AC274">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD274">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="AE274">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AF274">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AG274">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK274">
-        <v>2.8</v>
+        <v>3.58</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-19 15:15:00</t>
+          <t>2026-09-19 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,80 +45134,80 @@
         </is>
       </c>
       <c r="N275">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>3.85</v>
+        <v>1.83</v>
       </c>
       <c r="R275">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="S275">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T275">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U275">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="V275">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W275">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X275">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z275">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AA275">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB275">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC275">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD275">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE275">
+        <v>1.13</v>
+      </c>
+      <c r="AF275">
+        <v>1.91</v>
+      </c>
+      <c r="AG275">
+        <v>1.78</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ275">
         <v>1.14</v>
       </c>
-      <c r="AF275">
-        <v>1.55</v>
-      </c>
-      <c r="AG275">
-        <v>2.3</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ275">
-        <v>1.26</v>
-      </c>
       <c r="AK275">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="O276">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="P276">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="Q276">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="R276">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="S276">
+        <v>1.25</v>
+      </c>
+      <c r="T276">
+        <v>3.6</v>
+      </c>
+      <c r="U276">
+        <v>2.3</v>
+      </c>
+      <c r="V276">
+        <v>1.52</v>
+      </c>
+      <c r="W276">
+        <v>1.11</v>
+      </c>
+      <c r="X276">
+        <v>1</v>
+      </c>
+      <c r="Y276">
+        <v>1.17</v>
+      </c>
+      <c r="Z276">
+        <v>4</v>
+      </c>
+      <c r="AA276">
+        <v>1.6</v>
+      </c>
+      <c r="AB276">
+        <v>2.08</v>
+      </c>
+      <c r="AC276">
+        <v>2.6</v>
+      </c>
+      <c r="AD276">
+        <v>1.46</v>
+      </c>
+      <c r="AE276">
         <v>1.14</v>
       </c>
-      <c r="T276">
-        <v>4.8</v>
-      </c>
-      <c r="U276">
-        <v>1.95</v>
-      </c>
-      <c r="V276">
-        <v>1.74</v>
-      </c>
-      <c r="W276">
-        <v>1.18</v>
-      </c>
-      <c r="X276">
-        <v>1.01</v>
-      </c>
-      <c r="Y276">
-        <v>1.11</v>
-      </c>
-      <c r="Z276">
-        <v>6.66</v>
-      </c>
-      <c r="AA276">
-        <v>1.4</v>
-      </c>
-      <c r="AB276">
-        <v>2.87</v>
-      </c>
-      <c r="AC276">
-        <v>1.95</v>
-      </c>
-      <c r="AD276">
-        <v>1.88</v>
-      </c>
-      <c r="AE276">
-        <v>1.31</v>
-      </c>
       <c r="AF276">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG276">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK276">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-09-19 15:30:00</t>
+          <t>2026-09-19 15:15:00</t>
         </is>
       </c>
     </row>
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O277">
-        <v>2.62</v>
+        <v>4.9</v>
       </c>
       <c r="P277">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AA277">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AB277">
-        <v>1.36</v>
+        <v>2.87</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="O278">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="P278">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Q278">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R278">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S278">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T278">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U278">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V278">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W278">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X278">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y278">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z278">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA278">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB278">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC278">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AD278">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE278">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF278">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG278">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK278">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O279">
+        <v>3.25</v>
+      </c>
+      <c r="P279">
+        <v>5.25</v>
+      </c>
+      <c r="Q279">
+        <v>2.33</v>
+      </c>
+      <c r="R279">
+        <v>1.88</v>
+      </c>
+      <c r="S279">
+        <v>1.53</v>
+      </c>
+      <c r="T279">
+        <v>2.2</v>
+      </c>
+      <c r="U279">
+        <v>3.5</v>
+      </c>
+      <c r="V279">
+        <v>1.25</v>
+      </c>
+      <c r="W279">
+        <v>1.04</v>
+      </c>
+      <c r="X279">
+        <v>1.11</v>
+      </c>
+      <c r="Y279">
+        <v>1.54</v>
+      </c>
+      <c r="Z279">
+        <v>2.42</v>
+      </c>
+      <c r="AA279">
         <v>2.7</v>
       </c>
-      <c r="P279">
+      <c r="AB279">
+        <v>1.44</v>
+      </c>
+      <c r="AC279">
+        <v>4.85</v>
+      </c>
+      <c r="AD279">
+        <v>1.11</v>
+      </c>
+      <c r="AE279">
+        <v>1.01</v>
+      </c>
+      <c r="AF279">
         <v>2.4</v>
       </c>
-      <c r="Q279">
-        <v>4.11</v>
-      </c>
-      <c r="R279">
-        <v>1.85</v>
-      </c>
-      <c r="S279">
-        <v>1.57</v>
-      </c>
-      <c r="T279">
-        <v>2.13</v>
-      </c>
-      <c r="U279">
-        <v>3.6</v>
-      </c>
-      <c r="V279">
-        <v>1.22</v>
-      </c>
-      <c r="W279">
-        <v>1.03</v>
-      </c>
-      <c r="X279">
-        <v>1.13</v>
-      </c>
-      <c r="Y279">
-        <v>1.57</v>
-      </c>
-      <c r="Z279">
-        <v>2.2</v>
-      </c>
-      <c r="AA279">
-        <v>2.87</v>
-      </c>
-      <c r="AB279">
-        <v>1.35</v>
-      </c>
-      <c r="AC279">
-        <v>5.55</v>
-      </c>
-      <c r="AD279">
-        <v>1.08</v>
-      </c>
-      <c r="AE279">
-        <v>1.03</v>
-      </c>
-      <c r="AF279">
-        <v>2.23</v>
-      </c>
       <c r="AG279">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK279">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O280">
         <v>2.7</v>
       </c>
       <c r="P280">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA280">
         <v>2.87</v>
       </c>
       <c r="AB280">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -47763,16 +47763,16 @@
         <v>3.32</v>
       </c>
       <c r="U291">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="V291">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W291">
         <v>1.12</v>
       </c>
       <c r="X291">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
         <v>1.2</v>
@@ -48578,16 +48578,16 @@
         <v>2.2</v>
       </c>
       <c r="U296">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="V296">
         <v>1.2</v>
       </c>
       <c r="W296">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X296">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y296">
         <v>1.53</v>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK296">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48678,22 +48678,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,80 +48720,80 @@
         </is>
       </c>
       <c r="N297">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="O297">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="P297">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="Q297">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R297">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="S297">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="T297">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="U297">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="V297">
+        <v>1.17</v>
+      </c>
+      <c r="W297">
+        <v>1.02</v>
+      </c>
+      <c r="X297">
+        <v>1.09</v>
+      </c>
+      <c r="Y297">
+        <v>1.67</v>
+      </c>
+      <c r="Z297">
+        <v>2.03</v>
+      </c>
+      <c r="AA297">
+        <v>3.05</v>
+      </c>
+      <c r="AB297">
+        <v>1.28</v>
+      </c>
+      <c r="AC297">
+        <v>6.55</v>
+      </c>
+      <c r="AD297">
+        <v>1.05</v>
+      </c>
+      <c r="AE297">
+        <v>1.02</v>
+      </c>
+      <c r="AF297">
+        <v>2.4</v>
+      </c>
+      <c r="AG297">
+        <v>1.5</v>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ297">
+        <v>1.33</v>
+      </c>
+      <c r="AK297">
         <v>1.41</v>
-      </c>
-      <c r="W297">
-        <v>1.06</v>
-      </c>
-      <c r="X297">
-        <v>1.03</v>
-      </c>
-      <c r="Y297">
-        <v>1.25</v>
-      </c>
-      <c r="Z297">
-        <v>3.5</v>
-      </c>
-      <c r="AA297">
-        <v>1.93</v>
-      </c>
-      <c r="AB297">
-        <v>1.89</v>
-      </c>
-      <c r="AC297">
-        <v>2.92</v>
-      </c>
-      <c r="AD297">
-        <v>1.32</v>
-      </c>
-      <c r="AE297">
-        <v>1.09</v>
-      </c>
-      <c r="AF297">
-        <v>1.7</v>
-      </c>
-      <c r="AG297">
-        <v>2.01</v>
-      </c>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI297" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ297">
-        <v>1.3</v>
-      </c>
-      <c r="AK297">
-        <v>1.22</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -48841,22 +48841,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O298">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P298">
+        <v>2</v>
+      </c>
+      <c r="Q298">
+        <v>4</v>
+      </c>
+      <c r="R298">
+        <v>2.2</v>
+      </c>
+      <c r="S298">
+        <v>1.39</v>
+      </c>
+      <c r="T298">
+        <v>2.7</v>
+      </c>
+      <c r="U298">
         <v>2.63</v>
       </c>
-      <c r="Q298">
-        <v>0</v>
-      </c>
-      <c r="R298">
-        <v>0</v>
-      </c>
-      <c r="S298">
-        <v>0</v>
-      </c>
-      <c r="T298">
-        <v>0</v>
-      </c>
-      <c r="U298">
-        <v>0</v>
-      </c>
       <c r="V298">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W298">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y298">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z298">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA298">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB298">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC298">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD298">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE298">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG298">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK298">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49004,22 +49004,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,64 +49046,64 @@
         </is>
       </c>
       <c r="N299">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="O299">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="P299">
-        <v>1.18</v>
+        <v>2.63</v>
       </c>
       <c r="Q299">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="R299">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S299">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T299">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="U299">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="V299">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W299">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X299">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y299">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z299">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA299">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB299">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AC299">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD299">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE299">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF299">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG299">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK299">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.55</v>
+        <v>13</v>
       </c>
       <c r="O300">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="P300">
-        <v>2.55</v>
+        <v>1.18</v>
       </c>
       <c r="Q300">
-        <v>2.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R300">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="S300">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="T300">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="U300">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="V300">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="W300">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X300">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y300">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z300">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="AA300">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AB300">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC300">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="AD300">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AE300">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AF300">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AG300">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AK300">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="O301">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P301">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q301">
-        <v>2.29</v>
+        <v>2.92</v>
       </c>
       <c r="R301">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S301">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T301">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U301">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="V301">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W301">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X301">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y301">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z301">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="AA301">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AB301">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC301">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AD301">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AE301">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF301">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AG301">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK301">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-19 16:30:00</t>
+          <t>2026-09-19 16:00:00</t>
         </is>
       </c>
     </row>
@@ -49493,22 +49493,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="O302">
-        <v>7.2</v>
+        <v>4.05</v>
       </c>
       <c r="P302">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="Q302">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="R302">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="S302">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T302">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U302">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V302">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W302">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X302">
         <v>1.01</v>
       </c>
       <c r="Y302">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z302">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AA302">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB302">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AC302">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AD302">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AE302">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AF302">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="AG302">
-        <v>1.8</v>
+        <v>2.81</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK302">
-        <v>4.6</v>
+        <v>1.89</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49656,22 +49656,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="O303">
+        <v>7.2</v>
+      </c>
+      <c r="P303">
+        <v>13</v>
+      </c>
+      <c r="Q303">
+        <v>1.53</v>
+      </c>
+      <c r="R303">
+        <v>2.9</v>
+      </c>
+      <c r="S303">
+        <v>1.22</v>
+      </c>
+      <c r="T303">
+        <v>3.75</v>
+      </c>
+      <c r="U303">
+        <v>1.9</v>
+      </c>
+      <c r="V303">
+        <v>1.68</v>
+      </c>
+      <c r="W303">
+        <v>1.22</v>
+      </c>
+      <c r="X303">
+        <v>1.01</v>
+      </c>
+      <c r="Y303">
+        <v>1.06</v>
+      </c>
+      <c r="Z303">
+        <v>7</v>
+      </c>
+      <c r="AA303">
+        <v>1.36</v>
+      </c>
+      <c r="AB303">
         <v>3</v>
       </c>
-      <c r="P303">
-        <v>3</v>
-      </c>
-      <c r="Q303">
-        <v>3.05</v>
-      </c>
-      <c r="R303">
+      <c r="AC303">
         <v>2.03</v>
       </c>
-      <c r="S303">
-        <v>1.49</v>
-      </c>
-      <c r="T303">
-        <v>2.53</v>
-      </c>
-      <c r="U303">
-        <v>3.4</v>
-      </c>
-      <c r="V303">
-        <v>1.29</v>
-      </c>
-      <c r="W303">
-        <v>1.04</v>
-      </c>
-      <c r="X303">
-        <v>1.05</v>
-      </c>
-      <c r="Y303">
-        <v>1.4</v>
-      </c>
-      <c r="Z303">
-        <v>2.56</v>
-      </c>
-      <c r="AA303">
-        <v>2.25</v>
-      </c>
-      <c r="AB303">
-        <v>1.55</v>
-      </c>
-      <c r="AC303">
-        <v>4.53</v>
-      </c>
       <c r="AD303">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="AE303">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="AF303">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG303">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK303">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O304">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P304">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q304">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="R304">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="S304">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="T304">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="U304">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="V304">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W304">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X304">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y304">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z304">
-        <v>3.42</v>
+        <v>2.56</v>
       </c>
       <c r="AA304">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB304">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AC304">
-        <v>2.88</v>
+        <v>4.53</v>
       </c>
       <c r="AD304">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AE304">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AF304">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG304">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK304">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-19 17:00:00</t>
+          <t>2026-09-19 16:30:00</t>
         </is>
       </c>
     </row>
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G306">
@@ -50196,55 +50196,55 @@
         <v>0</v>
       </c>
       <c r="Q306">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R306">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S306">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T306">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U306">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V306">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W306">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X306">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y306">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z306">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA306">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB306">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC306">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD306">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE306">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF306">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG306">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK306">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
         <v>2.5</v>
       </c>
-      <c r="O307">
-        <v>2.7</v>
-      </c>
-      <c r="P307">
-        <v>2.8</v>
-      </c>
-      <c r="Q307">
-        <v>3.42</v>
-      </c>
       <c r="R307">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="S307">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="T307">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="U307">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="V307">
+        <v>1.58</v>
+      </c>
+      <c r="W307">
+        <v>1.14</v>
+      </c>
+      <c r="X307">
+        <v>1.02</v>
+      </c>
+      <c r="Y307">
+        <v>1.14</v>
+      </c>
+      <c r="Z307">
+        <v>4.7</v>
+      </c>
+      <c r="AA307">
+        <v>1.5</v>
+      </c>
+      <c r="AB307">
+        <v>2.33</v>
+      </c>
+      <c r="AC307">
+        <v>2.29</v>
+      </c>
+      <c r="AD307">
+        <v>1.53</v>
+      </c>
+      <c r="AE307">
         <v>1.17</v>
       </c>
-      <c r="W307">
-        <v>1.02</v>
-      </c>
-      <c r="X307">
-        <v>1.1</v>
-      </c>
-      <c r="Y307">
-        <v>1.68</v>
-      </c>
-      <c r="Z307">
-        <v>2.02</v>
-      </c>
-      <c r="AA307">
-        <v>3.05</v>
-      </c>
-      <c r="AB307">
-        <v>1.28</v>
-      </c>
-      <c r="AC307">
-        <v>6.55</v>
-      </c>
-      <c r="AD307">
-        <v>1.05</v>
-      </c>
-      <c r="AE307">
-        <v>1.02</v>
-      </c>
       <c r="AF307">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG307">
-        <v>1.49</v>
+        <v>2.38</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK307">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-19 18:00:00</t>
+          <t>2026-09-19 17:00:00</t>
         </is>
       </c>
     </row>
@@ -51352,7 +51352,7 @@
         <v>2.16</v>
       </c>
       <c r="V313">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W313">
         <v>1.17</v>
@@ -51542,7 +51542,7 @@
         <v>1.59</v>
       </c>
       <c r="AE314">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF314">
         <v>1.61</v>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK314">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51663,7 +51663,7 @@
         <v>2.8</v>
       </c>
       <c r="Q315">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="R315">
         <v>2.15</v>
@@ -51681,25 +51681,25 @@
         <v>1.44</v>
       </c>
       <c r="W315">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X315">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y315">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z315">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA315">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB315">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC315">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD315">
         <v>1.37</v>
@@ -51708,10 +51708,10 @@
         <v>1.14</v>
       </c>
       <c r="AF315">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG315">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK315">
         <v>1.49</v>
@@ -51826,16 +51826,16 @@
         <v>3.4</v>
       </c>
       <c r="Q316">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="R316">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S316">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T316">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U316">
         <v>3.4</v>
@@ -51850,16 +51850,16 @@
         <v>1.05</v>
       </c>
       <c r="Y316">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z316">
         <v>2.44</v>
       </c>
       <c r="AA316">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AB316">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC316">
         <v>4.8</v>
@@ -51871,10 +51871,10 @@
         <v>1</v>
       </c>
       <c r="AF316">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AG316">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK316">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -52010,7 +52010,7 @@
         <v>1.09</v>
       </c>
       <c r="X317">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y317">
         <v>1.18</v>
@@ -52336,7 +52336,7 @@
         <v>1.09</v>
       </c>
       <c r="X319">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y319">
         <v>1.14</v>
@@ -52487,46 +52487,46 @@
         <v>1.22</v>
       </c>
       <c r="T320">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U320">
         <v>2.2</v>
       </c>
       <c r="V320">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W320">
         <v>1.17</v>
       </c>
       <c r="X320">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y320">
         <v>1.1</v>
       </c>
       <c r="Z320">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA320">
         <v>1.5</v>
       </c>
       <c r="AB320">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AC320">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AD320">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE320">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF320">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG320">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -54914,25 +54914,25 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="O335">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P335">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q335">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="R335">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S335">
         <v>1.25</v>
       </c>
       <c r="T335">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U335">
         <v>2.25</v>
@@ -54941,22 +54941,22 @@
         <v>1.57</v>
       </c>
       <c r="W335">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X335">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y335">
         <v>1.15</v>
       </c>
       <c r="Z335">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA335">
         <v>1.6</v>
       </c>
       <c r="AB335">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC335">
         <v>2.38</v>
@@ -54968,10 +54968,10 @@
         <v>1.16</v>
       </c>
       <c r="AF335">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG335">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK335">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55575,10 +55575,10 @@
         <v>2.87</v>
       </c>
       <c r="Q339">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="R339">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S339">
         <v>1.33</v>
@@ -55620,7 +55620,7 @@
         <v>1.16</v>
       </c>
       <c r="AF339">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG339">
         <v>2.25</v>
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="O340">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P340">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q340">
         <v>2.58</v>
@@ -55759,13 +55759,13 @@
         <v>1.07</v>
       </c>
       <c r="X340">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y340">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z340">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA340">
         <v>1.72</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="V4">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.35</v>
+        <v>3.79</v>
       </c>
       <c r="AA4">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC4">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="R5">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>4.35</v>
+      </c>
+      <c r="AA5">
+        <v>1.57</v>
+      </c>
+      <c r="AB5">
+        <v>2.3</v>
+      </c>
+      <c r="AC5">
+        <v>2.5</v>
+      </c>
+      <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
+        <v>1.15</v>
+      </c>
+      <c r="AF5">
+        <v>1.57</v>
+      </c>
+      <c r="AG5">
+        <v>2.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.22</v>
       </c>
-      <c r="Z5">
-        <v>3.79</v>
-      </c>
-      <c r="AA5">
-        <v>1.8</v>
-      </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
-      <c r="AC5">
-        <v>3.1</v>
-      </c>
-      <c r="AD5">
-        <v>1.37</v>
-      </c>
-      <c r="AE5">
-        <v>1.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.65</v>
-      </c>
-      <c r="AG5">
-        <v>2.07</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.23</v>
-      </c>
       <c r="AK5">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="R17">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="U17">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AB17">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AD17">
         <v>1.19</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK17">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="O18">
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="U18">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="V18">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA18">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC18">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AD18">
         <v>1.19</v>
       </c>
       <c r="AE18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>4.2</v>
+        <v>3.11</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="AA48">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB48">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AC48">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="AD48">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="O49">
         <v>3.9</v>
       </c>
       <c r="P49">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
         <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.52</v>
+        <v>4.85</v>
       </c>
       <c r="AA49">
         <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>2.14</v>
+        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q50">
-        <v>3.11</v>
+        <v>2.14</v>
       </c>
       <c r="R50">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.83</v>
+        <v>2.34</v>
       </c>
       <c r="V50">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>3.34</v>
+        <v>4.52</v>
       </c>
       <c r="AA50">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB50">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AC50">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD50">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="R52">
+        <v>2.15</v>
+      </c>
+      <c r="S52">
+        <v>1.28</v>
+      </c>
+      <c r="T52">
+        <v>3.25</v>
+      </c>
+      <c r="U52">
+        <v>2.32</v>
+      </c>
+      <c r="V52">
+        <v>1.49</v>
+      </c>
+      <c r="W52">
+        <v>1.09</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.16</v>
+      </c>
+      <c r="Z52">
+        <v>4.15</v>
+      </c>
+      <c r="AA52">
+        <v>1.64</v>
+      </c>
+      <c r="AB52">
         <v>2.08</v>
       </c>
-      <c r="S52">
-        <v>1.33</v>
-      </c>
-      <c r="T52">
-        <v>2.85</v>
-      </c>
-      <c r="U52">
-        <v>2.75</v>
-      </c>
-      <c r="V52">
+      <c r="AC52">
+        <v>2.56</v>
+      </c>
+      <c r="AD52">
         <v>1.4</v>
       </c>
-      <c r="W52">
-        <v>1.04</v>
-      </c>
-      <c r="X52">
-        <v>1</v>
-      </c>
-      <c r="Y52">
-        <v>1.22</v>
-      </c>
-      <c r="Z52">
-        <v>3.5</v>
-      </c>
-      <c r="AA52">
-        <v>1.81</v>
-      </c>
-      <c r="AB52">
-        <v>1.86</v>
-      </c>
-      <c r="AC52">
-        <v>3.04</v>
-      </c>
-      <c r="AD52">
-        <v>1.29</v>
-      </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF52">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AG52">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK52">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G53">
@@ -8957,55 +8957,55 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="U53">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AA53">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB53">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AC53">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="AD53">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE53">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AG53">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AK53">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
         <v>3.6</v>
       </c>
       <c r="P65">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T65">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="U65">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
         <v>1.14</v>
@@ -10937,31 +10937,31 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AA65">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="AC65">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AD65">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF65">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,31 +11067,31 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O66">
         <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q66">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="R66">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="U66">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V66">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W66">
         <v>1.14</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z66">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA66">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AC66">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AD66">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AG66">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="Q91">
-        <v>2.69</v>
+        <v>2.31</v>
       </c>
       <c r="R91">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="S91">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T91">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="U91">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="V91">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15178,28 +15178,28 @@
         <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="AA91">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB91">
         <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD91">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q92">
-        <v>5.29</v>
+        <v>2.69</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S92">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T92">
-        <v>3.09</v>
+        <v>3.26</v>
       </c>
       <c r="U92">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="V92">
         <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>3.72</v>
+        <v>4.07</v>
       </c>
       <c r="AA92">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB92">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="AD92">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG92">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>2.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>1.14</v>
+        <v>1.65</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>2.31</v>
+        <v>5.29</v>
       </c>
       <c r="R93">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T93">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="U93">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V93">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W93">
+        <v>1.07</v>
+      </c>
+      <c r="X93">
+        <v>1.03</v>
+      </c>
+      <c r="Y93">
+        <v>1.25</v>
+      </c>
+      <c r="Z93">
+        <v>3.72</v>
+      </c>
+      <c r="AA93">
+        <v>1.85</v>
+      </c>
+      <c r="AB93">
+        <v>1.9</v>
+      </c>
+      <c r="AC93">
+        <v>3.1</v>
+      </c>
+      <c r="AD93">
+        <v>1.33</v>
+      </c>
+      <c r="AE93">
         <v>1.08</v>
       </c>
-      <c r="X93">
-        <v>1.02</v>
-      </c>
-      <c r="Y93">
-        <v>1.2</v>
-      </c>
-      <c r="Z93">
-        <v>3.94</v>
-      </c>
-      <c r="AA93">
-        <v>1.69</v>
-      </c>
-      <c r="AB93">
-        <v>2.08</v>
-      </c>
-      <c r="AC93">
-        <v>2.62</v>
-      </c>
-      <c r="AD93">
-        <v>1.38</v>
-      </c>
-      <c r="AE93">
-        <v>1.11</v>
-      </c>
       <c r="AF93">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG93">
+        <v>1.95</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>2.16</v>
       </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.25</v>
-      </c>
       <c r="AK93">
-        <v>1.87</v>
+        <v>1.14</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="O114">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="P114">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="Q114">
-        <v>2.25</v>
+        <v>4.82</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T114">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U114">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="V114">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W114">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z114">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA114">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AB114">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC114">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AD114">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="P115">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q115">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R115">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S115">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U115">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V115">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W115">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z115">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="AA115">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AB115">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC115">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AD115">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AE115">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF115">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG115">
+        <v>2.08</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
+        <v>1.2</v>
+      </c>
+      <c r="AK115">
         <v>2.1</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.18</v>
-      </c>
-      <c r="AK115">
-        <v>2.23</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="O116">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P116">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q116">
-        <v>4.82</v>
+        <v>2</v>
       </c>
       <c r="R116">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S116">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U116">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V116">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA116">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AB116">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC116">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AD116">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AE116">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG116">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK116">
-        <v>1.13</v>
+        <v>2.23</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.7</v>
+        <v>2.09</v>
       </c>
       <c r="O122">
         <v>3.55</v>
       </c>
       <c r="P122">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="R122">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T122">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="U122">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
         <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC122">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF122">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="O123">
         <v>3.55</v>
       </c>
       <c r="P123">
-        <v>3.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q123">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S123">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V123">
         <v>1.44</v>
       </c>
       <c r="W123">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA123">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB123">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC123">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD123">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE123">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF123">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AG123">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK123">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O133">
         <v>3.5</v>
       </c>
       <c r="P133">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q133">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R133">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S133">
+        <v>1.33</v>
+      </c>
+      <c r="T133">
+        <v>2.97</v>
+      </c>
+      <c r="U133">
+        <v>2.56</v>
+      </c>
+      <c r="V133">
         <v>1.43</v>
       </c>
-      <c r="T133">
-        <v>2.88</v>
-      </c>
-      <c r="U133">
-        <v>3.07</v>
-      </c>
-      <c r="V133">
-        <v>1.37</v>
-      </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AA133">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB133">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC133">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG133">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK133">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O134">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q134">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R134">
         <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T134">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V134">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA134">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB134">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD134">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG134">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="O135">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="Q135">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R135">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="T135">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="U135">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="V135">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="W135">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
         <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z135">
-        <v>5.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA135">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AB135">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="AC135">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD135">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE135">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="T136">
+        <v>2.88</v>
+      </c>
+      <c r="U136">
+        <v>3.07</v>
+      </c>
+      <c r="V136">
+        <v>1.37</v>
+      </c>
+      <c r="W136">
+        <v>1.05</v>
+      </c>
+      <c r="X136">
+        <v>1.01</v>
+      </c>
+      <c r="Y136">
+        <v>1.3</v>
+      </c>
+      <c r="Z136">
         <v>2.97</v>
       </c>
-      <c r="U136">
-        <v>2.56</v>
-      </c>
-      <c r="V136">
-        <v>1.43</v>
-      </c>
-      <c r="W136">
-        <v>1.07</v>
-      </c>
-      <c r="X136">
-        <v>1.03</v>
-      </c>
-      <c r="Y136">
-        <v>1.26</v>
-      </c>
-      <c r="Z136">
-        <v>3.6</v>
-      </c>
       <c r="AA136">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB136">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD136">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AK136">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P137">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="Q137">
+        <v>1.87</v>
+      </c>
+      <c r="R137">
+        <v>2.6</v>
+      </c>
+      <c r="S137">
+        <v>1.19</v>
+      </c>
+      <c r="T137">
+        <v>3.8</v>
+      </c>
+      <c r="U137">
+        <v>2.15</v>
+      </c>
+      <c r="V137">
+        <v>1.67</v>
+      </c>
+      <c r="W137">
+        <v>1.15</v>
+      </c>
+      <c r="X137">
+        <v>1.02</v>
+      </c>
+      <c r="Y137">
+        <v>1.13</v>
+      </c>
+      <c r="Z137">
+        <v>5.62</v>
+      </c>
+      <c r="AA137">
+        <v>1.47</v>
+      </c>
+      <c r="AB137">
+        <v>2.43</v>
+      </c>
+      <c r="AC137">
+        <v>2.2</v>
+      </c>
+      <c r="AD137">
+        <v>1.62</v>
+      </c>
+      <c r="AE137">
+        <v>1.22</v>
+      </c>
+      <c r="AF137">
+        <v>1.62</v>
+      </c>
+      <c r="AG137">
+        <v>2.16</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>1.08</v>
+      </c>
+      <c r="AK137">
         <v>2.5</v>
-      </c>
-      <c r="R137">
-        <v>2.1</v>
-      </c>
-      <c r="S137">
-        <v>1.4</v>
-      </c>
-      <c r="T137">
-        <v>2.88</v>
-      </c>
-      <c r="U137">
-        <v>2.88</v>
-      </c>
-      <c r="V137">
-        <v>1.4</v>
-      </c>
-      <c r="W137">
-        <v>1.08</v>
-      </c>
-      <c r="X137">
-        <v>1.05</v>
-      </c>
-      <c r="Y137">
-        <v>1.28</v>
-      </c>
-      <c r="Z137">
-        <v>3.08</v>
-      </c>
-      <c r="AA137">
-        <v>1.97</v>
-      </c>
-      <c r="AB137">
-        <v>1.75</v>
-      </c>
-      <c r="AC137">
-        <v>3.42</v>
-      </c>
-      <c r="AD137">
-        <v>1.3</v>
-      </c>
-      <c r="AE137">
-        <v>1.1</v>
-      </c>
-      <c r="AF137">
-        <v>1.83</v>
-      </c>
-      <c r="AG137">
-        <v>1.9</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.27</v>
-      </c>
-      <c r="AK137">
-        <v>1.78</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O144">
+        <v>3.46</v>
+      </c>
+      <c r="P144">
+        <v>2.3</v>
+      </c>
+      <c r="Q144">
+        <v>3.5</v>
+      </c>
+      <c r="R144">
+        <v>2.4</v>
+      </c>
+      <c r="S144">
+        <v>1.29</v>
+      </c>
+      <c r="T144">
         <v>3.4</v>
       </c>
-      <c r="P144">
-        <v>3.11</v>
-      </c>
-      <c r="Q144">
-        <v>2.68</v>
-      </c>
-      <c r="R144">
-        <v>2.05</v>
-      </c>
-      <c r="S144">
-        <v>1.4</v>
-      </c>
-      <c r="T144">
-        <v>2.88</v>
-      </c>
       <c r="U144">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="V144">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="W144">
+        <v>1.1</v>
+      </c>
+      <c r="X144">
         <v>1.02</v>
       </c>
-      <c r="X144">
-        <v>1.05</v>
-      </c>
       <c r="Y144">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z144">
-        <v>2.94</v>
+        <v>4.15</v>
       </c>
       <c r="AA144">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AB144">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC144">
-        <v>3.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD144">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE144">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF144">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG144">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK144">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
+        <v>2.1</v>
+      </c>
+      <c r="O145">
+        <v>3.4</v>
+      </c>
+      <c r="P145">
+        <v>3.11</v>
+      </c>
+      <c r="Q145">
+        <v>2.68</v>
+      </c>
+      <c r="R145">
+        <v>2.05</v>
+      </c>
+      <c r="S145">
+        <v>1.4</v>
+      </c>
+      <c r="T145">
         <v>2.88</v>
       </c>
-      <c r="O145">
-        <v>3.46</v>
-      </c>
-      <c r="P145">
-        <v>2.3</v>
-      </c>
-      <c r="Q145">
-        <v>3.5</v>
-      </c>
-      <c r="R145">
-        <v>2.4</v>
-      </c>
-      <c r="S145">
-        <v>1.29</v>
-      </c>
-      <c r="T145">
-        <v>3.4</v>
-      </c>
       <c r="U145">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="V145">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W145">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z145">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA145">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB145">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC145">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD145">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE145">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG145">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK145">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O146">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P146">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q146">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="R146">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T146">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U146">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V146">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W146">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z146">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA146">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC146">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD146">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE146">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG146">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK146">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="O147">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q147">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="R147">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S147">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T147">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U147">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V147">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W147">
+        <v>1.08</v>
+      </c>
+      <c r="X147">
+        <v>1.04</v>
+      </c>
+      <c r="Y147">
+        <v>1.29</v>
+      </c>
+      <c r="Z147">
+        <v>3.2</v>
+      </c>
+      <c r="AA147">
+        <v>1.84</v>
+      </c>
+      <c r="AB147">
+        <v>1.83</v>
+      </c>
+      <c r="AC147">
+        <v>2.97</v>
+      </c>
+      <c r="AD147">
+        <v>1.29</v>
+      </c>
+      <c r="AE147">
         <v>1.07</v>
       </c>
-      <c r="X147">
-        <v>1.02</v>
-      </c>
-      <c r="Y147">
-        <v>1.19</v>
-      </c>
-      <c r="Z147">
-        <v>3.78</v>
-      </c>
-      <c r="AA147">
-        <v>1.8</v>
-      </c>
-      <c r="AB147">
-        <v>1.99</v>
-      </c>
-      <c r="AC147">
-        <v>2.83</v>
-      </c>
-      <c r="AD147">
-        <v>1.33</v>
-      </c>
-      <c r="AE147">
-        <v>1.09</v>
-      </c>
       <c r="AF147">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG147">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>2.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P157">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="Q157">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R157">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S157">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T157">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="U157">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V157">
         <v>1.43</v>
       </c>
       <c r="W157">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X157">
         <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z157">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA157">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB157">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC157">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AD157">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE157">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF157">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG157">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK157">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="O158">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P158">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="Q158">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R158">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="S158">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U158">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V158">
         <v>1.52</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
         <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA158">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB158">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC158">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD158">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE158">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF158">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG158">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK158">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="O159">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P159">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="Q159">
-        <v>3.4</v>
+        <v>4.46</v>
       </c>
       <c r="R159">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="S159">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U159">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W159">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X159">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
+        <v>1.23</v>
+      </c>
+      <c r="Z159">
+        <v>3.6</v>
+      </c>
+      <c r="AA159">
+        <v>1.67</v>
+      </c>
+      <c r="AB159">
+        <v>2.15</v>
+      </c>
+      <c r="AC159">
+        <v>2.62</v>
+      </c>
+      <c r="AD159">
+        <v>1.38</v>
+      </c>
+      <c r="AE159">
+        <v>1.13</v>
+      </c>
+      <c r="AF159">
+        <v>1.72</v>
+      </c>
+      <c r="AG159">
+        <v>1.98</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.15</v>
       </c>
-      <c r="Z159">
-        <v>3.8</v>
-      </c>
-      <c r="AA159">
-        <v>1.62</v>
-      </c>
-      <c r="AB159">
-        <v>2.25</v>
-      </c>
-      <c r="AC159">
-        <v>2.49</v>
-      </c>
-      <c r="AD159">
-        <v>1.47</v>
-      </c>
-      <c r="AE159">
-        <v>1.18</v>
-      </c>
-      <c r="AF159">
-        <v>1.53</v>
-      </c>
-      <c r="AG159">
-        <v>2.35</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.25</v>
-      </c>
       <c r="AK159">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="O160">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P160">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="Q160">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R160">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="S160">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T160">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U160">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V160">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z160">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA160">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB160">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AC160">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="AD160">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE160">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF160">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AG160">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK160">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="O161">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P161">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q161">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="R161">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S161">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U161">
+        <v>2.74</v>
+      </c>
+      <c r="V161">
+        <v>1.43</v>
+      </c>
+      <c r="W161">
+        <v>1.06</v>
+      </c>
+      <c r="X161">
+        <v>1.02</v>
+      </c>
+      <c r="Y161">
+        <v>1.22</v>
+      </c>
+      <c r="Z161">
+        <v>3.5</v>
+      </c>
+      <c r="AA161">
+        <v>1.78</v>
+      </c>
+      <c r="AB161">
+        <v>2</v>
+      </c>
+      <c r="AC161">
         <v>2.88</v>
       </c>
-      <c r="V161">
-        <v>1.42</v>
-      </c>
-      <c r="W161">
-        <v>1.08</v>
-      </c>
-      <c r="X161">
-        <v>1.03</v>
-      </c>
-      <c r="Y161">
-        <v>1.28</v>
-      </c>
-      <c r="Z161">
-        <v>3.6</v>
-      </c>
-      <c r="AA161">
-        <v>1.89</v>
-      </c>
-      <c r="AB161">
-        <v>1.93</v>
-      </c>
-      <c r="AC161">
-        <v>3.05</v>
-      </c>
       <c r="AD161">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE161">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK161">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>5</v>
+        <v>2.06</v>
       </c>
       <c r="O162">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="P162">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="Q162">
-        <v>4.46</v>
+        <v>2.67</v>
       </c>
       <c r="R162">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="S162">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T162">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U162">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V162">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y162">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z162">
         <v>3.6</v>
       </c>
       <c r="AA162">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AB162">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC162">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AD162">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE162">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF162">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG162">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AK162">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O279">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P279">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q279">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="R279">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="S279">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T279">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V279">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y279">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z279">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="AA279">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
+        <v>1.35</v>
+      </c>
+      <c r="AC279">
+        <v>5.55</v>
+      </c>
+      <c r="AD279">
+        <v>1.08</v>
+      </c>
+      <c r="AE279">
+        <v>1.03</v>
+      </c>
+      <c r="AF279">
+        <v>2.23</v>
+      </c>
+      <c r="AG279">
+        <v>1.57</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.44</v>
       </c>
-      <c r="AC279">
-        <v>4.85</v>
-      </c>
-      <c r="AD279">
-        <v>1.11</v>
-      </c>
-      <c r="AE279">
-        <v>1.01</v>
-      </c>
-      <c r="AF279">
-        <v>2.4</v>
-      </c>
-      <c r="AG279">
-        <v>1.48</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.26</v>
-      </c>
       <c r="AK279">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O280">
+        <v>3.25</v>
+      </c>
+      <c r="P280">
+        <v>5.25</v>
+      </c>
+      <c r="Q280">
+        <v>2.33</v>
+      </c>
+      <c r="R280">
+        <v>1.88</v>
+      </c>
+      <c r="S280">
+        <v>1.53</v>
+      </c>
+      <c r="T280">
+        <v>2.2</v>
+      </c>
+      <c r="U280">
+        <v>3.5</v>
+      </c>
+      <c r="V280">
+        <v>1.25</v>
+      </c>
+      <c r="W280">
+        <v>1.04</v>
+      </c>
+      <c r="X280">
+        <v>1.11</v>
+      </c>
+      <c r="Y280">
+        <v>1.54</v>
+      </c>
+      <c r="Z280">
+        <v>2.42</v>
+      </c>
+      <c r="AA280">
         <v>2.7</v>
       </c>
-      <c r="P280">
+      <c r="AB280">
+        <v>1.44</v>
+      </c>
+      <c r="AC280">
+        <v>4.85</v>
+      </c>
+      <c r="AD280">
+        <v>1.11</v>
+      </c>
+      <c r="AE280">
+        <v>1.01</v>
+      </c>
+      <c r="AF280">
         <v>2.4</v>
       </c>
-      <c r="Q280">
-        <v>4</v>
-      </c>
-      <c r="R280">
-        <v>1.75</v>
-      </c>
-      <c r="S280">
-        <v>1.57</v>
-      </c>
-      <c r="T280">
-        <v>2.13</v>
-      </c>
-      <c r="U280">
-        <v>3.8</v>
-      </c>
-      <c r="V280">
-        <v>1.22</v>
-      </c>
-      <c r="W280">
-        <v>1.03</v>
-      </c>
-      <c r="X280">
-        <v>1.09</v>
-      </c>
-      <c r="Y280">
-        <v>1.57</v>
-      </c>
-      <c r="Z280">
-        <v>2.26</v>
-      </c>
-      <c r="AA280">
-        <v>2.87</v>
-      </c>
-      <c r="AB280">
-        <v>1.35</v>
-      </c>
-      <c r="AC280">
-        <v>5.55</v>
-      </c>
-      <c r="AD280">
-        <v>1.08</v>
-      </c>
-      <c r="AE280">
-        <v>1.03</v>
-      </c>
-      <c r="AF280">
-        <v>2.23</v>
-      </c>
       <c r="AG280">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK280">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL280">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="R4">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
+        <v>1.14</v>
+      </c>
+      <c r="Z4">
+        <v>4.35</v>
+      </c>
+      <c r="AA4">
+        <v>1.57</v>
+      </c>
+      <c r="AB4">
+        <v>2.3</v>
+      </c>
+      <c r="AC4">
+        <v>2.5</v>
+      </c>
+      <c r="AD4">
+        <v>1.45</v>
+      </c>
+      <c r="AE4">
+        <v>1.15</v>
+      </c>
+      <c r="AF4">
+        <v>1.57</v>
+      </c>
+      <c r="AG4">
+        <v>2.25</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.22</v>
       </c>
-      <c r="Z4">
-        <v>3.79</v>
-      </c>
-      <c r="AA4">
-        <v>1.8</v>
-      </c>
-      <c r="AB4">
-        <v>2</v>
-      </c>
-      <c r="AC4">
-        <v>3.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.37</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.65</v>
-      </c>
-      <c r="AG4">
-        <v>2.07</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.23</v>
-      </c>
       <c r="AK4">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>3.79</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD5">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
         <v>3.45</v>
@@ -1302,13 +1302,13 @@
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
         <v>2.54</v>
       </c>
       <c r="U6">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1335,7 +1335,7 @@
         <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
         <v>1.05</v>
@@ -1344,7 +1344,7 @@
         <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O43">
         <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="Q43">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S43">
         <v>1.36</v>
@@ -7339,7 +7339,7 @@
         <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="V43">
         <v>1.36</v>
@@ -7357,10 +7357,10 @@
         <v>3.2</v>
       </c>
       <c r="AA43">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB43">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC43">
         <v>3.2</v>
@@ -7372,10 +7372,10 @@
         <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG43">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P48">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.34</v>
+        <v>4.85</v>
       </c>
       <c r="AA48">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB48">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AC48">
-        <v>3.08</v>
+        <v>2.48</v>
       </c>
       <c r="AD48">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AE48">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q49">
-        <v>4.2</v>
+        <v>3.11</v>
       </c>
       <c r="R49">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>4.85</v>
+        <v>3.34</v>
       </c>
       <c r="AA49">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AC49">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="AD49">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE49">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
         <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="R65">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V65">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
         <v>1.14</v>
@@ -10937,31 +10937,31 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA65">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AD65">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>2.44</v>
+        <v>2.81</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="U66">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="V66">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W66">
         <v>1.14</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AB66">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AC66">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="AD66">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE66">
         <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G67">
@@ -11233,77 +11233,77 @@
         <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="R67">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T67">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="U67">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V67">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W67">
         <v>1.14</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA67">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AB67">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="AC67">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="AD67">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AE67">
+        <v>1.24</v>
+      </c>
+      <c r="AF67">
+        <v>1.39</v>
+      </c>
+      <c r="AG67">
+        <v>2.73</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.2</v>
       </c>
-      <c r="AF67">
-        <v>1.48</v>
-      </c>
-      <c r="AG67">
-        <v>2.4</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.24</v>
-      </c>
       <c r="AK67">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11885,7 +11885,7 @@
         <v>1.48</v>
       </c>
       <c r="O71">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="P71">
         <v>5</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P77">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q77">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T77">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z77">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA77">
+        <v>2</v>
+      </c>
+      <c r="AB77">
         <v>1.76</v>
       </c>
-      <c r="AB77">
-        <v>2.03</v>
-      </c>
       <c r="AC77">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AD77">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="O78">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q78">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R78">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB78">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AC78">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD78">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>2.31</v>
+        <v>2.69</v>
       </c>
       <c r="R91">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="S91">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V91">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15178,28 +15178,28 @@
         <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>3.94</v>
+        <v>4.07</v>
       </c>
       <c r="AA91">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB91">
         <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AD91">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE91">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="Q92">
-        <v>2.69</v>
+        <v>2.31</v>
       </c>
       <c r="R92">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="S92">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T92">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="U92">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W92">
         <v>1.08</v>
@@ -15341,28 +15341,28 @@
         <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="AA92">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB92">
         <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD92">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="O114">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="P114">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="Q114">
-        <v>4.82</v>
+        <v>2.25</v>
       </c>
       <c r="R114">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T114">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U114">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="V114">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W114">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z114">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA114">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AB114">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC114">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD114">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>1.13</v>
+        <v>2.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="O115">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="P115">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="Q115">
-        <v>2.25</v>
+        <v>4.82</v>
       </c>
       <c r="R115">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T115">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U115">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="V115">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W115">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z115">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA115">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AB115">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC115">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE115">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF115">
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.2</v>
       </c>
       <c r="AK115">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O133">
         <v>3.5</v>
       </c>
       <c r="P133">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
       </c>
       <c r="R133">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U133">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V133">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z133">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AA133">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AB133">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC133">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD133">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE133">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF133">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG133">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK133">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P134">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="Q134">
+        <v>1.87</v>
+      </c>
+      <c r="R134">
+        <v>2.6</v>
+      </c>
+      <c r="S134">
+        <v>1.19</v>
+      </c>
+      <c r="T134">
+        <v>3.8</v>
+      </c>
+      <c r="U134">
+        <v>2.15</v>
+      </c>
+      <c r="V134">
+        <v>1.67</v>
+      </c>
+      <c r="W134">
+        <v>1.15</v>
+      </c>
+      <c r="X134">
+        <v>1.02</v>
+      </c>
+      <c r="Y134">
+        <v>1.13</v>
+      </c>
+      <c r="Z134">
+        <v>5.62</v>
+      </c>
+      <c r="AA134">
+        <v>1.47</v>
+      </c>
+      <c r="AB134">
+        <v>2.43</v>
+      </c>
+      <c r="AC134">
+        <v>2.2</v>
+      </c>
+      <c r="AD134">
+        <v>1.62</v>
+      </c>
+      <c r="AE134">
+        <v>1.22</v>
+      </c>
+      <c r="AF134">
+        <v>1.62</v>
+      </c>
+      <c r="AG134">
+        <v>2.16</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>1.08</v>
+      </c>
+      <c r="AK134">
         <v>2.5</v>
-      </c>
-      <c r="R134">
-        <v>2.1</v>
-      </c>
-      <c r="S134">
-        <v>1.4</v>
-      </c>
-      <c r="T134">
-        <v>2.88</v>
-      </c>
-      <c r="U134">
-        <v>2.88</v>
-      </c>
-      <c r="V134">
-        <v>1.4</v>
-      </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
-      <c r="Y134">
-        <v>1.28</v>
-      </c>
-      <c r="Z134">
-        <v>3.08</v>
-      </c>
-      <c r="AA134">
-        <v>1.97</v>
-      </c>
-      <c r="AB134">
-        <v>1.75</v>
-      </c>
-      <c r="AC134">
-        <v>3.42</v>
-      </c>
-      <c r="AD134">
-        <v>1.3</v>
-      </c>
-      <c r="AE134">
-        <v>1.1</v>
-      </c>
-      <c r="AF134">
-        <v>1.83</v>
-      </c>
-      <c r="AG134">
-        <v>1.9</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.27</v>
-      </c>
-      <c r="AK134">
-        <v>1.78</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
+        <v>2.8</v>
+      </c>
+      <c r="Q135">
         <v>3.1</v>
       </c>
-      <c r="Q135">
+      <c r="R135">
+        <v>2</v>
+      </c>
+      <c r="S135">
+        <v>1.43</v>
+      </c>
+      <c r="T135">
         <v>2.88</v>
       </c>
-      <c r="R135">
-        <v>2.1</v>
-      </c>
-      <c r="S135">
+      <c r="U135">
+        <v>3.07</v>
+      </c>
+      <c r="V135">
         <v>1.37</v>
       </c>
-      <c r="T135">
-        <v>2.78</v>
-      </c>
-      <c r="U135">
-        <v>2.68</v>
-      </c>
-      <c r="V135">
-        <v>1.39</v>
-      </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z135">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA135">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB135">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC135">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE135">
         <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG135">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.97</v>
+      </c>
+      <c r="U136">
+        <v>2.56</v>
+      </c>
+      <c r="V136">
         <v>1.43</v>
       </c>
-      <c r="T136">
-        <v>2.88</v>
-      </c>
-      <c r="U136">
-        <v>3.07</v>
-      </c>
-      <c r="V136">
-        <v>1.37</v>
-      </c>
       <c r="W136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z136">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB136">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC136">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD136">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG136">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="O137">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="R137">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="T137">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="U137">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="V137">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="W137">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X137">
         <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>5.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA137">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AB137">
-        <v>2.43</v>
+        <v>1.81</v>
       </c>
       <c r="AC137">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD137">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE137">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AF137">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG137">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AK137">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
+        <v>2.8</v>
+      </c>
+      <c r="O144">
+        <v>3.4</v>
+      </c>
+      <c r="P144">
+        <v>2.45</v>
+      </c>
+      <c r="Q144">
+        <v>3.4</v>
+      </c>
+      <c r="R144">
+        <v>2.09</v>
+      </c>
+      <c r="S144">
+        <v>1.35</v>
+      </c>
+      <c r="T144">
         <v>2.88</v>
       </c>
-      <c r="O144">
-        <v>3.46</v>
-      </c>
-      <c r="P144">
-        <v>2.3</v>
-      </c>
-      <c r="Q144">
-        <v>3.5</v>
-      </c>
-      <c r="R144">
-        <v>2.4</v>
-      </c>
-      <c r="S144">
+      <c r="U144">
+        <v>2.75</v>
+      </c>
+      <c r="V144">
+        <v>1.4</v>
+      </c>
+      <c r="W144">
+        <v>1.08</v>
+      </c>
+      <c r="X144">
+        <v>1.04</v>
+      </c>
+      <c r="Y144">
         <v>1.29</v>
       </c>
-      <c r="T144">
-        <v>3.4</v>
-      </c>
-      <c r="U144">
-        <v>2.47</v>
-      </c>
-      <c r="V144">
-        <v>1.52</v>
-      </c>
-      <c r="W144">
-        <v>1.1</v>
-      </c>
-      <c r="X144">
-        <v>1.02</v>
-      </c>
-      <c r="Y144">
-        <v>1.16</v>
-      </c>
       <c r="Z144">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA144">
+        <v>1.84</v>
+      </c>
+      <c r="AB144">
+        <v>1.83</v>
+      </c>
+      <c r="AC144">
+        <v>2.97</v>
+      </c>
+      <c r="AD144">
+        <v>1.29</v>
+      </c>
+      <c r="AE144">
+        <v>1.07</v>
+      </c>
+      <c r="AF144">
         <v>1.65</v>
       </c>
-      <c r="AB144">
-        <v>2.15</v>
-      </c>
-      <c r="AC144">
-        <v>2.49</v>
-      </c>
-      <c r="AD144">
-        <v>1.42</v>
-      </c>
-      <c r="AE144">
-        <v>1.13</v>
-      </c>
-      <c r="AF144">
-        <v>1.57</v>
-      </c>
       <c r="AG144">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.68</v>
+        <v>2.88</v>
       </c>
       <c r="O146">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="P146">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q146">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="R146">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T146">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U146">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="V146">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X146">
         <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z146">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB146">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AC146">
-        <v>2.83</v>
+        <v>2.49</v>
       </c>
       <c r="AD146">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE146">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="AK146">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P147">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q147">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="R147">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S147">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T147">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U147">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V147">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W147">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X147">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z147">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA147">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB147">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC147">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD147">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE147">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF147">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG147">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK147">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O159">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P159">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="Q159">
-        <v>4.46</v>
+        <v>2.4</v>
       </c>
       <c r="R159">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="S159">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T159">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U159">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="V159">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W159">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X159">
         <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z159">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA159">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AB159">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC159">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD159">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF159">
         <v>1.72</v>
       </c>
       <c r="AG159">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK159">
-        <v>1.13</v>
+        <v>1.91</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,65 +26552,65 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="O161">
+        <v>3.42</v>
+      </c>
+      <c r="P161">
+        <v>3.45</v>
+      </c>
+      <c r="Q161">
+        <v>2.67</v>
+      </c>
+      <c r="R161">
+        <v>2.12</v>
+      </c>
+      <c r="S161">
+        <v>1.33</v>
+      </c>
+      <c r="T161">
+        <v>2.96</v>
+      </c>
+      <c r="U161">
+        <v>2.88</v>
+      </c>
+      <c r="V161">
+        <v>1.42</v>
+      </c>
+      <c r="W161">
+        <v>1.08</v>
+      </c>
+      <c r="X161">
+        <v>1.03</v>
+      </c>
+      <c r="Y161">
+        <v>1.28</v>
+      </c>
+      <c r="Z161">
         <v>3.6</v>
       </c>
-      <c r="P161">
-        <v>4</v>
-      </c>
-      <c r="Q161">
-        <v>2.4</v>
-      </c>
-      <c r="R161">
-        <v>2.11</v>
-      </c>
-      <c r="S161">
-        <v>1.36</v>
-      </c>
-      <c r="T161">
-        <v>2.82</v>
-      </c>
-      <c r="U161">
-        <v>2.74</v>
-      </c>
-      <c r="V161">
-        <v>1.43</v>
-      </c>
-      <c r="W161">
-        <v>1.06</v>
-      </c>
-      <c r="X161">
-        <v>1.02</v>
-      </c>
-      <c r="Y161">
-        <v>1.22</v>
-      </c>
-      <c r="Z161">
-        <v>3.5</v>
-      </c>
       <c r="AA161">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB161">
+        <v>1.93</v>
+      </c>
+      <c r="AC161">
+        <v>3.05</v>
+      </c>
+      <c r="AD161">
+        <v>1.33</v>
+      </c>
+      <c r="AE161">
+        <v>1.07</v>
+      </c>
+      <c r="AF161">
+        <v>1.73</v>
+      </c>
+      <c r="AG161">
         <v>2</v>
       </c>
-      <c r="AC161">
-        <v>2.88</v>
-      </c>
-      <c r="AD161">
-        <v>1.35</v>
-      </c>
-      <c r="AE161">
-        <v>1.12</v>
-      </c>
-      <c r="AF161">
-        <v>1.72</v>
-      </c>
-      <c r="AG161">
-        <v>2.01</v>
-      </c>
       <c r="AH161" t="inlineStr">
         <is>
           <t>[]</t>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="O162">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="P162">
-        <v>3.45</v>
+        <v>1.61</v>
       </c>
       <c r="Q162">
-        <v>2.67</v>
+        <v>4.46</v>
       </c>
       <c r="R162">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="S162">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U162">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="V162">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W162">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X162">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z162">
         <v>3.6</v>
       </c>
       <c r="AA162">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AB162">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC162">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AD162">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE162">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF162">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG162">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK162">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O195">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="P195">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="O214">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P214">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="O217">
         <v>3.05</v>
       </c>
       <c r="P217">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="Q217">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="R217">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S217">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T217">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="U217">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="V217">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W217">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X217">
         <v>1.05</v>
       </c>
       <c r="Y217">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z217">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA217">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AB217">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC217">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="AD217">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE217">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF217">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AG217">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>1.28</v>
       </c>
       <c r="AK217">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -36495,65 +36495,65 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="O222">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P222">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Q222">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R222">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S222">
         <v>1.36</v>
       </c>
       <c r="T222">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U222">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="V222">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W222">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X222">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y222">
+        <v>1.26</v>
+      </c>
+      <c r="Z222">
+        <v>3.2</v>
+      </c>
+      <c r="AA222">
+        <v>1.95</v>
+      </c>
+      <c r="AB222">
+        <v>1.81</v>
+      </c>
+      <c r="AC222">
+        <v>3.28</v>
+      </c>
+      <c r="AD222">
         <v>1.25</v>
       </c>
-      <c r="Z222">
-        <v>3.28</v>
-      </c>
-      <c r="AA222">
+      <c r="AE222">
+        <v>1.05</v>
+      </c>
+      <c r="AF222">
+        <v>1.74</v>
+      </c>
+      <c r="AG222">
         <v>1.91</v>
       </c>
-      <c r="AB222">
-        <v>1.82</v>
-      </c>
-      <c r="AC222">
-        <v>3.14</v>
-      </c>
-      <c r="AD222">
-        <v>1.27</v>
-      </c>
-      <c r="AE222">
-        <v>1.06</v>
-      </c>
-      <c r="AF222">
-        <v>1.73</v>
-      </c>
-      <c r="AG222">
-        <v>2</v>
-      </c>
       <c r="AH222" t="inlineStr">
         <is>
           <t>[]</t>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK222">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O223">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P223">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q223">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="R223">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S223">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T223">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U223">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V223">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W223">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X223">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z223">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA223">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB223">
         <v>1.72</v>
       </c>
       <c r="AC223">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD223">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE223">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF223">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG223">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK223">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O228">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P228">
         <v>2</v>
@@ -37485,7 +37485,7 @@
         <v>3.68</v>
       </c>
       <c r="R228">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S228">
         <v>1.26</v>
@@ -37494,7 +37494,7 @@
         <v>3.24</v>
       </c>
       <c r="U228">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V228">
         <v>1.51</v>
@@ -37512,10 +37512,10 @@
         <v>4.3</v>
       </c>
       <c r="AA228">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB228">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC228">
         <v>2.43</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O231">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P231">
-        <v>3.1</v>
+        <v>4.02</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q247">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="R247">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T247">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="U247">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="V247">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W247">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z247">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="AA247">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB247">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC247">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AD247">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE247">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG247">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK247">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,80 +40733,80 @@
         </is>
       </c>
       <c r="N248">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S248">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T248">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="U248">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="V248">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W248">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X248">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z248">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="AA248">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB248">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC248">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="AD248">
+        <v>1.31</v>
+      </c>
+      <c r="AE248">
+        <v>1.06</v>
+      </c>
+      <c r="AF248">
+        <v>1.66</v>
+      </c>
+      <c r="AG248">
+        <v>2.07</v>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ248">
+        <v>1.38</v>
+      </c>
+      <c r="AK248">
         <v>1.43</v>
-      </c>
-      <c r="AE248">
-        <v>1.12</v>
-      </c>
-      <c r="AF248">
-        <v>1.6</v>
-      </c>
-      <c r="AG248">
-        <v>2.18</v>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ248">
-        <v>1.26</v>
-      </c>
-      <c r="AK248">
-        <v>1.24</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="O249">
         <v>3</v>
       </c>
       <c r="P249">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -42040,10 +42040,10 @@
         <v>2.05</v>
       </c>
       <c r="O256">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P256">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
+        <v>1.8</v>
+      </c>
+      <c r="AB256">
         <v>2</v>
-      </c>
-      <c r="AB256">
-        <v>1.8</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O260">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="P260">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O265">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P265">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43543,10 +43543,10 @@
         <v>0</v>
       </c>
       <c r="AA265">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB265">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC265">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="O282">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P282">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="Q282">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>4.07</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="U11">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="V11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.69</v>
+        <v>3.99</v>
       </c>
       <c r="AA11">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AC11">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
+        <v>1.64</v>
+      </c>
+      <c r="AG11">
+        <v>2.13</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.75</v>
       </c>
-      <c r="AG11">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.3</v>
-      </c>
       <c r="AK11">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>4.07</v>
+        <v>2.4</v>
       </c>
       <c r="R12">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z12">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="O48">
+        <v>3.9</v>
+      </c>
+      <c r="P48">
+        <v>1.8</v>
+      </c>
+      <c r="Q48">
         <v>4</v>
       </c>
-      <c r="P48">
-        <v>4.2</v>
-      </c>
-      <c r="Q48">
-        <v>2.25</v>
-      </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="V48">
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA48">
         <v>1.58</v>
       </c>
       <c r="AB48">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AC48">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
         <v>2.3</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>2.14</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q49">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="R49">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U49">
-        <v>2.21</v>
+        <v>2.73</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>4.85</v>
+        <v>3.25</v>
       </c>
       <c r="AA49">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AB49">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AC49">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AD49">
+        <v>1.3</v>
+      </c>
+      <c r="AE49">
+        <v>1.08</v>
+      </c>
+      <c r="AF49">
+        <v>1.64</v>
+      </c>
+      <c r="AG49">
+        <v>2.1</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.33</v>
+      </c>
+      <c r="AK49">
         <v>1.5</v>
-      </c>
-      <c r="AE49">
-        <v>1.18</v>
-      </c>
-      <c r="AF49">
-        <v>1.53</v>
-      </c>
-      <c r="AG49">
-        <v>2.3</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.25</v>
-      </c>
-      <c r="AK49">
-        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q50">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="R50">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AB50">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AC50">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="AD50">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
+        <v>2.48</v>
+      </c>
+      <c r="Q55">
+        <v>2.9</v>
+      </c>
+      <c r="R55">
+        <v>2.2</v>
+      </c>
+      <c r="S55">
+        <v>1.35</v>
+      </c>
+      <c r="T55">
+        <v>3</v>
+      </c>
+      <c r="U55">
+        <v>2.7</v>
+      </c>
+      <c r="V55">
+        <v>1.4</v>
+      </c>
+      <c r="W55">
+        <v>1.08</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
+        <v>3.65</v>
+      </c>
+      <c r="AA55">
+        <v>1.9</v>
+      </c>
+      <c r="AB55">
+        <v>1.9</v>
+      </c>
+      <c r="AC55">
+        <v>3.04</v>
+      </c>
+      <c r="AD55">
+        <v>1.29</v>
+      </c>
+      <c r="AE55">
+        <v>1.07</v>
+      </c>
+      <c r="AF55">
+        <v>1.73</v>
+      </c>
+      <c r="AG55">
         <v>2.05</v>
       </c>
-      <c r="Q55">
-        <v>3.13</v>
-      </c>
-      <c r="R55">
-        <v>2.5</v>
-      </c>
-      <c r="S55">
-        <v>1.22</v>
-      </c>
-      <c r="T55">
-        <v>3.48</v>
-      </c>
-      <c r="U55">
-        <v>2.1</v>
-      </c>
-      <c r="V55">
-        <v>1.67</v>
-      </c>
-      <c r="W55">
-        <v>1.17</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.11</v>
-      </c>
-      <c r="Z55">
-        <v>5.75</v>
-      </c>
-      <c r="AA55">
-        <v>1.46</v>
-      </c>
-      <c r="AB55">
-        <v>2.47</v>
-      </c>
-      <c r="AC55">
-        <v>2.17</v>
-      </c>
-      <c r="AD55">
-        <v>1.7</v>
-      </c>
-      <c r="AE55">
-        <v>1.23</v>
-      </c>
-      <c r="AF55">
-        <v>1.44</v>
-      </c>
-      <c r="AG55">
-        <v>2.62</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O56">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="Q56">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="U56">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>3.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA56">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB56">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="AC56">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="AD56">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AE56">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AF56">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG56">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
+        <v>1.95</v>
+      </c>
+      <c r="O66">
+        <v>3.6</v>
+      </c>
+      <c r="P66">
+        <v>3.1</v>
+      </c>
+      <c r="Q66">
+        <v>2.4</v>
+      </c>
+      <c r="R66">
+        <v>2.4</v>
+      </c>
+      <c r="S66">
+        <v>1.22</v>
+      </c>
+      <c r="T66">
+        <v>3.52</v>
+      </c>
+      <c r="U66">
         <v>2.25</v>
       </c>
-      <c r="O66">
-        <v>3.4</v>
-      </c>
-      <c r="P66">
-        <v>2.62</v>
-      </c>
-      <c r="Q66">
-        <v>2.81</v>
-      </c>
-      <c r="R66">
-        <v>2.21</v>
-      </c>
-      <c r="S66">
-        <v>1.25</v>
-      </c>
-      <c r="T66">
-        <v>3.46</v>
-      </c>
-      <c r="U66">
+      <c r="V66">
+        <v>1.62</v>
+      </c>
+      <c r="W66">
+        <v>1.14</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.12</v>
+      </c>
+      <c r="Z66">
+        <v>4.7</v>
+      </c>
+      <c r="AA66">
+        <v>1.48</v>
+      </c>
+      <c r="AB66">
+        <v>2.33</v>
+      </c>
+      <c r="AC66">
         <v>2.22</v>
       </c>
-      <c r="V66">
-        <v>1.53</v>
-      </c>
-      <c r="W66">
-        <v>1.11</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.13</v>
-      </c>
-      <c r="Z66">
-        <v>4.55</v>
-      </c>
-      <c r="AA66">
+      <c r="AD66">
         <v>1.56</v>
       </c>
-      <c r="AB66">
-        <v>2.22</v>
-      </c>
-      <c r="AC66">
-        <v>2.46</v>
-      </c>
-      <c r="AD66">
-        <v>1.52</v>
-      </c>
       <c r="AE66">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG66">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,65 +11230,65 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q67">
+        <v>2.81</v>
+      </c>
+      <c r="R67">
+        <v>2.21</v>
+      </c>
+      <c r="S67">
+        <v>1.25</v>
+      </c>
+      <c r="T67">
+        <v>3.46</v>
+      </c>
+      <c r="U67">
+        <v>2.22</v>
+      </c>
+      <c r="V67">
+        <v>1.53</v>
+      </c>
+      <c r="W67">
+        <v>1.11</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.13</v>
+      </c>
+      <c r="Z67">
+        <v>4.55</v>
+      </c>
+      <c r="AA67">
+        <v>1.56</v>
+      </c>
+      <c r="AB67">
+        <v>2.22</v>
+      </c>
+      <c r="AC67">
+        <v>2.46</v>
+      </c>
+      <c r="AD67">
+        <v>1.52</v>
+      </c>
+      <c r="AE67">
+        <v>1.15</v>
+      </c>
+      <c r="AF67">
+        <v>1.48</v>
+      </c>
+      <c r="AG67">
         <v>2.4</v>
       </c>
-      <c r="R67">
-        <v>2.4</v>
-      </c>
-      <c r="S67">
-        <v>1.22</v>
-      </c>
-      <c r="T67">
-        <v>3.52</v>
-      </c>
-      <c r="U67">
-        <v>2.25</v>
-      </c>
-      <c r="V67">
-        <v>1.62</v>
-      </c>
-      <c r="W67">
-        <v>1.14</v>
-      </c>
-      <c r="X67">
-        <v>1.02</v>
-      </c>
-      <c r="Y67">
-        <v>1.12</v>
-      </c>
-      <c r="Z67">
-        <v>4.7</v>
-      </c>
-      <c r="AA67">
-        <v>1.48</v>
-      </c>
-      <c r="AB67">
-        <v>2.33</v>
-      </c>
-      <c r="AC67">
-        <v>2.22</v>
-      </c>
-      <c r="AD67">
-        <v>1.56</v>
-      </c>
-      <c r="AE67">
-        <v>1.2</v>
-      </c>
-      <c r="AF67">
-        <v>1.46</v>
-      </c>
-      <c r="AG67">
-        <v>2.5</v>
-      </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q79">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U79">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="V79">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="Z79">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AA79">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC79">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="AD79">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF79">
         <v>1.85</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="O80">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="Q80">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R80">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="S80">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T80">
         <v>2.88</v>
       </c>
       <c r="U80">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W80">
         <v>1.04</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA80">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC80">
-        <v>3.53</v>
+        <v>3.26</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE80">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG80">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK80">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,65 +13512,65 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q81">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="S81">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T81">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA81">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AB81">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC81">
-        <v>3.04</v>
+        <v>3.53</v>
       </c>
       <c r="AD81">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE81">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
+        <v>1.75</v>
+      </c>
+      <c r="AG81">
         <v>1.91</v>
       </c>
-      <c r="AG81">
-        <v>1.8</v>
-      </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK81">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="R82">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
+        <v>1.33</v>
+      </c>
+      <c r="T82">
+        <v>2.9</v>
+      </c>
+      <c r="U82">
+        <v>2.75</v>
+      </c>
+      <c r="V82">
         <v>1.4</v>
       </c>
-      <c r="T82">
-        <v>2.39</v>
-      </c>
-      <c r="U82">
-        <v>3.18</v>
-      </c>
-      <c r="V82">
-        <v>1.27</v>
-      </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>2.74</v>
+        <v>3.48</v>
       </c>
       <c r="AA82">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AB82">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="AD82">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG82">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q85">
-        <v>2.08</v>
+        <v>3.54</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="V85">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z85">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB85">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC85">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="AD85">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE85">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AK85">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P86">
+        <v>5.25</v>
+      </c>
+      <c r="Q86">
+        <v>2.08</v>
+      </c>
+      <c r="R86">
         <v>2.3</v>
       </c>
-      <c r="Q86">
-        <v>3.54</v>
-      </c>
-      <c r="R86">
-        <v>2.1</v>
-      </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T86">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U86">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="V86">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z86">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA86">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AB86">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC86">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="AD86">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>2.19</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>2.31</v>
+        <v>2.69</v>
       </c>
       <c r="R91">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="S91">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>2.87</v>
+        <v>3.26</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V91">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15175,31 +15175,31 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>3.94</v>
+        <v>4.07</v>
       </c>
       <c r="AA91">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB91">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AD91">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
+        <v>3.6</v>
+      </c>
+      <c r="Q92">
+        <v>2.31</v>
+      </c>
+      <c r="R92">
+        <v>2.14</v>
+      </c>
+      <c r="S92">
+        <v>1.29</v>
+      </c>
+      <c r="T92">
         <v>2.87</v>
       </c>
-      <c r="Q92">
-        <v>2.69</v>
-      </c>
-      <c r="R92">
-        <v>2.33</v>
-      </c>
-      <c r="S92">
-        <v>1.28</v>
-      </c>
-      <c r="T92">
-        <v>3.26</v>
-      </c>
       <c r="U92">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W92">
         <v>1.08</v>
@@ -15338,31 +15338,31 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="AA92">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD92">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P122">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q122">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="R122">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S122">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.39</v>
+        <v>3.09</v>
       </c>
       <c r="U122">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V122">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA122">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG122">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK122">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="O123">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="Q123">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="R123">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T123">
-        <v>3.09</v>
+        <v>2.39</v>
       </c>
       <c r="U123">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W123">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA123">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB123">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC123">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF123">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P132">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="Q132">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="R132">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S132">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="U132">
-        <v>2.4</v>
+        <v>3.07</v>
       </c>
       <c r="V132">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z132">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA132">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AB132">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC132">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="AD132">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AE132">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF132">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AG132">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK132">
         <v>1.53</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O133">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R133">
         <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="U133">
-        <v>3.07</v>
+        <v>2.67</v>
       </c>
       <c r="V133">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB133">
+        <v>1.76</v>
+      </c>
+      <c r="AC133">
+        <v>3.28</v>
+      </c>
+      <c r="AD133">
+        <v>1.25</v>
+      </c>
+      <c r="AE133">
+        <v>1.11</v>
+      </c>
+      <c r="AF133">
         <v>1.73</v>
       </c>
-      <c r="AC133">
-        <v>3.5</v>
-      </c>
-      <c r="AD133">
-        <v>1.22</v>
-      </c>
-      <c r="AE133">
-        <v>1.05</v>
-      </c>
-      <c r="AF133">
-        <v>1.8</v>
-      </c>
       <c r="AG133">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q134">
         <v>2.5</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S134">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T134">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U134">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V134">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W134">
         <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA134">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AB134">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC134">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD134">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF134">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG134">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK134">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O136">
         <v>3.4</v>
       </c>
       <c r="P136">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="Q136">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S136">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T136">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U136">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="V136">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA136">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AB136">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC136">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AE136">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF136">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG136">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="O137">
         <v>3.5</v>
       </c>
       <c r="P137">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q137">
         <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U137">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W137">
         <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA137">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AB137">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC137">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD137">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE137">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG137">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK137">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O145">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P145">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q145">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="R145">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S145">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T145">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U145">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="V145">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W145">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y145">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z145">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA145">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB145">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AC145">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD145">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE145">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG145">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.29</v>
       </c>
       <c r="AK145">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
+        <v>2.8</v>
+      </c>
+      <c r="O146">
+        <v>3.6</v>
+      </c>
+      <c r="P146">
+        <v>2.3</v>
+      </c>
+      <c r="Q146">
+        <v>3.5</v>
+      </c>
+      <c r="R146">
+        <v>2.4</v>
+      </c>
+      <c r="S146">
+        <v>1.29</v>
+      </c>
+      <c r="T146">
+        <v>3.4</v>
+      </c>
+      <c r="U146">
+        <v>2.47</v>
+      </c>
+      <c r="V146">
+        <v>1.52</v>
+      </c>
+      <c r="W146">
+        <v>1.1</v>
+      </c>
+      <c r="X146">
+        <v>1.02</v>
+      </c>
+      <c r="Y146">
+        <v>1.16</v>
+      </c>
+      <c r="Z146">
+        <v>4.15</v>
+      </c>
+      <c r="AA146">
+        <v>1.65</v>
+      </c>
+      <c r="AB146">
         <v>2.15</v>
       </c>
-      <c r="O146">
-        <v>3.4</v>
-      </c>
-      <c r="P146">
-        <v>3.3</v>
-      </c>
-      <c r="Q146">
+      <c r="AC146">
         <v>2.49</v>
       </c>
-      <c r="R146">
-        <v>2.1</v>
-      </c>
-      <c r="S146">
-        <v>1.36</v>
-      </c>
-      <c r="T146">
-        <v>3</v>
-      </c>
-      <c r="U146">
-        <v>2.92</v>
-      </c>
-      <c r="V146">
-        <v>1.37</v>
-      </c>
-      <c r="W146">
-        <v>1.02</v>
-      </c>
-      <c r="X146">
-        <v>1.04</v>
-      </c>
-      <c r="Y146">
-        <v>1.33</v>
-      </c>
-      <c r="Z146">
-        <v>2.94</v>
-      </c>
-      <c r="AA146">
-        <v>2.05</v>
-      </c>
-      <c r="AB146">
-        <v>1.76</v>
-      </c>
-      <c r="AC146">
-        <v>3.42</v>
-      </c>
       <c r="AD146">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE146">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF146">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O151">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P151">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q151">
-        <v>2.47</v>
+        <v>3.64</v>
       </c>
       <c r="R151">
+        <v>2.2</v>
+      </c>
+      <c r="S151">
+        <v>1.3</v>
+      </c>
+      <c r="T151">
+        <v>2.95</v>
+      </c>
+      <c r="U151">
+        <v>2.5</v>
+      </c>
+      <c r="V151">
+        <v>1.5</v>
+      </c>
+      <c r="W151">
+        <v>1.07</v>
+      </c>
+      <c r="X151">
+        <v>1.03</v>
+      </c>
+      <c r="Y151">
+        <v>1.2</v>
+      </c>
+      <c r="Z151">
+        <v>4.1</v>
+      </c>
+      <c r="AA151">
+        <v>1.71</v>
+      </c>
+      <c r="AB151">
         <v>2.06</v>
       </c>
-      <c r="S151">
-        <v>1.33</v>
-      </c>
-      <c r="T151">
-        <v>3.1</v>
-      </c>
-      <c r="U151">
-        <v>2.62</v>
-      </c>
-      <c r="V151">
-        <v>1.44</v>
-      </c>
-      <c r="W151">
-        <v>1.06</v>
-      </c>
-      <c r="X151">
-        <v>1.01</v>
-      </c>
-      <c r="Y151">
-        <v>1.25</v>
-      </c>
-      <c r="Z151">
-        <v>3.6</v>
-      </c>
-      <c r="AA151">
-        <v>1.9</v>
-      </c>
-      <c r="AB151">
-        <v>1.85</v>
-      </c>
       <c r="AC151">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD151">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE151">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF151">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG151">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK151">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O152">
+        <v>3.45</v>
+      </c>
+      <c r="P152">
+        <v>3.3</v>
+      </c>
+      <c r="Q152">
+        <v>2.47</v>
+      </c>
+      <c r="R152">
+        <v>2.06</v>
+      </c>
+      <c r="S152">
+        <v>1.33</v>
+      </c>
+      <c r="T152">
+        <v>3.1</v>
+      </c>
+      <c r="U152">
+        <v>2.62</v>
+      </c>
+      <c r="V152">
+        <v>1.44</v>
+      </c>
+      <c r="W152">
+        <v>1.06</v>
+      </c>
+      <c r="X152">
+        <v>1.01</v>
+      </c>
+      <c r="Y152">
+        <v>1.25</v>
+      </c>
+      <c r="Z152">
         <v>3.6</v>
       </c>
-      <c r="P152">
-        <v>2.25</v>
-      </c>
-      <c r="Q152">
-        <v>3.64</v>
-      </c>
-      <c r="R152">
-        <v>2.2</v>
-      </c>
-      <c r="S152">
-        <v>1.3</v>
-      </c>
-      <c r="T152">
-        <v>2.95</v>
-      </c>
-      <c r="U152">
-        <v>2.5</v>
-      </c>
-      <c r="V152">
-        <v>1.5</v>
-      </c>
-      <c r="W152">
-        <v>1.07</v>
-      </c>
-      <c r="X152">
-        <v>1.03</v>
-      </c>
-      <c r="Y152">
-        <v>1.2</v>
-      </c>
-      <c r="Z152">
-        <v>4.1</v>
-      </c>
       <c r="AA152">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB152">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AC152">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AD152">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE152">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF152">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG152">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O157">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q157">
-        <v>4.46</v>
+        <v>2.8</v>
       </c>
       <c r="R157">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S157">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U157">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="V157">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z157">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA157">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB157">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC157">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD157">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE157">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF157">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG157">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,34 +26063,34 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="O158">
+        <v>3.45</v>
+      </c>
+      <c r="P158">
+        <v>2.13</v>
+      </c>
+      <c r="Q158">
+        <v>3.2</v>
+      </c>
+      <c r="R158">
+        <v>2.31</v>
+      </c>
+      <c r="S158">
+        <v>1.29</v>
+      </c>
+      <c r="T158">
         <v>3.6</v>
       </c>
-      <c r="P158">
+      <c r="U158">
         <v>2.45</v>
-      </c>
-      <c r="Q158">
-        <v>2.8</v>
-      </c>
-      <c r="R158">
-        <v>2.3</v>
-      </c>
-      <c r="S158">
-        <v>1.27</v>
-      </c>
-      <c r="T158">
-        <v>3.32</v>
-      </c>
-      <c r="U158">
-        <v>2.3</v>
       </c>
       <c r="V158">
         <v>1.52</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X158">
         <v>1.03</v>
@@ -26099,28 +26099,28 @@
         <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA158">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB158">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC158">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD158">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE158">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF158">
         <v>1.53</v>
       </c>
       <c r="AG158">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK158">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.76</v>
+        <v>2.06</v>
       </c>
       <c r="O159">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P159">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="Q159">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="R159">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="S159">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T159">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="U159">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W159">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X159">
         <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z159">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA159">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB159">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="AC159">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="AD159">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE159">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF159">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG159">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK159">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O161">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P161">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="Q161">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R161">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S161">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T161">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U161">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="V161">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W161">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X161">
         <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z161">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AA161">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB161">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC161">
-        <v>3.07</v>
+        <v>2.62</v>
       </c>
       <c r="AD161">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE161">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF161">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK161">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="O162">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q162">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="R162">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S162">
         <v>1.33</v>
       </c>
       <c r="T162">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="U162">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V162">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W162">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z162">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA162">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB162">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC162">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AD162">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE162">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF162">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG162">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK162">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.02</v>
+        <v>3.64</v>
       </c>
       <c r="O179">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P179">
+        <v>2.05</v>
+      </c>
+      <c r="Q179">
         <v>4</v>
       </c>
-      <c r="Q179">
-        <v>2.62</v>
-      </c>
       <c r="R179">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S179">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T179">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="U179">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V179">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W179">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X179">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Z179">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AA179">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB179">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC179">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AD179">
         <v>1.22</v>
       </c>
       <c r="AE179">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF179">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG179">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AK179">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>3.64</v>
+        <v>2.02</v>
       </c>
       <c r="O180">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P180">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="Q180">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R180">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S180">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T180">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="U180">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V180">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W180">
+        <v>1.06</v>
+      </c>
+      <c r="X180">
         <v>1.03</v>
       </c>
-      <c r="X180">
-        <v>1.02</v>
-      </c>
       <c r="Y180">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Z180">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AA180">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB180">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC180">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD180">
         <v>1.22</v>
       </c>
       <c r="AE180">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF180">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG180">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AK180">
-        <v>1.29</v>
+        <v>1.82</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O235">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P235">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q235">
         <v>3.1</v>
       </c>
       <c r="R235">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S235">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T235">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="U235">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="V235">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W235">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X235">
         <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z235">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA235">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AB235">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC235">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD235">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE235">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF235">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG235">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK235">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q236">
         <v>3.1</v>
       </c>
       <c r="R236">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S236">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T236">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="U236">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="V236">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W236">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X236">
         <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z236">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA236">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AB236">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC236">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD236">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE236">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF236">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG236">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK236">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,61 +40570,61 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q247">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="R247">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T247">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U247">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="V247">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W247">
         <v>1.05</v>
       </c>
       <c r="X247">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y247">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z247">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA247">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB247">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC247">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="AD247">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE247">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG247">
         <v>2.15</v>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,61 +40733,61 @@
         </is>
       </c>
       <c r="N248">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S248">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T248">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U248">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="V248">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W248">
         <v>1.05</v>
       </c>
       <c r="X248">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z248">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA248">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB248">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC248">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD248">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE248">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF248">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG248">
         <v>2.15</v>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK248">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -51171,13 +51171,13 @@
         <v>4.6</v>
       </c>
       <c r="P312">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q312">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R312">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="S312">
         <v>1.2</v>
@@ -51186,7 +51186,7 @@
         <v>4</v>
       </c>
       <c r="U312">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V312">
         <v>1.67</v>
@@ -51198,25 +51198,25 @@
         <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z312">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA312">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB312">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AC312">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AD312">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AE312">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF312">
         <v>1.57</v>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK312">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51376,7 +51376,7 @@
         <v>2.17</v>
       </c>
       <c r="AD313">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE313">
         <v>1.21</v>
@@ -51491,16 +51491,16 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="O314">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P314">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q314">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R314">
         <v>2.18</v>
@@ -51521,7 +51521,7 @@
         <v>1.08</v>
       </c>
       <c r="X314">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y314">
         <v>1.2</v>
@@ -51530,7 +51530,7 @@
         <v>3.72</v>
       </c>
       <c r="AA314">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB314">
         <v>2</v>
@@ -51564,7 +51564,7 @@
         <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51817,19 +51817,19 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O316">
         <v>4.05</v>
       </c>
       <c r="P316">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="Q316">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R316">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="S316">
         <v>1.3</v>
@@ -51844,7 +51844,7 @@
         <v>1.5</v>
       </c>
       <c r="W316">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X316">
         <v>1.02</v>
@@ -51853,7 +51853,7 @@
         <v>1.17</v>
       </c>
       <c r="Z316">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA316">
         <v>1.7</v>
@@ -51862,13 +51862,13 @@
         <v>2.1</v>
       </c>
       <c r="AC316">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD316">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE316">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF316">
         <v>1.7</v>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK316">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -52330,7 +52330,7 @@
         <v>2.2</v>
       </c>
       <c r="V319">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W319">
         <v>1.16</v>
@@ -52342,7 +52342,7 @@
         <v>1.1</v>
       </c>
       <c r="Z319">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA319">
         <v>1.5</v>
@@ -55433,7 +55433,7 @@
         <v>1.08</v>
       </c>
       <c r="X338">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y338">
         <v>1.18</v>
@@ -55575,7 +55575,7 @@
         <v>3.25</v>
       </c>
       <c r="Q339">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R339">
         <v>2.21</v>
@@ -55605,7 +55605,7 @@
         <v>3.72</v>
       </c>
       <c r="AA339">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB339">
         <v>1.96</v>
@@ -55620,10 +55620,10 @@
         <v>1.1</v>
       </c>
       <c r="AF339">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG339">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>1.25</v>
       </c>
       <c r="AK339">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1302,7 +1302,7 @@
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
         <v>2.54</v>
@@ -1317,7 +1317,7 @@
         <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.33</v>
@@ -1326,16 +1326,16 @@
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB6">
         <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE6">
         <v>1.05</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="Q8">
-        <v>3.16</v>
+        <v>4.27</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U8">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="Q9">
-        <v>4.27</v>
+        <v>3.16</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA9">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK9">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O26">
         <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q48">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="R48">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U48">
-        <v>2.21</v>
+        <v>2.73</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z48">
-        <v>4.85</v>
+        <v>3.25</v>
       </c>
       <c r="AA48">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AC48">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AD48">
+        <v>1.3</v>
+      </c>
+      <c r="AE48">
+        <v>1.08</v>
+      </c>
+      <c r="AF48">
+        <v>1.64</v>
+      </c>
+      <c r="AG48">
+        <v>2.1</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.33</v>
+      </c>
+      <c r="AK48">
         <v>1.5</v>
-      </c>
-      <c r="AE48">
-        <v>1.18</v>
-      </c>
-      <c r="AF48">
-        <v>1.53</v>
-      </c>
-      <c r="AG48">
-        <v>2.3</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.25</v>
-      </c>
-      <c r="AK48">
-        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q49">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="S49">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.73</v>
+        <v>2.21</v>
       </c>
       <c r="V49">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA49">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
-        <v>2.97</v>
+        <v>2.31</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
+        <v>2.2</v>
+      </c>
+      <c r="O63">
         <v>3.25</v>
       </c>
-      <c r="O63">
-        <v>3.1</v>
-      </c>
       <c r="P63">
+        <v>3</v>
+      </c>
+      <c r="Q63">
+        <v>2.8</v>
+      </c>
+      <c r="R63">
+        <v>2.2</v>
+      </c>
+      <c r="S63">
+        <v>1.35</v>
+      </c>
+      <c r="T63">
+        <v>2.88</v>
+      </c>
+      <c r="U63">
+        <v>2.43</v>
+      </c>
+      <c r="V63">
+        <v>1.51</v>
+      </c>
+      <c r="W63">
+        <v>1.1</v>
+      </c>
+      <c r="X63">
+        <v>1.02</v>
+      </c>
+      <c r="Y63">
+        <v>1.17</v>
+      </c>
+      <c r="Z63">
+        <v>4</v>
+      </c>
+      <c r="AA63">
+        <v>1.7</v>
+      </c>
+      <c r="AB63">
         <v>2.05</v>
       </c>
-      <c r="Q63">
-        <v>4.1</v>
-      </c>
-      <c r="R63">
-        <v>2.02</v>
-      </c>
-      <c r="S63">
+      <c r="AC63">
+        <v>2.89</v>
+      </c>
+      <c r="AD63">
         <v>1.4</v>
       </c>
-      <c r="T63">
-        <v>2.53</v>
-      </c>
-      <c r="U63">
-        <v>2.83</v>
-      </c>
-      <c r="V63">
-        <v>1.36</v>
-      </c>
-      <c r="W63">
-        <v>1.07</v>
-      </c>
-      <c r="X63">
-        <v>1.04</v>
-      </c>
-      <c r="Y63">
-        <v>1.28</v>
-      </c>
-      <c r="Z63">
-        <v>3.05</v>
-      </c>
-      <c r="AA63">
-        <v>2.04</v>
-      </c>
-      <c r="AB63">
-        <v>1.69</v>
-      </c>
-      <c r="AC63">
-        <v>3.91</v>
-      </c>
-      <c r="AD63">
-        <v>1.24</v>
-      </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O64">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P64">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Q64">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R64">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S64">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="U64">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="V64">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AA64">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AB64">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AC64">
-        <v>2.89</v>
+        <v>3.91</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG64">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AK64">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
+        <v>2.81</v>
+      </c>
+      <c r="R66">
+        <v>2.21</v>
+      </c>
+      <c r="S66">
+        <v>1.25</v>
+      </c>
+      <c r="T66">
+        <v>3.46</v>
+      </c>
+      <c r="U66">
+        <v>2.22</v>
+      </c>
+      <c r="V66">
+        <v>1.53</v>
+      </c>
+      <c r="W66">
+        <v>1.11</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.13</v>
+      </c>
+      <c r="Z66">
+        <v>4.55</v>
+      </c>
+      <c r="AA66">
+        <v>1.56</v>
+      </c>
+      <c r="AB66">
+        <v>2.22</v>
+      </c>
+      <c r="AC66">
+        <v>2.46</v>
+      </c>
+      <c r="AD66">
+        <v>1.52</v>
+      </c>
+      <c r="AE66">
+        <v>1.15</v>
+      </c>
+      <c r="AF66">
+        <v>1.48</v>
+      </c>
+      <c r="AG66">
         <v>2.4</v>
       </c>
-      <c r="R66">
-        <v>2.4</v>
-      </c>
-      <c r="S66">
-        <v>1.22</v>
-      </c>
-      <c r="T66">
-        <v>3.52</v>
-      </c>
-      <c r="U66">
-        <v>2.25</v>
-      </c>
-      <c r="V66">
-        <v>1.62</v>
-      </c>
-      <c r="W66">
-        <v>1.14</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.12</v>
-      </c>
-      <c r="Z66">
-        <v>4.7</v>
-      </c>
-      <c r="AA66">
-        <v>1.48</v>
-      </c>
-      <c r="AB66">
-        <v>2.33</v>
-      </c>
-      <c r="AC66">
-        <v>2.22</v>
-      </c>
-      <c r="AD66">
-        <v>1.56</v>
-      </c>
-      <c r="AE66">
-        <v>1.2</v>
-      </c>
-      <c r="AF66">
-        <v>1.46</v>
-      </c>
-      <c r="AG66">
-        <v>2.5</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
+        <v>2.99</v>
+      </c>
+      <c r="Q67">
+        <v>2.5</v>
+      </c>
+      <c r="R67">
+        <v>2.36</v>
+      </c>
+      <c r="S67">
+        <v>1.19</v>
+      </c>
+      <c r="T67">
+        <v>4</v>
+      </c>
+      <c r="U67">
+        <v>2.1</v>
+      </c>
+      <c r="V67">
+        <v>1.65</v>
+      </c>
+      <c r="W67">
+        <v>1.13</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.08</v>
+      </c>
+      <c r="Z67">
+        <v>5.7</v>
+      </c>
+      <c r="AA67">
+        <v>1.44</v>
+      </c>
+      <c r="AB67">
         <v>2.62</v>
       </c>
-      <c r="Q67">
-        <v>2.81</v>
-      </c>
-      <c r="R67">
-        <v>2.21</v>
-      </c>
-      <c r="S67">
-        <v>1.25</v>
-      </c>
-      <c r="T67">
-        <v>3.46</v>
-      </c>
-      <c r="U67">
-        <v>2.22</v>
-      </c>
-      <c r="V67">
-        <v>1.53</v>
-      </c>
-      <c r="W67">
-        <v>1.11</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.13</v>
-      </c>
-      <c r="Z67">
-        <v>4.55</v>
-      </c>
-      <c r="AA67">
-        <v>1.56</v>
-      </c>
-      <c r="AB67">
-        <v>2.22</v>
-      </c>
       <c r="AC67">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="AD67">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AE67">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF67">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O68">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="Q68">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="U68">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V68">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W68">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AA68">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB68">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AC68">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="AD68">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AE68">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG68">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="O85">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P85">
+        <v>5.25</v>
+      </c>
+      <c r="Q85">
+        <v>2.08</v>
+      </c>
+      <c r="R85">
         <v>2.3</v>
       </c>
-      <c r="Q85">
-        <v>3.54</v>
-      </c>
-      <c r="R85">
-        <v>2.1</v>
-      </c>
       <c r="S85">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T85">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U85">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="V85">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W85">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z85">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA85">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AC85">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="AD85">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE85">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF85">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="AK85">
-        <v>1.36</v>
+        <v>2.19</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="O86">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q86">
-        <v>2.08</v>
+        <v>3.54</v>
       </c>
       <c r="R86">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T86">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U86">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA86">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB86">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC86">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="AD86">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE86">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG86">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AK86">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -19893,10 +19893,10 @@
         <v>2.2</v>
       </c>
       <c r="V120">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="W120">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X120">
         <v>1.02</v>
@@ -19908,16 +19908,16 @@
         <v>4.85</v>
       </c>
       <c r="AA120">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB120">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="AC120">
         <v>2.24</v>
       </c>
       <c r="AD120">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE120">
         <v>1.15</v>
@@ -19942,7 +19942,7 @@
         <v>1.12</v>
       </c>
       <c r="AK120">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,16 +20041,16 @@
         <v>2.03</v>
       </c>
       <c r="Q121">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="R121">
         <v>2.17</v>
       </c>
       <c r="S121">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T121">
-        <v>2.37</v>
+        <v>3.17</v>
       </c>
       <c r="U121">
         <v>2.45</v>
@@ -20204,7 +20204,7 @@
         <v>1.86</v>
       </c>
       <c r="Q122">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="R122">
         <v>2.05</v>
@@ -20249,7 +20249,7 @@
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AG122">
         <v>1.98</v>
@@ -20373,10 +20373,10 @@
         <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T123">
-        <v>2.39</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
         <v>2.5</v>
@@ -20524,7 +20524,7 @@
         <v>2.69</v>
       </c>
       <c r="O124">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P124">
         <v>2.25</v>
@@ -20551,13 +20551,13 @@
         <v>1.1</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
         <v>1.2</v>
       </c>
       <c r="Z124">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA124">
         <v>1.9</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="O132">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="Q132">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R132">
         <v>2.1</v>
@@ -21843,46 +21843,46 @@
         <v>1.36</v>
       </c>
       <c r="T132">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="U132">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="V132">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W132">
+        <v>1.07</v>
+      </c>
+      <c r="X132">
         <v>1.05</v>
       </c>
-      <c r="X132">
-        <v>1.01</v>
-      </c>
       <c r="Y132">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z132">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA132">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB132">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC132">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD132">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
         <v>1.8</v>
       </c>
       <c r="AG132">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.55</v>
+        <v>2.67</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R134">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S134">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T134">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="U134">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V134">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z134">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB134">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AC134">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD134">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AE134">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF134">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG134">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.46</v>
+        <v>2.4</v>
       </c>
       <c r="O135">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="P135">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="Q135">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="R135">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T135">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="U135">
-        <v>2.15</v>
+        <v>3.07</v>
       </c>
       <c r="V135">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="W135">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z135">
-        <v>5.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA135">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="AB135">
-        <v>2.43</v>
+        <v>1.73</v>
       </c>
       <c r="AC135">
-        <v>2.19</v>
+        <v>3.5</v>
       </c>
       <c r="AD135">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AE135">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG135">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AK135">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,65 +22477,65 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="O136">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="P136">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="Q136">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="R136">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="S136">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T136">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U136">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V136">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W136">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X136">
         <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z136">
-        <v>4.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA136">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB136">
+        <v>2.43</v>
+      </c>
+      <c r="AC136">
+        <v>2.19</v>
+      </c>
+      <c r="AD136">
+        <v>1.62</v>
+      </c>
+      <c r="AE136">
+        <v>1.24</v>
+      </c>
+      <c r="AF136">
+        <v>1.62</v>
+      </c>
+      <c r="AG136">
         <v>2.15</v>
       </c>
-      <c r="AC136">
-        <v>2.59</v>
-      </c>
-      <c r="AD136">
-        <v>1.43</v>
-      </c>
-      <c r="AE136">
-        <v>1.13</v>
-      </c>
-      <c r="AF136">
-        <v>1.54</v>
-      </c>
-      <c r="AG136">
-        <v>2.4</v>
-      </c>
       <c r="AH136" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK136">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="O137">
         <v>3.5</v>
       </c>
       <c r="P137">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q137">
         <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V137">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
         <v>1.07</v>
       </c>
       <c r="X137">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA137">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AB137">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC137">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD137">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE137">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF137">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG137">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK137">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,16 +23781,16 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O144">
         <v>3.4</v>
       </c>
       <c r="P144">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="R144">
         <v>2.1</v>
@@ -23799,62 +23799,62 @@
         <v>1.36</v>
       </c>
       <c r="T144">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U144">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y144">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z144">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA144">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB144">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC144">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="AD144">
+        <v>1.23</v>
+      </c>
+      <c r="AE144">
+        <v>1.04</v>
+      </c>
+      <c r="AF144">
+        <v>1.79</v>
+      </c>
+      <c r="AG144">
+        <v>1.93</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.29</v>
       </c>
-      <c r="AE144">
-        <v>1.07</v>
-      </c>
-      <c r="AF144">
-        <v>1.73</v>
-      </c>
-      <c r="AG144">
-        <v>2.08</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.3</v>
-      </c>
       <c r="AK144">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
+        <v>2.8</v>
+      </c>
+      <c r="O145">
+        <v>3.6</v>
+      </c>
+      <c r="P145">
+        <v>2.3</v>
+      </c>
+      <c r="Q145">
+        <v>3.5</v>
+      </c>
+      <c r="R145">
+        <v>2.4</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
+        <v>3.4</v>
+      </c>
+      <c r="U145">
+        <v>2.47</v>
+      </c>
+      <c r="V145">
+        <v>1.52</v>
+      </c>
+      <c r="W145">
+        <v>1.1</v>
+      </c>
+      <c r="X145">
+        <v>1.02</v>
+      </c>
+      <c r="Y145">
+        <v>1.16</v>
+      </c>
+      <c r="Z145">
+        <v>4.15</v>
+      </c>
+      <c r="AA145">
+        <v>1.65</v>
+      </c>
+      <c r="AB145">
         <v>2.15</v>
       </c>
-      <c r="O145">
-        <v>3.4</v>
-      </c>
-      <c r="P145">
-        <v>3.3</v>
-      </c>
-      <c r="Q145">
+      <c r="AC145">
         <v>2.49</v>
       </c>
-      <c r="R145">
-        <v>2.1</v>
-      </c>
-      <c r="S145">
-        <v>1.36</v>
-      </c>
-      <c r="T145">
-        <v>3</v>
-      </c>
-      <c r="U145">
-        <v>2.92</v>
-      </c>
-      <c r="V145">
-        <v>1.37</v>
-      </c>
-      <c r="W145">
-        <v>1.02</v>
-      </c>
-      <c r="X145">
-        <v>1.04</v>
-      </c>
-      <c r="Y145">
-        <v>1.33</v>
-      </c>
-      <c r="Z145">
-        <v>2.94</v>
-      </c>
-      <c r="AA145">
-        <v>2.05</v>
-      </c>
-      <c r="AB145">
-        <v>1.76</v>
-      </c>
-      <c r="AC145">
-        <v>3.42</v>
-      </c>
       <c r="AD145">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF145">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.29</v>
       </c>
       <c r="AK145">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G146">
@@ -24110,61 +24110,61 @@
         <v>2.8</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q146">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R146">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S146">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T146">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U146">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V146">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W146">
         <v>1.1</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z146">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="AA146">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AB146">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC146">
-        <v>2.49</v>
+        <v>2.99</v>
       </c>
       <c r="AD146">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF146">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG146">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK146">
         <v>1.37</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="P157">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q157">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="R157">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S157">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T157">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="U157">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V157">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W157">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X157">
         <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z157">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA157">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB157">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AC157">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD157">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE157">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF157">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG157">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK157">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
+        <v>1.83</v>
+      </c>
+      <c r="O158">
+        <v>3.7</v>
+      </c>
+      <c r="P158">
+        <v>4</v>
+      </c>
+      <c r="Q158">
+        <v>2.4</v>
+      </c>
+      <c r="R158">
+        <v>2.11</v>
+      </c>
+      <c r="S158">
+        <v>1.36</v>
+      </c>
+      <c r="T158">
         <v>2.76</v>
       </c>
-      <c r="O158">
-        <v>3.45</v>
-      </c>
-      <c r="P158">
-        <v>2.13</v>
-      </c>
-      <c r="Q158">
-        <v>3.2</v>
-      </c>
-      <c r="R158">
-        <v>2.31</v>
-      </c>
-      <c r="S158">
-        <v>1.29</v>
-      </c>
-      <c r="T158">
-        <v>3.6</v>
-      </c>
       <c r="U158">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V158">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W158">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z158">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA158">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB158">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AC158">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD158">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE158">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF158">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AG158">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="O159">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P159">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q159">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="R159">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S159">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T159">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="U159">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="V159">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W159">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X159">
         <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z159">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA159">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB159">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="AC159">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="AD159">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE159">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF159">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG159">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK159">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,80 +26389,80 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.83</v>
+        <v>2.76</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P160">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="Q160">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R160">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="S160">
+        <v>1.29</v>
+      </c>
+      <c r="T160">
+        <v>3.6</v>
+      </c>
+      <c r="U160">
+        <v>2.45</v>
+      </c>
+      <c r="V160">
+        <v>1.52</v>
+      </c>
+      <c r="W160">
+        <v>1.12</v>
+      </c>
+      <c r="X160">
+        <v>1.03</v>
+      </c>
+      <c r="Y160">
+        <v>1.15</v>
+      </c>
+      <c r="Z160">
+        <v>3.8</v>
+      </c>
+      <c r="AA160">
+        <v>1.62</v>
+      </c>
+      <c r="AB160">
+        <v>2.24</v>
+      </c>
+      <c r="AC160">
+        <v>2.49</v>
+      </c>
+      <c r="AD160">
+        <v>1.42</v>
+      </c>
+      <c r="AE160">
+        <v>1.18</v>
+      </c>
+      <c r="AF160">
+        <v>1.53</v>
+      </c>
+      <c r="AG160">
+        <v>2.35</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ160">
+        <v>1.25</v>
+      </c>
+      <c r="AK160">
         <v>1.36</v>
-      </c>
-      <c r="T160">
-        <v>2.76</v>
-      </c>
-      <c r="U160">
-        <v>2.74</v>
-      </c>
-      <c r="V160">
-        <v>1.43</v>
-      </c>
-      <c r="W160">
-        <v>1.1</v>
-      </c>
-      <c r="X160">
-        <v>1.04</v>
-      </c>
-      <c r="Y160">
-        <v>1.22</v>
-      </c>
-      <c r="Z160">
-        <v>3.5</v>
-      </c>
-      <c r="AA160">
-        <v>1.81</v>
-      </c>
-      <c r="AB160">
-        <v>2</v>
-      </c>
-      <c r="AC160">
-        <v>2.88</v>
-      </c>
-      <c r="AD160">
-        <v>1.32</v>
-      </c>
-      <c r="AE160">
-        <v>1.08</v>
-      </c>
-      <c r="AF160">
-        <v>1.72</v>
-      </c>
-      <c r="AG160">
-        <v>2.01</v>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ160">
-        <v>1.22</v>
-      </c>
-      <c r="AK160">
-        <v>1.91</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O161">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P161">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="Q161">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="R161">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S161">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T161">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U161">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="V161">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W161">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X161">
         <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z161">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="AA161">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB161">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC161">
-        <v>2.62</v>
+        <v>3.07</v>
       </c>
       <c r="AD161">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE161">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG161">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK161">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P162">
-        <v>2.62</v>
+        <v>1.48</v>
       </c>
       <c r="Q162">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R162">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S162">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T162">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U162">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="V162">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W162">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X162">
         <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z162">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="AA162">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB162">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC162">
-        <v>3.07</v>
+        <v>2.62</v>
       </c>
       <c r="AD162">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE162">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF162">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG162">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK162">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -30796,10 +30796,10 @@
         <v>2.9</v>
       </c>
       <c r="P187">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q187">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="R187">
         <v>1.85</v>
@@ -30832,7 +30832,7 @@
         <v>2.83</v>
       </c>
       <c r="AB187">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC187">
         <v>6</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="O195">
         <v>2.81</v>
       </c>
       <c r="P195">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O214">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P214">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35230,10 +35230,10 @@
         <v>0</v>
       </c>
       <c r="AA214">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB214">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC214">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O217">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P217">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q217">
         <v>2.62</v>
@@ -35695,10 +35695,10 @@
         <v>1.95</v>
       </c>
       <c r="S217">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="T217">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="U217">
         <v>3.3</v>
@@ -35710,28 +35710,28 @@
         <v>1.05</v>
       </c>
       <c r="X217">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y217">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z217">
         <v>2.5</v>
       </c>
       <c r="AA217">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB217">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC217">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD217">
         <v>1.12</v>
       </c>
       <c r="AE217">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF217">
         <v>2.1</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O222">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P222">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q222">
         <v>2.7</v>
@@ -36522,7 +36522,7 @@
         <v>1.38</v>
       </c>
       <c r="W222">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X222">
         <v>1.01</v>
@@ -36537,7 +36537,7 @@
         <v>1.95</v>
       </c>
       <c r="AB222">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC222">
         <v>3.28</v>
@@ -36565,7 +36565,7 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK222">
         <v>1.62</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O223">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P223">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="Q223">
         <v>3.2</v>
@@ -36697,7 +36697,7 @@
         <v>2.92</v>
       </c>
       <c r="AA223">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB223">
         <v>1.72</v>
@@ -37968,7 +37968,7 @@
         <v>2.9</v>
       </c>
       <c r="P231">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>0</v>
       </c>
       <c r="AA231">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB231">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC231">
         <v>0</v>
@@ -40452,13 +40452,13 @@
         <v>2.62</v>
       </c>
       <c r="AC246">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AD246">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AE246">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF246">
         <v>2.12</v>
@@ -40899,7 +40899,7 @@
         <v>2.5</v>
       </c>
       <c r="O249">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P249">
         <v>2.8</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O256">
         <v>3.3</v>
       </c>
       <c r="P256">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="O260">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="P260">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42728,10 +42728,10 @@
         <v>0</v>
       </c>
       <c r="AA260">
+        <v>1.95</v>
+      </c>
+      <c r="AB260">
         <v>1.85</v>
-      </c>
-      <c r="AB260">
-        <v>1.95</v>
       </c>
       <c r="AC260">
         <v>0</v>
@@ -43504,10 +43504,10 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O265">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="P265">
         <v>2.88</v>
@@ -44008,13 +44008,13 @@
         <v>1.87</v>
       </c>
       <c r="S268">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="T268">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U268">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="V268">
         <v>1.19</v>
@@ -44029,7 +44029,7 @@
         <v>1.61</v>
       </c>
       <c r="Z268">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AA268">
         <v>2.91</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="O282">
         <v>3.28</v>
       </c>
       <c r="P282">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,10 +46314,10 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB282">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC282">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>4.7</v>
       </c>
       <c r="AA306">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AB306">
-        <v>2.33</v>
+        <v>2.02</v>
       </c>
       <c r="AC306">
         <v>2.29</v>
@@ -50238,7 +50238,7 @@
         <v>1.53</v>
       </c>
       <c r="AE306">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF306">
         <v>1.44</v>
@@ -51011,7 +51011,7 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="R311">
         <v>2.3</v>
@@ -51029,7 +51029,7 @@
         <v>1.52</v>
       </c>
       <c r="W311">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X311">
         <v>1.03</v>
@@ -51044,7 +51044,7 @@
         <v>1.57</v>
       </c>
       <c r="AB311">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC311">
         <v>2.46</v>
@@ -51075,7 +51075,7 @@
         <v>1.2</v>
       </c>
       <c r="AK311">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -54600,7 +54600,7 @@
         <v>2.2</v>
       </c>
       <c r="R333">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S333">
         <v>1.25</v>
@@ -54645,7 +54645,7 @@
         <v>1.57</v>
       </c>
       <c r="AG333">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK333">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AL333">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1335,7 +1335,7 @@
         <v>3.42</v>
       </c>
       <c r="AD6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE6">
         <v>1.05</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="Q8">
-        <v>4.8</v>
+        <v>3.16</v>
       </c>
       <c r="R8">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T8">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z8">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA8">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB8">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK8">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="Q9">
-        <v>3.16</v>
+        <v>4.8</v>
       </c>
       <c r="R9">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S9">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U9">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA9">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC9">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -5054,10 +5054,10 @@
         <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="U29">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="V29">
         <v>1.3</v>
@@ -5069,10 +5069,10 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z29">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="O48">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P48">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="S48">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.58</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA48">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AC48">
-        <v>2.97</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
+        <v>1.75</v>
+      </c>
+      <c r="O49">
         <v>4</v>
       </c>
-      <c r="O49">
-        <v>3.9</v>
-      </c>
       <c r="P49">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="R49">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="V49">
         <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA49">
+        <v>1.58</v>
+      </c>
+      <c r="AB49">
+        <v>2.17</v>
+      </c>
+      <c r="AC49">
+        <v>2.4</v>
+      </c>
+      <c r="AD49">
+        <v>1.44</v>
+      </c>
+      <c r="AE49">
+        <v>1.15</v>
+      </c>
+      <c r="AF49">
         <v>1.57</v>
       </c>
-      <c r="AB49">
-        <v>2.31</v>
-      </c>
-      <c r="AC49">
-        <v>2.31</v>
-      </c>
-      <c r="AD49">
-        <v>1.5</v>
-      </c>
-      <c r="AE49">
-        <v>1.18</v>
-      </c>
-      <c r="AF49">
-        <v>1.53</v>
-      </c>
       <c r="AG49">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U50">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA50">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O71">
         <v>4</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q78">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z78">
-        <v>2.74</v>
+        <v>3.93</v>
       </c>
       <c r="AA78">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AB78">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AC78">
-        <v>4</v>
+        <v>2.87</v>
       </c>
       <c r="AD78">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AE78">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,65 +13186,65 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P79">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q79">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R79">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="U79">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="V79">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z79">
-        <v>3.93</v>
+        <v>2.74</v>
       </c>
       <c r="AA79">
+        <v>2.18</v>
+      </c>
+      <c r="AB79">
+        <v>1.58</v>
+      </c>
+      <c r="AC79">
+        <v>4</v>
+      </c>
+      <c r="AD79">
+        <v>1.17</v>
+      </c>
+      <c r="AE79">
+        <v>1.04</v>
+      </c>
+      <c r="AF79">
+        <v>1.85</v>
+      </c>
+      <c r="AG79">
         <v>1.76</v>
       </c>
-      <c r="AB79">
-        <v>2.05</v>
-      </c>
-      <c r="AC79">
-        <v>2.87</v>
-      </c>
-      <c r="AD79">
-        <v>1.39</v>
-      </c>
-      <c r="AE79">
-        <v>1.11</v>
-      </c>
-      <c r="AF79">
-        <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.1</v>
-      </c>
       <c r="AH79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q85">
-        <v>2.05</v>
+        <v>3.54</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="V85">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W85">
         <v>1.09</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AB85">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC85">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="AD85">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE85">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AK85">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P86">
+        <v>5.25</v>
+      </c>
+      <c r="Q86">
+        <v>2.05</v>
+      </c>
+      <c r="R86">
         <v>2.3</v>
       </c>
-      <c r="Q86">
-        <v>3.54</v>
-      </c>
-      <c r="R86">
-        <v>2.1</v>
-      </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T86">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U86">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="V86">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W86">
         <v>1.09</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z86">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA86">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB86">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AC86">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD86">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF86">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>2.19</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,28 +18891,28 @@
         </is>
       </c>
       <c r="N114">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="O114">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P114">
-        <v>1.73</v>
+        <v>4.33</v>
       </c>
       <c r="Q114">
-        <v>4.99</v>
+        <v>2.3</v>
       </c>
       <c r="R114">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S114">
         <v>1.33</v>
       </c>
       <c r="T114">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="U114">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V114">
         <v>1.49</v>
@@ -18921,34 +18921,34 @@
         <v>1.11</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y114">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA114">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB114">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AC114">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD114">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF114">
         <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK114">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P115">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q115">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R115">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T115">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U115">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V115">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W115">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z115">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA115">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB115">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AC115">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE115">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG115">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,61 +19217,61 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="O116">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P116">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="Q116">
-        <v>2.1</v>
+        <v>4.99</v>
       </c>
       <c r="R116">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="S116">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="U116">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="V116">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W116">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z116">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA116">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB116">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AC116">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AD116">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AE116">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
         <v>2.05</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
+        <v>1.25</v>
+      </c>
+      <c r="AK116">
         <v>1.18</v>
-      </c>
-      <c r="AK116">
-        <v>2.27</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O117">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P117">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q117">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="R117">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S117">
         <v>1.4</v>
       </c>
       <c r="T117">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="U117">
+        <v>3.4</v>
+      </c>
+      <c r="V117">
+        <v>1.28</v>
+      </c>
+      <c r="W117">
+        <v>1</v>
+      </c>
+      <c r="X117">
+        <v>1.02</v>
+      </c>
+      <c r="Y117">
+        <v>1.4</v>
+      </c>
+      <c r="Z117">
         <v>2.75</v>
       </c>
-      <c r="V117">
-        <v>1.34</v>
-      </c>
-      <c r="W117">
-        <v>1.03</v>
-      </c>
-      <c r="X117">
-        <v>1.04</v>
-      </c>
-      <c r="Y117">
-        <v>1.33</v>
-      </c>
-      <c r="Z117">
-        <v>3.32</v>
-      </c>
       <c r="AA117">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB117">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC117">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD117">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE117">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF117">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AG117">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,65 +19543,65 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O118">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P118">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R118">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S118">
         <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U118">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W118">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z118">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AA118">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB118">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC118">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD118">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF118">
+        <v>1.77</v>
+      </c>
+      <c r="AG118">
         <v>1.93</v>
       </c>
-      <c r="AG118">
-        <v>1.87</v>
-      </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK118">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P122">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q122">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="R122">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.39</v>
+        <v>3.09</v>
       </c>
       <c r="U122">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V122">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z122">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AA122">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AB122">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AD122">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG122">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK122">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="O123">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>1.86</v>
+        <v>3.25</v>
       </c>
       <c r="Q123">
-        <v>4.4</v>
+        <v>2.69</v>
       </c>
       <c r="R123">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T123">
-        <v>3.09</v>
+        <v>2.39</v>
       </c>
       <c r="U123">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W123">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y123">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA123">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AB123">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC123">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF123">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG123">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O125">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P125">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q125">
         <v>2.3</v>
@@ -20738,10 +20738,10 @@
         <v>1.05</v>
       </c>
       <c r="AF125">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG125">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q132">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R132">
         <v>2.1</v>
       </c>
       <c r="S132">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="U132">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="V132">
         <v>1.4</v>
       </c>
       <c r="W132">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X132">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y132">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z132">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA132">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB132">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC132">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="AD132">
         <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG132">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,65 +22151,65 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="O134">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="P134">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="Q134">
-        <v>2.86</v>
+        <v>1.87</v>
       </c>
       <c r="R134">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="S134">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="T134">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U134">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V134">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X134">
         <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z134">
-        <v>4.1</v>
+        <v>5.62</v>
       </c>
       <c r="AA134">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB134">
+        <v>2.43</v>
+      </c>
+      <c r="AC134">
+        <v>2.22</v>
+      </c>
+      <c r="AD134">
+        <v>1.62</v>
+      </c>
+      <c r="AE134">
+        <v>1.24</v>
+      </c>
+      <c r="AF134">
+        <v>1.62</v>
+      </c>
+      <c r="AG134">
         <v>2.15</v>
       </c>
-      <c r="AC134">
-        <v>2.59</v>
-      </c>
-      <c r="AD134">
-        <v>1.43</v>
-      </c>
-      <c r="AE134">
-        <v>1.13</v>
-      </c>
-      <c r="AF134">
-        <v>1.54</v>
-      </c>
-      <c r="AG134">
-        <v>2.4</v>
-      </c>
       <c r="AH134" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK134">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P135">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q135">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R135">
         <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T135">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U135">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="V135">
         <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z135">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA135">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB135">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC135">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="AD135">
         <v>1.25</v>
       </c>
       <c r="AE135">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK135">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="O136">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U136">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V136">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z136">
-        <v>5.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA136">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB136">
-        <v>2.43</v>
+        <v>1.86</v>
       </c>
       <c r="AC136">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="AD136">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AF136">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG136">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>3.55</v>
+        <v>2.67</v>
       </c>
       <c r="Q137">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="R137">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T137">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U137">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA137">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB137">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AC137">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD137">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AE137">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF137">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG137">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O144">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P144">
+        <v>4.5</v>
+      </c>
+      <c r="Q144">
+        <v>2.25</v>
+      </c>
+      <c r="R144">
+        <v>2.13</v>
+      </c>
+      <c r="S144">
+        <v>1.32</v>
+      </c>
+      <c r="T144">
+        <v>3.02</v>
+      </c>
+      <c r="U144">
+        <v>2.69</v>
+      </c>
+      <c r="V144">
+        <v>1.44</v>
+      </c>
+      <c r="W144">
+        <v>1.07</v>
+      </c>
+      <c r="X144">
+        <v>1.01</v>
+      </c>
+      <c r="Y144">
+        <v>1.2</v>
+      </c>
+      <c r="Z144">
         <v>3.35</v>
       </c>
-      <c r="Q144">
-        <v>2.49</v>
-      </c>
-      <c r="R144">
+      <c r="AA144">
+        <v>1.8</v>
+      </c>
+      <c r="AB144">
+        <v>1.95</v>
+      </c>
+      <c r="AC144">
+        <v>2.88</v>
+      </c>
+      <c r="AD144">
+        <v>1.32</v>
+      </c>
+      <c r="AE144">
+        <v>1.14</v>
+      </c>
+      <c r="AF144">
+        <v>1.7</v>
+      </c>
+      <c r="AG144">
+        <v>2</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>1.13</v>
+      </c>
+      <c r="AK144">
         <v>2.05</v>
-      </c>
-      <c r="S144">
-        <v>1.36</v>
-      </c>
-      <c r="T144">
-        <v>3</v>
-      </c>
-      <c r="U144">
-        <v>2.92</v>
-      </c>
-      <c r="V144">
-        <v>1.37</v>
-      </c>
-      <c r="W144">
-        <v>1.02</v>
-      </c>
-      <c r="X144">
-        <v>1.04</v>
-      </c>
-      <c r="Y144">
-        <v>1.33</v>
-      </c>
-      <c r="Z144">
-        <v>2.94</v>
-      </c>
-      <c r="AA144">
-        <v>2.05</v>
-      </c>
-      <c r="AB144">
-        <v>1.76</v>
-      </c>
-      <c r="AC144">
-        <v>3.42</v>
-      </c>
-      <c r="AD144">
-        <v>1.23</v>
-      </c>
-      <c r="AE144">
-        <v>1.04</v>
-      </c>
-      <c r="AF144">
-        <v>1.79</v>
-      </c>
-      <c r="AG144">
-        <v>1.93</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.29</v>
-      </c>
-      <c r="AK144">
-        <v>1.72</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,80 +23944,80 @@
         </is>
       </c>
       <c r="N145">
+        <v>2.8</v>
+      </c>
+      <c r="O145">
+        <v>3.4</v>
+      </c>
+      <c r="P145">
+        <v>2.45</v>
+      </c>
+      <c r="Q145">
+        <v>3.51</v>
+      </c>
+      <c r="R145">
+        <v>2.1</v>
+      </c>
+      <c r="S145">
+        <v>1.36</v>
+      </c>
+      <c r="T145">
+        <v>2.9</v>
+      </c>
+      <c r="U145">
+        <v>2.75</v>
+      </c>
+      <c r="V145">
+        <v>1.4</v>
+      </c>
+      <c r="W145">
+        <v>1.1</v>
+      </c>
+      <c r="X145">
+        <v>1.03</v>
+      </c>
+      <c r="Y145">
+        <v>1.25</v>
+      </c>
+      <c r="Z145">
+        <v>3.15</v>
+      </c>
+      <c r="AA145">
+        <v>1.84</v>
+      </c>
+      <c r="AB145">
+        <v>1.9</v>
+      </c>
+      <c r="AC145">
+        <v>2.98</v>
+      </c>
+      <c r="AD145">
+        <v>1.29</v>
+      </c>
+      <c r="AE145">
+        <v>1.07</v>
+      </c>
+      <c r="AF145">
         <v>1.73</v>
       </c>
-      <c r="O145">
-        <v>4</v>
-      </c>
-      <c r="P145">
-        <v>4.5</v>
-      </c>
-      <c r="Q145">
-        <v>2.25</v>
-      </c>
-      <c r="R145">
-        <v>2.13</v>
-      </c>
-      <c r="S145">
-        <v>1.32</v>
-      </c>
-      <c r="T145">
-        <v>3.02</v>
-      </c>
-      <c r="U145">
-        <v>2.69</v>
-      </c>
-      <c r="V145">
+      <c r="AG145">
+        <v>2.08</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ145">
+        <v>1.3</v>
+      </c>
+      <c r="AK145">
         <v>1.44</v>
-      </c>
-      <c r="W145">
-        <v>1.07</v>
-      </c>
-      <c r="X145">
-        <v>1.01</v>
-      </c>
-      <c r="Y145">
-        <v>1.2</v>
-      </c>
-      <c r="Z145">
-        <v>3.35</v>
-      </c>
-      <c r="AA145">
-        <v>1.8</v>
-      </c>
-      <c r="AB145">
-        <v>1.95</v>
-      </c>
-      <c r="AC145">
-        <v>2.88</v>
-      </c>
-      <c r="AD145">
-        <v>1.32</v>
-      </c>
-      <c r="AE145">
-        <v>1.14</v>
-      </c>
-      <c r="AF145">
-        <v>1.7</v>
-      </c>
-      <c r="AG145">
-        <v>2</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>1.13</v>
-      </c>
-      <c r="AK145">
-        <v>2.05</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O146">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q146">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="R146">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S146">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T146">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U146">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="V146">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W146">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y146">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z146">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA146">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB146">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC146">
-        <v>2.49</v>
+        <v>3.42</v>
       </c>
       <c r="AD146">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF146">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AG146">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G147">
@@ -24273,77 +24273,77 @@
         <v>2.8</v>
       </c>
       <c r="O147">
+        <v>3.6</v>
+      </c>
+      <c r="P147">
+        <v>2.3</v>
+      </c>
+      <c r="Q147">
+        <v>3.5</v>
+      </c>
+      <c r="R147">
+        <v>2.4</v>
+      </c>
+      <c r="S147">
+        <v>1.29</v>
+      </c>
+      <c r="T147">
         <v>3.4</v>
       </c>
-      <c r="P147">
-        <v>2.45</v>
-      </c>
-      <c r="Q147">
-        <v>3.51</v>
-      </c>
-      <c r="R147">
-        <v>2.1</v>
-      </c>
-      <c r="S147">
-        <v>1.36</v>
-      </c>
-      <c r="T147">
-        <v>2.9</v>
-      </c>
       <c r="U147">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V147">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W147">
         <v>1.1</v>
       </c>
       <c r="X147">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z147">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="AA147">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB147">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC147">
-        <v>2.98</v>
+        <v>2.49</v>
       </c>
       <c r="AD147">
+        <v>1.42</v>
+      </c>
+      <c r="AE147">
+        <v>1.14</v>
+      </c>
+      <c r="AF147">
+        <v>1.57</v>
+      </c>
+      <c r="AG147">
+        <v>2.33</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
         <v>1.29</v>
       </c>
-      <c r="AE147">
-        <v>1.07</v>
-      </c>
-      <c r="AF147">
-        <v>1.73</v>
-      </c>
-      <c r="AG147">
-        <v>2.08</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>1.3</v>
-      </c>
       <c r="AK147">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
+        <v>2.62</v>
+      </c>
+      <c r="O157">
+        <v>3.6</v>
+      </c>
+      <c r="P157">
         <v>2.45</v>
       </c>
-      <c r="O157">
+      <c r="Q157">
+        <v>2.8</v>
+      </c>
+      <c r="R157">
+        <v>2.3</v>
+      </c>
+      <c r="S157">
+        <v>1.27</v>
+      </c>
+      <c r="T157">
         <v>3.5</v>
       </c>
-      <c r="P157">
-        <v>2.62</v>
-      </c>
-      <c r="Q157">
-        <v>3</v>
-      </c>
-      <c r="R157">
-        <v>2.16</v>
-      </c>
-      <c r="S157">
-        <v>1.33</v>
-      </c>
-      <c r="T157">
-        <v>3.14</v>
-      </c>
       <c r="U157">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V157">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W157">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z157">
-        <v>3.82</v>
+        <v>4.59</v>
       </c>
       <c r="AA157">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB157">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AC157">
-        <v>3.07</v>
+        <v>2.42</v>
       </c>
       <c r="AD157">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE157">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF157">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG157">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK157">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="O158">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="P158">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="Q158">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="R158">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S158">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T158">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U158">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="V158">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X158">
         <v>1.03</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z158">
-        <v>4.59</v>
+        <v>3.6</v>
       </c>
       <c r="AA158">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB158">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AC158">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD158">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE158">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG158">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK158">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="O161">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P161">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q161">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="R161">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S161">
         <v>1.33</v>
       </c>
       <c r="T161">
-        <v>2.96</v>
+        <v>3.14</v>
       </c>
       <c r="U161">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V161">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W161">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X161">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z161">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA161">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB161">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AC161">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AD161">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE161">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK161">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -34542,7 +34542,7 @@
         <v>3.4</v>
       </c>
       <c r="O210">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P210">
         <v>1.89</v>
@@ -34572,7 +34572,7 @@
         <v>1</v>
       </c>
       <c r="Y210">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z210">
         <v>3.75</v>
@@ -34612,7 +34612,7 @@
         <v>1.21</v>
       </c>
       <c r="AK210">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,65 +38614,65 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q235">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R235">
+        <v>2.08</v>
+      </c>
+      <c r="S235">
+        <v>1.37</v>
+      </c>
+      <c r="T235">
+        <v>2.95</v>
+      </c>
+      <c r="U235">
+        <v>2.69</v>
+      </c>
+      <c r="V235">
+        <v>1.39</v>
+      </c>
+      <c r="W235">
+        <v>1.06</v>
+      </c>
+      <c r="X235">
+        <v>1.04</v>
+      </c>
+      <c r="Y235">
+        <v>1.3</v>
+      </c>
+      <c r="Z235">
+        <v>3.25</v>
+      </c>
+      <c r="AA235">
+        <v>1.98</v>
+      </c>
+      <c r="AB235">
+        <v>1.76</v>
+      </c>
+      <c r="AC235">
+        <v>3.34</v>
+      </c>
+      <c r="AD235">
+        <v>1.24</v>
+      </c>
+      <c r="AE235">
+        <v>1.06</v>
+      </c>
+      <c r="AF235">
+        <v>1.75</v>
+      </c>
+      <c r="AG235">
         <v>2</v>
       </c>
-      <c r="S235">
-        <v>1.4</v>
-      </c>
-      <c r="T235">
-        <v>2.75</v>
-      </c>
-      <c r="U235">
-        <v>2.87</v>
-      </c>
-      <c r="V235">
-        <v>1.35</v>
-      </c>
-      <c r="W235">
-        <v>1.04</v>
-      </c>
-      <c r="X235">
-        <v>1.01</v>
-      </c>
-      <c r="Y235">
-        <v>1.36</v>
-      </c>
-      <c r="Z235">
-        <v>2.9</v>
-      </c>
-      <c r="AA235">
-        <v>2.19</v>
-      </c>
-      <c r="AB235">
-        <v>1.66</v>
-      </c>
-      <c r="AC235">
-        <v>4.1</v>
-      </c>
-      <c r="AD235">
-        <v>1.19</v>
-      </c>
-      <c r="AE235">
-        <v>1.04</v>
-      </c>
-      <c r="AF235">
-        <v>1.91</v>
-      </c>
-      <c r="AG235">
-        <v>1.85</v>
-      </c>
       <c r="AH235" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK235">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O236">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P236">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q236">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R236">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S236">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T236">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U236">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="V236">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W236">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X236">
+        <v>1.01</v>
+      </c>
+      <c r="Y236">
+        <v>1.36</v>
+      </c>
+      <c r="Z236">
+        <v>2.9</v>
+      </c>
+      <c r="AA236">
+        <v>2.19</v>
+      </c>
+      <c r="AB236">
+        <v>1.66</v>
+      </c>
+      <c r="AC236">
+        <v>4.1</v>
+      </c>
+      <c r="AD236">
+        <v>1.19</v>
+      </c>
+      <c r="AE236">
         <v>1.04</v>
       </c>
-      <c r="Y236">
-        <v>1.3</v>
-      </c>
-      <c r="Z236">
-        <v>3.25</v>
-      </c>
-      <c r="AA236">
-        <v>1.98</v>
-      </c>
-      <c r="AB236">
-        <v>1.76</v>
-      </c>
-      <c r="AC236">
-        <v>3.34</v>
-      </c>
-      <c r="AD236">
-        <v>1.24</v>
-      </c>
-      <c r="AE236">
-        <v>1.06</v>
-      </c>
       <c r="AF236">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG236">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,31 +40570,31 @@
         </is>
       </c>
       <c r="N247">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O247">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P247">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q247">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="R247">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S247">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T247">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="U247">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="V247">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W247">
         <v>1.05</v>
@@ -40603,31 +40603,31 @@
         <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z247">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA247">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB247">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC247">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AD247">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE247">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF247">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG247">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK247">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,31 +40733,31 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q248">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="R248">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T248">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="U248">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="V248">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W248">
         <v>1.05</v>
@@ -40766,31 +40766,31 @@
         <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z248">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA248">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB248">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC248">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD248">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE248">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF248">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG248">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK248">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -47769,7 +47769,7 @@
         <v>1.55</v>
       </c>
       <c r="W291">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X291">
         <v>1</v>
@@ -48397,10 +48397,10 @@
         <v>1.45</v>
       </c>
       <c r="O295">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="P295">
-        <v>7</v>
+        <v>7.48</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -49864,19 +49864,19 @@
         <v>2.2</v>
       </c>
       <c r="O304">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="P304">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="Q304">
         <v>2.62</v>
       </c>
       <c r="R304">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S304">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T304">
         <v>2.92</v>
@@ -49894,28 +49894,28 @@
         <v>1</v>
       </c>
       <c r="Y304">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z304">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA304">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB304">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC304">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD304">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE304">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF304">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG304">
         <v>2.1</v>
@@ -49934,7 +49934,7 @@
         <v>1.33</v>
       </c>
       <c r="AK304">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50513,25 +50513,25 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O308">
         <v>3.35</v>
       </c>
       <c r="P308">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q308">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="R308">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S308">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T308">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U308">
         <v>2.75</v>
@@ -50567,10 +50567,10 @@
         <v>1.07</v>
       </c>
       <c r="AF308">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG308">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AK308">
         <v>1.4</v>
@@ -51165,10 +51165,10 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O312">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="P312">
         <v>5.3</v>
@@ -51177,7 +51177,7 @@
         <v>1.85</v>
       </c>
       <c r="R312">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="S312">
         <v>1.2</v>
@@ -51189,7 +51189,7 @@
         <v>2.2</v>
       </c>
       <c r="V312">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W312">
         <v>1.17</v>
@@ -51198,7 +51198,7 @@
         <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z312">
         <v>5.4</v>
@@ -51238,7 +51238,7 @@
         <v>1.12</v>
       </c>
       <c r="AK312">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51331,7 +51331,7 @@
         <v>1.46</v>
       </c>
       <c r="O313">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P313">
         <v>5.6</v>
@@ -51349,7 +51349,7 @@
         <v>3.68</v>
       </c>
       <c r="U313">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V313">
         <v>1.62</v>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK313">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51491,16 +51491,16 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O314">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P314">
         <v>2.75</v>
       </c>
       <c r="Q314">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R314">
         <v>2.18</v>
@@ -51512,7 +51512,7 @@
         <v>3.19</v>
       </c>
       <c r="U314">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="V314">
         <v>1.44</v>
@@ -51521,7 +51521,7 @@
         <v>1.08</v>
       </c>
       <c r="X314">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y314">
         <v>1.2</v>
@@ -51545,7 +51545,7 @@
         <v>1.08</v>
       </c>
       <c r="AF314">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG314">
         <v>2.15</v>
@@ -51564,7 +51564,7 @@
         <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51708,7 +51708,7 @@
         <v>1</v>
       </c>
       <c r="AF315">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG315">
         <v>1.65</v>
@@ -51826,7 +51826,7 @@
         <v>4.45</v>
       </c>
       <c r="Q316">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R316">
         <v>2.34</v>
@@ -51998,7 +51998,7 @@
         <v>1.37</v>
       </c>
       <c r="T317">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="U317">
         <v>2.53</v>
@@ -52013,7 +52013,7 @@
         <v>1</v>
       </c>
       <c r="Y317">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z317">
         <v>3.5</v>
@@ -52034,10 +52034,10 @@
         <v>1.08</v>
       </c>
       <c r="AF317">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG317">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52053,7 +52053,7 @@
         <v>1.25</v>
       </c>
       <c r="AK317">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52167,7 +52167,7 @@
         <v>2.3</v>
       </c>
       <c r="V318">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W318">
         <v>1.09</v>
@@ -52191,7 +52191,7 @@
         <v>2.56</v>
       </c>
       <c r="AD318">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE318">
         <v>1.14</v>
@@ -52306,31 +52306,31 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="O319">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P319">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Q319">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R319">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="S319">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T319">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U319">
         <v>2.2</v>
       </c>
       <c r="V319">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W319">
         <v>1.16</v>
@@ -52342,13 +52342,13 @@
         <v>1.1</v>
       </c>
       <c r="Z319">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA319">
         <v>1.5</v>
       </c>
       <c r="AB319">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC319">
         <v>2.26</v>
@@ -52360,7 +52360,7 @@
         <v>1.21</v>
       </c>
       <c r="AF319">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG319">
         <v>2.05</v>
@@ -53121,19 +53121,19 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O324">
         <v>3.4</v>
       </c>
       <c r="P324">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q324">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R324">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S324">
         <v>1.42</v>
@@ -53160,13 +53160,13 @@
         <v>3.08</v>
       </c>
       <c r="AA324">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB324">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC324">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD324">
         <v>1.22</v>
@@ -53175,10 +53175,10 @@
         <v>1.04</v>
       </c>
       <c r="AF324">
+        <v>1.85</v>
+      </c>
+      <c r="AG324">
         <v>1.83</v>
-      </c>
-      <c r="AG324">
-        <v>1.85</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>1.3</v>
       </c>
       <c r="AK324">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -54751,7 +54751,7 @@
         </is>
       </c>
       <c r="N334">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O334">
         <v>3.8</v>
@@ -54760,7 +54760,7 @@
         <v>3.75</v>
       </c>
       <c r="Q334">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R334">
         <v>2.4</v>
@@ -54769,7 +54769,7 @@
         <v>1.25</v>
       </c>
       <c r="T334">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U334">
         <v>2.48</v>
@@ -54778,7 +54778,7 @@
         <v>1.51</v>
       </c>
       <c r="W334">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X334">
         <v>1.02</v>
@@ -54787,19 +54787,19 @@
         <v>1.17</v>
       </c>
       <c r="Z334">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA334">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB334">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC334">
         <v>2.49</v>
       </c>
       <c r="AD334">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE334">
         <v>1.14</v>
@@ -54821,7 +54821,7 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK334">
         <v>1.91</v>
@@ -55412,7 +55412,7 @@
         <v>2.81</v>
       </c>
       <c r="Q338">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="R338">
         <v>2.08</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O339">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P339">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q339">
         <v>2.56</v>
@@ -55599,10 +55599,10 @@
         <v>1.03</v>
       </c>
       <c r="Y339">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z339">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA339">
         <v>1.72</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="R4">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA4">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="R5">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
+        <v>1.14</v>
+      </c>
+      <c r="Z5">
+        <v>4.4</v>
+      </c>
+      <c r="AA5">
+        <v>1.6</v>
+      </c>
+      <c r="AB5">
+        <v>2.19</v>
+      </c>
+      <c r="AC5">
+        <v>2.51</v>
+      </c>
+      <c r="AD5">
+        <v>1.46</v>
+      </c>
+      <c r="AE5">
+        <v>1.15</v>
+      </c>
+      <c r="AF5">
+        <v>1.5</v>
+      </c>
+      <c r="AG5">
+        <v>2.25</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.22</v>
       </c>
-      <c r="Z5">
-        <v>4.1</v>
-      </c>
-      <c r="AA5">
-        <v>1.8</v>
-      </c>
-      <c r="AB5">
-        <v>1.95</v>
-      </c>
-      <c r="AC5">
-        <v>2.9</v>
-      </c>
-      <c r="AD5">
-        <v>1.4</v>
-      </c>
-      <c r="AE5">
-        <v>1.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.67</v>
-      </c>
-      <c r="AG5">
-        <v>2.1</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.23</v>
-      </c>
       <c r="AK5">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1308,7 +1308,7 @@
         <v>2.54</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
         <v>1.36</v>
@@ -1320,16 +1320,16 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
         <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
         <v>3.42</v>
@@ -1341,10 +1341,10 @@
         <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1456,22 +1456,22 @@
         <v>4</v>
       </c>
       <c r="P7">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="U7">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="V7">
         <v>1.39</v>
@@ -1480,34 +1480,34 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB7">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC7">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK7">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="Q8">
-        <v>3.16</v>
+        <v>4.8</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="U8">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA8">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB8">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="Q9">
-        <v>4.8</v>
+        <v>3.16</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA9">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB9">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK9">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R17">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="S17">
         <v>1.42</v>
@@ -3101,43 +3101,43 @@
         <v>2.51</v>
       </c>
       <c r="U17">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
+        <v>1.02</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
+        <v>1.37</v>
+      </c>
+      <c r="Z17">
+        <v>2.97</v>
+      </c>
+      <c r="AA17">
+        <v>2.1</v>
+      </c>
+      <c r="AB17">
+        <v>1.66</v>
+      </c>
+      <c r="AC17">
+        <v>3.76</v>
+      </c>
+      <c r="AD17">
+        <v>1.19</v>
+      </c>
+      <c r="AE17">
         <v>1.03</v>
       </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
-      <c r="Y17">
-        <v>1.36</v>
-      </c>
-      <c r="Z17">
-        <v>2.69</v>
-      </c>
-      <c r="AA17">
-        <v>2.2</v>
-      </c>
-      <c r="AB17">
-        <v>1.57</v>
-      </c>
-      <c r="AC17">
-        <v>4.33</v>
-      </c>
-      <c r="AD17">
-        <v>1.2</v>
-      </c>
-      <c r="AE17">
-        <v>1.01</v>
-      </c>
       <c r="AF17">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
+        <v>1.35</v>
+      </c>
+      <c r="AK17">
         <v>1.62</v>
-      </c>
-      <c r="AK17">
-        <v>1.27</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
         <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R18">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
         <v>1.42</v>
@@ -3264,43 +3264,43 @@
         <v>2.51</v>
       </c>
       <c r="U18">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="AA18">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB18">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>3.76</v>
+        <v>4.33</v>
       </c>
       <c r="AD18">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q40">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R40">
         <v>2.33</v>
@@ -6853,7 +6853,7 @@
         <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
         <v>1.1</v>
@@ -6874,10 +6874,10 @@
         <v>2</v>
       </c>
       <c r="AC40">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD40">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.1</v>
@@ -6886,7 +6886,7 @@
         <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q41">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="R41">
         <v>2.3</v>
@@ -7022,13 +7022,13 @@
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA41">
         <v>1.65</v>
@@ -7046,10 +7046,10 @@
         <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>1.75</v>
+      </c>
+      <c r="O48">
         <v>4</v>
       </c>
-      <c r="O48">
-        <v>3.9</v>
-      </c>
       <c r="P48">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q48">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="R48">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
+        <v>1.58</v>
+      </c>
+      <c r="AB48">
+        <v>2.17</v>
+      </c>
+      <c r="AC48">
+        <v>2.4</v>
+      </c>
+      <c r="AD48">
+        <v>1.44</v>
+      </c>
+      <c r="AE48">
+        <v>1.15</v>
+      </c>
+      <c r="AF48">
         <v>1.57</v>
       </c>
-      <c r="AB48">
-        <v>2.31</v>
-      </c>
-      <c r="AC48">
-        <v>2.31</v>
-      </c>
-      <c r="AD48">
-        <v>1.5</v>
-      </c>
-      <c r="AE48">
-        <v>1.18</v>
-      </c>
-      <c r="AF48">
-        <v>1.53</v>
-      </c>
       <c r="AG48">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
+        <v>1.8</v>
+      </c>
+      <c r="Q49">
         <v>4.2</v>
       </c>
-      <c r="Q49">
-        <v>2.25</v>
-      </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
         <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="V49">
         <v>1.57</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA49">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AC49">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>2.14</v>
+        <v>1.22</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q52">
         <v>2.05</v>
@@ -8806,7 +8806,7 @@
         <v>3.11</v>
       </c>
       <c r="U52">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="V52">
         <v>1.53</v>
@@ -8815,34 +8815,34 @@
         <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.16</v>
       </c>
       <c r="Z52">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA52">
         <v>1.63</v>
       </c>
       <c r="AB52">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC52">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AD52">
         <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG52">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q53">
         <v>2.83</v>
@@ -8963,19 +8963,19 @@
         <v>2.15</v>
       </c>
       <c r="S53">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="U53">
         <v>2.8</v>
       </c>
       <c r="V53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W53">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8987,25 +8987,25 @@
         <v>3.26</v>
       </c>
       <c r="AA53">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AB53">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC53">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD53">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG53">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9138,10 +9138,10 @@
         <v>1.36</v>
       </c>
       <c r="W54">
+        <v>1.07</v>
+      </c>
+      <c r="X54">
         <v>1.04</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.28</v>
@@ -9153,22 +9153,22 @@
         <v>2.01</v>
       </c>
       <c r="AB54">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC54">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD54">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE54">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF54">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG54">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
         <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R65">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AD65">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF65">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG65">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="R66">
+        <v>2.21</v>
+      </c>
+      <c r="S66">
+        <v>1.23</v>
+      </c>
+      <c r="T66">
+        <v>3.46</v>
+      </c>
+      <c r="U66">
+        <v>2.22</v>
+      </c>
+      <c r="V66">
+        <v>1.53</v>
+      </c>
+      <c r="W66">
+        <v>1.11</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.13</v>
+      </c>
+      <c r="Z66">
+        <v>4.6</v>
+      </c>
+      <c r="AA66">
+        <v>1.56</v>
+      </c>
+      <c r="AB66">
+        <v>2.22</v>
+      </c>
+      <c r="AC66">
+        <v>2.46</v>
+      </c>
+      <c r="AD66">
+        <v>1.52</v>
+      </c>
+      <c r="AE66">
+        <v>1.15</v>
+      </c>
+      <c r="AF66">
+        <v>1.48</v>
+      </c>
+      <c r="AG66">
         <v>2.4</v>
       </c>
-      <c r="S66">
-        <v>1.22</v>
-      </c>
-      <c r="T66">
-        <v>3.52</v>
-      </c>
-      <c r="U66">
-        <v>2.25</v>
-      </c>
-      <c r="V66">
-        <v>1.62</v>
-      </c>
-      <c r="W66">
-        <v>1.15</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.12</v>
-      </c>
-      <c r="Z66">
-        <v>4.7</v>
-      </c>
-      <c r="AA66">
-        <v>1.48</v>
-      </c>
-      <c r="AB66">
-        <v>2.33</v>
-      </c>
-      <c r="AC66">
-        <v>2.22</v>
-      </c>
-      <c r="AD66">
-        <v>1.45</v>
-      </c>
-      <c r="AE66">
-        <v>1.24</v>
-      </c>
-      <c r="AF66">
-        <v>1.46</v>
-      </c>
-      <c r="AG66">
-        <v>2.5</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q67">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R67">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="S67">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T67">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U67">
         <v>2.1</v>
       </c>
       <c r="V67">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z67">
-        <v>5.21</v>
+        <v>5.7</v>
       </c>
       <c r="AA67">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB67">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AC67">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD67">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE67">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF67">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG67">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="R68">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="S68">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="U68">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>4.6</v>
+        <v>5.21</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AB68">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="AC68">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="AD68">
+        <v>1.64</v>
+      </c>
+      <c r="AE68">
+        <v>1.28</v>
+      </c>
+      <c r="AF68">
+        <v>1.39</v>
+      </c>
+      <c r="AG68">
+        <v>2.67</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.38</v>
+      </c>
+      <c r="AK68">
         <v>1.52</v>
-      </c>
-      <c r="AE68">
-        <v>1.15</v>
-      </c>
-      <c r="AF68">
-        <v>1.48</v>
-      </c>
-      <c r="AG68">
-        <v>2.4</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.29</v>
-      </c>
-      <c r="AK68">
-        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11888,7 +11888,7 @@
         <v>4</v>
       </c>
       <c r="P71">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O114">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P114">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="Q114">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R114">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S114">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T114">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U114">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V114">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W114">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X114">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z114">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA114">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB114">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AC114">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="AD114">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE114">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF114">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG114">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK114">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O115">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P115">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q115">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R115">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S115">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U115">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V115">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W115">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z115">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA115">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB115">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AC115">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="AD115">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AE115">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF115">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK115">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,65 +19380,65 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O117">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P117">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q117">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R117">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S117">
         <v>1.4</v>
       </c>
       <c r="T117">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U117">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V117">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W117">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z117">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AA117">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB117">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC117">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD117">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
+        <v>1.77</v>
+      </c>
+      <c r="AG117">
         <v>1.93</v>
       </c>
-      <c r="AG117">
-        <v>1.87</v>
-      </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK117">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O118">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="R118">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S118">
         <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="U118">
+        <v>3.4</v>
+      </c>
+      <c r="V118">
+        <v>1.28</v>
+      </c>
+      <c r="W118">
+        <v>1</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.4</v>
+      </c>
+      <c r="Z118">
         <v>2.75</v>
       </c>
-      <c r="V118">
-        <v>1.34</v>
-      </c>
-      <c r="W118">
-        <v>1.03</v>
-      </c>
-      <c r="X118">
-        <v>1.04</v>
-      </c>
-      <c r="Y118">
-        <v>1.33</v>
-      </c>
-      <c r="Z118">
-        <v>3.32</v>
-      </c>
       <c r="AA118">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB118">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC118">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD118">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF118">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AG118">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="O121">
         <v>3.6</v>
       </c>
       <c r="P121">
-        <v>2.03</v>
+        <v>3.25</v>
       </c>
       <c r="Q121">
-        <v>3.76</v>
+        <v>2.69</v>
       </c>
       <c r="R121">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T121">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="U121">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V121">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W121">
         <v>1.11</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y121">
         <v>1.2</v>
       </c>
       <c r="Z121">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="AA121">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AB121">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AC121">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AD121">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE121">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF121">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG121">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="O122">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="Q122">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
         <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
         <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AA122">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB122">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG122">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P123">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q123">
-        <v>2.69</v>
+        <v>4.4</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T123">
-        <v>2.39</v>
+        <v>3.09</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V123">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z123">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AA123">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AB123">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC123">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="AD123">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF123">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG123">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK123">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
+        <v>1.4</v>
+      </c>
+      <c r="O132">
+        <v>4.7</v>
+      </c>
+      <c r="P132">
+        <v>6</v>
+      </c>
+      <c r="Q132">
         <v>1.87</v>
       </c>
-      <c r="O132">
-        <v>3.5</v>
-      </c>
-      <c r="P132">
-        <v>3.7</v>
-      </c>
-      <c r="Q132">
+      <c r="R132">
         <v>2.5</v>
       </c>
-      <c r="R132">
-        <v>2.1</v>
-      </c>
       <c r="S132">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T132">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U132">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="V132">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X132">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z132">
-        <v>3.08</v>
+        <v>5.62</v>
       </c>
       <c r="AA132">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="AB132">
-        <v>1.75</v>
+        <v>2.43</v>
       </c>
       <c r="AC132">
-        <v>3.41</v>
+        <v>2.22</v>
       </c>
       <c r="AD132">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE132">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AF132">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG132">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK132">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O133">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R133">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="U133">
-        <v>3.07</v>
+        <v>2.68</v>
       </c>
       <c r="V133">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB133">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC133">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE133">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG133">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
+        <v>1.87</v>
+      </c>
+      <c r="O134">
+        <v>3.5</v>
+      </c>
+      <c r="P134">
+        <v>3.7</v>
+      </c>
+      <c r="Q134">
+        <v>2.5</v>
+      </c>
+      <c r="R134">
+        <v>2.1</v>
+      </c>
+      <c r="S134">
+        <v>1.36</v>
+      </c>
+      <c r="T134">
+        <v>2.88</v>
+      </c>
+      <c r="U134">
+        <v>3</v>
+      </c>
+      <c r="V134">
         <v>1.4</v>
       </c>
-      <c r="O134">
-        <v>4.7</v>
-      </c>
-      <c r="P134">
-        <v>6</v>
-      </c>
-      <c r="Q134">
-        <v>1.87</v>
-      </c>
-      <c r="R134">
-        <v>2.5</v>
-      </c>
-      <c r="S134">
-        <v>1.19</v>
-      </c>
-      <c r="T134">
-        <v>3.8</v>
-      </c>
-      <c r="U134">
-        <v>2.15</v>
-      </c>
-      <c r="V134">
-        <v>1.68</v>
-      </c>
       <c r="W134">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>5.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA134">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AB134">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>2.22</v>
+        <v>3.41</v>
       </c>
       <c r="AD134">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE134">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG134">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AK134">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P135">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q135">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R135">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S135">
+        <v>1.36</v>
+      </c>
+      <c r="T135">
+        <v>2.83</v>
+      </c>
+      <c r="U135">
+        <v>3.07</v>
+      </c>
+      <c r="V135">
         <v>1.37</v>
       </c>
-      <c r="T135">
-        <v>2.78</v>
-      </c>
-      <c r="U135">
-        <v>2.68</v>
-      </c>
-      <c r="V135">
-        <v>1.4</v>
-      </c>
       <c r="W135">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z135">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA135">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB135">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC135">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="AD135">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE135">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG135">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O151">
+        <v>3.45</v>
+      </c>
+      <c r="P151">
+        <v>3.25</v>
+      </c>
+      <c r="Q151">
+        <v>2.59</v>
+      </c>
+      <c r="R151">
+        <v>2.15</v>
+      </c>
+      <c r="S151">
+        <v>1.33</v>
+      </c>
+      <c r="T151">
+        <v>3.1</v>
+      </c>
+      <c r="U151">
+        <v>2.62</v>
+      </c>
+      <c r="V151">
+        <v>1.44</v>
+      </c>
+      <c r="W151">
+        <v>1.06</v>
+      </c>
+      <c r="X151">
+        <v>1.01</v>
+      </c>
+      <c r="Y151">
+        <v>1.25</v>
+      </c>
+      <c r="Z151">
         <v>3.6</v>
       </c>
-      <c r="P151">
-        <v>2.29</v>
-      </c>
-      <c r="Q151">
-        <v>3.62</v>
-      </c>
-      <c r="R151">
-        <v>2.2</v>
-      </c>
-      <c r="S151">
-        <v>1.3</v>
-      </c>
-      <c r="T151">
-        <v>2.95</v>
-      </c>
-      <c r="U151">
-        <v>2.5</v>
-      </c>
-      <c r="V151">
-        <v>1.5</v>
-      </c>
-      <c r="W151">
-        <v>1.07</v>
-      </c>
-      <c r="X151">
-        <v>1.03</v>
-      </c>
-      <c r="Y151">
-        <v>1.2</v>
-      </c>
-      <c r="Z151">
-        <v>4.1</v>
-      </c>
       <c r="AA151">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB151">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AC151">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AD151">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE151">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF151">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG151">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O152">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P152">
-        <v>3.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q152">
-        <v>2.59</v>
+        <v>3.62</v>
       </c>
       <c r="R152">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T152">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U152">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V152">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W152">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z152">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA152">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AB152">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC152">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD152">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF152">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK152">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,34 +25900,34 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O157">
+        <v>3.45</v>
+      </c>
+      <c r="P157">
+        <v>2.12</v>
+      </c>
+      <c r="Q157">
+        <v>3.44</v>
+      </c>
+      <c r="R157">
+        <v>2.31</v>
+      </c>
+      <c r="S157">
+        <v>1.29</v>
+      </c>
+      <c r="T157">
         <v>3.6</v>
       </c>
-      <c r="P157">
+      <c r="U157">
         <v>2.45</v>
-      </c>
-      <c r="Q157">
-        <v>2.8</v>
-      </c>
-      <c r="R157">
-        <v>2.3</v>
-      </c>
-      <c r="S157">
-        <v>1.27</v>
-      </c>
-      <c r="T157">
-        <v>3.5</v>
-      </c>
-      <c r="U157">
-        <v>2.3</v>
       </c>
       <c r="V157">
         <v>1.52</v>
       </c>
       <c r="W157">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X157">
         <v>1.03</v>
@@ -25936,28 +25936,28 @@
         <v>1.15</v>
       </c>
       <c r="Z157">
-        <v>4.59</v>
+        <v>3.8</v>
       </c>
       <c r="AA157">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB157">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC157">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD157">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE157">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF157">
         <v>1.53</v>
       </c>
       <c r="AG157">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK157">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="O158">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="P158">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Q158">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="R158">
         <v>2.12</v>
       </c>
       <c r="S158">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="U158">
+        <v>2.74</v>
+      </c>
+      <c r="V158">
+        <v>1.43</v>
+      </c>
+      <c r="W158">
+        <v>1.1</v>
+      </c>
+      <c r="X158">
+        <v>1.04</v>
+      </c>
+      <c r="Y158">
+        <v>1.22</v>
+      </c>
+      <c r="Z158">
+        <v>3.5</v>
+      </c>
+      <c r="AA158">
+        <v>1.82</v>
+      </c>
+      <c r="AB158">
+        <v>2</v>
+      </c>
+      <c r="AC158">
         <v>2.88</v>
       </c>
-      <c r="V158">
-        <v>1.42</v>
-      </c>
-      <c r="W158">
+      <c r="AD158">
+        <v>1.32</v>
+      </c>
+      <c r="AE158">
         <v>1.08</v>
       </c>
-      <c r="X158">
-        <v>1.03</v>
-      </c>
-      <c r="Y158">
-        <v>1.28</v>
-      </c>
-      <c r="Z158">
-        <v>3.6</v>
-      </c>
-      <c r="AA158">
-        <v>1.9</v>
-      </c>
-      <c r="AB158">
-        <v>1.92</v>
-      </c>
-      <c r="AC158">
-        <v>3.05</v>
-      </c>
-      <c r="AD158">
-        <v>1.33</v>
-      </c>
-      <c r="AE158">
-        <v>1.12</v>
-      </c>
       <c r="AF158">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG158">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="O159">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="P159">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="Q159">
-        <v>3.44</v>
+        <v>4.46</v>
       </c>
       <c r="R159">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="S159">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
+        <v>3.3</v>
+      </c>
+      <c r="U159">
+        <v>2.54</v>
+      </c>
+      <c r="V159">
+        <v>1.45</v>
+      </c>
+      <c r="W159">
+        <v>1.07</v>
+      </c>
+      <c r="X159">
+        <v>1.02</v>
+      </c>
+      <c r="Y159">
+        <v>1.23</v>
+      </c>
+      <c r="Z159">
         <v>3.6</v>
       </c>
-      <c r="U159">
-        <v>2.45</v>
-      </c>
-      <c r="V159">
-        <v>1.52</v>
-      </c>
-      <c r="W159">
-        <v>1.12</v>
-      </c>
-      <c r="X159">
-        <v>1.03</v>
-      </c>
-      <c r="Y159">
+      <c r="AA159">
+        <v>1.67</v>
+      </c>
+      <c r="AB159">
+        <v>2.15</v>
+      </c>
+      <c r="AC159">
+        <v>2.62</v>
+      </c>
+      <c r="AD159">
+        <v>1.38</v>
+      </c>
+      <c r="AE159">
+        <v>1.13</v>
+      </c>
+      <c r="AF159">
+        <v>1.72</v>
+      </c>
+      <c r="AG159">
+        <v>2.1</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.15</v>
       </c>
-      <c r="Z159">
-        <v>3.8</v>
-      </c>
-      <c r="AA159">
-        <v>1.62</v>
-      </c>
-      <c r="AB159">
-        <v>2.24</v>
-      </c>
-      <c r="AC159">
-        <v>2.49</v>
-      </c>
-      <c r="AD159">
-        <v>1.42</v>
-      </c>
-      <c r="AE159">
-        <v>1.18</v>
-      </c>
-      <c r="AF159">
-        <v>1.53</v>
-      </c>
-      <c r="AG159">
-        <v>2.35</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.25</v>
-      </c>
       <c r="AK159">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P160">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Q160">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R160">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S160">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T160">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="U160">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="V160">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W160">
         <v>1.1</v>
       </c>
       <c r="X160">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z160">
-        <v>3.5</v>
+        <v>4.59</v>
       </c>
       <c r="AA160">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB160">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AC160">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AD160">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE160">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF160">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AG160">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK160">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="O161">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P161">
-        <v>2.62</v>
+        <v>3.45</v>
       </c>
       <c r="Q161">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="R161">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S161">
         <v>1.33</v>
       </c>
       <c r="T161">
-        <v>3.14</v>
+        <v>2.96</v>
       </c>
       <c r="U161">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W161">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X161">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z161">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA161">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB161">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AC161">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AD161">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE161">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF161">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O162">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>1.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q162">
-        <v>4.46</v>
+        <v>3</v>
       </c>
       <c r="R162">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S162">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T162">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U162">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="V162">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
         <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z162">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA162">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB162">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC162">
-        <v>2.62</v>
+        <v>3.07</v>
       </c>
       <c r="AD162">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE162">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF162">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG162">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK162">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O235">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P235">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q235">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R235">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S235">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T235">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U235">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="V235">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W235">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X235">
+        <v>1.01</v>
+      </c>
+      <c r="Y235">
+        <v>1.36</v>
+      </c>
+      <c r="Z235">
+        <v>2.9</v>
+      </c>
+      <c r="AA235">
+        <v>2.19</v>
+      </c>
+      <c r="AB235">
+        <v>1.66</v>
+      </c>
+      <c r="AC235">
+        <v>4.1</v>
+      </c>
+      <c r="AD235">
+        <v>1.19</v>
+      </c>
+      <c r="AE235">
         <v>1.04</v>
       </c>
-      <c r="Y235">
-        <v>1.3</v>
-      </c>
-      <c r="Z235">
-        <v>3.25</v>
-      </c>
-      <c r="AA235">
-        <v>1.98</v>
-      </c>
-      <c r="AB235">
-        <v>1.76</v>
-      </c>
-      <c r="AC235">
-        <v>3.34</v>
-      </c>
-      <c r="AD235">
-        <v>1.24</v>
-      </c>
-      <c r="AE235">
-        <v>1.06</v>
-      </c>
       <c r="AF235">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG235">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK235">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,65 +38777,65 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q236">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R236">
+        <v>2.08</v>
+      </c>
+      <c r="S236">
+        <v>1.37</v>
+      </c>
+      <c r="T236">
+        <v>2.95</v>
+      </c>
+      <c r="U236">
+        <v>2.69</v>
+      </c>
+      <c r="V236">
+        <v>1.39</v>
+      </c>
+      <c r="W236">
+        <v>1.06</v>
+      </c>
+      <c r="X236">
+        <v>1.04</v>
+      </c>
+      <c r="Y236">
+        <v>1.3</v>
+      </c>
+      <c r="Z236">
+        <v>3.25</v>
+      </c>
+      <c r="AA236">
+        <v>1.98</v>
+      </c>
+      <c r="AB236">
+        <v>1.76</v>
+      </c>
+      <c r="AC236">
+        <v>3.34</v>
+      </c>
+      <c r="AD236">
+        <v>1.24</v>
+      </c>
+      <c r="AE236">
+        <v>1.06</v>
+      </c>
+      <c r="AF236">
+        <v>1.75</v>
+      </c>
+      <c r="AG236">
         <v>2</v>
       </c>
-      <c r="S236">
-        <v>1.4</v>
-      </c>
-      <c r="T236">
-        <v>2.75</v>
-      </c>
-      <c r="U236">
-        <v>2.87</v>
-      </c>
-      <c r="V236">
-        <v>1.35</v>
-      </c>
-      <c r="W236">
-        <v>1.04</v>
-      </c>
-      <c r="X236">
-        <v>1.01</v>
-      </c>
-      <c r="Y236">
-        <v>1.36</v>
-      </c>
-      <c r="Z236">
-        <v>2.9</v>
-      </c>
-      <c r="AA236">
-        <v>2.19</v>
-      </c>
-      <c r="AB236">
-        <v>1.66</v>
-      </c>
-      <c r="AC236">
-        <v>4.1</v>
-      </c>
-      <c r="AD236">
-        <v>1.19</v>
-      </c>
-      <c r="AE236">
-        <v>1.04</v>
-      </c>
-      <c r="AF236">
-        <v>1.91</v>
-      </c>
-      <c r="AG236">
-        <v>1.85</v>
-      </c>
       <c r="AH236" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK236">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,31 +40570,31 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q247">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="R247">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T247">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="U247">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="V247">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W247">
         <v>1.05</v>
@@ -40603,31 +40603,31 @@
         <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z247">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA247">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB247">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC247">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="AD247">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE247">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG247">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,31 +40733,31 @@
         </is>
       </c>
       <c r="N248">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q248">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S248">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T248">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="U248">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="V248">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W248">
         <v>1.05</v>
@@ -40766,31 +40766,31 @@
         <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z248">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA248">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB248">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC248">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="AD248">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE248">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF248">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG248">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK248">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AL248">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="Q21">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>2.22</v>
+        <v>2.51</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="U21">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R22">
-        <v>2.51</v>
+        <v>2.22</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z22">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC22">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD22">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4734,7 +4734,7 @@
         <v>2.18</v>
       </c>
       <c r="V27">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W27">
         <v>1.14</v>
@@ -4746,7 +4746,7 @@
         <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
         <v>1.49</v>
@@ -4755,13 +4755,13 @@
         <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AD27">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF27">
         <v>1.53</v>
@@ -5054,10 +5054,10 @@
         <v>1.43</v>
       </c>
       <c r="T29">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="V29">
         <v>1.3</v>
@@ -5069,10 +5069,10 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="O37">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P37">
-        <v>3.75</v>
+        <v>2.23</v>
       </c>
       <c r="Q37">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.64</v>
+        <v>6.25</v>
       </c>
       <c r="AA37">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AB37">
-        <v>2.46</v>
+        <v>3.13</v>
       </c>
       <c r="AC37">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AD37">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AE37">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF37">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG37">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.75</v>
+        <v>1.79</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P38">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q38">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="R38">
         <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="T38">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
+        <v>2.12</v>
+      </c>
+      <c r="V38">
+        <v>1.62</v>
+      </c>
+      <c r="W38">
+        <v>1.17</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.13</v>
+      </c>
+      <c r="Z38">
+        <v>5.64</v>
+      </c>
+      <c r="AA38">
+        <v>1.43</v>
+      </c>
+      <c r="AB38">
+        <v>2.46</v>
+      </c>
+      <c r="AC38">
+        <v>2.13</v>
+      </c>
+      <c r="AD38">
+        <v>1.63</v>
+      </c>
+      <c r="AE38">
+        <v>1.26</v>
+      </c>
+      <c r="AF38">
+        <v>1.44</v>
+      </c>
+      <c r="AG38">
+        <v>2.49</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.22</v>
+      </c>
+      <c r="AK38">
         <v>1.95</v>
-      </c>
-      <c r="V38">
-        <v>1.77</v>
-      </c>
-      <c r="W38">
-        <v>1.22</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.11</v>
-      </c>
-      <c r="Z38">
-        <v>6.25</v>
-      </c>
-      <c r="AA38">
-        <v>1.32</v>
-      </c>
-      <c r="AB38">
-        <v>3.13</v>
-      </c>
-      <c r="AC38">
-        <v>1.83</v>
-      </c>
-      <c r="AD38">
-        <v>1.9</v>
-      </c>
-      <c r="AE38">
-        <v>1.38</v>
-      </c>
-      <c r="AF38">
-        <v>1.3</v>
-      </c>
-      <c r="AG38">
-        <v>3.1</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.24</v>
-      </c>
-      <c r="AK38">
-        <v>1.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="O40">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P40">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q40">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P41">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q41">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R41">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
+        <v>2.12</v>
+      </c>
+      <c r="AC41">
+        <v>2.57</v>
+      </c>
+      <c r="AD41">
+        <v>1.41</v>
+      </c>
+      <c r="AE41">
+        <v>1.13</v>
+      </c>
+      <c r="AF41">
+        <v>1.64</v>
+      </c>
+      <c r="AG41">
+        <v>2.08</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.19</v>
+      </c>
+      <c r="AK41">
         <v>2</v>
-      </c>
-      <c r="AC41">
-        <v>2.81</v>
-      </c>
-      <c r="AD41">
-        <v>1.4</v>
-      </c>
-      <c r="AE41">
-        <v>1.1</v>
-      </c>
-      <c r="AF41">
-        <v>1.73</v>
-      </c>
-      <c r="AG41">
-        <v>1.94</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.25</v>
-      </c>
-      <c r="AK41">
-        <v>2.02</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7493,13 +7493,13 @@
         <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
         <v>2.62</v>
@@ -7508,31 +7508,31 @@
         <v>1.44</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AA44">
         <v>1.82</v>
       </c>
       <c r="AB44">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC44">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
         <v>1.62</v>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="O48">
         <v>3.9</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q48">
-        <v>2.28</v>
+        <v>4.2</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.6</v>
       </c>
       <c r="U48">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.37</v>
+        <v>4.98</v>
       </c>
       <c r="AA48">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AC48">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="Q49">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AA49">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="AB49">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.9</v>
+        <v>2.36</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q50">
-        <v>4.2</v>
+        <v>2.93</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U50">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z50">
-        <v>4.84</v>
+        <v>3.25</v>
       </c>
       <c r="AA50">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AB50">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>11</v>
       </c>
       <c r="R51">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="S51">
         <v>1.22</v>
@@ -8646,13 +8646,13 @@
         <v>2.19</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W51">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.14</v>
@@ -8661,13 +8661,13 @@
         <v>4.8</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC51">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AD51">
         <v>1.53</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="AK51">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,65 +8948,65 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
-        <v>4.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q53">
+        <v>3.6</v>
+      </c>
+      <c r="R53">
+        <v>2.15</v>
+      </c>
+      <c r="S53">
+        <v>1.36</v>
+      </c>
+      <c r="T53">
+        <v>2.77</v>
+      </c>
+      <c r="U53">
+        <v>2.8</v>
+      </c>
+      <c r="V53">
+        <v>1.36</v>
+      </c>
+      <c r="W53">
+        <v>1.04</v>
+      </c>
+      <c r="X53">
+        <v>1.04</v>
+      </c>
+      <c r="Y53">
+        <v>1.28</v>
+      </c>
+      <c r="Z53">
+        <v>3.08</v>
+      </c>
+      <c r="AA53">
+        <v>2.01</v>
+      </c>
+      <c r="AB53">
+        <v>1.75</v>
+      </c>
+      <c r="AC53">
+        <v>3.4</v>
+      </c>
+      <c r="AD53">
+        <v>1.25</v>
+      </c>
+      <c r="AE53">
+        <v>1.1</v>
+      </c>
+      <c r="AF53">
+        <v>1.73</v>
+      </c>
+      <c r="AG53">
         <v>2.05</v>
       </c>
-      <c r="R53">
-        <v>2.3</v>
-      </c>
-      <c r="S53">
-        <v>1.33</v>
-      </c>
-      <c r="T53">
-        <v>3.11</v>
-      </c>
-      <c r="U53">
-        <v>2.42</v>
-      </c>
-      <c r="V53">
-        <v>1.53</v>
-      </c>
-      <c r="W53">
-        <v>1.12</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.16</v>
-      </c>
-      <c r="Z53">
-        <v>4.2</v>
-      </c>
-      <c r="AA53">
-        <v>1.63</v>
-      </c>
-      <c r="AB53">
-        <v>2.2</v>
-      </c>
-      <c r="AC53">
-        <v>2.58</v>
-      </c>
-      <c r="AD53">
-        <v>1.41</v>
-      </c>
-      <c r="AE53">
-        <v>1.17</v>
-      </c>
-      <c r="AF53">
-        <v>1.62</v>
-      </c>
-      <c r="AG53">
-        <v>2.12</v>
-      </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="O54">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="Q54">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="R54">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
-        <v>2.77</v>
+        <v>3.11</v>
       </c>
       <c r="U54">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AB54">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="AD54">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF54">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>3.5</v>
       </c>
       <c r="AA62">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB62">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC62">
         <v>2.92</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="Q65">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="R65">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="S65">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="T65">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="V65">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="W65">
+        <v>1.11</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
         <v>1.13</v>
       </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
-      <c r="Y65">
-        <v>1.08</v>
-      </c>
       <c r="Z65">
-        <v>5.7</v>
+        <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB65">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AC65">
-        <v>2.02</v>
+        <v>2.48</v>
       </c>
       <c r="AD65">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG65">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="Q66">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="R66">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T66">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="U66">
         <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z66">
-        <v>5.15</v>
+        <v>5.7</v>
       </c>
       <c r="AA66">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB66">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AC66">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD66">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE66">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
         <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="R68">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="S68">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="U68">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>4.55</v>
+        <v>5.15</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB68">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="AC68">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="AD68">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK68">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12540,7 +12540,7 @@
         <v>3.55</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q75">
         <v>2.61</v>
@@ -12558,7 +12558,7 @@
         <v>2.42</v>
       </c>
       <c r="V75">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
         <v>1.09</v>
@@ -12582,10 +12582,10 @@
         <v>2.9</v>
       </c>
       <c r="AD75">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE75">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
         <v>1.62</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O78">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P78">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q78">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="R78">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>2.84</v>
+        <v>2.39</v>
       </c>
       <c r="U78">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W78">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z78">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AA78">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="AB78">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AC78">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="AD78">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE78">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P79">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Q79">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="R79">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="S79">
+        <v>1.41</v>
+      </c>
+      <c r="T79">
+        <v>2.84</v>
+      </c>
+      <c r="U79">
+        <v>3.07</v>
+      </c>
+      <c r="V79">
+        <v>1.36</v>
+      </c>
+      <c r="W79">
+        <v>1.04</v>
+      </c>
+      <c r="X79">
+        <v>1.03</v>
+      </c>
+      <c r="Y79">
         <v>1.3</v>
       </c>
-      <c r="T79">
-        <v>3.2</v>
-      </c>
-      <c r="U79">
-        <v>2.64</v>
-      </c>
-      <c r="V79">
-        <v>1.42</v>
-      </c>
-      <c r="W79">
-        <v>1.07</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
-        <v>1.21</v>
-      </c>
       <c r="Z79">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="AA79">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AB79">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AC79">
-        <v>2.7</v>
+        <v>3.56</v>
       </c>
       <c r="AD79">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O80">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q80">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R80">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S80">
+        <v>1.3</v>
+      </c>
+      <c r="T80">
+        <v>3.2</v>
+      </c>
+      <c r="U80">
+        <v>2.64</v>
+      </c>
+      <c r="V80">
+        <v>1.42</v>
+      </c>
+      <c r="W80">
+        <v>1.07</v>
+      </c>
+      <c r="X80">
+        <v>1</v>
+      </c>
+      <c r="Y80">
+        <v>1.21</v>
+      </c>
+      <c r="Z80">
+        <v>3.58</v>
+      </c>
+      <c r="AA80">
+        <v>1.72</v>
+      </c>
+      <c r="AB80">
+        <v>2.05</v>
+      </c>
+      <c r="AC80">
+        <v>2.7</v>
+      </c>
+      <c r="AD80">
         <v>1.4</v>
       </c>
-      <c r="T80">
-        <v>2.39</v>
-      </c>
-      <c r="U80">
-        <v>3.18</v>
-      </c>
-      <c r="V80">
-        <v>1.27</v>
-      </c>
-      <c r="W80">
-        <v>1.06</v>
-      </c>
-      <c r="X80">
-        <v>1.03</v>
-      </c>
-      <c r="Y80">
-        <v>1.35</v>
-      </c>
-      <c r="Z80">
-        <v>2.74</v>
-      </c>
-      <c r="AA80">
-        <v>2.28</v>
-      </c>
-      <c r="AB80">
-        <v>1.59</v>
-      </c>
-      <c r="AC80">
-        <v>4.2</v>
-      </c>
-      <c r="AD80">
-        <v>1.17</v>
-      </c>
       <c r="AE80">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF80">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK80">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.25</v>
       </c>
       <c r="Q85">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="R85">
         <v>2.1</v>
@@ -14206,10 +14206,10 @@
         <v>1.79</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC85">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AD85">
         <v>1.3</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK85">
         <v>1.36</v>
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O86">
         <v>4.1</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q86">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="R86">
         <v>2.3</v>
@@ -14366,10 +14366,10 @@
         <v>4.1</v>
       </c>
       <c r="AA86">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB86">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC86">
         <v>2.46</v>
@@ -14378,10 +14378,10 @@
         <v>1.43</v>
       </c>
       <c r="AE86">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF86">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG86">
         <v>2</v>
@@ -14526,7 +14526,7 @@
         <v>1.3</v>
       </c>
       <c r="Z87">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AA87">
         <v>1.93</v>
@@ -14535,7 +14535,7 @@
         <v>1.73</v>
       </c>
       <c r="AC87">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AD87">
         <v>1.28</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q91">
-        <v>2.31</v>
+        <v>2.74</v>
       </c>
       <c r="R91">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="S91">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T91">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V91">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15175,31 +15175,31 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="AA91">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB91">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC91">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AD91">
         <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF91">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q92">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="R92">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="S92">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T92">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="U92">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W92">
         <v>1.08</v>
@@ -15338,31 +15338,31 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="AA92">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB92">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AD92">
         <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O104">
         <v>3.6</v>
@@ -17282,7 +17282,7 @@
         <v>3</v>
       </c>
       <c r="U104">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="V104">
         <v>1.44</v>
@@ -17297,25 +17297,25 @@
         <v>1.21</v>
       </c>
       <c r="Z104">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AA104">
         <v>1.74</v>
       </c>
       <c r="AB104">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC104">
         <v>2.78</v>
       </c>
       <c r="AD104">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE104">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG104">
         <v>2.07</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O105">
         <v>3.35</v>
@@ -17439,22 +17439,22 @@
         <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="U105">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="V105">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
         <v>1.21</v>
@@ -17463,7 +17463,7 @@
         <v>3.58</v>
       </c>
       <c r="AA105">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB105">
         <v>1.96</v>
@@ -17481,7 +17481,7 @@
         <v>1.6</v>
       </c>
       <c r="AG105">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>3.08</v>
       </c>
       <c r="U106">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V106">
         <v>1.44</v>
@@ -17626,10 +17626,10 @@
         <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB106">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC106">
         <v>2.92</v>
@@ -17660,7 +17660,7 @@
         <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17986,7 +17986,7 @@
         <v>1.22</v>
       </c>
       <c r="AK108">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O112">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="Q112">
-        <v>3.58</v>
+        <v>2.79</v>
       </c>
       <c r="R112">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S112">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T112">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U112">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="V112">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W112">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z112">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA112">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB112">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC112">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AD112">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE112">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF112">
+        <v>1.4</v>
+      </c>
+      <c r="AG112">
+        <v>2.89</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
         <v>1.44</v>
       </c>
-      <c r="AG112">
-        <v>2.66</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.62</v>
-      </c>
       <c r="AK112">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O113">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P113">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="Q113">
-        <v>2.79</v>
+        <v>3.58</v>
       </c>
       <c r="R113">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S113">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U113">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="V113">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W113">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z113">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA113">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AB113">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC113">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AD113">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AE113">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF113">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AK113">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18924,25 +18924,25 @@
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA114">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB114">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC114">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD114">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE114">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF114">
         <v>1.66</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O115">
         <v>3.8</v>
       </c>
       <c r="P115">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q115">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="R115">
         <v>2.19</v>
@@ -19072,7 +19072,7 @@
         <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="U115">
         <v>2.57</v>
@@ -19087,22 +19087,22 @@
         <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z115">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA115">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB115">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC115">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD115">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE115">
         <v>1.13</v>
@@ -19111,7 +19111,7 @@
         <v>1.67</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19220,13 +19220,13 @@
         <v>1.6</v>
       </c>
       <c r="O116">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P116">
         <v>5</v>
       </c>
       <c r="Q116">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R116">
         <v>2.5</v>
@@ -19250,7 +19250,7 @@
         <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
         <v>4.25</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="P120">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q120">
-        <v>1.57</v>
+        <v>2.79</v>
       </c>
       <c r="R120">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="S120">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T120">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="U120">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V120">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="W120">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="Z120">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA120">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AB120">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AC120">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="AD120">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AE120">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF120">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AG120">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK120">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>4.1</v>
+        <v>1.27</v>
       </c>
       <c r="O121">
+        <v>5.8</v>
+      </c>
+      <c r="P121">
+        <v>7.8</v>
+      </c>
+      <c r="Q121">
+        <v>1.57</v>
+      </c>
+      <c r="R121">
+        <v>2.7</v>
+      </c>
+      <c r="S121">
+        <v>1.25</v>
+      </c>
+      <c r="T121">
         <v>3.75</v>
       </c>
-      <c r="P121">
-        <v>1.79</v>
-      </c>
-      <c r="Q121">
-        <v>4.61</v>
-      </c>
-      <c r="R121">
-        <v>2.34</v>
-      </c>
-      <c r="S121">
-        <v>1.3</v>
-      </c>
-      <c r="T121">
-        <v>3.15</v>
-      </c>
       <c r="U121">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="V121">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W121">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="Z121">
-        <v>3.58</v>
+        <v>4.75</v>
       </c>
       <c r="AA121">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AC121">
-        <v>3.1</v>
+        <v>2.13</v>
       </c>
       <c r="AD121">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AE121">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF121">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AG121">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK121">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P122">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="Q122">
-        <v>3.4</v>
+        <v>4.61</v>
       </c>
       <c r="R122">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="S122">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="U122">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V122">
         <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z122">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA122">
         <v>1.8</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD122">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG122">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK122">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,46 +20358,46 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="O123">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q123">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="R123">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T123">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U123">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="V123">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
         <v>1.11</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA123">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB123">
         <v>1.92</v>
@@ -20409,13 +20409,13 @@
         <v>1.32</v>
       </c>
       <c r="AE123">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF123">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG123">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20859,7 +20859,7 @@
         <v>2.5</v>
       </c>
       <c r="R126">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S126">
         <v>1.5</v>
@@ -20868,13 +20868,13 @@
         <v>2.37</v>
       </c>
       <c r="U126">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="V126">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W126">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
         <v>1.07</v>
@@ -20892,7 +20892,7 @@
         <v>1.6</v>
       </c>
       <c r="AC126">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="AD126">
         <v>1.17</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="O127">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P127">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q127">
-        <v>2.46</v>
+        <v>4.78</v>
       </c>
       <c r="R127">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S127">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U127">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W127">
         <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z127">
-        <v>3.3</v>
+        <v>4.23</v>
       </c>
       <c r="AA127">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AB127">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AC127">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD127">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE127">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF127">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG127">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="O128">
+        <v>3.3</v>
+      </c>
+      <c r="P128">
         <v>3.6</v>
       </c>
-      <c r="P128">
-        <v>1.7</v>
-      </c>
       <c r="Q128">
-        <v>4.78</v>
+        <v>2.5</v>
       </c>
       <c r="R128">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S128">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T128">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="U128">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V128">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W128">
         <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y128">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z128">
-        <v>4.19</v>
+        <v>3.08</v>
       </c>
       <c r="AA128">
+        <v>1.92</v>
+      </c>
+      <c r="AB128">
         <v>1.75</v>
       </c>
-      <c r="AB128">
-        <v>2.01</v>
-      </c>
       <c r="AC128">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AD128">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE128">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF128">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG128">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK128">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O129">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q129">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R129">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S129">
         <v>1.36</v>
       </c>
       <c r="T129">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="U129">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="V129">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W129">
         <v>1.08</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
+        <v>1.29</v>
+      </c>
+      <c r="Z129">
+        <v>3.3</v>
+      </c>
+      <c r="AA129">
+        <v>1.98</v>
+      </c>
+      <c r="AB129">
+        <v>1.79</v>
+      </c>
+      <c r="AC129">
+        <v>3.3</v>
+      </c>
+      <c r="AD129">
         <v>1.28</v>
       </c>
-      <c r="Z129">
-        <v>3.35</v>
-      </c>
-      <c r="AA129">
-        <v>1.92</v>
-      </c>
-      <c r="AB129">
-        <v>1.76</v>
-      </c>
-      <c r="AC129">
-        <v>3.6</v>
-      </c>
-      <c r="AD129">
-        <v>1.29</v>
-      </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF129">
         <v>1.8</v>
       </c>
       <c r="AG129">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,80 +21662,80 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="O131">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P131">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q131">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="R131">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
+        <v>1.37</v>
+      </c>
+      <c r="T131">
+        <v>2.78</v>
+      </c>
+      <c r="U131">
+        <v>2.7</v>
+      </c>
+      <c r="V131">
+        <v>1.39</v>
+      </c>
+      <c r="W131">
+        <v>1.03</v>
+      </c>
+      <c r="X131">
+        <v>1.05</v>
+      </c>
+      <c r="Y131">
+        <v>1.26</v>
+      </c>
+      <c r="Z131">
+        <v>3.2</v>
+      </c>
+      <c r="AA131">
+        <v>1.95</v>
+      </c>
+      <c r="AB131">
+        <v>1.76</v>
+      </c>
+      <c r="AC131">
+        <v>3.34</v>
+      </c>
+      <c r="AD131">
+        <v>1.24</v>
+      </c>
+      <c r="AE131">
+        <v>1.11</v>
+      </c>
+      <c r="AF131">
+        <v>1.75</v>
+      </c>
+      <c r="AG131">
+        <v>1.95</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ131">
         <v>1.28</v>
       </c>
-      <c r="T131">
-        <v>3.28</v>
-      </c>
-      <c r="U131">
-        <v>2.62</v>
-      </c>
-      <c r="V131">
-        <v>1.49</v>
-      </c>
-      <c r="W131">
-        <v>1.11</v>
-      </c>
-      <c r="X131">
-        <v>1.03</v>
-      </c>
-      <c r="Y131">
-        <v>1.22</v>
-      </c>
-      <c r="Z131">
-        <v>4.2</v>
-      </c>
-      <c r="AA131">
-        <v>1.75</v>
-      </c>
-      <c r="AB131">
-        <v>1.97</v>
-      </c>
-      <c r="AC131">
-        <v>2.7</v>
-      </c>
-      <c r="AD131">
-        <v>1.36</v>
-      </c>
-      <c r="AE131">
-        <v>1.14</v>
-      </c>
-      <c r="AF131">
-        <v>1.62</v>
-      </c>
-      <c r="AG131">
-        <v>2.14</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>1.25</v>
-      </c>
       <c r="AK131">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P132">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q132">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S132">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T132">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="U132">
+        <v>2.62</v>
+      </c>
+      <c r="V132">
+        <v>1.49</v>
+      </c>
+      <c r="W132">
+        <v>1.11</v>
+      </c>
+      <c r="X132">
+        <v>1.03</v>
+      </c>
+      <c r="Y132">
+        <v>1.22</v>
+      </c>
+      <c r="Z132">
+        <v>4.2</v>
+      </c>
+      <c r="AA132">
+        <v>1.75</v>
+      </c>
+      <c r="AB132">
+        <v>1.97</v>
+      </c>
+      <c r="AC132">
         <v>2.7</v>
       </c>
-      <c r="V132">
-        <v>1.39</v>
-      </c>
-      <c r="W132">
-        <v>1.03</v>
-      </c>
-      <c r="X132">
-        <v>1.05</v>
-      </c>
-      <c r="Y132">
-        <v>1.26</v>
-      </c>
-      <c r="Z132">
-        <v>3.2</v>
-      </c>
-      <c r="AA132">
-        <v>1.95</v>
-      </c>
-      <c r="AB132">
-        <v>1.76</v>
-      </c>
-      <c r="AC132">
-        <v>3.34</v>
-      </c>
       <c r="AD132">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF132">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG132">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="O133">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P133">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q133">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="R133">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S133">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T133">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="U133">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="V133">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z133">
-        <v>5.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA133">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="AB133">
-        <v>2.43</v>
+        <v>1.72</v>
       </c>
       <c r="AC133">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="AD133">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AE133">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF133">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="O134">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P134">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q134">
+        <v>2.5</v>
+      </c>
+      <c r="R134">
+        <v>2.1</v>
+      </c>
+      <c r="S134">
+        <v>1.35</v>
+      </c>
+      <c r="T134">
         <v>3</v>
       </c>
-      <c r="R134">
-        <v>2</v>
-      </c>
-      <c r="S134">
-        <v>1.36</v>
-      </c>
-      <c r="T134">
-        <v>2.83</v>
-      </c>
       <c r="U134">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V134">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W134">
+        <v>1.08</v>
+      </c>
+      <c r="X134">
         <v>1.05</v>
       </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
       <c r="Y134">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA134">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB134">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC134">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="AD134">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG134">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK134">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="O135">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P135">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q135">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="R135">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S135">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T135">
         <v>3.8</v>
       </c>
       <c r="U135">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="V135">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="W135">
         <v>1.15</v>
       </c>
       <c r="X135">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z135">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="AA135">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB135">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AC135">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AD135">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE135">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF135">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG135">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK135">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P136">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="Q136">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="R136">
-        <v>2.09</v>
+        <v>2.62</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T136">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="U136">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="V136">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="Z136">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA136">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AB136">
-        <v>1.86</v>
+        <v>2.29</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="AD136">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF136">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG136">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK136">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="O137">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="Q137">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R137">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="S137">
+        <v>1.33</v>
+      </c>
+      <c r="T137">
+        <v>2.97</v>
+      </c>
+      <c r="U137">
+        <v>2.75</v>
+      </c>
+      <c r="V137">
+        <v>1.43</v>
+      </c>
+      <c r="W137">
+        <v>1.07</v>
+      </c>
+      <c r="X137">
+        <v>1.03</v>
+      </c>
+      <c r="Y137">
+        <v>1.26</v>
+      </c>
+      <c r="Z137">
+        <v>3.5</v>
+      </c>
+      <c r="AA137">
+        <v>1.84</v>
+      </c>
+      <c r="AB137">
+        <v>1.86</v>
+      </c>
+      <c r="AC137">
+        <v>3.2</v>
+      </c>
+      <c r="AD137">
         <v>1.29</v>
       </c>
-      <c r="T137">
-        <v>3.3</v>
-      </c>
-      <c r="U137">
-        <v>2.4</v>
-      </c>
-      <c r="V137">
-        <v>1.53</v>
-      </c>
-      <c r="W137">
-        <v>1.08</v>
-      </c>
-      <c r="X137">
-        <v>1.02</v>
-      </c>
-      <c r="Y137">
-        <v>1.16</v>
-      </c>
-      <c r="Z137">
-        <v>4.1</v>
-      </c>
-      <c r="AA137">
-        <v>1.65</v>
-      </c>
-      <c r="AB137">
-        <v>2.16</v>
-      </c>
-      <c r="AC137">
-        <v>2.59</v>
-      </c>
-      <c r="AD137">
-        <v>1.39</v>
-      </c>
       <c r="AE137">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK137">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="O138">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P138">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q138">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="R138">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S138">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T138">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U138">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V138">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W138">
         <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z138">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA138">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB138">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="AC138">
-        <v>3.23</v>
+        <v>2.59</v>
       </c>
       <c r="AD138">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE138">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF138">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AG138">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK138">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.87</v>
+        <v>1.73</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P143">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q143">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="R143">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S143">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T143">
         <v>3.2</v>
       </c>
       <c r="U143">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V143">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X143">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z143">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="AA143">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB143">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC143">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD143">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE143">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF143">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG143">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK143">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O144">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q144">
-        <v>2.23</v>
+        <v>3.62</v>
       </c>
       <c r="R144">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S144">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U144">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V144">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X144">
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z144">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA144">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB144">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC144">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AD144">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE144">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF144">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG144">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,80 +23944,80 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="O145">
         <v>3.4</v>
       </c>
       <c r="P145">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q145">
-        <v>3.62</v>
+        <v>2.74</v>
       </c>
       <c r="R145">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S145">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T145">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U145">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V145">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W145">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="Z145">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AA145">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="AB145">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC145">
-        <v>3.05</v>
+        <v>3.48</v>
       </c>
       <c r="AD145">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
+        <v>1.79</v>
+      </c>
+      <c r="AG145">
+        <v>1.89</v>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ145">
+        <v>1.29</v>
+      </c>
+      <c r="AK145">
         <v>1.67</v>
-      </c>
-      <c r="AG145">
-        <v>2.04</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>1.3</v>
-      </c>
-      <c r="AK145">
-        <v>1.36</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,80 +24107,80 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="O146">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P146">
+        <v>2.3</v>
+      </c>
+      <c r="Q146">
+        <v>3.46</v>
+      </c>
+      <c r="R146">
+        <v>2.2</v>
+      </c>
+      <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
         <v>3.2</v>
       </c>
-      <c r="Q146">
-        <v>2.74</v>
-      </c>
-      <c r="R146">
-        <v>2.01</v>
-      </c>
-      <c r="S146">
-        <v>1.36</v>
-      </c>
-      <c r="T146">
-        <v>3</v>
-      </c>
       <c r="U146">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="V146">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X146">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y146">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>2.91</v>
+        <v>4.25</v>
       </c>
       <c r="AA146">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AB146">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC146">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="AD146">
+        <v>1.39</v>
+      </c>
+      <c r="AE146">
+        <v>1.12</v>
+      </c>
+      <c r="AF146">
+        <v>1.56</v>
+      </c>
+      <c r="AG146">
+        <v>2.28</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
         <v>1.22</v>
       </c>
-      <c r="AE146">
-        <v>1.04</v>
-      </c>
-      <c r="AF146">
-        <v>1.79</v>
-      </c>
-      <c r="AG146">
-        <v>1.91</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>1.29</v>
-      </c>
       <c r="AK146">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24279,7 +24279,7 @@
         <v>2.3</v>
       </c>
       <c r="Q147">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="R147">
         <v>2.42</v>
@@ -24312,7 +24312,7 @@
         <v>1.68</v>
       </c>
       <c r="AB147">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC147">
         <v>2.49</v>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="O148">
         <v>3.75</v>
@@ -24442,28 +24442,28 @@
         <v>4.2</v>
       </c>
       <c r="Q148">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R148">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S148">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T148">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U148">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="V148">
         <v>1.45</v>
       </c>
       <c r="W148">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X148">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y148">
         <v>1.27</v>
@@ -24472,25 +24472,25 @@
         <v>3.58</v>
       </c>
       <c r="AA148">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB148">
         <v>1.9</v>
       </c>
       <c r="AC148">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AD148">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE148">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF148">
         <v>1.7</v>
       </c>
       <c r="AG148">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G155">
@@ -25577,77 +25577,77 @@
         <v>2.37</v>
       </c>
       <c r="O155">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P155">
+        <v>2.8</v>
+      </c>
+      <c r="Q155">
         <v>3</v>
       </c>
-      <c r="Q155">
-        <v>2.99</v>
-      </c>
       <c r="R155">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T155">
-        <v>2.64</v>
+        <v>3.46</v>
       </c>
       <c r="U155">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="V155">
+        <v>1.56</v>
+      </c>
+      <c r="W155">
+        <v>1.11</v>
+      </c>
+      <c r="X155">
+        <v>1.02</v>
+      </c>
+      <c r="Y155">
+        <v>1.13</v>
+      </c>
+      <c r="Z155">
+        <v>5</v>
+      </c>
+      <c r="AA155">
+        <v>1.61</v>
+      </c>
+      <c r="AB155">
+        <v>2.29</v>
+      </c>
+      <c r="AC155">
+        <v>2.49</v>
+      </c>
+      <c r="AD155">
+        <v>1.47</v>
+      </c>
+      <c r="AE155">
+        <v>1.2</v>
+      </c>
+      <c r="AF155">
+        <v>1.5</v>
+      </c>
+      <c r="AG155">
+        <v>2.5</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.35</v>
       </c>
-      <c r="W155">
-        <v>1.07</v>
-      </c>
-      <c r="X155">
-        <v>1.03</v>
-      </c>
-      <c r="Y155">
-        <v>1.33</v>
-      </c>
-      <c r="Z155">
-        <v>3.1</v>
-      </c>
-      <c r="AA155">
-        <v>2.2</v>
-      </c>
-      <c r="AB155">
-        <v>1.65</v>
-      </c>
-      <c r="AC155">
-        <v>3.55</v>
-      </c>
-      <c r="AD155">
-        <v>1.2</v>
-      </c>
-      <c r="AE155">
-        <v>1.07</v>
-      </c>
-      <c r="AF155">
-        <v>1.84</v>
-      </c>
-      <c r="AG155">
-        <v>1.86</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.33</v>
-      </c>
       <c r="AK155">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.37</v>
+        <v>5</v>
       </c>
       <c r="O156">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P156">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q156">
-        <v>3</v>
+        <v>4.46</v>
       </c>
       <c r="R156">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T156">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U156">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="V156">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W156">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
         <v>1.02</v>
       </c>
       <c r="Y156">
+        <v>1.23</v>
+      </c>
+      <c r="Z156">
+        <v>3.6</v>
+      </c>
+      <c r="AA156">
+        <v>1.67</v>
+      </c>
+      <c r="AB156">
+        <v>2.15</v>
+      </c>
+      <c r="AC156">
+        <v>2.62</v>
+      </c>
+      <c r="AD156">
+        <v>1.38</v>
+      </c>
+      <c r="AE156">
         <v>1.13</v>
       </c>
-      <c r="Z156">
-        <v>5</v>
-      </c>
-      <c r="AA156">
-        <v>1.61</v>
-      </c>
-      <c r="AB156">
-        <v>2.29</v>
-      </c>
-      <c r="AC156">
-        <v>2.49</v>
-      </c>
-      <c r="AD156">
-        <v>1.47</v>
-      </c>
-      <c r="AE156">
-        <v>1.2</v>
-      </c>
       <c r="AF156">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AK156">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O157">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q157">
-        <v>4.46</v>
+        <v>2.8</v>
       </c>
       <c r="R157">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="S157">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U157">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="V157">
+        <v>1.52</v>
+      </c>
+      <c r="W157">
+        <v>1.1</v>
+      </c>
+      <c r="X157">
+        <v>1.03</v>
+      </c>
+      <c r="Y157">
+        <v>1.17</v>
+      </c>
+      <c r="Z157">
+        <v>4.5</v>
+      </c>
+      <c r="AA157">
+        <v>1.61</v>
+      </c>
+      <c r="AB157">
+        <v>2.23</v>
+      </c>
+      <c r="AC157">
+        <v>2.42</v>
+      </c>
+      <c r="AD157">
+        <v>1.44</v>
+      </c>
+      <c r="AE157">
+        <v>1.17</v>
+      </c>
+      <c r="AF157">
+        <v>1.47</v>
+      </c>
+      <c r="AG157">
+        <v>2.55</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
+        <v>1.25</v>
+      </c>
+      <c r="AK157">
         <v>1.45</v>
-      </c>
-      <c r="W157">
-        <v>1.07</v>
-      </c>
-      <c r="X157">
-        <v>1.02</v>
-      </c>
-      <c r="Y157">
-        <v>1.23</v>
-      </c>
-      <c r="Z157">
-        <v>3.6</v>
-      </c>
-      <c r="AA157">
-        <v>1.67</v>
-      </c>
-      <c r="AB157">
-        <v>2.15</v>
-      </c>
-      <c r="AC157">
-        <v>2.62</v>
-      </c>
-      <c r="AD157">
-        <v>1.38</v>
-      </c>
-      <c r="AE157">
-        <v>1.13</v>
-      </c>
-      <c r="AF157">
-        <v>1.73</v>
-      </c>
-      <c r="AG157">
-        <v>2.1</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.15</v>
-      </c>
-      <c r="AK157">
-        <v>1.13</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
+        <v>1.83</v>
+      </c>
+      <c r="O158">
+        <v>3.7</v>
+      </c>
+      <c r="P158">
+        <v>4</v>
+      </c>
+      <c r="Q158">
         <v>2.4</v>
       </c>
-      <c r="O158">
-        <v>3.6</v>
-      </c>
-      <c r="P158">
-        <v>2.62</v>
-      </c>
-      <c r="Q158">
-        <v>3</v>
-      </c>
       <c r="R158">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S158">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T158">
-        <v>3.17</v>
+        <v>2.76</v>
       </c>
       <c r="U158">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V158">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W158">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
         <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z158">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA158">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB158">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC158">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AD158">
         <v>1.36</v>
       </c>
       <c r="AE158">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF158">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG158">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,16 +26226,16 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O159">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P159">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q159">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="R159">
         <v>2.31</v>
@@ -26247,43 +26247,43 @@
         <v>3.4</v>
       </c>
       <c r="U159">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V159">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X159">
         <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z159">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA159">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB159">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AC159">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AD159">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF159">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG159">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>1.25</v>
       </c>
       <c r="AK159">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O160">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P160">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q160">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R160">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S160">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="T160">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="U160">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="V160">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W160">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X160">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z160">
         <v>3.8</v>
       </c>
       <c r="AA160">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AB160">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="AC160">
-        <v>2.49</v>
+        <v>3.12</v>
       </c>
       <c r="AD160">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE160">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AF160">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG160">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="O161">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="P161">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Q161">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="R161">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="S161">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T161">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="U161">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V161">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W161">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X161">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z161">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA161">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AB161">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC161">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD161">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE161">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF161">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK161">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.12</v>
+        <v>2.37</v>
       </c>
       <c r="O162">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P162">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q162">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="R162">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S162">
+        <v>1.4</v>
+      </c>
+      <c r="T162">
+        <v>2.64</v>
+      </c>
+      <c r="U162">
+        <v>2.9</v>
+      </c>
+      <c r="V162">
         <v>1.35</v>
       </c>
-      <c r="T162">
-        <v>2.88</v>
-      </c>
-      <c r="U162">
-        <v>2.88</v>
-      </c>
-      <c r="V162">
-        <v>1.41</v>
-      </c>
       <c r="W162">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X162">
         <v>1.03</v>
       </c>
       <c r="Y162">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z162">
+        <v>3.1</v>
+      </c>
+      <c r="AA162">
+        <v>2.2</v>
+      </c>
+      <c r="AB162">
+        <v>1.65</v>
+      </c>
+      <c r="AC162">
         <v>3.55</v>
       </c>
-      <c r="AA162">
-        <v>1.96</v>
-      </c>
-      <c r="AB162">
-        <v>1.89</v>
-      </c>
-      <c r="AC162">
-        <v>3.14</v>
-      </c>
       <c r="AD162">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE162">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF162">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG162">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK162">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -28517,7 +28517,7 @@
         <v>3.4</v>
       </c>
       <c r="Q173">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R173">
         <v>2.01</v>
@@ -28535,10 +28535,10 @@
         <v>1.3</v>
       </c>
       <c r="W173">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X173">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y173">
         <v>1.33</v>
@@ -28547,7 +28547,7 @@
         <v>3</v>
       </c>
       <c r="AA173">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB173">
         <v>1.66</v>
@@ -32755,19 +32755,19 @@
         <v>3.5</v>
       </c>
       <c r="Q199">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="R199">
         <v>2.1</v>
       </c>
       <c r="S199">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T199">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U199">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="V199">
         <v>1.38</v>
@@ -32776,7 +32776,7 @@
         <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y199">
         <v>1.26</v>
@@ -32788,16 +32788,16 @@
         <v>2</v>
       </c>
       <c r="AB199">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC199">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="AD199">
         <v>1.25</v>
       </c>
       <c r="AE199">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF199">
         <v>1.75</v>
@@ -32816,7 +32816,7 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK199">
         <v>1.73</v>
@@ -33090,7 +33090,7 @@
         <v>1.29</v>
       </c>
       <c r="T201">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U201">
         <v>2.4</v>
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O203">
         <v>3.6</v>
@@ -33428,25 +33428,25 @@
         <v>1.08</v>
       </c>
       <c r="X203">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
         <v>1.19</v>
       </c>
       <c r="Z203">
-        <v>4.48</v>
+        <v>4.64</v>
       </c>
       <c r="AA203">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB203">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC203">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD203">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE203">
         <v>1.15</v>
@@ -33733,7 +33733,7 @@
         <v>2.7</v>
       </c>
       <c r="Q205">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="R205">
         <v>2.16</v>
@@ -33745,10 +33745,10 @@
         <v>2.91</v>
       </c>
       <c r="U205">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V205">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W205">
         <v>1.11</v>
@@ -33757,19 +33757,19 @@
         <v>1.02</v>
       </c>
       <c r="Y205">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z205">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA205">
         <v>1.66</v>
       </c>
       <c r="AB205">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC205">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD205">
         <v>1.4</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O227">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P227">
-        <v>5.44</v>
+        <v>4.7</v>
       </c>
       <c r="Q227">
         <v>2.21</v>
@@ -37337,7 +37337,7 @@
         <v>1.44</v>
       </c>
       <c r="W227">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X227">
         <v>1.02</v>
@@ -37383,7 +37383,7 @@
         <v>1.2</v>
       </c>
       <c r="AK227">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O230">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P230">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q230">
         <v>2.02</v>
@@ -37835,10 +37835,10 @@
         <v>1.26</v>
       </c>
       <c r="Z230">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA230">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB230">
         <v>2.13</v>
@@ -37853,7 +37853,7 @@
         <v>1.11</v>
       </c>
       <c r="AF230">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG230">
         <v>1.91</v>
@@ -37968,10 +37968,10 @@
         <v>3</v>
       </c>
       <c r="P231">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="Q231">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="R231">
         <v>1.95</v>
@@ -37980,7 +37980,7 @@
         <v>1.4</v>
       </c>
       <c r="T231">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U231">
         <v>3.2</v>
@@ -37998,7 +37998,7 @@
         <v>1.36</v>
       </c>
       <c r="Z231">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AA231">
         <v>2.04</v>
@@ -38013,7 +38013,7 @@
         <v>1.26</v>
       </c>
       <c r="AE231">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF231">
         <v>1.77</v>
@@ -38454,7 +38454,7 @@
         <v>1.85</v>
       </c>
       <c r="O234">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P234">
         <v>3.9</v>
@@ -38499,7 +38499,7 @@
         <v>2.41</v>
       </c>
       <c r="AD234">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE234">
         <v>1.14</v>
@@ -38623,7 +38623,7 @@
         <v>0</v>
       </c>
       <c r="Q235">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="R235">
         <v>2.5</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q236">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R236">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S236">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U236">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="V236">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W236">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X236">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y236">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z236">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA236">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB236">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC236">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AD236">
         <v>1.24</v>
       </c>
       <c r="AE236">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF236">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AG236">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK236">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O237">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P237">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q237">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R237">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S237">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T237">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U237">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="V237">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W237">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X237">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z237">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AA237">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB237">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC237">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AD237">
         <v>1.24</v>
       </c>
       <c r="AE237">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF237">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AG237">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK237">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39284,7 +39284,7 @@
         <v>1.4</v>
       </c>
       <c r="T239">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="U239">
         <v>2.8</v>
@@ -39296,7 +39296,7 @@
         <v>1.02</v>
       </c>
       <c r="X239">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
         <v>1.31</v>
@@ -39314,7 +39314,7 @@
         <v>3.48</v>
       </c>
       <c r="AD239">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE239">
         <v>1.06</v>
@@ -39444,10 +39444,10 @@
         <v>1.88</v>
       </c>
       <c r="S240">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T240">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U240">
         <v>3.17</v>
@@ -40096,7 +40096,7 @@
         <v>2.5</v>
       </c>
       <c r="S244">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T244">
         <v>3.75</v>
@@ -40135,7 +40135,7 @@
         <v>1.21</v>
       </c>
       <c r="AF244">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG244">
         <v>2.42</v>
@@ -43036,7 +43036,7 @@
         <v>3</v>
       </c>
       <c r="U262">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V262">
         <v>1.41</v>
@@ -43063,13 +43063,13 @@
         <v>3.3</v>
       </c>
       <c r="AD262">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE262">
         <v>1.07</v>
       </c>
       <c r="AF262">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG262">
         <v>2</v>
@@ -45466,10 +45466,10 @@
         <v>3.6</v>
       </c>
       <c r="P277">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q277">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="R277">
         <v>2.25</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O279">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P279">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q279">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="R279">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="S279">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T279">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V279">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W279">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y279">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z279">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="AA279">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB279">
+        <v>1.35</v>
+      </c>
+      <c r="AC279">
+        <v>5.55</v>
+      </c>
+      <c r="AD279">
+        <v>1.08</v>
+      </c>
+      <c r="AE279">
+        <v>1.03</v>
+      </c>
+      <c r="AF279">
+        <v>2.23</v>
+      </c>
+      <c r="AG279">
+        <v>1.57</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.44</v>
       </c>
-      <c r="AC279">
-        <v>4.85</v>
-      </c>
-      <c r="AD279">
-        <v>1.11</v>
-      </c>
-      <c r="AE279">
-        <v>1.01</v>
-      </c>
-      <c r="AF279">
-        <v>2.4</v>
-      </c>
-      <c r="AG279">
-        <v>1.48</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.26</v>
-      </c>
       <c r="AK279">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="O280">
+        <v>3.25</v>
+      </c>
+      <c r="P280">
+        <v>5.25</v>
+      </c>
+      <c r="Q280">
+        <v>2.33</v>
+      </c>
+      <c r="R280">
+        <v>1.88</v>
+      </c>
+      <c r="S280">
+        <v>1.53</v>
+      </c>
+      <c r="T280">
+        <v>2.2</v>
+      </c>
+      <c r="U280">
+        <v>3.5</v>
+      </c>
+      <c r="V280">
+        <v>1.25</v>
+      </c>
+      <c r="W280">
+        <v>1.04</v>
+      </c>
+      <c r="X280">
+        <v>1.11</v>
+      </c>
+      <c r="Y280">
+        <v>1.54</v>
+      </c>
+      <c r="Z280">
+        <v>2.42</v>
+      </c>
+      <c r="AA280">
         <v>2.7</v>
       </c>
-      <c r="P280">
+      <c r="AB280">
+        <v>1.44</v>
+      </c>
+      <c r="AC280">
+        <v>4.85</v>
+      </c>
+      <c r="AD280">
+        <v>1.11</v>
+      </c>
+      <c r="AE280">
+        <v>1.01</v>
+      </c>
+      <c r="AF280">
         <v>2.4</v>
       </c>
-      <c r="Q280">
-        <v>4</v>
-      </c>
-      <c r="R280">
-        <v>1.75</v>
-      </c>
-      <c r="S280">
-        <v>1.57</v>
-      </c>
-      <c r="T280">
-        <v>2.13</v>
-      </c>
-      <c r="U280">
-        <v>3.8</v>
-      </c>
-      <c r="V280">
-        <v>1.22</v>
-      </c>
-      <c r="W280">
-        <v>1.03</v>
-      </c>
-      <c r="X280">
-        <v>1.09</v>
-      </c>
-      <c r="Y280">
-        <v>1.57</v>
-      </c>
-      <c r="Z280">
-        <v>2.26</v>
-      </c>
-      <c r="AA280">
-        <v>2.87</v>
-      </c>
-      <c r="AB280">
-        <v>1.35</v>
-      </c>
-      <c r="AC280">
-        <v>5.55</v>
-      </c>
-      <c r="AD280">
-        <v>1.08</v>
-      </c>
-      <c r="AE280">
-        <v>1.03</v>
-      </c>
-      <c r="AF280">
-        <v>2.23</v>
-      </c>
       <c r="AG280">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK280">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O287">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P287">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q287">
         <v>2.9</v>
@@ -47105,49 +47105,49 @@
         <v>2.05</v>
       </c>
       <c r="S287">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T287">
         <v>2.83</v>
       </c>
       <c r="U287">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="V287">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W287">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X287">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y287">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z287">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="AA287">
         <v>1.9</v>
       </c>
       <c r="AB287">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC287">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD287">
         <v>1.33</v>
       </c>
       <c r="AE287">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF287">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG287">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK287">
         <v>1.62</v>
@@ -47253,7 +47253,7 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O288">
         <v>3.4</v>
@@ -47262,46 +47262,46 @@
         <v>2.6</v>
       </c>
       <c r="Q288">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R288">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S288">
         <v>1.36</v>
       </c>
       <c r="T288">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U288">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V288">
         <v>1.44</v>
       </c>
       <c r="W288">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X288">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y288">
         <v>1.26</v>
       </c>
       <c r="Z288">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="AA288">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB288">
         <v>2.06</v>
       </c>
       <c r="AC288">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AD288">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE288">
         <v>1.13</v>
@@ -47310,7 +47310,7 @@
         <v>1.6</v>
       </c>
       <c r="AG288">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47416,34 +47416,34 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O289">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P289">
         <v>4.4</v>
       </c>
       <c r="Q289">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R289">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="S289">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T289">
         <v>3.3</v>
       </c>
       <c r="U289">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V289">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W289">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X289">
         <v>1</v>
@@ -47452,28 +47452,28 @@
         <v>1.27</v>
       </c>
       <c r="Z289">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA289">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB289">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC289">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="AD289">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE289">
         <v>1.13</v>
       </c>
       <c r="AF289">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG289">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK289">
         <v>2.14</v>
@@ -47597,13 +47597,13 @@
         <v>1.27</v>
       </c>
       <c r="T290">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U290">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V290">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W290">
         <v>1.11</v>
@@ -47633,10 +47633,10 @@
         <v>1.21</v>
       </c>
       <c r="AF290">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG290">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47754,13 +47754,13 @@
         <v>7.47</v>
       </c>
       <c r="R291">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S291">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T291">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="U291">
         <v>2.3</v>
@@ -47769,10 +47769,10 @@
         <v>1.55</v>
       </c>
       <c r="W291">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
         <v>1.2</v>
@@ -47796,7 +47796,7 @@
         <v>1.15</v>
       </c>
       <c r="AF291">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG291">
         <v>1.91</v>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK291">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48397,16 +48397,16 @@
         <v>1.43</v>
       </c>
       <c r="O295">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="P295">
         <v>7.2</v>
       </c>
       <c r="Q295">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R295">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S295">
         <v>1.28</v>
@@ -48421,10 +48421,10 @@
         <v>1.48</v>
       </c>
       <c r="W295">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X295">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y295">
         <v>1.19</v>
@@ -48445,13 +48445,13 @@
         <v>1.38</v>
       </c>
       <c r="AE295">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF295">
         <v>1.88</v>
       </c>
       <c r="AG295">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK295">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48913,7 +48913,7 @@
         <v>1.06</v>
       </c>
       <c r="X298">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y298">
         <v>1.25</v>
@@ -49046,7 +49046,7 @@
         </is>
       </c>
       <c r="N299">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="O299">
         <v>7.5</v>
@@ -49073,7 +49073,7 @@
         <v>2</v>
       </c>
       <c r="W299">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X299">
         <v>1.01</v>
@@ -49082,7 +49082,7 @@
         <v>1.05</v>
       </c>
       <c r="Z299">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA299">
         <v>1.22</v>
@@ -49097,13 +49097,13 @@
         <v>2.2</v>
       </c>
       <c r="AE299">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AF299">
         <v>1.62</v>
       </c>
       <c r="AG299">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49864,10 +49864,10 @@
         <v>2.1</v>
       </c>
       <c r="O304">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="P304">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q304">
         <v>2.62</v>
@@ -49897,10 +49897,10 @@
         <v>1.22</v>
       </c>
       <c r="Z304">
-        <v>3.58</v>
+        <v>4.03</v>
       </c>
       <c r="AA304">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB304">
         <v>2.03</v>
@@ -50522,7 +50522,7 @@
         <v>2.45</v>
       </c>
       <c r="Q308">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="R308">
         <v>2.07</v>
@@ -50534,10 +50534,10 @@
         <v>2.7</v>
       </c>
       <c r="U308">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V308">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W308">
         <v>1.1</v>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK308">
         <v>1.4</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="O312">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="P312">
-        <v>5.8</v>
+        <v>4.45</v>
       </c>
       <c r="Q312">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="R312">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="S312">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T312">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="U312">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="V312">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W312">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X312">
         <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z312">
-        <v>5.4</v>
+        <v>3.96</v>
       </c>
       <c r="AA312">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB312">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC312">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AD312">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AE312">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF312">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG312">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK312">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="O313">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P313">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="Q313">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="R313">
-        <v>2.18</v>
+        <v>2.67</v>
       </c>
       <c r="S313">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U313">
-        <v>2.67</v>
+        <v>2.22</v>
       </c>
       <c r="V313">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="W313">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X313">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z313">
-        <v>3.72</v>
+        <v>5.35</v>
       </c>
       <c r="AA313">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="AB313">
-        <v>2.01</v>
+        <v>2.49</v>
       </c>
       <c r="AC313">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD313">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AE313">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF313">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG313">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK313">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="O314">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P314">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q314">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="R314">
+        <v>2.18</v>
+      </c>
+      <c r="S314">
+        <v>1.3</v>
+      </c>
+      <c r="T314">
+        <v>3.2</v>
+      </c>
+      <c r="U314">
         <v>2.67</v>
       </c>
-      <c r="S314">
+      <c r="V314">
+        <v>1.45</v>
+      </c>
+      <c r="W314">
+        <v>1.08</v>
+      </c>
+      <c r="X314">
+        <v>1.01</v>
+      </c>
+      <c r="Y314">
         <v>1.2</v>
       </c>
-      <c r="T314">
-        <v>4</v>
-      </c>
-      <c r="U314">
-        <v>2.22</v>
-      </c>
-      <c r="V314">
-        <v>1.65</v>
-      </c>
-      <c r="W314">
-        <v>1.15</v>
-      </c>
-      <c r="X314">
-        <v>1.02</v>
-      </c>
-      <c r="Y314">
-        <v>1.13</v>
-      </c>
       <c r="Z314">
-        <v>5.35</v>
+        <v>3.72</v>
       </c>
       <c r="AA314">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AB314">
-        <v>2.49</v>
+        <v>2.01</v>
       </c>
       <c r="AC314">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="AD314">
+        <v>1.32</v>
+      </c>
+      <c r="AE314">
+        <v>1.08</v>
+      </c>
+      <c r="AF314">
         <v>1.61</v>
       </c>
-      <c r="AE314">
-        <v>1.24</v>
-      </c>
-      <c r="AF314">
-        <v>1.56</v>
-      </c>
       <c r="AG314">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O315">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="P315">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q315">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="R315">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="S315">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T315">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="U315">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="V315">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W315">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X315">
         <v>1.02</v>
       </c>
       <c r="Y315">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z315">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="AA315">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB315">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC315">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="AD315">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AE315">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF315">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG315">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK315">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51998,7 +51998,7 @@
         <v>1.37</v>
       </c>
       <c r="T317">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U317">
         <v>2.53</v>
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK317">
         <v>2.46</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garudayaksa FC</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>2.06</v>
+      </c>
+      <c r="O6">
+        <v>3.15</v>
+      </c>
+      <c r="P6">
+        <v>3.45</v>
+      </c>
+      <c r="Q6">
+        <v>2.6</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>1.41</v>
+      </c>
+      <c r="T6">
+        <v>2.51</v>
+      </c>
+      <c r="U6">
+        <v>2.9</v>
+      </c>
+      <c r="V6">
         <v>1.36</v>
       </c>
-      <c r="O6">
-        <v>4.2</v>
-      </c>
-      <c r="P6">
-        <v>6.03</v>
-      </c>
-      <c r="Q6">
-        <v>1.93</v>
-      </c>
-      <c r="R6">
-        <v>2.16</v>
-      </c>
-      <c r="S6">
-        <v>1.36</v>
-      </c>
-      <c r="T6">
-        <v>3.11</v>
-      </c>
-      <c r="U6">
-        <v>2.6</v>
-      </c>
-      <c r="V6">
-        <v>1.41</v>
-      </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z6">
-        <v>3.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>2.46</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Garudayaksa FC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.06</v>
+        <v>1.36</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="P7">
-        <v>3.45</v>
+        <v>6.03</v>
       </c>
       <c r="Q7">
+        <v>1.93</v>
+      </c>
+      <c r="R7">
+        <v>2.16</v>
+      </c>
+      <c r="S7">
+        <v>1.36</v>
+      </c>
+      <c r="T7">
+        <v>3.11</v>
+      </c>
+      <c r="U7">
         <v>2.6</v>
       </c>
-      <c r="R7">
-        <v>2.1</v>
-      </c>
-      <c r="S7">
+      <c r="V7">
         <v>1.41</v>
       </c>
-      <c r="T7">
-        <v>2.51</v>
-      </c>
-      <c r="U7">
-        <v>2.9</v>
-      </c>
-      <c r="V7">
+      <c r="W7">
+        <v>1.06</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.22</v>
+      </c>
+      <c r="Z7">
+        <v>3.59</v>
+      </c>
+      <c r="AA7">
+        <v>1.83</v>
+      </c>
+      <c r="AB7">
+        <v>1.93</v>
+      </c>
+      <c r="AC7">
+        <v>2.83</v>
+      </c>
+      <c r="AD7">
         <v>1.36</v>
       </c>
-      <c r="W7">
-        <v>1.04</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.34</v>
-      </c>
-      <c r="Z7">
-        <v>2.97</v>
-      </c>
-      <c r="AA7">
-        <v>2.08</v>
-      </c>
-      <c r="AB7">
-        <v>1.75</v>
-      </c>
-      <c r="AC7">
-        <v>3.42</v>
-      </c>
-      <c r="AD7">
-        <v>1.23</v>
-      </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P40">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q40">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R40">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
+        <v>2.12</v>
+      </c>
+      <c r="AC40">
+        <v>2.57</v>
+      </c>
+      <c r="AD40">
+        <v>1.41</v>
+      </c>
+      <c r="AE40">
+        <v>1.13</v>
+      </c>
+      <c r="AF40">
+        <v>1.64</v>
+      </c>
+      <c r="AG40">
+        <v>2.08</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.19</v>
+      </c>
+      <c r="AK40">
         <v>2</v>
-      </c>
-      <c r="AC40">
-        <v>2.81</v>
-      </c>
-      <c r="AD40">
-        <v>1.4</v>
-      </c>
-      <c r="AE40">
-        <v>1.1</v>
-      </c>
-      <c r="AF40">
-        <v>1.73</v>
-      </c>
-      <c r="AG40">
-        <v>1.94</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.25</v>
-      </c>
-      <c r="AK40">
-        <v>2.02</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="O41">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q41">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="O52">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="Q52">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="R52">
         <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U52">
         <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB52">
+        <v>1.75</v>
+      </c>
+      <c r="AC52">
+        <v>3.4</v>
+      </c>
+      <c r="AD52">
+        <v>1.25</v>
+      </c>
+      <c r="AE52">
+        <v>1.1</v>
+      </c>
+      <c r="AF52">
         <v>1.73</v>
       </c>
-      <c r="AC52">
-        <v>3.42</v>
-      </c>
-      <c r="AD52">
-        <v>1.23</v>
-      </c>
-      <c r="AE52">
-        <v>1.04</v>
-      </c>
-      <c r="AF52">
-        <v>1.74</v>
-      </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="O53">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="Q53">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.77</v>
+        <v>3.11</v>
       </c>
       <c r="U53">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z53">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AB53">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC53">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF53">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="Q54">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S54">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T54">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="U54">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="V54">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z54">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="AA54">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AB54">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AC54">
-        <v>2.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AE54">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG54">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AK54">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q63">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="R63">
+        <v>2.2</v>
+      </c>
+      <c r="S63">
+        <v>1.35</v>
+      </c>
+      <c r="T63">
+        <v>2.87</v>
+      </c>
+      <c r="U63">
+        <v>2.44</v>
+      </c>
+      <c r="V63">
+        <v>1.5</v>
+      </c>
+      <c r="W63">
+        <v>1.11</v>
+      </c>
+      <c r="X63">
+        <v>1.02</v>
+      </c>
+      <c r="Y63">
+        <v>1.18</v>
+      </c>
+      <c r="Z63">
+        <v>3.88</v>
+      </c>
+      <c r="AA63">
+        <v>1.74</v>
+      </c>
+      <c r="AB63">
         <v>2</v>
       </c>
-      <c r="S63">
-        <v>1.4</v>
-      </c>
-      <c r="T63">
-        <v>2.5</v>
-      </c>
-      <c r="U63">
-        <v>2.86</v>
-      </c>
-      <c r="V63">
-        <v>1.35</v>
-      </c>
-      <c r="W63">
-        <v>1.07</v>
-      </c>
-      <c r="X63">
-        <v>1.06</v>
-      </c>
-      <c r="Y63">
-        <v>1.28</v>
-      </c>
-      <c r="Z63">
-        <v>3.08</v>
-      </c>
-      <c r="AA63">
-        <v>2.04</v>
-      </c>
-      <c r="AB63">
-        <v>1.68</v>
-      </c>
       <c r="AC63">
-        <v>4.02</v>
+        <v>2.88</v>
       </c>
       <c r="AD63">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG63">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P64">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q64">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R64">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S64">
+        <v>1.4</v>
+      </c>
+      <c r="T64">
+        <v>2.5</v>
+      </c>
+      <c r="U64">
+        <v>2.86</v>
+      </c>
+      <c r="V64">
         <v>1.35</v>
       </c>
-      <c r="T64">
-        <v>2.87</v>
-      </c>
-      <c r="U64">
-        <v>2.44</v>
-      </c>
-      <c r="V64">
-        <v>1.5</v>
-      </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z64">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA64">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="AB64">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AC64">
-        <v>2.88</v>
+        <v>4.02</v>
       </c>
       <c r="AD64">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AG64">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.69</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q65">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="R65">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="S65">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.46</v>
+        <v>3.68</v>
       </c>
       <c r="U65">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V65">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>4.55</v>
+        <v>5.15</v>
       </c>
       <c r="AA65">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AB65">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="AC65">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="AD65">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF65">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG65">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK65">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Q66">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R66">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="U66">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB66">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AC66">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AD66">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG66">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q67">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="R67">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T67">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="U67">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="V67">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA67">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AB67">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC67">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="AD67">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG67">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="Q68">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="R68">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T68">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="U68">
         <v>2.1</v>
       </c>
       <c r="V68">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z68">
-        <v>5.15</v>
+        <v>5.7</v>
       </c>
       <c r="AA68">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB68">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AC68">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD68">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AE68">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF68">
         <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P77">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q77">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="R77">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="S77">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U77">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
         <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z77">
-        <v>3.32</v>
+        <v>2.97</v>
       </c>
       <c r="AA77">
         <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC77">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AD77">
         <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG77">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="O78">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q78">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S78">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T78">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U78">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="V78">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
         <v>1.06</v>
@@ -13056,31 +13056,31 @@
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z78">
-        <v>2.74</v>
+        <v>3.32</v>
       </c>
       <c r="AA78">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD78">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
         <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="O79">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q79">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="R79">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="S79">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U79">
-        <v>3.07</v>
+        <v>2.64</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AB79">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AC79">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P80">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q80">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R80">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T80">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="U80">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="V80">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z80">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="AA80">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="AB80">
-        <v>2.05</v>
+        <v>1.59</v>
       </c>
       <c r="AC80">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD80">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AE80">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG80">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK80">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,31 +15142,31 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q91">
-        <v>2.74</v>
+        <v>2.31</v>
       </c>
       <c r="R91">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="S91">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T91">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="U91">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V91">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W91">
         <v>1.08</v>
@@ -15175,31 +15175,31 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="AA91">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB91">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC91">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AD91">
         <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG91">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,31 +15305,31 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q92">
-        <v>2.31</v>
+        <v>2.74</v>
       </c>
       <c r="R92">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="S92">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T92">
-        <v>2.86</v>
+        <v>3.26</v>
       </c>
       <c r="U92">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V92">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
         <v>1.08</v>
@@ -15338,31 +15338,31 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="AA92">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB92">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC92">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AD92">
         <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG92">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.88</v>
+        <v>3.1</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P104">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q104">
+        <v>3.87</v>
+      </c>
+      <c r="R104">
         <v>2.25</v>
       </c>
-      <c r="R104">
-        <v>2.3</v>
-      </c>
       <c r="S104">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="U104">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="V104">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
         <v>1.21</v>
       </c>
       <c r="Z104">
-        <v>3.88</v>
+        <v>3.58</v>
       </c>
       <c r="AA104">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB104">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC104">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD104">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG104">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK104">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="Q105">
-        <v>3.87</v>
+        <v>2.25</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="U105">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="V105">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
         <v>1.21</v>
       </c>
       <c r="Z105">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA105">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AB105">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC105">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD105">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG105">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="O115">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="P115">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q115">
-        <v>4.84</v>
+        <v>2</v>
       </c>
       <c r="R115">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S115">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T115">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="U115">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="V115">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W115">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA115">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB115">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC115">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD115">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE115">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG115">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>1.22</v>
+        <v>2.29</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O116">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P116">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="Q116">
-        <v>2</v>
+        <v>4.84</v>
       </c>
       <c r="R116">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="S116">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="U116">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="V116">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z116">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA116">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AB116">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC116">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AD116">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,46 +19869,46 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="O120">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q120">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="R120">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T120">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U120">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="V120">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
         <v>1.11</v>
       </c>
       <c r="X120">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z120">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA120">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB120">
         <v>1.92</v>
@@ -19920,13 +19920,13 @@
         <v>1.32</v>
       </c>
       <c r="AE120">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG120">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.27</v>
+        <v>4.1</v>
       </c>
       <c r="O121">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
-        <v>7.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q121">
-        <v>1.57</v>
+        <v>4.61</v>
       </c>
       <c r="R121">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="S121">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="U121">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="V121">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W121">
+        <v>1.1</v>
+      </c>
+      <c r="X121">
+        <v>1.03</v>
+      </c>
+      <c r="Y121">
+        <v>1.21</v>
+      </c>
+      <c r="Z121">
+        <v>3.58</v>
+      </c>
+      <c r="AA121">
+        <v>1.8</v>
+      </c>
+      <c r="AB121">
+        <v>1.9</v>
+      </c>
+      <c r="AC121">
+        <v>3.1</v>
+      </c>
+      <c r="AD121">
+        <v>1.36</v>
+      </c>
+      <c r="AE121">
+        <v>1.08</v>
+      </c>
+      <c r="AF121">
+        <v>1.74</v>
+      </c>
+      <c r="AG121">
+        <v>1.96</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.17</v>
       </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.12</v>
-      </c>
-      <c r="Z121">
-        <v>4.75</v>
-      </c>
-      <c r="AA121">
-        <v>1.36</v>
-      </c>
-      <c r="AB121">
-        <v>2.37</v>
-      </c>
-      <c r="AC121">
-        <v>2.13</v>
-      </c>
-      <c r="AD121">
-        <v>1.61</v>
-      </c>
-      <c r="AE121">
-        <v>1.22</v>
-      </c>
-      <c r="AF121">
-        <v>1.91</v>
-      </c>
-      <c r="AG121">
-        <v>1.83</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.12</v>
-      </c>
       <c r="AK121">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,37 +20195,37 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="O122">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P122">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="Q122">
-        <v>4.61</v>
+        <v>2.79</v>
       </c>
       <c r="R122">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="S122">
         <v>1.3</v>
       </c>
       <c r="T122">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U122">
-        <v>2.62</v>
+        <v>2.13</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W122">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y122">
         <v>1.21</v>
@@ -20234,25 +20234,25 @@
         <v>3.58</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF122">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AG122">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK122">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.35</v>
+        <v>1.27</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="P123">
-        <v>2.03</v>
+        <v>7.8</v>
       </c>
       <c r="Q123">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="S123">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T123">
-        <v>3.19</v>
+        <v>3.75</v>
       </c>
       <c r="U123">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V123">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W123">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X123">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z123">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA123">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB123">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="AC123">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="AD123">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF123">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG123">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK123">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,55 +21173,55 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="O128">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P128">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q128">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R128">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S128">
         <v>1.36</v>
       </c>
       <c r="T128">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="U128">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="V128">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W128">
         <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
+        <v>1.29</v>
+      </c>
+      <c r="Z128">
+        <v>3.3</v>
+      </c>
+      <c r="AA128">
+        <v>1.98</v>
+      </c>
+      <c r="AB128">
+        <v>1.79</v>
+      </c>
+      <c r="AC128">
+        <v>3.3</v>
+      </c>
+      <c r="AD128">
         <v>1.28</v>
-      </c>
-      <c r="Z128">
-        <v>3.08</v>
-      </c>
-      <c r="AA128">
-        <v>1.92</v>
-      </c>
-      <c r="AB128">
-        <v>1.75</v>
-      </c>
-      <c r="AC128">
-        <v>3.6</v>
-      </c>
-      <c r="AD128">
-        <v>1.29</v>
       </c>
       <c r="AE128">
         <v>1.06</v>
@@ -21230,7 +21230,7 @@
         <v>1.8</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,55 +21336,55 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="O129">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q129">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R129">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S129">
         <v>1.36</v>
       </c>
       <c r="T129">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="U129">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="V129">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W129">
         <v>1.08</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y129">
+        <v>1.28</v>
+      </c>
+      <c r="Z129">
+        <v>3.08</v>
+      </c>
+      <c r="AA129">
+        <v>1.92</v>
+      </c>
+      <c r="AB129">
+        <v>1.75</v>
+      </c>
+      <c r="AC129">
+        <v>3.6</v>
+      </c>
+      <c r="AD129">
         <v>1.29</v>
-      </c>
-      <c r="Z129">
-        <v>3.3</v>
-      </c>
-      <c r="AA129">
-        <v>1.98</v>
-      </c>
-      <c r="AB129">
-        <v>1.79</v>
-      </c>
-      <c r="AC129">
-        <v>3.3</v>
-      </c>
-      <c r="AD129">
-        <v>1.28</v>
       </c>
       <c r="AE129">
         <v>1.06</v>
@@ -21393,7 +21393,7 @@
         <v>1.8</v>
       </c>
       <c r="AG129">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK129">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P134">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="S134">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U134">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="V134">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="W134">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X134">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="Z134">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA134">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB134">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AC134">
-        <v>3.23</v>
+        <v>2.36</v>
       </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE134">
+        <v>1.2</v>
+      </c>
+      <c r="AF134">
+        <v>1.6</v>
+      </c>
+      <c r="AG134">
+        <v>2.2</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.12</v>
       </c>
-      <c r="AF134">
-        <v>1.76</v>
-      </c>
-      <c r="AG134">
-        <v>1.95</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.26</v>
-      </c>
       <c r="AK134">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="O136">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="Q136">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="R136">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="S136">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T136">
-        <v>3.8</v>
+        <v>2.97</v>
       </c>
       <c r="U136">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="V136">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="W136">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="Z136">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA136">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AB136">
-        <v>2.29</v>
+        <v>1.86</v>
       </c>
       <c r="AC136">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="AD136">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK136">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="O137">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q137">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="R137">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S137">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T137">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U137">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA137">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AB137">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AC137">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD137">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AG137">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AK137">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="O138">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P138">
-        <v>2.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q138">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="R138">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S138">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T138">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U138">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V138">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W138">
         <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y138">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z138">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA138">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB138">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AC138">
-        <v>2.59</v>
+        <v>3.23</v>
       </c>
       <c r="AD138">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE138">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF138">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="AG138">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK138">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="O145">
+        <v>3.6</v>
+      </c>
+      <c r="P145">
+        <v>2.3</v>
+      </c>
+      <c r="Q145">
+        <v>3.44</v>
+      </c>
+      <c r="R145">
+        <v>2.42</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
         <v>3.4</v>
       </c>
-      <c r="P145">
-        <v>3.2</v>
-      </c>
-      <c r="Q145">
-        <v>2.74</v>
-      </c>
-      <c r="R145">
-        <v>2.04</v>
-      </c>
-      <c r="S145">
-        <v>1.4</v>
-      </c>
-      <c r="T145">
-        <v>2.88</v>
-      </c>
       <c r="U145">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="V145">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W145">
+        <v>1.1</v>
+      </c>
+      <c r="X145">
         <v>1.02</v>
       </c>
-      <c r="X145">
-        <v>1.05</v>
-      </c>
       <c r="Y145">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="Z145">
-        <v>2.91</v>
+        <v>4.15</v>
       </c>
       <c r="AA145">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AB145">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC145">
-        <v>3.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF145">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG145">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK145">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="O146">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q146">
-        <v>3.46</v>
+        <v>2.74</v>
       </c>
       <c r="R146">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T146">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U146">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W146">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X146">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="Z146">
-        <v>4.25</v>
+        <v>2.91</v>
       </c>
       <c r="AA146">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AB146">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC146">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="AD146">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE146">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF146">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AG146">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK146">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O147">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P147">
         <v>2.3</v>
       </c>
       <c r="Q147">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="R147">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T147">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U147">
         <v>2.5</v>
       </c>
       <c r="V147">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W147">
         <v>1.1</v>
       </c>
       <c r="X147">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y147">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z147">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AA147">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB147">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC147">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="AD147">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE147">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF147">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG147">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK147">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O151">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P151">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="Q151">
-        <v>3.62</v>
+        <v>2.59</v>
       </c>
       <c r="R151">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S151">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T151">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="U151">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V151">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W151">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z151">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA151">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AB151">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AC151">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AD151">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE151">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF151">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AG151">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O152">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>3.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q152">
-        <v>2.59</v>
+        <v>3.62</v>
       </c>
       <c r="R152">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S152">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T152">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="U152">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V152">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W152">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z152">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA152">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AB152">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC152">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD152">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE152">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF152">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK152">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="O156">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q156">
-        <v>4.46</v>
+        <v>2.8</v>
       </c>
       <c r="R156">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="S156">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T156">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U156">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="V156">
+        <v>1.52</v>
+      </c>
+      <c r="W156">
+        <v>1.1</v>
+      </c>
+      <c r="X156">
+        <v>1.03</v>
+      </c>
+      <c r="Y156">
+        <v>1.17</v>
+      </c>
+      <c r="Z156">
+        <v>4.5</v>
+      </c>
+      <c r="AA156">
+        <v>1.61</v>
+      </c>
+      <c r="AB156">
+        <v>2.23</v>
+      </c>
+      <c r="AC156">
+        <v>2.42</v>
+      </c>
+      <c r="AD156">
+        <v>1.44</v>
+      </c>
+      <c r="AE156">
+        <v>1.17</v>
+      </c>
+      <c r="AF156">
+        <v>1.47</v>
+      </c>
+      <c r="AG156">
+        <v>2.55</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
+        <v>1.25</v>
+      </c>
+      <c r="AK156">
         <v>1.45</v>
-      </c>
-      <c r="W156">
-        <v>1.07</v>
-      </c>
-      <c r="X156">
-        <v>1.02</v>
-      </c>
-      <c r="Y156">
-        <v>1.23</v>
-      </c>
-      <c r="Z156">
-        <v>3.6</v>
-      </c>
-      <c r="AA156">
-        <v>1.67</v>
-      </c>
-      <c r="AB156">
-        <v>2.15</v>
-      </c>
-      <c r="AC156">
-        <v>2.62</v>
-      </c>
-      <c r="AD156">
-        <v>1.38</v>
-      </c>
-      <c r="AE156">
-        <v>1.13</v>
-      </c>
-      <c r="AF156">
-        <v>1.73</v>
-      </c>
-      <c r="AG156">
-        <v>2.1</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.15</v>
-      </c>
-      <c r="AK156">
-        <v>1.13</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q157">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="R157">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S157">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="T157">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="U157">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="V157">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W157">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X157">
         <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="Z157">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA157">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AB157">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="AC157">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD157">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AE157">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF157">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AG157">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK157">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="O158">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P158">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="Q158">
-        <v>2.4</v>
+        <v>4.46</v>
       </c>
       <c r="R158">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="S158">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="U158">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="V158">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W158">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X158">
         <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z158">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA158">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AB158">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC158">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD158">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE158">
         <v>1.13</v>
       </c>
       <c r="AF158">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG158">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK158">
-        <v>1.91</v>
+        <v>1.13</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O160">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P160">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q160">
+        <v>2.68</v>
+      </c>
+      <c r="R160">
+        <v>2.06</v>
+      </c>
+      <c r="S160">
+        <v>1.33</v>
+      </c>
+      <c r="T160">
         <v>3</v>
       </c>
-      <c r="R160">
-        <v>2.15</v>
-      </c>
-      <c r="S160">
-        <v>1.34</v>
-      </c>
-      <c r="T160">
-        <v>3.17</v>
-      </c>
       <c r="U160">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V160">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X160">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z160">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA160">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB160">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AC160">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AD160">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE160">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF160">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG160">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK160">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
+        <v>1.83</v>
+      </c>
+      <c r="O161">
+        <v>3.7</v>
+      </c>
+      <c r="P161">
+        <v>4</v>
+      </c>
+      <c r="Q161">
+        <v>2.4</v>
+      </c>
+      <c r="R161">
         <v>2.12</v>
       </c>
-      <c r="O161">
-        <v>3.38</v>
-      </c>
-      <c r="P161">
-        <v>3.3</v>
-      </c>
-      <c r="Q161">
-        <v>2.87</v>
-      </c>
-      <c r="R161">
-        <v>2.09</v>
-      </c>
       <c r="S161">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T161">
+        <v>2.76</v>
+      </c>
+      <c r="U161">
+        <v>2.77</v>
+      </c>
+      <c r="V161">
+        <v>1.43</v>
+      </c>
+      <c r="W161">
+        <v>1.1</v>
+      </c>
+      <c r="X161">
+        <v>1.02</v>
+      </c>
+      <c r="Y161">
+        <v>1.22</v>
+      </c>
+      <c r="Z161">
+        <v>3.5</v>
+      </c>
+      <c r="AA161">
+        <v>1.81</v>
+      </c>
+      <c r="AB161">
+        <v>2</v>
+      </c>
+      <c r="AC161">
         <v>2.88</v>
       </c>
-      <c r="U161">
-        <v>2.88</v>
-      </c>
-      <c r="V161">
-        <v>1.41</v>
-      </c>
-      <c r="W161">
-        <v>1.08</v>
-      </c>
-      <c r="X161">
-        <v>1.03</v>
-      </c>
-      <c r="Y161">
-        <v>1.3</v>
-      </c>
-      <c r="Z161">
-        <v>3.55</v>
-      </c>
-      <c r="AA161">
-        <v>1.96</v>
-      </c>
-      <c r="AB161">
-        <v>1.89</v>
-      </c>
-      <c r="AC161">
-        <v>3.14</v>
-      </c>
       <c r="AD161">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE161">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG161">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK161">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,65 +26715,65 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O162">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P162">
+        <v>2.62</v>
+      </c>
+      <c r="Q162">
         <v>3</v>
       </c>
-      <c r="Q162">
-        <v>2.99</v>
-      </c>
       <c r="R162">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S162">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T162">
-        <v>2.64</v>
+        <v>3.17</v>
       </c>
       <c r="U162">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="V162">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W162">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X162">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z162">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA162">
+        <v>1.77</v>
+      </c>
+      <c r="AB162">
+        <v>2.09</v>
+      </c>
+      <c r="AC162">
+        <v>3.12</v>
+      </c>
+      <c r="AD162">
+        <v>1.36</v>
+      </c>
+      <c r="AE162">
+        <v>1.1</v>
+      </c>
+      <c r="AF162">
+        <v>1.57</v>
+      </c>
+      <c r="AG162">
         <v>2.2</v>
       </c>
-      <c r="AB162">
-        <v>1.65</v>
-      </c>
-      <c r="AC162">
-        <v>3.55</v>
-      </c>
-      <c r="AD162">
-        <v>1.2</v>
-      </c>
-      <c r="AE162">
-        <v>1.07</v>
-      </c>
-      <c r="AF162">
-        <v>1.84</v>
-      </c>
-      <c r="AG162">
-        <v>1.86</v>
-      </c>
       <c r="AH162" t="inlineStr">
         <is>
           <t>[]</t>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK162">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O163">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P163">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q163">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="R163">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S163">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T163">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U163">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V163">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W163">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X163">
         <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z163">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA163">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AB163">
         <v>1.89</v>
       </c>
       <c r="AC163">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD163">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE163">
         <v>1.06</v>
       </c>
       <c r="AF163">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG163">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK163">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,80 +29160,80 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="O177">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q177">
-        <v>1.67</v>
+        <v>3.16</v>
       </c>
       <c r="R177">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="S177">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T177">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="U177">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V177">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W177">
+        <v>1.1</v>
+      </c>
+      <c r="X177">
+        <v>1.03</v>
+      </c>
+      <c r="Y177">
         <v>1.17</v>
       </c>
-      <c r="X177">
-        <v>1.01</v>
-      </c>
-      <c r="Y177">
-        <v>1.08</v>
-      </c>
       <c r="Z177">
-        <v>5.65</v>
+        <v>4</v>
       </c>
       <c r="AA177">
+        <v>1.64</v>
+      </c>
+      <c r="AB177">
+        <v>2.08</v>
+      </c>
+      <c r="AC177">
+        <v>2.59</v>
+      </c>
+      <c r="AD177">
+        <v>1.43</v>
+      </c>
+      <c r="AE177">
+        <v>1.12</v>
+      </c>
+      <c r="AF177">
+        <v>1.53</v>
+      </c>
+      <c r="AG177">
+        <v>2.31</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ177">
+        <v>1.22</v>
+      </c>
+      <c r="AK177">
         <v>1.38</v>
-      </c>
-      <c r="AB177">
-        <v>2.62</v>
-      </c>
-      <c r="AC177">
-        <v>2.07</v>
-      </c>
-      <c r="AD177">
-        <v>1.67</v>
-      </c>
-      <c r="AE177">
-        <v>1.25</v>
-      </c>
-      <c r="AF177">
-        <v>1.74</v>
-      </c>
-      <c r="AG177">
-        <v>1.93</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ177">
-        <v>1.08</v>
-      </c>
-      <c r="AK177">
-        <v>3.36</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="O178">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P178">
-        <v>2.45</v>
+        <v>6.5</v>
       </c>
       <c r="Q178">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="R178">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="S178">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T178">
-        <v>3.24</v>
+        <v>3.78</v>
       </c>
       <c r="U178">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V178">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W178">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X178">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z178">
-        <v>4</v>
+        <v>5.65</v>
       </c>
       <c r="AA178">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AB178">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="AC178">
-        <v>2.59</v>
+        <v>2.07</v>
       </c>
       <c r="AD178">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AE178">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF178">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AG178">
-        <v>2.31</v>
+        <v>1.93</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK178">
-        <v>1.38</v>
+        <v>3.36</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,65 +29486,65 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.13</v>
+        <v>2.02</v>
       </c>
       <c r="O179">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P179">
-        <v>1.98</v>
+        <v>4</v>
       </c>
       <c r="Q179">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R179">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S179">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T179">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U179">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V179">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W179">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X179">
         <v>1.05</v>
       </c>
       <c r="Y179">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="Z179">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AA179">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB179">
+        <v>1.61</v>
+      </c>
+      <c r="AC179">
+        <v>4.33</v>
+      </c>
+      <c r="AD179">
+        <v>1.17</v>
+      </c>
+      <c r="AE179">
+        <v>1.02</v>
+      </c>
+      <c r="AF179">
+        <v>2</v>
+      </c>
+      <c r="AG179">
         <v>1.73</v>
       </c>
-      <c r="AC179">
-        <v>3.8</v>
-      </c>
-      <c r="AD179">
-        <v>1.22</v>
-      </c>
-      <c r="AE179">
-        <v>1.04</v>
-      </c>
-      <c r="AF179">
-        <v>1.83</v>
-      </c>
-      <c r="AG179">
-        <v>1.86</v>
-      </c>
       <c r="AH179" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AK179">
-        <v>1.29</v>
+        <v>1.81</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.02</v>
+        <v>3.13</v>
       </c>
       <c r="O180">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P180">
+        <v>1.98</v>
+      </c>
+      <c r="Q180">
         <v>4</v>
       </c>
-      <c r="Q180">
-        <v>2.62</v>
-      </c>
       <c r="R180">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S180">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T180">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U180">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V180">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W180">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X180">
         <v>1.05</v>
       </c>
       <c r="Y180">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="Z180">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AA180">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AB180">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC180">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AD180">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE180">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF180">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG180">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AK180">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,80 +41548,80 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="O253">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P253">
-        <v>7</v>
+        <v>1.53</v>
       </c>
       <c r="Q253">
+        <v>4.2</v>
+      </c>
+      <c r="R253">
+        <v>2.6</v>
+      </c>
+      <c r="S253">
+        <v>1.15</v>
+      </c>
+      <c r="T253">
+        <v>4</v>
+      </c>
+      <c r="U253">
+        <v>2.01</v>
+      </c>
+      <c r="V253">
+        <v>1.69</v>
+      </c>
+      <c r="W253">
+        <v>1.17</v>
+      </c>
+      <c r="X253">
+        <v>1.01</v>
+      </c>
+      <c r="Y253">
+        <v>1.1</v>
+      </c>
+      <c r="Z253">
+        <v>5.66</v>
+      </c>
+      <c r="AA253">
+        <v>1.44</v>
+      </c>
+      <c r="AB253">
+        <v>2.7</v>
+      </c>
+      <c r="AC253">
+        <v>2.01</v>
+      </c>
+      <c r="AD253">
         <v>1.7</v>
       </c>
-      <c r="R253">
-        <v>2.7</v>
-      </c>
-      <c r="S253">
-        <v>1.22</v>
-      </c>
-      <c r="T253">
-        <v>3.9</v>
-      </c>
-      <c r="U253">
-        <v>2.12</v>
-      </c>
-      <c r="V253">
-        <v>1.65</v>
-      </c>
-      <c r="W253">
+      <c r="AE253">
+        <v>1.25</v>
+      </c>
+      <c r="AF253">
+        <v>1.44</v>
+      </c>
+      <c r="AG253">
+        <v>2.5</v>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ253">
+        <v>2.28</v>
+      </c>
+      <c r="AK253">
         <v>1.15</v>
-      </c>
-      <c r="X253">
-        <v>1.02</v>
-      </c>
-      <c r="Y253">
-        <v>1.13</v>
-      </c>
-      <c r="Z253">
-        <v>5</v>
-      </c>
-      <c r="AA253">
-        <v>1.47</v>
-      </c>
-      <c r="AB253">
-        <v>2.55</v>
-      </c>
-      <c r="AC253">
-        <v>2.24</v>
-      </c>
-      <c r="AD253">
-        <v>1.64</v>
-      </c>
-      <c r="AE253">
-        <v>1.21</v>
-      </c>
-      <c r="AF253">
-        <v>1.79</v>
-      </c>
-      <c r="AG253">
-        <v>1.95</v>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ253">
-        <v>1.03</v>
-      </c>
-      <c r="AK253">
-        <v>3.3</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="O254">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P254">
-        <v>1.53</v>
+        <v>7</v>
       </c>
       <c r="Q254">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="R254">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S254">
+        <v>1.22</v>
+      </c>
+      <c r="T254">
+        <v>3.9</v>
+      </c>
+      <c r="U254">
+        <v>2.12</v>
+      </c>
+      <c r="V254">
+        <v>1.65</v>
+      </c>
+      <c r="W254">
         <v>1.15</v>
       </c>
-      <c r="T254">
-        <v>4</v>
-      </c>
-      <c r="U254">
-        <v>2.01</v>
-      </c>
-      <c r="V254">
-        <v>1.69</v>
-      </c>
-      <c r="W254">
-        <v>1.17</v>
-      </c>
       <c r="X254">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z254">
-        <v>5.66</v>
+        <v>5</v>
       </c>
       <c r="AA254">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB254">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC254">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="AD254">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AE254">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF254">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AG254">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="AK254">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,64 +46438,64 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.61</v>
+        <v>2.9</v>
       </c>
       <c r="O283">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="P283">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q283">
-        <v>2.25</v>
+        <v>3.46</v>
       </c>
       <c r="R283">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="S283">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="T283">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="U283">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="V283">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W283">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X283">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y283">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z283">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA283">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB283">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AC283">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AD283">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AE283">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF283">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AG283">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AK283">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,37 +46601,37 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O284">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P284">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q284">
         <v>2.25</v>
       </c>
       <c r="R284">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S284">
         <v>1.3</v>
       </c>
       <c r="T284">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="U284">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V284">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W284">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X284">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y284">
         <v>1.22</v>
@@ -46643,7 +46643,7 @@
         <v>1.83</v>
       </c>
       <c r="AB284">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC284">
         <v>2.88</v>
@@ -46655,10 +46655,10 @@
         <v>1.08</v>
       </c>
       <c r="AF284">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG284">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK284">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="O285">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P285">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q285">
-        <v>3.46</v>
+        <v>2.25</v>
       </c>
       <c r="R285">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="S285">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="T285">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="U285">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="V285">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W285">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X285">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y285">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z285">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA285">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AB285">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AC285">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AD285">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AE285">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF285">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG285">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK285">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.71</v>
+        <v>1.77</v>
       </c>
       <c r="O293">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P293">
-        <v>2.5</v>
+        <v>4.64</v>
       </c>
       <c r="Q293">
-        <v>3.24</v>
+        <v>2.27</v>
       </c>
       <c r="R293">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S293">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T293">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="U293">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="V293">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W293">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X293">
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z293">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="AA293">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB293">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC293">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD293">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE293">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF293">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG293">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK293">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.77</v>
+        <v>2.71</v>
       </c>
       <c r="O294">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P294">
-        <v>4.64</v>
+        <v>2.5</v>
       </c>
       <c r="Q294">
-        <v>2.27</v>
+        <v>3.24</v>
       </c>
       <c r="R294">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S294">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T294">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U294">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V294">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W294">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X294">
         <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z294">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="AA294">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB294">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AC294">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD294">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE294">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF294">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG294">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK294">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -49716,13 +49716,13 @@
         <v>1.44</v>
       </c>
       <c r="T303">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U303">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V303">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W303">
         <v>1.05</v>
@@ -49743,10 +49743,10 @@
         <v>1.53</v>
       </c>
       <c r="AC303">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD303">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE303">
         <v>1.01</v>
@@ -49771,7 +49771,7 @@
         <v>1.33</v>
       </c>
       <c r="AK303">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -50839,22 +50839,22 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O310">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P310">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
       </c>
       <c r="R310">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="S310">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T310">
         <v>2.4</v>
@@ -50875,7 +50875,7 @@
         <v>1.52</v>
       </c>
       <c r="Z310">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AA310">
         <v>2.41</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,80 +51165,80 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="O312">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="P312">
-        <v>4.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q312">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="R312">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="S312">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T312">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U312">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="V312">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W312">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X312">
         <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z312">
-        <v>3.96</v>
+        <v>5.35</v>
       </c>
       <c r="AA312">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AB312">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="AC312">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="AD312">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE312">
+        <v>1.24</v>
+      </c>
+      <c r="AF312">
+        <v>1.56</v>
+      </c>
+      <c r="AG312">
+        <v>2.25</v>
+      </c>
+      <c r="AH312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI312" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ312">
         <v>1.13</v>
       </c>
-      <c r="AF312">
-        <v>1.7</v>
-      </c>
-      <c r="AG312">
-        <v>2</v>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ312">
-        <v>1.16</v>
-      </c>
       <c r="AK312">
-        <v>2.22</v>
+        <v>2.55</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="O313">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P313">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q313">
-        <v>1.87</v>
+        <v>2.84</v>
       </c>
       <c r="R313">
+        <v>2.18</v>
+      </c>
+      <c r="S313">
+        <v>1.3</v>
+      </c>
+      <c r="T313">
+        <v>3.2</v>
+      </c>
+      <c r="U313">
         <v>2.67</v>
       </c>
-      <c r="S313">
+      <c r="V313">
+        <v>1.45</v>
+      </c>
+      <c r="W313">
+        <v>1.08</v>
+      </c>
+      <c r="X313">
+        <v>1.01</v>
+      </c>
+      <c r="Y313">
         <v>1.2</v>
       </c>
-      <c r="T313">
-        <v>4</v>
-      </c>
-      <c r="U313">
-        <v>2.22</v>
-      </c>
-      <c r="V313">
-        <v>1.65</v>
-      </c>
-      <c r="W313">
-        <v>1.15</v>
-      </c>
-      <c r="X313">
-        <v>1.02</v>
-      </c>
-      <c r="Y313">
-        <v>1.13</v>
-      </c>
       <c r="Z313">
-        <v>5.35</v>
+        <v>3.72</v>
       </c>
       <c r="AA313">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AB313">
-        <v>2.49</v>
+        <v>2.01</v>
       </c>
       <c r="AC313">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="AD313">
+        <v>1.32</v>
+      </c>
+      <c r="AE313">
+        <v>1.08</v>
+      </c>
+      <c r="AF313">
         <v>1.61</v>
       </c>
-      <c r="AE313">
-        <v>1.24</v>
-      </c>
-      <c r="AF313">
-        <v>1.56</v>
-      </c>
       <c r="AG313">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK313">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O314">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="P314">
-        <v>2.65</v>
+        <v>4.45</v>
       </c>
       <c r="Q314">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="R314">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="S314">
         <v>1.3</v>
       </c>
       <c r="T314">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U314">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="V314">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W314">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X314">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y314">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z314">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="AA314">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB314">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AC314">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AD314">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE314">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF314">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG314">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK314">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.45</v>
+        <v>1.99</v>
       </c>
       <c r="O315">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P315">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q315">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="R315">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="S315">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="T315">
-        <v>3.72</v>
+        <v>2.38</v>
       </c>
       <c r="U315">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="V315">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="W315">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X315">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y315">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="Z315">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="AA315">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="AB315">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC315">
-        <v>2.12</v>
+        <v>4.8</v>
       </c>
       <c r="AD315">
-        <v>1.62</v>
+        <v>1.12</v>
       </c>
       <c r="AE315">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="AF315">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG315">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK315">
-        <v>2.66</v>
+        <v>1.6</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,64 +51817,64 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="O316">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P316">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="Q316">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="R316">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="S316">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="T316">
-        <v>2.38</v>
+        <v>3.72</v>
       </c>
       <c r="U316">
-        <v>3.4</v>
+        <v>2.21</v>
       </c>
       <c r="V316">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="W316">
+        <v>1.17</v>
+      </c>
+      <c r="X316">
         <v>1.02</v>
       </c>
-      <c r="X316">
-        <v>1.05</v>
-      </c>
       <c r="Y316">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="Z316">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="AA316">
-        <v>2.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB316">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC316">
-        <v>4.8</v>
+        <v>2.12</v>
       </c>
       <c r="AD316">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="AE316">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AF316">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AG316">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK316">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X320">
         <v>0</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q321">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R321">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S321">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T321">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U321">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V321">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W321">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X321">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z321">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AA321">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB321">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC321">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD321">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE321">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF321">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG321">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK321">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q322">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R322">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S322">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T322">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U322">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V322">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W322">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X322">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA322">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB322">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC322">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD322">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE322">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF322">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG322">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK322">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q323">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R323">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T323">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U323">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V323">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W323">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X323">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA323">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB323">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC323">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD323">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE323">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF323">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG323">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK323">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y328">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z328">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X330">
         <v>0</v>
       </c>
       <c r="Y330">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z330">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54262,64 +54262,64 @@
         </is>
       </c>
       <c r="N331">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O331">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P331">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q331">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R331">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S331">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T331">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U331">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V331">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W331">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X331">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y331">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z331">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA331">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB331">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC331">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD331">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE331">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF331">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG331">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK331">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL331">
         <v>0</v>
@@ -54425,64 +54425,64 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q332">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R332">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S332">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T332">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U332">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V332">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W332">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X332">
         <v>0</v>
       </c>
       <c r="Y332">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z332">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA332">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB332">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC332">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD332">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE332">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF332">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG332">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK332">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54914,64 +54914,64 @@
         </is>
       </c>
       <c r="N335">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O335">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P335">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q335">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R335">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S335">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T335">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U335">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V335">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W335">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X335">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y335">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z335">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA335">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB335">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC335">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD335">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE335">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF335">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG335">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK335">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O336">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q336">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R336">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S336">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T336">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U336">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V336">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W336">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X336">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y336">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z336">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA336">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB336">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC336">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD336">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE336">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF336">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG336">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK336">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O337">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P337">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q337">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R337">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S337">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T337">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U337">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V337">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W337">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X337">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y337">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z337">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC337">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD337">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE337">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF337">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG337">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK337">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55729,64 +55729,64 @@
         </is>
       </c>
       <c r="N340">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O340">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P340">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q340">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R340">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S340">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T340">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U340">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V340">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W340">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X340">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y340">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z340">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA340">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB340">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC340">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD340">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE340">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF340">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG340">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK340">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL340">
         <v>0</v>

--- a/jogos_2026-09-19.xlsx
+++ b/jogos_2026-09-19.xlsx
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -790,21 +790,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O3">
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="Q3">
         <v>3.28</v>
@@ -816,7 +816,7 @@
         <v>1.38</v>
       </c>
       <c r="T3">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="U3">
         <v>2.88</v>
@@ -837,13 +837,13 @@
         <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD3">
         <v>1.28</v>
@@ -864,41 +864,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77", "86"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,33 +938,33 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
         <v>2.08</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
         <v>3.2</v>
@@ -976,10 +976,10 @@
         <v>2.09</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -991,19 +991,19 @@
         <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
         <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
         <v>2.9</v>
@@ -1015,53 +1015,53 @@
         <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "42", "90+1"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1133,10 +1133,10 @@
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1145,10 +1145,10 @@
         <v>3.5</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1160,28 +1160,28 @@
         <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AC5">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD5">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "56", "64"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1276,14 +1276,14 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "83"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "74"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,42 +1590,42 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="O8">
         <v>3.75</v>
       </c>
       <c r="P8">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="Q8">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R8">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S8">
         <v>1.26</v>
@@ -1634,7 +1634,7 @@
         <v>3.4</v>
       </c>
       <c r="U8">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="V8">
         <v>1.53</v>
@@ -1649,19 +1649,19 @@
         <v>1.15</v>
       </c>
       <c r="Z8">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB8">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
         <v>1.14</v>
@@ -1674,16 +1674,16 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "54", "90+7"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "67", "83"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AK8">
         <v>1.42</v>
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1768,11 +1768,11 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1785,19 +1785,19 @@
         <v>1.61</v>
       </c>
       <c r="Q9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
         <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="U9">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V9">
         <v>1.44</v>
@@ -1812,13 +1812,13 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
         <v>1.81</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
@@ -1827,13 +1827,13 @@
         <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1931,11 +1931,11 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -1945,7 +1945,7 @@
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q10">
         <v>3.9</v>
@@ -1954,19 +1954,19 @@
         <v>2.2</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U10">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="V10">
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1975,71 +1975,71 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AK10">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2094,11 +2094,11 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2111,19 +2111,19 @@
         <v>4.6</v>
       </c>
       <c r="Q11">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="V11">
         <v>1.34</v>
@@ -2132,22 +2132,22 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.32</v>
       </c>
       <c r="Z11">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC11">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="AD11">
         <v>1.22</v>
@@ -2156,19 +2156,19 @@
         <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG11">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "32", "44"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,96 +2242,96 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
+        <v>1.03</v>
+      </c>
+      <c r="X12">
         <v>1.05</v>
       </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
       <c r="Y12">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.23</v>
       </c>
       <c r="AA12">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AC12">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "71"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,24 +2420,24 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P13">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="R13">
         <v>2.34</v>
@@ -2464,13 +2464,13 @@
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="AA13">
         <v>1.81</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC13">
         <v>2.74</v>
@@ -2482,19 +2482,19 @@
         <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O14">
         <v>3.55</v>
@@ -2603,16 +2603,16 @@
         <v>3.37</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V14">
         <v>1.5</v>
@@ -2621,34 +2621,34 @@
         <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AD14">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AE14">
         <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AK14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2772,7 +2772,7 @@
         <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="U15">
         <v>3</v>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "60"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2909,18 +2909,18 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
         <v>2.2</v>
@@ -2950,7 +2950,7 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
         <v>4.7</v>
@@ -2965,7 +2965,7 @@
         <v>2.49</v>
       </c>
       <c r="AD16">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE16">
         <v>1.16</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "87"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3072,11 +3072,11 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3279,16 +3279,16 @@
         <v>1.37</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA18">
         <v>2.11</v>
       </c>
       <c r="AB18">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC18">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AD18">
         <v>1.19</v>
@@ -3300,50 +3300,50 @@
         <v>1.86</v>
       </c>
       <c r="AG18">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ18">
         <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3395,14 +3395,14 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S19">
         <v>1.36</v>
@@ -3427,10 +3427,10 @@
         <v>2.9</v>
       </c>
       <c r="U19">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
         <v>1.04</v>
@@ -3442,37 +3442,37 @@
         <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA19">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB19">
         <v>1.79</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "66", "76"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,36 +3546,36 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="O20">
         <v>4.1</v>
       </c>
       <c r="P20">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q20">
         <v>2.1</v>
@@ -3584,28 +3584,28 @@
         <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="AA20">
         <v>1.69</v>
@@ -3614,62 +3614,62 @@
         <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE20">
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "90+1"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK20">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>2.52</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.42</v>
@@ -3759,7 +3759,7 @@
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3891,17 +3891,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
         <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q22">
         <v>3.02</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,36 +4035,36 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
         <v>1.87</v>
       </c>
       <c r="O23">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="P23">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
         <v>2.5</v>
@@ -4073,16 +4073,16 @@
         <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
         <v>1.08</v>
@@ -4097,7 +4097,7 @@
         <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
         <v>1.88</v>
@@ -4109,22 +4109,22 @@
         <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG23">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "90+2"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,33 +4210,33 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O24">
         <v>3.95</v>
       </c>
       <c r="P24">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="Q24">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
         <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
         <v>3.4</v>
@@ -4251,7 +4251,7 @@
         <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.17</v>
@@ -4263,10 +4263,10 @@
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC24">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AD24">
         <v>1.47</v>
@@ -4275,14 +4275,14 @@
         <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4294,34 +4294,34 @@
         <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4405,10 +4405,10 @@
         <v>2.72</v>
       </c>
       <c r="U25">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.06</v>
@@ -4432,7 +4432,7 @@
         <v>3.14</v>
       </c>
       <c r="AD25">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE25">
         <v>1.07</v>
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "74"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86", "90+4"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O28">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="P28">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R28">
         <v>2.16</v>
@@ -4891,10 +4891,10 @@
         <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -4909,10 +4909,10 @@
         <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
         <v>2.05</v>
@@ -4921,7 +4921,7 @@
         <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
         <v>1.11</v>
@@ -4946,7 +4946,7 @@
         <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.78</v>
+        <v>2.81</v>
       </c>
       <c r="O37">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q37">
-        <v>2.31</v>
+        <v>3.13</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA37">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AB37">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AD37">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF37">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG37">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AK37">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.81</v>
+        <v>1.78</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P38">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="Q38">
-        <v>3.13</v>
+        <v>2.31</v>
       </c>
       <c r="R38">
         <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="T38">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V38">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="W38">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="AA38">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AB38">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AC38">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AD38">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AE38">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P40">
         <v>4.25</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>2</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="O41">
         <v>3.8</v>
       </c>
       <c r="P41">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="Q41">
         <v>2.11</v>
@@ -7065,7 +7065,7 @@
         <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7132,26 +7132,26 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7167,16 +7167,16 @@
         <v>3.3</v>
       </c>
       <c r="R42">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S42">
         <v>1.48</v>
       </c>
       <c r="T42">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U42">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V42">
         <v>1.3</v>
@@ -7200,7 +7200,7 @@
         <v>1.61</v>
       </c>
       <c r="AC42">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AD42">
         <v>1.17</v>
@@ -7209,23 +7209,23 @@
         <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "36"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "89"]</t>
         </is>
       </c>
       <c r="AJ42">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AK42">
         <v>1.36</v>
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O49">
         <v>3.9</v>
       </c>
       <c r="P49">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>4.45</v>
+        <v>4.95</v>
       </c>
       <c r="AA49">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB49">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AC49">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="AD49">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
+        <v>1.24</v>
+      </c>
+      <c r="AK49">
         <v>1.22</v>
-      </c>
-      <c r="AK49">
-        <v>2.04</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
         <v>3.9</v>
       </c>
       <c r="P50">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q50">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T50">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA50">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="AC50">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="AD50">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG50">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,22 +8785,22 @@
         </is>
       </c>
       <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="O52">
+        <v>3.2</v>
+      </c>
+      <c r="P52">
         <v>2.15</v>
       </c>
-      <c r="O52">
-        <v>3.1</v>
-      </c>
-      <c r="P52">
-        <v>3</v>
-      </c>
       <c r="Q52">
-        <v>2.69</v>
+        <v>4.19</v>
       </c>
       <c r="R52">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
         <v>2.88</v>
@@ -8809,56 +8809,56 @@
         <v>2.8</v>
       </c>
       <c r="V52">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W52">
+        <v>1.05</v>
+      </c>
+      <c r="X52">
         <v>1.02</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
       <c r="Y52">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA52">
         <v>1.96</v>
       </c>
       <c r="AB52">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC52">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD52">
+        <v>1.27</v>
+      </c>
+      <c r="AE52">
+        <v>1.06</v>
+      </c>
+      <c r="AF52">
+        <v>1.75</v>
+      </c>
+      <c r="AG52">
+        <v>2.05</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.23</v>
       </c>
-      <c r="AE52">
-        <v>1.04</v>
-      </c>
-      <c r="AF52">
-        <v>1.78</v>
-      </c>
-      <c r="AG52">
-        <v>1.93</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.25</v>
-      </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q53">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R53">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.33</v>
@@ -8969,43 +8969,43 @@
         <v>3.11</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V53">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W53">
         <v>1.12</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z53">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB53">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD53">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK53">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="O54">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
-        <v>3.59</v>
+        <v>3.14</v>
       </c>
       <c r="R54">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T54">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U54">
         <v>2.8</v>
       </c>
       <c r="V54">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z54">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AA54">
         <v>2</v>
       </c>
       <c r="AB54">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC54">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AD54">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE54">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG54">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9606,25 +9606,25 @@
         <v>4.2</v>
       </c>
       <c r="P57">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q57">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="R57">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="S57">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U57">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V57">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
         <v>1.18</v>
@@ -9633,7 +9633,7 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
         <v>6.5</v>
@@ -9645,19 +9645,19 @@
         <v>2.87</v>
       </c>
       <c r="AC57">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AD57">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE57">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AG57">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.16</v>
+        <v>2.22</v>
       </c>
       <c r="AK57">
         <v>1.08</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="O58">
         <v>4.5</v>
       </c>
       <c r="P58">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q58">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="R58">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S58">
         <v>1.15</v>
       </c>
       <c r="T58">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U58">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V58">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="W58">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.03</v>
       </c>
       <c r="Z58">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="AA58">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AB58">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AC58">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AD58">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AE58">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF58">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG58">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK58">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
         <v>4.85</v>
       </c>
       <c r="P70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB70">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="O71">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P71">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="O73">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P73">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q73">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="R73">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="S73">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T73">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="U73">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
+        <v>1.05</v>
+      </c>
+      <c r="X73">
+        <v>1.05</v>
+      </c>
+      <c r="Y73">
+        <v>1.38</v>
+      </c>
+      <c r="Z73">
+        <v>2.62</v>
+      </c>
+      <c r="AA73">
+        <v>2.2</v>
+      </c>
+      <c r="AB73">
+        <v>1.47</v>
+      </c>
+      <c r="AC73">
+        <v>4.6</v>
+      </c>
+      <c r="AD73">
+        <v>1.2</v>
+      </c>
+      <c r="AE73">
         <v>1.03</v>
       </c>
-      <c r="X73">
-        <v>1.03</v>
-      </c>
-      <c r="Y73">
-        <v>1.27</v>
-      </c>
-      <c r="Z73">
-        <v>3.14</v>
-      </c>
-      <c r="AA73">
-        <v>2.01</v>
-      </c>
-      <c r="AB73">
-        <v>1.8</v>
-      </c>
-      <c r="AC73">
-        <v>3.34</v>
-      </c>
-      <c r="AD73">
-        <v>1.25</v>
-      </c>
-      <c r="AE73">
-        <v>1.04</v>
-      </c>
       <c r="AF73">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="O74">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q74">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="R74">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S74">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T74">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="U74">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V74">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W74">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z74">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="AA74">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB74">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD74">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AG74">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AK74">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="N109">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O109">
         <v>3.75</v>
@@ -18085,49 +18085,49 @@
         <v>1.64</v>
       </c>
       <c r="Q109">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S109">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="U109">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V109">
         <v>1.36</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y109">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z109">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AA109">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB109">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC109">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD109">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE109">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
         <v>1.8</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AK109">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P112">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="Q112">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
       <c r="R112">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S112">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T112">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U112">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="V112">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W112">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA112">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AB112">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AC112">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AD112">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AE112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AK112">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="Q113">
-        <v>3.54</v>
+        <v>2.81</v>
       </c>
       <c r="R113">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S113">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T113">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U113">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="V113">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W113">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z113">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA113">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AB113">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AC113">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AD113">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE113">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF113">
+        <v>1.4</v>
+      </c>
+      <c r="AG113">
+        <v>2.8</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
         <v>1.44</v>
       </c>
-      <c r="AG113">
-        <v>2.73</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.62</v>
-      </c>
       <c r="AK113">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O115">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P115">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="Q115">
-        <v>2.1</v>
+        <v>4.87</v>
       </c>
       <c r="R115">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="S115">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="U115">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="V115">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W115">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z115">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA115">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AB115">
         <v>2.18</v>
       </c>
       <c r="AC115">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AD115">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AE115">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG115">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="O116">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P116">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q116">
-        <v>4.87</v>
+        <v>2.1</v>
       </c>
       <c r="R116">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="U116">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="V116">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y116">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA116">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB116">
         <v>2.18</v>
       </c>
       <c r="AC116">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AD116">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AE116">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF116">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK116">
-        <v>1.22</v>
+        <v>2.29</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,65 +19380,65 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O117">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P117">
         <v>3.4</v>
       </c>
       <c r="Q117">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="R117">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S117">
         <v>1.4</v>
       </c>
       <c r="T117">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="U117">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="V117">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="W117">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
         <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z117">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AA117">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB117">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AC117">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD117">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE117">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF117">
+        <v>1.77</v>
+      </c>
+      <c r="AG117">
         <v>1.93</v>
       </c>
-      <c r="AG117">
-        <v>1.75</v>
-      </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK117">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,65 +19543,65 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O118">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
         <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="R118">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S118">
         <v>1.4</v>
       </c>
       <c r="T118">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="U118">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="V118">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="W118">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X118">
         <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z118">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AA118">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AB118">
+        <v>1.64</v>
+      </c>
+      <c r="AC118">
+        <v>4.4</v>
+      </c>
+      <c r="AD118">
+        <v>1.18</v>
+      </c>
+      <c r="AE118">
+        <v>1.01</v>
+      </c>
+      <c r="AF118">
+        <v>1.93</v>
+      </c>
+      <c r="AG118">
         <v>1.75</v>
       </c>
-      <c r="AC118">
-        <v>3.6</v>
-      </c>
-      <c r="AD118">
-        <v>1.25</v>
-      </c>
-      <c r="AE118">
-        <v>1.06</v>
-      </c>
-      <c r="AF118">
-        <v>1.77</v>
-      </c>
-      <c r="AG118">
-        <v>1.93</v>
-      </c>
       <c r="AH118" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="O120">
-        <v>5.8</v>
+        <v>3.55</v>
       </c>
       <c r="P120">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q120">
-        <v>1.57</v>
+        <v>2.74</v>
       </c>
       <c r="R120">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="S120">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T120">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U120">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V120">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z120">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA120">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AB120">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC120">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="AD120">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF120">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AG120">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK120">
-        <v>3.44</v>
+        <v>1.6</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="O121">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="Q121">
-        <v>3.4</v>
+        <v>4.56</v>
       </c>
       <c r="R121">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S121">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="U121">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V121">
         <v>1.44</v>
       </c>
       <c r="W121">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z121">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA121">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB121">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC121">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD121">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE121">
         <v>1.08</v>
       </c>
       <c r="AF121">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG121">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK121">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="O122">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P122">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="Q122">
-        <v>4.56</v>
+        <v>3.4</v>
       </c>
       <c r="R122">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T122">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="U122">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
         <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB122">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD122">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AG122">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="O123">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="P123">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="Q123">
-        <v>2.74</v>
+        <v>1.57</v>
       </c>
       <c r="R123">
+        <v>2.8</v>
+      </c>
+      <c r="S123">
+        <v>1.2</v>
+      </c>
+      <c r="T123">
+        <v>3.8</v>
+      </c>
+      <c r="U123">
+        <v>2.19</v>
+      </c>
+      <c r="V123">
+        <v>1.67</v>
+      </c>
+      <c r="W123">
+        <v>1.17</v>
+      </c>
+      <c r="X123">
+        <v>1.02</v>
+      </c>
+      <c r="Y123">
+        <v>1.1</v>
+      </c>
+      <c r="Z123">
+        <v>5.2</v>
+      </c>
+      <c r="AA123">
+        <v>1.36</v>
+      </c>
+      <c r="AB123">
+        <v>2.5</v>
+      </c>
+      <c r="AC123">
         <v>2.13</v>
       </c>
-      <c r="S123">
-        <v>1.33</v>
-      </c>
-      <c r="T123">
-        <v>3.2</v>
-      </c>
-      <c r="U123">
-        <v>2.13</v>
-      </c>
-      <c r="V123">
-        <v>1.44</v>
-      </c>
-      <c r="W123">
-        <v>1.11</v>
-      </c>
-      <c r="X123">
-        <v>1</v>
-      </c>
-      <c r="Y123">
+      <c r="AD123">
+        <v>1.61</v>
+      </c>
+      <c r="AE123">
         <v>1.18</v>
       </c>
-      <c r="Z123">
-        <v>3.58</v>
-      </c>
-      <c r="AA123">
-        <v>1.61</v>
-      </c>
-      <c r="AB123">
-        <v>1.93</v>
-      </c>
-      <c r="AC123">
-        <v>2.83</v>
-      </c>
-      <c r="AD123">
-        <v>1.33</v>
-      </c>
-      <c r="AE123">
-        <v>1.14</v>
-      </c>
       <c r="AF123">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AG123">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK123">
-        <v>1.6</v>
+        <v>3.44</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="O126">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P126">
-        <v>3.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q126">
-        <v>2.5</v>
+        <v>4.78</v>
       </c>
       <c r="R126">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S126">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="U126">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="V126">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W126">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X126">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y126">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Z126">
+        <v>4.34</v>
+      </c>
+      <c r="AA126">
+        <v>1.75</v>
+      </c>
+      <c r="AB126">
+        <v>2.04</v>
+      </c>
+      <c r="AC126">
         <v>2.75</v>
       </c>
-      <c r="AA126">
-        <v>2.19</v>
-      </c>
-      <c r="AB126">
-        <v>1.6</v>
-      </c>
-      <c r="AC126">
-        <v>4</v>
-      </c>
       <c r="AD126">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE126">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF126">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AG126">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK126">
-        <v>1.83</v>
+        <v>1.18</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
      